--- a/data/teams/leagues/Averages_Russian_Premier_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Russian_Premier_League_2025-2026.xlsx
@@ -137,7 +137,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AveragesTable" displayName="AveragesTable" ref="A1:EC17" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AveragesTable_Russian_Pr" displayName="AveragesTable_Russian_Pr" ref="A1:EC17" headerRowCount="1">
   <autoFilter ref="A1:EC17"/>
   <tableColumns count="133">
     <tableColumn id="1" name="team_name"/>

--- a/data/teams/leagues/Averages_Russian_Premier_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Russian_Premier_League_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" t="n">
         <v>7</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" t="n">
         <v>0.29</v>
@@ -1472,109 +1472,109 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AH2" t="n">
         <v>-1</v>
       </c>
       <c r="AI2" t="n">
-        <v>92.88</v>
+        <v>91.33</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK2" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>38.67</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>14.11</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>16.89</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>7.44</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>46.56</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>10.78</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>7.78</v>
+      </c>
+      <c r="BC2" t="n">
         <v>3</v>
       </c>
-      <c r="AL2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>41.88</v>
-      </c>
-      <c r="AO2" t="n">
+      <c r="BD2" t="n">
+        <v>21.56</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="BJ2" t="n">
         <v>0.75</v>
       </c>
-      <c r="AP2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>14.25</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>17.25</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>7.38</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>45.75</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>11.25</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>7.88</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>22.25</v>
-      </c>
-      <c r="BE2" t="n">
+      <c r="BK2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BO2" t="n">
         <v>1.25</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>1.33</v>
       </c>
       <c r="BP2" t="n">
         <v>-1</v>
@@ -1586,22 +1586,22 @@
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>86.67</v>
+        <v>81.25</v>
       </c>
       <c r="BT2" t="n">
-        <v>53.33</v>
+        <v>50</v>
       </c>
       <c r="BU2" t="n">
-        <v>26.67</v>
+        <v>25</v>
       </c>
       <c r="BV2" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BW2" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX2" t="n">
-        <v>60</v>
+        <v>56.25</v>
       </c>
       <c r="BY2" t="n">
         <v>2.68</v>
@@ -1610,25 +1610,25 @@
         <v>2.74</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="CC2" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="CD2" t="n">
         <v>3.45</v>
       </c>
-      <c r="CD2" t="n">
-        <v>3.54</v>
-      </c>
       <c r="CE2" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.83</v>
+        <v>2.81</v>
       </c>
       <c r="CH2" t="n">
         <v>1.4</v>
@@ -1640,25 +1640,25 @@
         <v>1.87</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CL2" t="n">
         <v>1.88</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CO2" t="n">
         <v>1.33</v>
       </c>
       <c r="CP2" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.48</v>
+        <v>3.52</v>
       </c>
       <c r="CR2" t="n">
         <v>1.39</v>
@@ -1679,7 +1679,7 @@
         <v>1.89</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CY2" t="n">
         <v>1.92</v>
@@ -1691,88 +1691,88 @@
         <v>1.89</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.61</v>
+        <v>3.64</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="DG2" t="n">
         <v>-1</v>
       </c>
       <c r="DH2" t="n">
-        <v>92.8</v>
+        <v>91.93000000000001</v>
       </c>
       <c r="DI2" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="DK2" t="n">
-        <v>4.67</v>
+        <v>4.56</v>
       </c>
       <c r="DL2" t="n">
         <v>-1</v>
       </c>
       <c r="DM2" t="n">
-        <v>45.4</v>
+        <v>43.38</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="DO2" t="n">
         <v>-1</v>
       </c>
       <c r="DP2" t="n">
-        <v>12.13</v>
+        <v>12.18</v>
       </c>
       <c r="DQ2" t="n">
-        <v>17.13</v>
+        <v>16.94</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.33</v>
+        <v>6.43</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>46.13</v>
+        <v>46.56</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="DX2" t="n">
-        <v>12.93</v>
+        <v>12.56</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.869999999999999</v>
+        <v>8.75</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.07</v>
+        <v>3.81</v>
       </c>
       <c r="EA2" t="n">
-        <v>22.2</v>
+        <v>21.81</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="3">
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
         <v>8</v>
@@ -1800,76 +1800,76 @@
         <v>-1</v>
       </c>
       <c r="H3" t="n">
-        <v>96.43000000000001</v>
+        <v>99.25</v>
       </c>
       <c r="I3" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="J3" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="K3" t="n">
-        <v>3.71</v>
+        <v>3.38</v>
       </c>
       <c r="L3" t="n">
         <v>-1</v>
       </c>
       <c r="M3" t="n">
-        <v>47.86</v>
+        <v>48.5</v>
       </c>
       <c r="N3" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="O3" t="n">
         <v>-1</v>
       </c>
       <c r="P3" t="n">
-        <v>15.57</v>
+        <v>15.38</v>
       </c>
       <c r="Q3" t="n">
-        <v>15.57</v>
+        <v>15.5</v>
       </c>
       <c r="R3" t="n">
-        <v>6.86</v>
+        <v>7</v>
       </c>
       <c r="S3" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="T3" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="U3" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="V3" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>44.14</v>
+        <v>44.75</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>11</v>
+        <v>10.88</v>
       </c>
       <c r="AA3" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>4</v>
+        <v>4.38</v>
       </c>
       <c r="AC3" t="n">
         <v>18</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AF3" t="n">
         <v>0.12</v>
@@ -1953,31 +1953,31 @@
         <v>2.25</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.53</v>
+        <v>2.69</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.199999999999999</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.53</v>
+        <v>2.69</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.47</v>
+        <v>0.62</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="BP3" t="n">
         <v>-1</v>
@@ -1989,34 +1989,34 @@
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BT3" t="n">
-        <v>46.67</v>
+        <v>50</v>
       </c>
       <c r="BU3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="BV3" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>66.67</v>
+        <v>68.75</v>
       </c>
       <c r="BY3" t="n">
-        <v>3.78</v>
+        <v>3.57</v>
       </c>
       <c r="BZ3" t="n">
-        <v>4.07</v>
+        <v>3.82</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.88</v>
+        <v>3.85</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.21</v>
+        <v>4.16</v>
       </c>
       <c r="CC3" t="n">
         <v>4.83</v>
@@ -2028,40 +2028,40 @@
         <v>1.32</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.37</v>
+        <v>3.33</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CI3" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CK3" t="n">
         <v>1.46</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.72</v>
+        <v>2.81</v>
       </c>
       <c r="CR3" t="n">
         <v>1.38</v>
@@ -2076,10 +2076,10 @@
         <v>1.47</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.21</v>
+        <v>2.18</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="CX3" t="n">
         <v>1.52</v>
@@ -2106,76 +2106,76 @@
         <v>0.06</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="DG3" t="n">
         <v>-1</v>
       </c>
       <c r="DH3" t="n">
-        <v>91.13</v>
+        <v>92.88</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="DK3" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="DL3" t="n">
         <v>-1</v>
       </c>
       <c r="DM3" t="n">
-        <v>44.2</v>
+        <v>44.75</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="DO3" t="n">
         <v>-1</v>
       </c>
       <c r="DP3" t="n">
-        <v>15.2</v>
+        <v>15.13</v>
       </c>
       <c r="DQ3" t="n">
-        <v>14.26</v>
+        <v>14.31</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.47</v>
+        <v>7.5</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>43.33</v>
+        <v>43.68</v>
       </c>
       <c r="DW3" t="n">
         <v>0</v>
       </c>
       <c r="DX3" t="n">
-        <v>11.06</v>
+        <v>11</v>
       </c>
       <c r="DY3" t="n">
-        <v>7.6</v>
+        <v>7.31</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.47</v>
+        <v>3.69</v>
       </c>
       <c r="EA3" t="n">
-        <v>18.2</v>
+        <v>18.19</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" t="n">
         <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E4" t="n">
         <v>0.43</v>
@@ -2275,112 +2275,112 @@
         <v>3</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="AH4" t="n">
         <v>-1</v>
       </c>
       <c r="AI4" t="n">
-        <v>92.75</v>
+        <v>92.67</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AK4" t="n">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="AL4" t="n">
-        <v>3.38</v>
+        <v>3.33</v>
       </c>
       <c r="AM4" t="n">
         <v>-1</v>
       </c>
       <c r="AN4" t="n">
-        <v>42.62</v>
+        <v>43.11</v>
       </c>
       <c r="AO4" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AP4" t="n">
         <v>-1</v>
       </c>
       <c r="AQ4" t="n">
-        <v>20</v>
+        <v>20.22</v>
       </c>
       <c r="AR4" t="n">
-        <v>13.38</v>
+        <v>13.56</v>
       </c>
       <c r="AS4" t="n">
-        <v>7.38</v>
+        <v>7.44</v>
       </c>
       <c r="AT4" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>48.22</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>12.56</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>8.109999999999999</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>21.22</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BJ4" t="n">
         <v>0.38</v>
       </c>
-      <c r="AU4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>47.5</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>13.12</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>8.380000000000001</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>19.75</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>0.4</v>
-      </c>
       <c r="BK4" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN4" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BP4" t="n">
         <v>-1</v>
@@ -2389,25 +2389,25 @@
         <v>-1</v>
       </c>
       <c r="BR4" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BS4" t="n">
-        <v>73.33</v>
+        <v>68.75</v>
       </c>
       <c r="BT4" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BU4" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BV4" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>33.33</v>
+        <v>31.25</v>
       </c>
       <c r="BY4" t="n">
         <v>2.49</v>
@@ -2416,31 +2416,31 @@
         <v>2.68</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.45</v>
+        <v>3.44</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.49</v>
+        <v>3.47</v>
       </c>
       <c r="CC4" t="n">
-        <v>3.51</v>
+        <v>3.37</v>
       </c>
       <c r="CD4" t="n">
-        <v>3.85</v>
+        <v>3.67</v>
       </c>
       <c r="CE4" t="n">
         <v>1.37</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="CH4" t="n">
         <v>1.26</v>
       </c>
       <c r="CI4" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CJ4" t="n">
         <v>1.89</v>
@@ -2452,19 +2452,19 @@
         <v>1.84</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CO4" t="n">
         <v>1.31</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.87</v>
+        <v>3.88</v>
       </c>
       <c r="CR4" t="n">
         <v>1.44</v>
@@ -2482,19 +2482,19 @@
         <v>1.81</v>
       </c>
       <c r="CW4" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="CY4" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="DB4" t="n">
         <v>1.42</v>
@@ -2506,79 +2506,79 @@
         <v>4.34</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="DG4" t="n">
         <v>-1</v>
       </c>
       <c r="DH4" t="n">
-        <v>89.40000000000001</v>
+        <v>89.56</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DJ4" t="n">
-        <v>3.27</v>
+        <v>3.25</v>
       </c>
       <c r="DK4" t="n">
-        <v>3.47</v>
+        <v>3.43</v>
       </c>
       <c r="DL4" t="n">
         <v>-1</v>
       </c>
       <c r="DM4" t="n">
-        <v>43.33</v>
+        <v>43.56</v>
       </c>
       <c r="DN4" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="DO4" t="n">
         <v>-1</v>
       </c>
       <c r="DP4" t="n">
-        <v>20.6</v>
+        <v>20.69</v>
       </c>
       <c r="DQ4" t="n">
-        <v>13</v>
+        <v>13.13</v>
       </c>
       <c r="DR4" t="n">
-        <v>7</v>
+        <v>7.06</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>45.6</v>
+        <v>46.12</v>
       </c>
       <c r="DW4" t="n">
         <v>0.06</v>
       </c>
       <c r="DX4" t="n">
-        <v>12.8</v>
+        <v>12.5</v>
       </c>
       <c r="DY4" t="n">
-        <v>8.470000000000001</v>
+        <v>8.31</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.33</v>
+        <v>4.19</v>
       </c>
       <c r="EA4" t="n">
-        <v>21.27</v>
+        <v>22</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="EC4" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="5">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" t="n">
         <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E5" t="n">
         <v>0.38</v>
@@ -2681,109 +2681,109 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AH5" t="n">
         <v>-1</v>
       </c>
       <c r="AI5" t="n">
-        <v>100.71</v>
+        <v>95.62</v>
       </c>
       <c r="AJ5" t="n">
         <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="AL5" t="n">
-        <v>5.71</v>
+        <v>5.5</v>
       </c>
       <c r="AM5" t="n">
         <v>-1</v>
       </c>
       <c r="AN5" t="n">
-        <v>46.71</v>
+        <v>44.75</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AP5" t="n">
         <v>-1</v>
       </c>
       <c r="AQ5" t="n">
-        <v>12.43</v>
+        <v>12.62</v>
       </c>
       <c r="AR5" t="n">
-        <v>12.43</v>
+        <v>13.38</v>
       </c>
       <c r="AS5" t="n">
-        <v>10.43</v>
+        <v>10.38</v>
       </c>
       <c r="AT5" t="n">
         <v>1</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>54</v>
+        <v>53.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="BA5" t="n">
-        <v>13.14</v>
+        <v>12.75</v>
       </c>
       <c r="BB5" t="n">
-        <v>8.57</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.57</v>
+        <v>4.12</v>
       </c>
       <c r="BD5" t="n">
-        <v>21.71</v>
+        <v>21.38</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="BH5" t="n">
-        <v>10.47</v>
+        <v>10.19</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="BN5" t="n">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="BP5" t="n">
         <v>-1</v>
@@ -2792,25 +2792,25 @@
         <v>-1</v>
       </c>
       <c r="BR5" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS5" t="n">
-        <v>66.67</v>
+        <v>62.5</v>
       </c>
       <c r="BT5" t="n">
-        <v>46.67</v>
+        <v>43.75</v>
       </c>
       <c r="BU5" t="n">
-        <v>33.33</v>
+        <v>31.25</v>
       </c>
       <c r="BV5" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BW5" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX5" t="n">
-        <v>53.33</v>
+        <v>50</v>
       </c>
       <c r="BY5" t="n">
         <v>1.86</v>
@@ -2819,46 +2819,46 @@
         <v>1.96</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.73</v>
+        <v>3.71</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.8</v>
+        <v>3.79</v>
       </c>
       <c r="CC5" t="n">
-        <v>2.63</v>
+        <v>2.71</v>
       </c>
       <c r="CD5" t="n">
-        <v>2.81</v>
+        <v>2.89</v>
       </c>
       <c r="CE5" t="n">
         <v>1.39</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="CH5" t="n">
         <v>1.45</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CK5" t="n">
         <v>1.5</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CO5" t="n">
         <v>1.28</v>
@@ -2867,7 +2867,7 @@
         <v>1.96</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.29</v>
+        <v>3.27</v>
       </c>
       <c r="CR5" t="n">
         <v>1.44</v>
@@ -2882,10 +2882,10 @@
         <v>1.38</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CX5" t="n">
         <v>1.6</v>
@@ -2903,82 +2903,82 @@
         <v>1.3</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.33</v>
+        <v>3.32</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="DG5" t="n">
         <v>-1</v>
       </c>
       <c r="DH5" t="n">
-        <v>103.6</v>
+        <v>100.87</v>
       </c>
       <c r="DI5" t="n">
         <v>0</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.06</v>
+        <v>5</v>
       </c>
       <c r="DL5" t="n">
         <v>-1</v>
       </c>
       <c r="DM5" t="n">
-        <v>50.6</v>
+        <v>49.38</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DO5" t="n">
         <v>-1</v>
       </c>
       <c r="DP5" t="n">
-        <v>11.87</v>
+        <v>12</v>
       </c>
       <c r="DQ5" t="n">
-        <v>15.67</v>
+        <v>15.94</v>
       </c>
       <c r="DR5" t="n">
-        <v>9.27</v>
+        <v>9.32</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.34</v>
+        <v>0.32</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.34</v>
+        <v>0.32</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>56</v>
+        <v>55.62</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DX5" t="n">
-        <v>14</v>
+        <v>13.75</v>
       </c>
       <c r="DY5" t="n">
         <v>9</v>
       </c>
       <c r="DZ5" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="EA5" t="n">
-        <v>21.6</v>
+        <v>21.44</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="EC5" t="n">
         <v>2</v>
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" t="n">
         <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3487,49 +3487,49 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AH7" t="n">
         <v>-1</v>
       </c>
       <c r="AI7" t="n">
-        <v>82.25</v>
+        <v>83.67</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="AL7" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AM7" t="n">
         <v>-1</v>
       </c>
       <c r="AN7" t="n">
-        <v>32.25</v>
+        <v>33.67</v>
       </c>
       <c r="AO7" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AP7" t="n">
         <v>-1</v>
       </c>
       <c r="AQ7" t="n">
-        <v>15.12</v>
+        <v>15.11</v>
       </c>
       <c r="AR7" t="n">
-        <v>14.62</v>
+        <v>14.56</v>
       </c>
       <c r="AS7" t="n">
-        <v>9.25</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="AT7" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="AU7" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="AV7" t="n">
         <v>0</v>
@@ -3541,55 +3541,55 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>46.62</v>
+        <v>47.11</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA7" t="n">
-        <v>7.38</v>
+        <v>8</v>
       </c>
       <c r="BB7" t="n">
-        <v>5</v>
+        <v>5.44</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="BD7" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.87</v>
+        <v>0.93</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.07</v>
+        <v>3.19</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.4</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.07</v>
+        <v>3.19</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BL7" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="BP7" t="n">
         <v>-1</v>
@@ -3598,25 +3598,25 @@
         <v>-1</v>
       </c>
       <c r="BR7" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS7" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BT7" t="n">
-        <v>66.67</v>
+        <v>68.75</v>
       </c>
       <c r="BU7" t="n">
-        <v>33.33</v>
+        <v>37.5</v>
       </c>
       <c r="BV7" t="n">
-        <v>13.33</v>
+        <v>18.75</v>
       </c>
       <c r="BW7" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BX7" t="n">
-        <v>53.33</v>
+        <v>56.25</v>
       </c>
       <c r="BY7" t="n">
         <v>4.24</v>
@@ -3625,31 +3625,31 @@
         <v>4.18</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.73</v>
+        <v>3.71</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.95</v>
+        <v>3.92</v>
       </c>
       <c r="CC7" t="n">
-        <v>5.04</v>
+        <v>4.89</v>
       </c>
       <c r="CD7" t="n">
-        <v>5.72</v>
+        <v>5.52</v>
       </c>
       <c r="CE7" t="n">
         <v>1.39</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.05</v>
+        <v>3.03</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CJ7" t="n">
         <v>1.87</v>
@@ -3661,19 +3661,19 @@
         <v>1.99</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CO7" t="n">
         <v>1.29</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.27</v>
+        <v>3.33</v>
       </c>
       <c r="CR7" t="n">
         <v>1.44</v>
@@ -3688,10 +3688,10 @@
         <v>1.41</v>
       </c>
       <c r="CV7" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CX7" t="n">
         <v>1.62</v>
@@ -3718,19 +3718,19 @@
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="DG7" t="n">
         <v>-1</v>
       </c>
       <c r="DH7" t="n">
-        <v>79.73</v>
+        <v>80.69</v>
       </c>
       <c r="DI7" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.47</v>
+        <v>2.37</v>
       </c>
       <c r="DK7" t="n">
         <v>3.13</v>
@@ -3739,22 +3739,22 @@
         <v>-1</v>
       </c>
       <c r="DM7" t="n">
-        <v>34.6</v>
+        <v>35.25</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="DO7" t="n">
         <v>-1</v>
       </c>
       <c r="DP7" t="n">
-        <v>14.46</v>
+        <v>14.5</v>
       </c>
       <c r="DQ7" t="n">
-        <v>14.66</v>
+        <v>14.63</v>
       </c>
       <c r="DR7" t="n">
-        <v>8.6</v>
+        <v>8.56</v>
       </c>
       <c r="DS7" t="n">
         <v>0</v>
@@ -3766,28 +3766,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>46.06</v>
+        <v>46.38</v>
       </c>
       <c r="DW7" t="n">
         <v>0.06</v>
       </c>
       <c r="DX7" t="n">
-        <v>7.67</v>
+        <v>8</v>
       </c>
       <c r="DY7" t="n">
-        <v>5.4</v>
+        <v>5.62</v>
       </c>
       <c r="DZ7" t="n">
-        <v>2.27</v>
+        <v>2.38</v>
       </c>
       <c r="EA7" t="n">
-        <v>18.73</v>
+        <v>18.5</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.9</v>
+        <v>0.93</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="8">
@@ -5812,94 +5812,94 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D13" t="n">
         <v>7</v>
       </c>
       <c r="E13" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="F13" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="G13" t="n">
         <v>-1</v>
       </c>
       <c r="H13" t="n">
-        <v>85.25</v>
+        <v>83.78</v>
       </c>
       <c r="I13" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="J13" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="K13" t="n">
-        <v>4.88</v>
+        <v>5.11</v>
       </c>
       <c r="L13" t="n">
         <v>-1</v>
       </c>
       <c r="M13" t="n">
-        <v>44.25</v>
+        <v>44</v>
       </c>
       <c r="N13" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="O13" t="n">
         <v>-1</v>
       </c>
       <c r="P13" t="n">
-        <v>16.88</v>
+        <v>16.44</v>
       </c>
       <c r="Q13" t="n">
-        <v>15</v>
+        <v>16.22</v>
       </c>
       <c r="R13" t="n">
-        <v>8.25</v>
+        <v>7.89</v>
       </c>
       <c r="S13" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="T13" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="V13" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>50.38</v>
+        <v>49.89</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>11.5</v>
+        <v>11.44</v>
       </c>
       <c r="AA13" t="n">
-        <v>8.25</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="AB13" t="n">
-        <v>3.25</v>
+        <v>3.33</v>
       </c>
       <c r="AC13" t="n">
-        <v>20.62</v>
+        <v>21.89</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -5983,31 +5983,31 @@
         <v>1.86</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.87</v>
+        <v>2.69</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.73</v>
+        <v>9.75</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.87</v>
+        <v>2.69</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="BL13" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="BP13" t="n">
         <v>-1</v>
@@ -6016,37 +6016,37 @@
         <v>-1</v>
       </c>
       <c r="BR13" t="n">
-        <v>93.33</v>
+        <v>87.5</v>
       </c>
       <c r="BS13" t="n">
-        <v>66.67</v>
+        <v>62.5</v>
       </c>
       <c r="BT13" t="n">
-        <v>53.33</v>
+        <v>50</v>
       </c>
       <c r="BU13" t="n">
-        <v>46.67</v>
+        <v>43.75</v>
       </c>
       <c r="BV13" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BW13" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX13" t="n">
-        <v>66.67</v>
+        <v>62.5</v>
       </c>
       <c r="BY13" t="n">
-        <v>3.7</v>
+        <v>3.67</v>
       </c>
       <c r="BZ13" t="n">
-        <v>4.43</v>
+        <v>4.35</v>
       </c>
       <c r="CA13" t="n">
-        <v>4.17</v>
+        <v>4.11</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.44</v>
+        <v>4.36</v>
       </c>
       <c r="CC13" t="n">
         <v>6.6</v>
@@ -6055,22 +6055,22 @@
         <v>6.88</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.57</v>
+        <v>2.61</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.27</v>
+        <v>3.23</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CK13" t="n">
         <v>1.38</v>
@@ -6079,19 +6079,19 @@
         <v>1.82</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.85</v>
+        <v>2.83</v>
       </c>
       <c r="CN13" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.83</v>
+        <v>2.9</v>
       </c>
       <c r="CR13" t="n">
         <v>1.4</v>
@@ -6106,22 +6106,22 @@
         <v>1.56</v>
       </c>
       <c r="CV13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="CW13" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="CX13" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="CY13" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="CZ13" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="DA13" t="n">
         <v>2.12</v>
-      </c>
-      <c r="CW13" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="CX13" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="CY13" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="CZ13" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="DA13" t="n">
-        <v>2.18</v>
       </c>
       <c r="DB13" t="n">
         <v>1.25</v>
@@ -6133,79 +6133,79 @@
         <v>2.97</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="DG13" t="n">
         <v>-1</v>
       </c>
       <c r="DH13" t="n">
-        <v>88.67</v>
+        <v>87.63</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.13</v>
+        <v>0.19</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.94</v>
+        <v>5.06</v>
       </c>
       <c r="DL13" t="n">
         <v>-1</v>
       </c>
       <c r="DM13" t="n">
-        <v>43.27</v>
+        <v>43.19</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.73</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="DO13" t="n">
         <v>-1</v>
       </c>
       <c r="DP13" t="n">
-        <v>15.07</v>
+        <v>14.94</v>
       </c>
       <c r="DQ13" t="n">
-        <v>15.6</v>
+        <v>16.25</v>
       </c>
       <c r="DR13" t="n">
-        <v>8.800000000000001</v>
+        <v>8.56</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>49.74</v>
+        <v>49.5</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DX13" t="n">
-        <v>10.8</v>
+        <v>10.81</v>
       </c>
       <c r="DY13" t="n">
-        <v>7.2</v>
+        <v>7.19</v>
       </c>
       <c r="DZ13" t="n">
-        <v>3.6</v>
+        <v>3.62</v>
       </c>
       <c r="EA13" t="n">
-        <v>22.2</v>
+        <v>22.81</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="14">
@@ -6618,10 +6618,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D15" t="n">
         <v>7</v>
@@ -6630,13 +6630,13 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="G15" t="n">
         <v>-1</v>
       </c>
       <c r="H15" t="n">
-        <v>86.75</v>
+        <v>85.78</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -6645,67 +6645,67 @@
         <v>2</v>
       </c>
       <c r="K15" t="n">
-        <v>4.62</v>
+        <v>4.44</v>
       </c>
       <c r="L15" t="n">
         <v>-1</v>
       </c>
       <c r="M15" t="n">
-        <v>38.5</v>
+        <v>36.78</v>
       </c>
       <c r="N15" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="O15" t="n">
         <v>-1</v>
       </c>
       <c r="P15" t="n">
-        <v>15.62</v>
+        <v>15.44</v>
       </c>
       <c r="Q15" t="n">
-        <v>14.38</v>
+        <v>14.22</v>
       </c>
       <c r="R15" t="n">
-        <v>8.5</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="S15" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="T15" t="n">
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="V15" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>40.12</v>
+        <v>40.89</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z15" t="n">
-        <v>10.38</v>
+        <v>10.22</v>
       </c>
       <c r="AA15" t="n">
-        <v>7.12</v>
+        <v>7</v>
       </c>
       <c r="AB15" t="n">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="AC15" t="n">
-        <v>20.62</v>
+        <v>21</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -6789,31 +6789,31 @@
         <v>2.43</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="BH15" t="n">
-        <v>8.130000000000001</v>
+        <v>8</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="BP15" t="n">
         <v>-1</v>
@@ -6822,37 +6822,37 @@
         <v>-1</v>
       </c>
       <c r="BR15" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BS15" t="n">
-        <v>60</v>
+        <v>56.25</v>
       </c>
       <c r="BT15" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="BU15" t="n">
-        <v>26.67</v>
+        <v>25</v>
       </c>
       <c r="BV15" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BW15" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX15" t="n">
-        <v>33.33</v>
+        <v>31.25</v>
       </c>
       <c r="BY15" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="BZ15" t="n">
-        <v>3.03</v>
+        <v>3</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.41</v>
+        <v>3.39</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.61</v>
+        <v>3.59</v>
       </c>
       <c r="CC15" t="n">
         <v>3.49</v>
@@ -6864,13 +6864,13 @@
         <v>1.42</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CI15" t="n">
         <v>1.96</v>
@@ -6879,7 +6879,7 @@
         <v>1.85</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CL15" t="n">
         <v>1.99</v>
@@ -6888,16 +6888,16 @@
         <v>2.42</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CP15" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.53</v>
+        <v>3.57</v>
       </c>
       <c r="CR15" t="n">
         <v>1.39</v>
@@ -6912,7 +6912,7 @@
         <v>1.42</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CW15" t="n">
         <v>1.88</v>
@@ -6933,85 +6933,85 @@
         <v>1.34</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.67</v>
+        <v>3.69</v>
       </c>
       <c r="DE15" t="n">
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="DG15" t="n">
         <v>-1</v>
       </c>
       <c r="DH15" t="n">
-        <v>85</v>
+        <v>84.56</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="DK15" t="n">
-        <v>4.8</v>
+        <v>4.69</v>
       </c>
       <c r="DL15" t="n">
         <v>-1</v>
       </c>
       <c r="DM15" t="n">
-        <v>39.4</v>
+        <v>38.38</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.73</v>
+        <v>0.68</v>
       </c>
       <c r="DO15" t="n">
         <v>-1</v>
       </c>
       <c r="DP15" t="n">
-        <v>16.4</v>
+        <v>16.25</v>
       </c>
       <c r="DQ15" t="n">
-        <v>14</v>
+        <v>13.94</v>
       </c>
       <c r="DR15" t="n">
-        <v>8.33</v>
+        <v>8.18</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>40.93</v>
+        <v>41.31</v>
       </c>
       <c r="DW15" t="n">
         <v>0.06</v>
       </c>
       <c r="DX15" t="n">
-        <v>10.73</v>
+        <v>10.62</v>
       </c>
       <c r="DY15" t="n">
-        <v>7.53</v>
+        <v>7.44</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="EA15" t="n">
-        <v>18.8</v>
+        <v>19.12</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="16">
@@ -7021,94 +7021,94 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D16" t="n">
         <v>7</v>
       </c>
       <c r="E16" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F16" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H16" t="n">
+        <v>98.33</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="K16" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="L16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>49.67</v>
+      </c>
+      <c r="N16" t="n">
         <v>1</v>
       </c>
-      <c r="G16" t="n">
-        <v>-1</v>
-      </c>
-      <c r="H16" t="n">
-        <v>103</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="K16" t="n">
-        <v>5.62</v>
-      </c>
-      <c r="L16" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M16" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="N16" t="n">
-        <v>1.12</v>
-      </c>
       <c r="O16" t="n">
         <v>-1</v>
       </c>
       <c r="P16" t="n">
-        <v>14.62</v>
+        <v>15.22</v>
       </c>
       <c r="Q16" t="n">
-        <v>15.62</v>
+        <v>15.44</v>
       </c>
       <c r="R16" t="n">
-        <v>6.25</v>
+        <v>6.67</v>
       </c>
       <c r="S16" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="T16" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="U16" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="V16" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>61.5</v>
+        <v>60.22</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="Z16" t="n">
-        <v>13.5</v>
+        <v>13.11</v>
       </c>
       <c r="AA16" t="n">
-        <v>9.119999999999999</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="AB16" t="n">
-        <v>4.38</v>
+        <v>4</v>
       </c>
       <c r="AC16" t="n">
-        <v>23</v>
+        <v>22.78</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.54</v>
+        <v>1.47</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -7192,31 +7192,31 @@
         <v>2.43</v>
       </c>
       <c r="BG16" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="BH16" t="n">
-        <v>8.869999999999999</v>
+        <v>8.69</v>
       </c>
       <c r="BI16" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="BP16" t="n">
         <v>-1</v>
@@ -7228,34 +7228,34 @@
         <v>100</v>
       </c>
       <c r="BS16" t="n">
-        <v>86.67</v>
+        <v>81.25</v>
       </c>
       <c r="BT16" t="n">
-        <v>66.67</v>
+        <v>62.5</v>
       </c>
       <c r="BU16" t="n">
-        <v>26.67</v>
+        <v>25</v>
       </c>
       <c r="BV16" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BW16" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX16" t="n">
-        <v>66.67</v>
+        <v>62.5</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="BZ16" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.99</v>
+        <v>3.96</v>
       </c>
       <c r="CB16" t="n">
-        <v>4.34</v>
+        <v>4.29</v>
       </c>
       <c r="CC16" t="n">
         <v>2.34</v>
@@ -7276,16 +7276,16 @@
         <v>1.48</v>
       </c>
       <c r="CI16" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="CK16" t="n">
         <v>1.43</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CM16" t="n">
         <v>2.63</v>
@@ -7297,7 +7297,7 @@
         <v>1.24</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CQ16" t="n">
         <v>2.99</v>
@@ -7315,10 +7315,10 @@
         <v>1.45</v>
       </c>
       <c r="CV16" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CX16" t="n">
         <v>1.54</v>
@@ -7339,82 +7339,82 @@
         <v>1.93</v>
       </c>
       <c r="DD16" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="DE16" t="n">
         <v>0.06</v>
       </c>
       <c r="DF16" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="DG16" t="n">
         <v>-1</v>
       </c>
       <c r="DH16" t="n">
-        <v>97.54000000000001</v>
+        <v>95.25</v>
       </c>
       <c r="DI16" t="n">
         <v>0</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.47</v>
+        <v>2.43</v>
       </c>
       <c r="DK16" t="n">
-        <v>5.13</v>
+        <v>4.94</v>
       </c>
       <c r="DL16" t="n">
         <v>-1</v>
       </c>
       <c r="DM16" t="n">
-        <v>49.33</v>
+        <v>47.94</v>
       </c>
       <c r="DN16" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="DO16" t="n">
         <v>-1</v>
       </c>
       <c r="DP16" t="n">
-        <v>15.87</v>
+        <v>16.13</v>
       </c>
       <c r="DQ16" t="n">
-        <v>16.13</v>
+        <v>16</v>
       </c>
       <c r="DR16" t="n">
-        <v>6.33</v>
+        <v>6.56</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>61.67</v>
+        <v>60.94</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DX16" t="n">
-        <v>13</v>
+        <v>12.81</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.800000000000001</v>
+        <v>8.81</v>
       </c>
       <c r="DZ16" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="EA16" t="n">
-        <v>21.07</v>
+        <v>21.06</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="17">

--- a/data/teams/leagues/Averages_Russian_Premier_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Russian_Premier_League_2025-2026.xlsx
@@ -1478,7 +1478,7 @@
         <v>-1</v>
       </c>
       <c r="AI2" t="n">
-        <v>91.33</v>
+        <v>93.22</v>
       </c>
       <c r="AJ2" t="n">
         <v>0.11</v>
@@ -1493,7 +1493,7 @@
         <v>-1</v>
       </c>
       <c r="AN2" t="n">
-        <v>38.67</v>
+        <v>42.22</v>
       </c>
       <c r="AO2" t="n">
         <v>0.78</v>
@@ -1505,7 +1505,7 @@
         <v>14.11</v>
       </c>
       <c r="AR2" t="n">
-        <v>16.89</v>
+        <v>17.11</v>
       </c>
       <c r="AS2" t="n">
         <v>7.44</v>
@@ -1544,7 +1544,7 @@
         <v>21.56</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="BF2" t="n">
         <v>1.67</v>
@@ -1613,13 +1613,13 @@
         <v>3.5</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.58</v>
+        <v>3.57</v>
       </c>
       <c r="CC2" t="n">
         <v>3.38</v>
       </c>
       <c r="CD2" t="n">
-        <v>3.45</v>
+        <v>3.46</v>
       </c>
       <c r="CE2" t="n">
         <v>1.42</v>
@@ -1673,31 +1673,31 @@
         <v>1.42</v>
       </c>
       <c r="CV2" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CW2" t="n">
         <v>1.89</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CY2" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.39</v>
+        <v>2.36</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="DB2" t="n">
         <v>1.34</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.64</v>
+        <v>3.68</v>
       </c>
       <c r="DE2" t="n">
         <v>0.13</v>
@@ -1709,7 +1709,7 @@
         <v>-1</v>
       </c>
       <c r="DH2" t="n">
-        <v>91.93000000000001</v>
+        <v>93</v>
       </c>
       <c r="DI2" t="n">
         <v>0.06</v>
@@ -1724,7 +1724,7 @@
         <v>-1</v>
       </c>
       <c r="DM2" t="n">
-        <v>43.38</v>
+        <v>45.37</v>
       </c>
       <c r="DN2" t="n">
         <v>0.5</v>
@@ -1736,7 +1736,7 @@
         <v>12.18</v>
       </c>
       <c r="DQ2" t="n">
-        <v>16.94</v>
+        <v>17.06</v>
       </c>
       <c r="DR2" t="n">
         <v>6.43</v>
@@ -1769,7 +1769,7 @@
         <v>21.81</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="EC2" t="n">
         <v>1.69</v>
@@ -2419,7 +2419,7 @@
         <v>3.44</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.47</v>
+        <v>3.48</v>
       </c>
       <c r="CC4" t="n">
         <v>3.37</v>
@@ -2479,7 +2479,7 @@
         <v>1.39</v>
       </c>
       <c r="CV4" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CW4" t="n">
         <v>2.07</v>
@@ -2491,7 +2491,7 @@
         <v>1.98</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="DA4" t="n">
         <v>1.86</v>
@@ -2500,10 +2500,10 @@
         <v>1.42</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="DD4" t="n">
-        <v>4.34</v>
+        <v>4.3</v>
       </c>
       <c r="DE4" t="n">
         <v>0.31</v>
@@ -2687,7 +2687,7 @@
         <v>-1</v>
       </c>
       <c r="AI5" t="n">
-        <v>95.62</v>
+        <v>99</v>
       </c>
       <c r="AJ5" t="n">
         <v>0</v>
@@ -2702,7 +2702,7 @@
         <v>-1</v>
       </c>
       <c r="AN5" t="n">
-        <v>44.75</v>
+        <v>46</v>
       </c>
       <c r="AO5" t="n">
         <v>0.5</v>
@@ -2714,7 +2714,7 @@
         <v>12.62</v>
       </c>
       <c r="AR5" t="n">
-        <v>13.38</v>
+        <v>13.25</v>
       </c>
       <c r="AS5" t="n">
         <v>10.38</v>
@@ -2753,7 +2753,7 @@
         <v>21.38</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="BF5" t="n">
         <v>2.12</v>
@@ -2822,13 +2822,13 @@
         <v>3.71</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.79</v>
+        <v>3.78</v>
       </c>
       <c r="CC5" t="n">
         <v>2.71</v>
       </c>
       <c r="CD5" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="CE5" t="n">
         <v>1.39</v>
@@ -2870,16 +2870,16 @@
         <v>3.27</v>
       </c>
       <c r="CR5" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CS5" t="n">
-        <v>3.11</v>
+        <v>3.06</v>
       </c>
       <c r="CT5" t="n">
-        <v>2.86</v>
+        <v>2.89</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CV5" t="n">
         <v>2.05</v>
@@ -2918,7 +2918,7 @@
         <v>-1</v>
       </c>
       <c r="DH5" t="n">
-        <v>100.87</v>
+        <v>102.56</v>
       </c>
       <c r="DI5" t="n">
         <v>0</v>
@@ -2933,7 +2933,7 @@
         <v>-1</v>
       </c>
       <c r="DM5" t="n">
-        <v>49.38</v>
+        <v>50</v>
       </c>
       <c r="DN5" t="n">
         <v>0.5600000000000001</v>
@@ -2945,7 +2945,7 @@
         <v>12</v>
       </c>
       <c r="DQ5" t="n">
-        <v>15.94</v>
+        <v>15.88</v>
       </c>
       <c r="DR5" t="n">
         <v>9.32</v>
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D6" t="n">
         <v>7</v>
@@ -3003,82 +3003,82 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="G6" t="n">
         <v>-1</v>
       </c>
       <c r="H6" t="n">
-        <v>102.88</v>
+        <v>102</v>
       </c>
       <c r="I6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="J6" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="K6" t="n">
-        <v>5.88</v>
+        <v>5.67</v>
       </c>
       <c r="L6" t="n">
         <v>-1</v>
       </c>
       <c r="M6" t="n">
-        <v>54.38</v>
+        <v>54</v>
       </c>
       <c r="N6" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="O6" t="n">
         <v>-1</v>
       </c>
       <c r="P6" t="n">
-        <v>12.38</v>
+        <v>12.44</v>
       </c>
       <c r="Q6" t="n">
-        <v>18.5</v>
+        <v>17.78</v>
       </c>
       <c r="R6" t="n">
-        <v>4.5</v>
+        <v>4.67</v>
       </c>
       <c r="S6" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="T6" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="U6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="V6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>58.38</v>
+        <v>58</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>17.38</v>
+        <v>16.44</v>
       </c>
       <c r="AA6" t="n">
-        <v>11.5</v>
+        <v>10.67</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.88</v>
+        <v>5.78</v>
       </c>
       <c r="AC6" t="n">
-        <v>22.38</v>
+        <v>21.44</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AF6" t="n">
         <v>0.14</v>
@@ -3165,28 +3165,28 @@
         <v>3</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.33</v>
+        <v>9.19</v>
       </c>
       <c r="BI6" t="n">
         <v>3</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="BP6" t="n">
         <v>-1</v>
@@ -3195,37 +3195,37 @@
         <v>-1</v>
       </c>
       <c r="BR6" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS6" t="n">
-        <v>73.33</v>
+        <v>75</v>
       </c>
       <c r="BT6" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="BU6" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="BV6" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BW6" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX6" t="n">
-        <v>66.67</v>
+        <v>62.5</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="BZ6" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="CA6" t="n">
         <v>3.85</v>
       </c>
       <c r="CB6" t="n">
-        <v>4.04</v>
+        <v>4.05</v>
       </c>
       <c r="CC6" t="n">
         <v>2.69</v>
@@ -3234,22 +3234,22 @@
         <v>2.62</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.35</v>
+        <v>3.32</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CK6" t="n">
         <v>1.45</v>
@@ -3258,7 +3258,7 @@
         <v>1.91</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.59</v>
+        <v>2.57</v>
       </c>
       <c r="CN6" t="n">
         <v>1.97</v>
@@ -3267,10 +3267,10 @@
         <v>1.23</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="CR6" t="n">
         <v>1.35</v>
@@ -3285,10 +3285,10 @@
         <v>1.52</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="CX6" t="n">
         <v>1.54</v>
@@ -3297,94 +3297,94 @@
         <v>1.9</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="DA6" t="n">
         <v>1.91</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.04</v>
+        <v>3.08</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="DG6" t="n">
         <v>-1</v>
       </c>
       <c r="DH6" t="n">
-        <v>98.94</v>
+        <v>98.69</v>
       </c>
       <c r="DI6" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.07</v>
+        <v>1.94</v>
       </c>
       <c r="DK6" t="n">
-        <v>5.27</v>
+        <v>5.19</v>
       </c>
       <c r="DL6" t="n">
         <v>-1</v>
       </c>
       <c r="DM6" t="n">
-        <v>51.73</v>
+        <v>51.69</v>
       </c>
       <c r="DN6" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DO6" t="n">
         <v>-1</v>
       </c>
       <c r="DP6" t="n">
-        <v>13.4</v>
+        <v>13.37</v>
       </c>
       <c r="DQ6" t="n">
-        <v>17.07</v>
+        <v>16.75</v>
       </c>
       <c r="DR6" t="n">
-        <v>5.47</v>
+        <v>5.5</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>55.73</v>
+        <v>55.69</v>
       </c>
       <c r="DW6" t="n">
         <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>15.54</v>
+        <v>15.12</v>
       </c>
       <c r="DY6" t="n">
-        <v>10.94</v>
+        <v>10.5</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.6</v>
+        <v>4.62</v>
       </c>
       <c r="EA6" t="n">
-        <v>21.87</v>
+        <v>21.37</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.07</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="7">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C8" t="n">
         <v>8</v>
       </c>
       <c r="D8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -3887,112 +3887,112 @@
         <v>2.75</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AH8" t="n">
         <v>-1</v>
       </c>
       <c r="AI8" t="n">
-        <v>89.29000000000001</v>
+        <v>89.75</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AL8" t="n">
-        <v>4.29</v>
+        <v>4.25</v>
       </c>
       <c r="AM8" t="n">
         <v>-1</v>
       </c>
       <c r="AN8" t="n">
-        <v>38.29</v>
+        <v>39.25</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AP8" t="n">
         <v>-1</v>
       </c>
       <c r="AQ8" t="n">
-        <v>14</v>
+        <v>13.62</v>
       </c>
       <c r="AR8" t="n">
-        <v>18.57</v>
+        <v>19.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="AU8" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>56</v>
+        <v>56.88</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BA8" t="n">
-        <v>11.71</v>
+        <v>13</v>
       </c>
       <c r="BB8" t="n">
-        <v>8.140000000000001</v>
+        <v>8.75</v>
       </c>
       <c r="BC8" t="n">
-        <v>3.57</v>
+        <v>4.25</v>
       </c>
       <c r="BD8" t="n">
-        <v>23</v>
+        <v>22.12</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="BH8" t="n">
-        <v>8.6</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="BP8" t="n">
         <v>-1</v>
@@ -4001,25 +4001,25 @@
         <v>-1</v>
       </c>
       <c r="BR8" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS8" t="n">
-        <v>73.33</v>
+        <v>75</v>
       </c>
       <c r="BT8" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="BU8" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BV8" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BW8" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BX8" t="n">
-        <v>40</v>
+        <v>43.75</v>
       </c>
       <c r="BY8" t="n">
         <v>1.79</v>
@@ -4028,46 +4028,46 @@
         <v>1.77</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.81</v>
+        <v>3.78</v>
       </c>
       <c r="CB8" t="n">
-        <v>4.08</v>
+        <v>4.04</v>
       </c>
       <c r="CC8" t="n">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="CD8" t="n">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="CE8" t="n">
         <v>1.37</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CI8" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CK8" t="n">
         <v>1.49</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CM8" t="n">
         <v>2.47</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CO8" t="n">
         <v>1.27</v>
@@ -4076,7 +4076,7 @@
         <v>1.9</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="CR8" t="n">
         <v>1.42</v>
@@ -4091,22 +4091,22 @@
         <v>1.44</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="DB8" t="n">
         <v>1.27</v>
@@ -4118,79 +4118,79 @@
         <v>3.07</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="DG8" t="n">
         <v>-1</v>
       </c>
       <c r="DH8" t="n">
-        <v>92.13</v>
+        <v>92.18000000000001</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="DL8" t="n">
         <v>-1</v>
       </c>
       <c r="DM8" t="n">
-        <v>44.8</v>
+        <v>44.88</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DO8" t="n">
         <v>-1</v>
       </c>
       <c r="DP8" t="n">
-        <v>14.13</v>
+        <v>13.93</v>
       </c>
       <c r="DQ8" t="n">
-        <v>17.33</v>
+        <v>17.88</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.4</v>
+        <v>7.69</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>57</v>
+        <v>57.38</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DX8" t="n">
-        <v>15.06</v>
+        <v>15.5</v>
       </c>
       <c r="DY8" t="n">
-        <v>10.8</v>
+        <v>10.93</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.27</v>
+        <v>4.56</v>
       </c>
       <c r="EA8" t="n">
-        <v>22.07</v>
+        <v>21.68</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="9">
@@ -4200,25 +4200,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D9" t="n">
         <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="F9" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="G9" t="n">
         <v>-1</v>
       </c>
       <c r="H9" t="n">
-        <v>83.86</v>
+        <v>82.38</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -4227,34 +4227,34 @@
         <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>4.14</v>
+        <v>3.62</v>
       </c>
       <c r="L9" t="n">
         <v>-1</v>
       </c>
       <c r="M9" t="n">
-        <v>41.57</v>
+        <v>39.12</v>
       </c>
       <c r="N9" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="O9" t="n">
         <v>-1</v>
       </c>
       <c r="P9" t="n">
-        <v>13.57</v>
+        <v>14.12</v>
       </c>
       <c r="Q9" t="n">
-        <v>14.43</v>
+        <v>14.75</v>
       </c>
       <c r="R9" t="n">
-        <v>9</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="S9" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="T9" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -4266,28 +4266,28 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>47.29</v>
+        <v>46.12</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z9" t="n">
-        <v>10.29</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="AA9" t="n">
-        <v>7.57</v>
+        <v>6.62</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AC9" t="n">
-        <v>20.29</v>
+        <v>20.88</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AF9" t="n">
         <v>0.12</v>
@@ -4371,31 +4371,31 @@
         <v>2.88</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.93</v>
+        <v>2.88</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.4</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.93</v>
+        <v>2.88</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL9" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="BP9" t="n">
         <v>-1</v>
@@ -4407,34 +4407,34 @@
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BT9" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="BU9" t="n">
-        <v>33.33</v>
+        <v>31.25</v>
       </c>
       <c r="BV9" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BW9" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX9" t="n">
-        <v>60</v>
+        <v>56.25</v>
       </c>
       <c r="BY9" t="n">
-        <v>3.61</v>
+        <v>3.54</v>
       </c>
       <c r="BZ9" t="n">
-        <v>3.92</v>
+        <v>3.82</v>
       </c>
       <c r="CA9" t="n">
         <v>3.72</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.83</v>
+        <v>3.8</v>
       </c>
       <c r="CC9" t="n">
         <v>4.88</v>
@@ -4443,43 +4443,43 @@
         <v>4.97</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="CH9" t="n">
         <v>1.42</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="CK9" t="n">
         <v>1.53</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.46</v>
+        <v>3.41</v>
       </c>
       <c r="CR9" t="n">
         <v>1.43</v>
@@ -4500,13 +4500,13 @@
         <v>1.91</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CY9" t="n">
         <v>2.03</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="DA9" t="n">
         <v>1.8</v>
@@ -4521,46 +4521,46 @@
         <v>3.6</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="DG9" t="n">
         <v>-1</v>
       </c>
       <c r="DH9" t="n">
-        <v>80.40000000000001</v>
+        <v>79.88</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="DK9" t="n">
-        <v>3.47</v>
+        <v>3.25</v>
       </c>
       <c r="DL9" t="n">
         <v>-1</v>
       </c>
       <c r="DM9" t="n">
-        <v>35.67</v>
+        <v>34.81</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="DO9" t="n">
         <v>-1</v>
       </c>
       <c r="DP9" t="n">
-        <v>14.33</v>
+        <v>14.56</v>
       </c>
       <c r="DQ9" t="n">
-        <v>14.6</v>
+        <v>14.75</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="DS9" t="n">
         <v>0.06</v>
@@ -4572,28 +4572,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>47.87</v>
+        <v>47.25</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DX9" t="n">
-        <v>9.199999999999999</v>
+        <v>8.82</v>
       </c>
       <c r="DY9" t="n">
-        <v>6.53</v>
+        <v>6.12</v>
       </c>
       <c r="DZ9" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="EA9" t="n">
-        <v>19.34</v>
+        <v>19.69</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="10">
@@ -4603,94 +4603,94 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D10" t="n">
         <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="F10" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="G10" t="n">
         <v>-1</v>
       </c>
       <c r="H10" t="n">
-        <v>95.14</v>
+        <v>93.62</v>
       </c>
       <c r="I10" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="J10" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="K10" t="n">
-        <v>3.29</v>
+        <v>3</v>
       </c>
       <c r="L10" t="n">
         <v>-1</v>
       </c>
       <c r="M10" t="n">
-        <v>44.57</v>
+        <v>45.62</v>
       </c>
       <c r="N10" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="O10" t="n">
         <v>-1</v>
       </c>
       <c r="P10" t="n">
-        <v>13.86</v>
+        <v>15.25</v>
       </c>
       <c r="Q10" t="n">
-        <v>13.57</v>
+        <v>13.88</v>
       </c>
       <c r="R10" t="n">
-        <v>7.14</v>
+        <v>7</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="U10" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="V10" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>45.29</v>
+        <v>44.25</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z10" t="n">
-        <v>15.29</v>
+        <v>15.25</v>
       </c>
       <c r="AA10" t="n">
-        <v>8.57</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="AB10" t="n">
-        <v>6.71</v>
+        <v>6.12</v>
       </c>
       <c r="AC10" t="n">
-        <v>18.14</v>
+        <v>18</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="AF10" t="n">
         <v>0.12</v>
@@ -4774,31 +4774,31 @@
         <v>2.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.33</v>
+        <v>3.25</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.4</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.33</v>
+        <v>3.25</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="BL10" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="BN10" t="n">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="BP10" t="n">
         <v>-1</v>
@@ -4810,34 +4810,34 @@
         <v>100</v>
       </c>
       <c r="BS10" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BT10" t="n">
-        <v>53.33</v>
+        <v>50</v>
       </c>
       <c r="BU10" t="n">
-        <v>33.33</v>
+        <v>31.25</v>
       </c>
       <c r="BV10" t="n">
-        <v>26.67</v>
+        <v>25</v>
       </c>
       <c r="BW10" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BX10" t="n">
-        <v>66.67</v>
+        <v>68.75</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.92</v>
+        <v>2.07</v>
       </c>
       <c r="BZ10" t="n">
-        <v>2.16</v>
+        <v>2.27</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.69</v>
+        <v>3.67</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.83</v>
+        <v>3.8</v>
       </c>
       <c r="CC10" t="n">
         <v>2.89</v>
@@ -4846,43 +4846,43 @@
         <v>3.23</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.52</v>
+        <v>2.55</v>
       </c>
       <c r="CR10" t="n">
         <v>1.38</v>
@@ -4903,10 +4903,10 @@
         <v>1.68</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CY10" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CZ10" t="n">
         <v>2.53</v>
@@ -4924,79 +4924,79 @@
         <v>2.95</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="DG10" t="n">
         <v>-1</v>
       </c>
       <c r="DH10" t="n">
-        <v>93.8</v>
+        <v>93.12</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="DK10" t="n">
-        <v>3.94</v>
+        <v>3.75</v>
       </c>
       <c r="DL10" t="n">
         <v>-1</v>
       </c>
       <c r="DM10" t="n">
-        <v>46.13</v>
+        <v>46.56</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.87</v>
+        <v>0.82</v>
       </c>
       <c r="DO10" t="n">
         <v>-1</v>
       </c>
       <c r="DP10" t="n">
-        <v>14.07</v>
+        <v>14.75</v>
       </c>
       <c r="DQ10" t="n">
-        <v>14.33</v>
+        <v>14.44</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.53</v>
+        <v>7.44</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>48.8</v>
+        <v>48.06</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX10" t="n">
-        <v>14.07</v>
+        <v>14.12</v>
       </c>
       <c r="DY10" t="n">
-        <v>8.6</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="DZ10" t="n">
-        <v>5.47</v>
+        <v>5.25</v>
       </c>
       <c r="EA10" t="n">
-        <v>17.53</v>
+        <v>17.5</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="11">
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
         <v>8</v>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E11" t="n">
         <v>0.25</v>
@@ -5099,49 +5099,49 @@
         <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AH11" t="n">
         <v>-1</v>
       </c>
       <c r="AI11" t="n">
-        <v>111.43</v>
+        <v>109.88</v>
       </c>
       <c r="AJ11" t="n">
         <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AL11" t="n">
-        <v>3.71</v>
+        <v>3.62</v>
       </c>
       <c r="AM11" t="n">
         <v>-1</v>
       </c>
       <c r="AN11" t="n">
-        <v>49.14</v>
+        <v>49.38</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="AP11" t="n">
         <v>-1</v>
       </c>
       <c r="AQ11" t="n">
-        <v>13.71</v>
+        <v>13.25</v>
       </c>
       <c r="AR11" t="n">
-        <v>20.14</v>
+        <v>19.75</v>
       </c>
       <c r="AS11" t="n">
-        <v>6.43</v>
+        <v>6.38</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AV11" t="n">
         <v>0</v>
@@ -5153,55 +5153,55 @@
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>49.14</v>
+        <v>48.62</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="BA11" t="n">
-        <v>10.71</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="BB11" t="n">
-        <v>7.43</v>
+        <v>6.88</v>
       </c>
       <c r="BC11" t="n">
-        <v>3.29</v>
+        <v>3</v>
       </c>
       <c r="BD11" t="n">
-        <v>24.57</v>
+        <v>23.25</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="BH11" t="n">
-        <v>7.93</v>
+        <v>7.88</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.47</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BN11" t="n">
-        <v>0.87</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BP11" t="n">
         <v>-1</v>
@@ -5210,16 +5210,16 @@
         <v>-1</v>
       </c>
       <c r="BR11" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS11" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="BT11" t="n">
-        <v>6.67</v>
+        <v>12.5</v>
       </c>
       <c r="BU11" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BV11" t="n">
         <v>0</v>
@@ -5228,7 +5228,7 @@
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>26.67</v>
+        <v>25</v>
       </c>
       <c r="BY11" t="n">
         <v>3.19</v>
@@ -5237,25 +5237,25 @@
         <v>3.34</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.48</v>
+        <v>3.51</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.56</v>
+        <v>3.59</v>
       </c>
       <c r="CC11" t="n">
-        <v>5.67</v>
+        <v>5.65</v>
       </c>
       <c r="CD11" t="n">
-        <v>6.07</v>
+        <v>6.01</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CF11" t="n">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="CH11" t="n">
         <v>1.33</v>
@@ -5264,28 +5264,28 @@
         <v>1.75</v>
       </c>
       <c r="CJ11" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CK11" t="n">
         <v>1.54</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CM11" t="n">
         <v>2.33</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CO11" t="n">
         <v>1.42</v>
       </c>
       <c r="CP11" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="CQ11" t="n">
-        <v>4.17</v>
+        <v>4.12</v>
       </c>
       <c r="CR11" t="n">
         <v>1.48</v>
@@ -5306,67 +5306,67 @@
         <v>2.15</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="DB11" t="n">
         <v>1.42</v>
       </c>
       <c r="DC11" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="DD11" t="n">
-        <v>4.3</v>
+        <v>4.24</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="DG11" t="n">
         <v>-1</v>
       </c>
       <c r="DH11" t="n">
-        <v>108.33</v>
+        <v>107.75</v>
       </c>
       <c r="DI11" t="n">
         <v>0</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.26</v>
+        <v>4.19</v>
       </c>
       <c r="DL11" t="n">
         <v>-1</v>
       </c>
       <c r="DM11" t="n">
-        <v>48.93</v>
+        <v>49.06</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DO11" t="n">
         <v>-1</v>
       </c>
       <c r="DP11" t="n">
-        <v>13.86</v>
+        <v>13.62</v>
       </c>
       <c r="DQ11" t="n">
-        <v>19.47</v>
+        <v>19.31</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.2</v>
+        <v>7.13</v>
       </c>
       <c r="DS11" t="n">
         <v>0</v>
@@ -5378,28 +5378,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>48</v>
+        <v>47.81</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="DX11" t="n">
-        <v>10.73</v>
+        <v>10.32</v>
       </c>
       <c r="DY11" t="n">
-        <v>7.67</v>
+        <v>7.38</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3.07</v>
+        <v>2.94</v>
       </c>
       <c r="EA11" t="n">
-        <v>24.74</v>
+        <v>24.06</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="12">
@@ -5409,10 +5409,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D12" t="n">
         <v>7</v>
@@ -5421,49 +5421,49 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="G12" t="n">
         <v>-1</v>
       </c>
       <c r="H12" t="n">
-        <v>91.5</v>
+        <v>90.44</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="K12" t="n">
-        <v>3.62</v>
+        <v>4</v>
       </c>
       <c r="L12" t="n">
         <v>-1</v>
       </c>
       <c r="M12" t="n">
-        <v>44.62</v>
+        <v>45.56</v>
       </c>
       <c r="N12" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="O12" t="n">
         <v>-1</v>
       </c>
       <c r="P12" t="n">
-        <v>16.62</v>
+        <v>17.22</v>
       </c>
       <c r="Q12" t="n">
-        <v>14.75</v>
+        <v>14.33</v>
       </c>
       <c r="R12" t="n">
-        <v>7.88</v>
+        <v>7.22</v>
       </c>
       <c r="S12" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="T12" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -5475,28 +5475,28 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>49.12</v>
+        <v>47.56</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z12" t="n">
-        <v>12.12</v>
+        <v>12.22</v>
       </c>
       <c r="AA12" t="n">
-        <v>7.38</v>
+        <v>7.67</v>
       </c>
       <c r="AB12" t="n">
-        <v>4.75</v>
+        <v>4.56</v>
       </c>
       <c r="AC12" t="n">
-        <v>17.12</v>
+        <v>16.56</v>
       </c>
       <c r="AD12" t="n">
         <v>1.42</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.88</v>
+        <v>2.56</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -5580,31 +5580,31 @@
         <v>2.71</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.6</v>
+        <v>9.69</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="BL12" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.47</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="BP12" t="n">
         <v>-1</v>
@@ -5613,37 +5613,37 @@
         <v>-1</v>
       </c>
       <c r="BR12" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BS12" t="n">
-        <v>73.33</v>
+        <v>75</v>
       </c>
       <c r="BT12" t="n">
-        <v>46.67</v>
+        <v>43.75</v>
       </c>
       <c r="BU12" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BV12" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>26.67</v>
+        <v>25</v>
       </c>
       <c r="BY12" t="n">
-        <v>3.66</v>
+        <v>4.28</v>
       </c>
       <c r="BZ12" t="n">
-        <v>4.02</v>
+        <v>4.56</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="CB12" t="n">
-        <v>4.35</v>
+        <v>4.39</v>
       </c>
       <c r="CC12" t="n">
         <v>7.85</v>
@@ -5655,28 +5655,28 @@
         <v>1.28</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="CH12" t="n">
         <v>1.37</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CL12" t="n">
         <v>1.78</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="CN12" t="n">
         <v>1.8</v>
@@ -5688,7 +5688,7 @@
         <v>1.8</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="CR12" t="n">
         <v>1.44</v>
@@ -5703,73 +5703,73 @@
         <v>1.44</v>
       </c>
       <c r="CV12" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="CW12" t="n">
         <v>1.94</v>
-      </c>
-      <c r="CW12" t="n">
-        <v>1.92</v>
       </c>
       <c r="CX12" t="n">
         <v>1.53</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="CZ12" t="n">
         <v>2.44</v>
       </c>
       <c r="DA12" t="n">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="DB12" t="n">
         <v>1.31</v>
       </c>
       <c r="DC12" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.45</v>
+        <v>3.42</v>
       </c>
       <c r="DE12" t="n">
         <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="DG12" t="n">
         <v>-1</v>
       </c>
       <c r="DH12" t="n">
-        <v>84.40000000000001</v>
+        <v>84.25</v>
       </c>
       <c r="DI12" t="n">
         <v>0</v>
       </c>
       <c r="DJ12" t="n">
-        <v>3</v>
+        <v>2.81</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.06</v>
+        <v>4.25</v>
       </c>
       <c r="DL12" t="n">
         <v>-1</v>
       </c>
       <c r="DM12" t="n">
-        <v>38.06</v>
+        <v>39</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="DO12" t="n">
         <v>-1</v>
       </c>
       <c r="DP12" t="n">
-        <v>17.06</v>
+        <v>17.37</v>
       </c>
       <c r="DQ12" t="n">
-        <v>14.4</v>
+        <v>14.19</v>
       </c>
       <c r="DR12" t="n">
-        <v>8.93</v>
+        <v>8.5</v>
       </c>
       <c r="DS12" t="n">
         <v>0</v>
@@ -5781,28 +5781,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>43.93</v>
+        <v>43.38</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX12" t="n">
-        <v>10.8</v>
+        <v>10.94</v>
       </c>
       <c r="DY12" t="n">
-        <v>6.87</v>
+        <v>7.07</v>
       </c>
       <c r="DZ12" t="n">
-        <v>3.93</v>
+        <v>3.88</v>
       </c>
       <c r="EA12" t="n">
-        <v>18.06</v>
+        <v>17.69</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="13">
@@ -6040,13 +6040,13 @@
         <v>3.67</v>
       </c>
       <c r="BZ13" t="n">
-        <v>4.35</v>
+        <v>4.33</v>
       </c>
       <c r="CA13" t="n">
         <v>4.11</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.36</v>
+        <v>4.37</v>
       </c>
       <c r="CC13" t="n">
         <v>6.6</v>
@@ -6106,13 +6106,13 @@
         <v>1.56</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CW13" t="n">
         <v>1.79</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CY13" t="n">
         <v>1.75</v>
@@ -6124,13 +6124,13 @@
         <v>2.12</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.97</v>
+        <v>3.05</v>
       </c>
       <c r="DE13" t="n">
         <v>0.12</v>
@@ -6215,13 +6215,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C14" t="n">
         <v>7</v>
       </c>
       <c r="D14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E14" t="n">
         <v>0.14</v>
@@ -6308,109 +6308,109 @@
         <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AH14" t="n">
         <v>-1</v>
       </c>
       <c r="AI14" t="n">
-        <v>88.62</v>
+        <v>91.33</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="AL14" t="n">
-        <v>3.75</v>
+        <v>3.89</v>
       </c>
       <c r="AM14" t="n">
         <v>-1</v>
       </c>
       <c r="AN14" t="n">
-        <v>43.75</v>
+        <v>47.56</v>
       </c>
       <c r="AO14" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AP14" t="n">
         <v>-1</v>
       </c>
       <c r="AQ14" t="n">
-        <v>15.12</v>
+        <v>15.22</v>
       </c>
       <c r="AR14" t="n">
-        <v>17.38</v>
+        <v>17.44</v>
       </c>
       <c r="AS14" t="n">
-        <v>7</v>
+        <v>6.67</v>
       </c>
       <c r="AT14" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AX14" t="n">
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>46.38</v>
+        <v>48.11</v>
       </c>
       <c r="AZ14" t="n">
         <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>11.25</v>
+        <v>11.89</v>
       </c>
       <c r="BB14" t="n">
-        <v>7.25</v>
+        <v>7.89</v>
       </c>
       <c r="BC14" t="n">
         <v>4</v>
       </c>
       <c r="BD14" t="n">
-        <v>21.12</v>
+        <v>21.33</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="BH14" t="n">
-        <v>7.67</v>
+        <v>7.5</v>
       </c>
       <c r="BI14" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BP14" t="n">
         <v>-1</v>
@@ -6419,25 +6419,25 @@
         <v>-1</v>
       </c>
       <c r="BR14" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BS14" t="n">
-        <v>40</v>
+        <v>43.75</v>
       </c>
       <c r="BT14" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BU14" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BV14" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BW14" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX14" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="BY14" t="n">
         <v>2.35</v>
@@ -6446,34 +6446,34 @@
         <v>2.42</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.65</v>
+        <v>3.66</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.75</v>
+        <v>3.73</v>
       </c>
       <c r="CC14" t="n">
-        <v>4.41</v>
+        <v>4.18</v>
       </c>
       <c r="CD14" t="n">
-        <v>4.48</v>
+        <v>4.25</v>
       </c>
       <c r="CE14" t="n">
         <v>1.4</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="CK14" t="n">
         <v>1.55</v>
@@ -6482,19 +6482,19 @@
         <v>2.13</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="CN14" t="n">
         <v>1.81</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="CP14" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.42</v>
+        <v>3.37</v>
       </c>
       <c r="CR14" t="n">
         <v>1.38</v>
@@ -6512,70 +6512,70 @@
         <v>1.97</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CY14" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="DA14" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="DB14" t="n">
         <v>1.34</v>
       </c>
       <c r="DC14" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="DD14" t="n">
         <v>3.63</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="DG14" t="n">
         <v>-1</v>
       </c>
       <c r="DH14" t="n">
-        <v>93.26000000000001</v>
+        <v>94.5</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.67</v>
+        <v>2.56</v>
       </c>
       <c r="DK14" t="n">
-        <v>3.87</v>
+        <v>3.94</v>
       </c>
       <c r="DL14" t="n">
         <v>-1</v>
       </c>
       <c r="DM14" t="n">
-        <v>48</v>
+        <v>49.88</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="DO14" t="n">
         <v>-1</v>
       </c>
       <c r="DP14" t="n">
-        <v>14.46</v>
+        <v>14.56</v>
       </c>
       <c r="DQ14" t="n">
-        <v>17.47</v>
+        <v>17.5</v>
       </c>
       <c r="DR14" t="n">
-        <v>6.33</v>
+        <v>6.19</v>
       </c>
       <c r="DS14" t="n">
         <v>0.06</v>
@@ -6587,28 +6587,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>49.07</v>
+        <v>49.87</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX14" t="n">
-        <v>11.87</v>
+        <v>12.19</v>
       </c>
       <c r="DY14" t="n">
-        <v>7.93</v>
+        <v>8.25</v>
       </c>
       <c r="DZ14" t="n">
-        <v>3.93</v>
+        <v>3.94</v>
       </c>
       <c r="EA14" t="n">
-        <v>21.2</v>
+        <v>21.31</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.53</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="15">
@@ -6636,7 +6636,7 @@
         <v>-1</v>
       </c>
       <c r="H15" t="n">
-        <v>85.78</v>
+        <v>87.56</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -6651,7 +6651,7 @@
         <v>-1</v>
       </c>
       <c r="M15" t="n">
-        <v>36.78</v>
+        <v>39.33</v>
       </c>
       <c r="N15" t="n">
         <v>0.44</v>
@@ -6663,7 +6663,7 @@
         <v>15.44</v>
       </c>
       <c r="Q15" t="n">
-        <v>14.22</v>
+        <v>14.56</v>
       </c>
       <c r="R15" t="n">
         <v>8.220000000000001</v>
@@ -6690,10 +6690,10 @@
         <v>0.11</v>
       </c>
       <c r="Z15" t="n">
-        <v>10.22</v>
+        <v>10.33</v>
       </c>
       <c r="AA15" t="n">
-        <v>7</v>
+        <v>7.11</v>
       </c>
       <c r="AB15" t="n">
         <v>3.22</v>
@@ -6702,7 +6702,7 @@
         <v>21</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AE15" t="n">
         <v>1.89</v>
@@ -6918,25 +6918,25 @@
         <v>1.88</v>
       </c>
       <c r="CX15" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="CY15" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="DB15" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.69</v>
+        <v>3.73</v>
       </c>
       <c r="DE15" t="n">
         <v>0</v>
@@ -6948,7 +6948,7 @@
         <v>-1</v>
       </c>
       <c r="DH15" t="n">
-        <v>84.56</v>
+        <v>85.56</v>
       </c>
       <c r="DI15" t="n">
         <v>0.06</v>
@@ -6963,7 +6963,7 @@
         <v>-1</v>
       </c>
       <c r="DM15" t="n">
-        <v>38.38</v>
+        <v>39.81</v>
       </c>
       <c r="DN15" t="n">
         <v>0.68</v>
@@ -6975,7 +6975,7 @@
         <v>16.25</v>
       </c>
       <c r="DQ15" t="n">
-        <v>13.94</v>
+        <v>14.13</v>
       </c>
       <c r="DR15" t="n">
         <v>8.18</v>
@@ -6996,10 +6996,10 @@
         <v>0.06</v>
       </c>
       <c r="DX15" t="n">
-        <v>10.62</v>
+        <v>10.68</v>
       </c>
       <c r="DY15" t="n">
-        <v>7.44</v>
+        <v>7.5</v>
       </c>
       <c r="DZ15" t="n">
         <v>3.18</v>
@@ -7008,7 +7008,7 @@
         <v>19.12</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="EC15" t="n">
         <v>2.13</v>
@@ -7039,7 +7039,7 @@
         <v>-1</v>
       </c>
       <c r="H16" t="n">
-        <v>98.33</v>
+        <v>101.44</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -7054,7 +7054,7 @@
         <v>-1</v>
       </c>
       <c r="M16" t="n">
-        <v>49.67</v>
+        <v>50.56</v>
       </c>
       <c r="N16" t="n">
         <v>1</v>
@@ -7105,7 +7105,7 @@
         <v>22.78</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AE16" t="n">
         <v>1.78</v>
@@ -7249,13 +7249,13 @@
         <v>1.63</v>
       </c>
       <c r="BZ16" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CA16" t="n">
         <v>3.96</v>
       </c>
       <c r="CB16" t="n">
-        <v>4.29</v>
+        <v>4.28</v>
       </c>
       <c r="CC16" t="n">
         <v>2.34</v>
@@ -7339,7 +7339,7 @@
         <v>1.93</v>
       </c>
       <c r="DD16" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="DE16" t="n">
         <v>0.06</v>
@@ -7351,7 +7351,7 @@
         <v>-1</v>
       </c>
       <c r="DH16" t="n">
-        <v>95.25</v>
+        <v>97</v>
       </c>
       <c r="DI16" t="n">
         <v>0</v>
@@ -7366,7 +7366,7 @@
         <v>-1</v>
       </c>
       <c r="DM16" t="n">
-        <v>47.94</v>
+        <v>48.44</v>
       </c>
       <c r="DN16" t="n">
         <v>1.25</v>
@@ -7424,13 +7424,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C17" t="n">
         <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E17" t="n">
         <v>0.14</v>
@@ -7523,130 +7523,130 @@
         <v>-1</v>
       </c>
       <c r="AI17" t="n">
+        <v>95.44</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>52.78</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>9.890000000000001</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>22.56</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>6.78</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>60.89</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>10.44</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>6.11</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>19.67</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>9.81</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BR17" t="n">
         <v>93.75</v>
       </c>
-      <c r="AJ17" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>6</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>53.25</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>22.25</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>7.12</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>60.38</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>10.88</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>4.38</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>19.38</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="BH17" t="n">
-        <v>9.73</v>
-      </c>
-      <c r="BI17" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="BJ17" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="BK17" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="BL17" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM17" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="BN17" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="BO17" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BP17" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BQ17" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BR17" t="n">
-        <v>93.33</v>
-      </c>
       <c r="BS17" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BT17" t="n">
-        <v>46.67</v>
+        <v>43.75</v>
       </c>
       <c r="BU17" t="n">
-        <v>26.67</v>
+        <v>25</v>
       </c>
       <c r="BV17" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BW17" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX17" t="n">
-        <v>53.33</v>
+        <v>50</v>
       </c>
       <c r="BY17" t="n">
         <v>1.39</v>
@@ -7655,43 +7655,43 @@
         <v>1.4</v>
       </c>
       <c r="CA17" t="n">
-        <v>4.67</v>
+        <v>4.68</v>
       </c>
       <c r="CB17" t="n">
-        <v>5</v>
+        <v>4.99</v>
       </c>
       <c r="CC17" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="CD17" t="n">
         <v>1.81</v>
       </c>
-      <c r="CD17" t="n">
-        <v>1.86</v>
-      </c>
       <c r="CE17" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="CG17" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CL17" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="CN17" t="n">
         <v>1.96</v>
@@ -7703,7 +7703,7 @@
         <v>1.85</v>
       </c>
       <c r="CQ17" t="n">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="CR17" t="n">
         <v>1.43</v>
@@ -7718,22 +7718,22 @@
         <v>1.52</v>
       </c>
       <c r="CV17" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CW17" t="n">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="CX17" t="n">
         <v>1.55</v>
       </c>
       <c r="CY17" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CZ17" t="n">
         <v>2.42</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="DB17" t="n">
         <v>1.28</v>
@@ -7745,79 +7745,79 @@
         <v>3.15</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="DG17" t="n">
         <v>-1</v>
       </c>
       <c r="DH17" t="n">
-        <v>91.8</v>
+        <v>92.87</v>
       </c>
       <c r="DI17" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ17" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="DK17" t="n">
-        <v>6.27</v>
+        <v>6.13</v>
       </c>
       <c r="DL17" t="n">
         <v>-1</v>
       </c>
       <c r="DM17" t="n">
-        <v>51.47</v>
+        <v>51.31</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DO17" t="n">
         <v>-1</v>
       </c>
       <c r="DP17" t="n">
-        <v>10</v>
+        <v>9.94</v>
       </c>
       <c r="DQ17" t="n">
-        <v>20.4</v>
+        <v>20.69</v>
       </c>
       <c r="DR17" t="n">
-        <v>5.93</v>
+        <v>5.81</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.4</v>
+        <v>0.37</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.4</v>
+        <v>0.37</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>60.14</v>
+        <v>60.44</v>
       </c>
       <c r="DW17" t="n">
         <v>0.06</v>
       </c>
       <c r="DX17" t="n">
-        <v>12.94</v>
+        <v>12.56</v>
       </c>
       <c r="DY17" t="n">
-        <v>7.13</v>
+        <v>6.88</v>
       </c>
       <c r="DZ17" t="n">
-        <v>5.8</v>
+        <v>5.69</v>
       </c>
       <c r="EA17" t="n">
-        <v>18.94</v>
+        <v>19.13</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Russian_Premier_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Russian_Premier_League_2025-2026.xlsx
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
         <v>8</v>
@@ -1794,82 +1794,82 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="G3" t="n">
         <v>-1</v>
       </c>
       <c r="H3" t="n">
-        <v>99.25</v>
+        <v>99.67</v>
       </c>
       <c r="I3" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="J3" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="K3" t="n">
-        <v>3.38</v>
+        <v>4.11</v>
       </c>
       <c r="L3" t="n">
         <v>-1</v>
       </c>
       <c r="M3" t="n">
-        <v>48.5</v>
+        <v>49.33</v>
       </c>
       <c r="N3" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="O3" t="n">
         <v>-1</v>
       </c>
       <c r="P3" t="n">
-        <v>15.38</v>
+        <v>15.11</v>
       </c>
       <c r="Q3" t="n">
-        <v>15.5</v>
+        <v>15.56</v>
       </c>
       <c r="R3" t="n">
-        <v>7</v>
+        <v>7.11</v>
       </c>
       <c r="S3" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="T3" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="U3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="V3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>44.75</v>
+        <v>46</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>10.88</v>
+        <v>11.11</v>
       </c>
       <c r="AA3" t="n">
-        <v>6.5</v>
+        <v>6.56</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.38</v>
+        <v>4.56</v>
       </c>
       <c r="AC3" t="n">
-        <v>18</v>
+        <v>18.67</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AF3" t="n">
         <v>0.12</v>
@@ -1953,31 +1953,31 @@
         <v>2.25</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="BH3" t="n">
-        <v>8.880000000000001</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.62</v>
+        <v>0.71</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="BP3" t="n">
         <v>-1</v>
@@ -1989,31 +1989,31 @@
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BT3" t="n">
-        <v>50</v>
+        <v>52.94</v>
       </c>
       <c r="BU3" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BV3" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>68.75</v>
+        <v>70.59</v>
       </c>
       <c r="BY3" t="n">
-        <v>3.57</v>
+        <v>3.38</v>
       </c>
       <c r="BZ3" t="n">
         <v>3.82</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.85</v>
+        <v>3.84</v>
       </c>
       <c r="CB3" t="n">
         <v>4.16</v>
@@ -2028,40 +2028,40 @@
         <v>1.32</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.33</v>
+        <v>3.31</v>
       </c>
       <c r="CH3" t="n">
         <v>1.52</v>
       </c>
       <c r="CI3" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CJ3" t="n">
         <v>1.69</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CO3" t="n">
         <v>1.22</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="CR3" t="n">
         <v>1.38</v>
@@ -2106,43 +2106,43 @@
         <v>0.06</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="DG3" t="n">
         <v>-1</v>
       </c>
       <c r="DH3" t="n">
-        <v>92.88</v>
+        <v>93.47</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="DK3" t="n">
-        <v>4</v>
+        <v>4.35</v>
       </c>
       <c r="DL3" t="n">
         <v>-1</v>
       </c>
       <c r="DM3" t="n">
-        <v>44.75</v>
+        <v>45.41</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="DO3" t="n">
         <v>-1</v>
       </c>
       <c r="DP3" t="n">
-        <v>15.13</v>
+        <v>15</v>
       </c>
       <c r="DQ3" t="n">
-        <v>14.31</v>
+        <v>14.41</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.5</v>
+        <v>7.53</v>
       </c>
       <c r="DS3" t="n">
         <v>0.18</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>43.68</v>
+        <v>44.41</v>
       </c>
       <c r="DW3" t="n">
         <v>0</v>
       </c>
       <c r="DX3" t="n">
-        <v>11</v>
+        <v>11.11</v>
       </c>
       <c r="DY3" t="n">
-        <v>7.31</v>
+        <v>7.29</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.69</v>
+        <v>3.83</v>
       </c>
       <c r="EA3" t="n">
-        <v>18.19</v>
+        <v>18.53</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="EC3" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="4">
@@ -2588,94 +2588,94 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" t="n">
         <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="F5" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="G5" t="n">
         <v>-1</v>
       </c>
       <c r="H5" t="n">
-        <v>106.12</v>
+        <v>94.33</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="K5" t="n">
-        <v>4.5</v>
+        <v>4.56</v>
       </c>
       <c r="L5" t="n">
         <v>-1</v>
       </c>
       <c r="M5" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="N5" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="O5" t="n">
         <v>-1</v>
       </c>
       <c r="P5" t="n">
-        <v>11.38</v>
+        <v>11.33</v>
       </c>
       <c r="Q5" t="n">
-        <v>18.5</v>
+        <v>17.56</v>
       </c>
       <c r="R5" t="n">
-        <v>8.25</v>
+        <v>8.33</v>
       </c>
       <c r="S5" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="T5" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="U5" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="V5" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>57.75</v>
+        <v>58.22</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>14.75</v>
+        <v>14.56</v>
       </c>
       <c r="AA5" t="n">
-        <v>9.380000000000001</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.38</v>
+        <v>5.44</v>
       </c>
       <c r="AC5" t="n">
-        <v>21.5</v>
+        <v>20.78</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.7</v>
+        <v>1.51</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -2759,31 +2759,31 @@
         <v>2.12</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="BH5" t="n">
-        <v>10.19</v>
+        <v>10.47</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.5</v>
+        <v>0.59</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="BN5" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.88</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="BP5" t="n">
         <v>-1</v>
@@ -2792,37 +2792,37 @@
         <v>-1</v>
       </c>
       <c r="BR5" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS5" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BT5" t="n">
-        <v>43.75</v>
+        <v>41.18</v>
       </c>
       <c r="BU5" t="n">
-        <v>31.25</v>
+        <v>29.41</v>
       </c>
       <c r="BV5" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BW5" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX5" t="n">
-        <v>50</v>
+        <v>47.06</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.71</v>
+        <v>3.76</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.78</v>
+        <v>3.85</v>
       </c>
       <c r="CC5" t="n">
         <v>2.71</v>
@@ -2831,13 +2831,13 @@
         <v>2.88</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.99</v>
+        <v>3.01</v>
       </c>
       <c r="CH5" t="n">
         <v>1.45</v>
@@ -2846,28 +2846,28 @@
         <v>1.96</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="CO5" t="n">
         <v>1.28</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.27</v>
+        <v>3.23</v>
       </c>
       <c r="CR5" t="n">
         <v>1.43</v>
@@ -2882,7 +2882,7 @@
         <v>1.39</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CW5" t="n">
         <v>1.84</v>
@@ -2909,22 +2909,22 @@
         <v>3.32</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="DG5" t="n">
         <v>-1</v>
       </c>
       <c r="DH5" t="n">
-        <v>102.56</v>
+        <v>96.53</v>
       </c>
       <c r="DI5" t="n">
         <v>0</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="DK5" t="n">
         <v>5</v>
@@ -2933,52 +2933,52 @@
         <v>-1</v>
       </c>
       <c r="DM5" t="n">
-        <v>50</v>
+        <v>47.06</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="DO5" t="n">
         <v>-1</v>
       </c>
       <c r="DP5" t="n">
-        <v>12</v>
+        <v>11.94</v>
       </c>
       <c r="DQ5" t="n">
-        <v>15.88</v>
+        <v>15.53</v>
       </c>
       <c r="DR5" t="n">
-        <v>9.32</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.32</v>
+        <v>0.29</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.32</v>
+        <v>0.29</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>55.62</v>
+        <v>56</v>
       </c>
       <c r="DW5" t="n">
         <v>0.12</v>
       </c>
       <c r="DX5" t="n">
-        <v>13.75</v>
+        <v>13.71</v>
       </c>
       <c r="DY5" t="n">
-        <v>9</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="DZ5" t="n">
-        <v>4.75</v>
+        <v>4.82</v>
       </c>
       <c r="EA5" t="n">
-        <v>21.44</v>
+        <v>21.06</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="EC5" t="n">
         <v>2</v>
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
         <v>9</v>
       </c>
       <c r="D12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -5502,109 +5502,109 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AH12" t="n">
         <v>-1</v>
       </c>
       <c r="AI12" t="n">
-        <v>76.29000000000001</v>
+        <v>75.88</v>
       </c>
       <c r="AJ12" t="n">
         <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AL12" t="n">
-        <v>4.57</v>
+        <v>4.38</v>
       </c>
       <c r="AM12" t="n">
         <v>-1</v>
       </c>
       <c r="AN12" t="n">
-        <v>30.57</v>
+        <v>31.12</v>
       </c>
       <c r="AO12" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AP12" t="n">
         <v>-1</v>
       </c>
       <c r="AQ12" t="n">
-        <v>17.57</v>
+        <v>16.88</v>
       </c>
       <c r="AR12" t="n">
-        <v>14</v>
+        <v>14.12</v>
       </c>
       <c r="AS12" t="n">
-        <v>10.14</v>
+        <v>10</v>
       </c>
       <c r="AT12" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.14</v>
+        <v>0.38</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AX12" t="n">
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>38</v>
+        <v>38.75</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BA12" t="n">
-        <v>9.289999999999999</v>
+        <v>10.12</v>
       </c>
       <c r="BB12" t="n">
-        <v>6.29</v>
+        <v>6.88</v>
       </c>
       <c r="BC12" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="BD12" t="n">
-        <v>19.14</v>
+        <v>19.25</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.69</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.25</v>
+        <v>0.35</v>
       </c>
       <c r="BL12" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.75</v>
+        <v>0.82</v>
       </c>
       <c r="BP12" t="n">
         <v>-1</v>
@@ -5613,25 +5613,25 @@
         <v>-1</v>
       </c>
       <c r="BR12" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BS12" t="n">
-        <v>75</v>
+        <v>76.47</v>
       </c>
       <c r="BT12" t="n">
-        <v>43.75</v>
+        <v>47.06</v>
       </c>
       <c r="BU12" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BV12" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>25</v>
+        <v>29.41</v>
       </c>
       <c r="BY12" t="n">
         <v>4.28</v>
@@ -5640,43 +5640,43 @@
         <v>4.56</v>
       </c>
       <c r="CA12" t="n">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="CB12" t="n">
         <v>4.39</v>
       </c>
       <c r="CC12" t="n">
-        <v>7.85</v>
+        <v>7.33</v>
       </c>
       <c r="CD12" t="n">
         <v>8.51</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="CH12" t="n">
         <v>1.37</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CJ12" t="n">
         <v>1.76</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="CN12" t="n">
         <v>1.8</v>
@@ -5685,7 +5685,7 @@
         <v>1.19</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CQ12" t="n">
         <v>2.99</v>
@@ -5733,76 +5733,76 @@
         <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="DG12" t="n">
         <v>-1</v>
       </c>
       <c r="DH12" t="n">
-        <v>84.25</v>
+        <v>83.59</v>
       </c>
       <c r="DI12" t="n">
         <v>0</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.81</v>
+        <v>2.77</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.25</v>
+        <v>4.18</v>
       </c>
       <c r="DL12" t="n">
         <v>-1</v>
       </c>
       <c r="DM12" t="n">
-        <v>39</v>
+        <v>38.76</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="DO12" t="n">
         <v>-1</v>
       </c>
       <c r="DP12" t="n">
-        <v>17.37</v>
+        <v>17.06</v>
       </c>
       <c r="DQ12" t="n">
-        <v>14.19</v>
+        <v>14.23</v>
       </c>
       <c r="DR12" t="n">
-        <v>8.5</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="DS12" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DT12" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>43.38</v>
+        <v>43.41</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX12" t="n">
-        <v>10.94</v>
+        <v>11.23</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.07</v>
+        <v>7.3</v>
       </c>
       <c r="DZ12" t="n">
-        <v>3.88</v>
+        <v>3.94</v>
       </c>
       <c r="EA12" t="n">
-        <v>17.69</v>
+        <v>17.83</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.63</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="13">
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
         <v>9</v>
       </c>
       <c r="D13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E13" t="n">
         <v>0.22</v>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AH13" t="n">
         <v>-1</v>
       </c>
       <c r="AI13" t="n">
-        <v>92.56999999999999</v>
+        <v>81</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
@@ -5920,94 +5920,94 @@
         <v>2</v>
       </c>
       <c r="AL13" t="n">
-        <v>5</v>
+        <v>5.62</v>
       </c>
       <c r="AM13" t="n">
         <v>-1</v>
       </c>
       <c r="AN13" t="n">
-        <v>42.14</v>
+        <v>36.88</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="AP13" t="n">
         <v>-1</v>
       </c>
       <c r="AQ13" t="n">
-        <v>13</v>
+        <v>12.62</v>
       </c>
       <c r="AR13" t="n">
-        <v>16.29</v>
+        <v>15.62</v>
       </c>
       <c r="AS13" t="n">
-        <v>9.43</v>
+        <v>9</v>
       </c>
       <c r="AT13" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AX13" t="n">
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>49</v>
+        <v>47.62</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BA13" t="n">
-        <v>10</v>
+        <v>10.88</v>
       </c>
       <c r="BB13" t="n">
-        <v>6</v>
+        <v>6.62</v>
       </c>
       <c r="BC13" t="n">
-        <v>4</v>
+        <v>4.25</v>
       </c>
       <c r="BD13" t="n">
-        <v>24</v>
+        <v>22.88</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.23</v>
+        <v>1.07</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.75</v>
+        <v>10.06</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="BP13" t="n">
         <v>-1</v>
@@ -6016,25 +6016,25 @@
         <v>-1</v>
       </c>
       <c r="BR13" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BS13" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BT13" t="n">
-        <v>50</v>
+        <v>47.06</v>
       </c>
       <c r="BU13" t="n">
-        <v>43.75</v>
+        <v>41.18</v>
       </c>
       <c r="BV13" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BW13" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX13" t="n">
-        <v>62.5</v>
+        <v>58.82</v>
       </c>
       <c r="BY13" t="n">
         <v>3.67</v>
@@ -6043,22 +6043,22 @@
         <v>4.33</v>
       </c>
       <c r="CA13" t="n">
-        <v>4.11</v>
+        <v>4.14</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.37</v>
+        <v>4.4</v>
       </c>
       <c r="CC13" t="n">
         <v>6.6</v>
       </c>
       <c r="CD13" t="n">
-        <v>6.88</v>
+        <v>6.96</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="CG13" t="n">
         <v>3.23</v>
@@ -6067,19 +6067,19 @@
         <v>1.52</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CK13" t="n">
         <v>1.38</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="CN13" t="n">
         <v>2.12</v>
@@ -6091,7 +6091,7 @@
         <v>1.79</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="CR13" t="n">
         <v>1.4</v>
@@ -6106,10 +6106,10 @@
         <v>1.56</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CW13" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CX13" t="n">
         <v>1.54</v>
@@ -6136,76 +6136,76 @@
         <v>0.12</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="DG13" t="n">
         <v>-1</v>
       </c>
       <c r="DH13" t="n">
-        <v>87.63</v>
+        <v>82.47</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.06</v>
+        <v>5.35</v>
       </c>
       <c r="DL13" t="n">
         <v>-1</v>
       </c>
       <c r="DM13" t="n">
-        <v>43.19</v>
+        <v>40.65</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="DO13" t="n">
         <v>-1</v>
       </c>
       <c r="DP13" t="n">
-        <v>14.94</v>
+        <v>14.64</v>
       </c>
       <c r="DQ13" t="n">
-        <v>16.25</v>
+        <v>15.94</v>
       </c>
       <c r="DR13" t="n">
-        <v>8.56</v>
+        <v>8.41</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>49.5</v>
+        <v>48.82</v>
       </c>
       <c r="DW13" t="n">
         <v>0.06</v>
       </c>
       <c r="DX13" t="n">
-        <v>10.81</v>
+        <v>11.18</v>
       </c>
       <c r="DY13" t="n">
-        <v>7.19</v>
+        <v>7.41</v>
       </c>
       <c r="DZ13" t="n">
-        <v>3.62</v>
+        <v>3.76</v>
       </c>
       <c r="EA13" t="n">
-        <v>22.81</v>
+        <v>22.36</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="14">

--- a/data/teams/leagues/Averages_Russian_Premier_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Russian_Premier_League_2025-2026.xlsx
@@ -1379,94 +1379,94 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
         <v>9</v>
       </c>
       <c r="E2" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="F2" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="G2" t="n">
         <v>-1</v>
       </c>
       <c r="H2" t="n">
-        <v>92.70999999999999</v>
+        <v>92</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="J2" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="K2" t="n">
-        <v>5.43</v>
+        <v>5.62</v>
       </c>
       <c r="L2" t="n">
         <v>-1</v>
       </c>
       <c r="M2" t="n">
-        <v>49.43</v>
+        <v>48.12</v>
       </c>
       <c r="N2" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="O2" t="n">
         <v>-1</v>
       </c>
       <c r="P2" t="n">
-        <v>9.710000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>17</v>
+        <v>16.38</v>
       </c>
       <c r="R2" t="n">
-        <v>5.14</v>
+        <v>5.25</v>
       </c>
       <c r="S2" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="T2" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="U2" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="V2" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>46.57</v>
+        <v>46.12</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>14.86</v>
+        <v>15.25</v>
       </c>
       <c r="AA2" t="n">
-        <v>10</v>
+        <v>10.25</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.86</v>
+        <v>5</v>
       </c>
       <c r="AC2" t="n">
-        <v>22.14</v>
+        <v>22.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -1550,31 +1550,31 @@
         <v>1.67</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="BH2" t="n">
-        <v>8.25</v>
+        <v>8.65</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.88</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="BP2" t="n">
         <v>-1</v>
@@ -1586,31 +1586,31 @@
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>81.25</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BT2" t="n">
-        <v>50</v>
+        <v>52.94</v>
       </c>
       <c r="BU2" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BV2" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW2" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX2" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.68</v>
+        <v>2.71</v>
       </c>
       <c r="BZ2" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.5</v>
+        <v>3.49</v>
       </c>
       <c r="CB2" t="n">
         <v>3.57</v>
@@ -1622,22 +1622,22 @@
         <v>3.46</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="CH2" t="n">
         <v>1.4</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="CK2" t="n">
         <v>1.48</v>
@@ -1646,7 +1646,7 @@
         <v>1.88</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="CN2" t="n">
         <v>1.94</v>
@@ -1655,10 +1655,10 @@
         <v>1.33</v>
       </c>
       <c r="CP2" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.52</v>
+        <v>3.49</v>
       </c>
       <c r="CR2" t="n">
         <v>1.39</v>
@@ -1673,106 +1673,106 @@
         <v>1.42</v>
       </c>
       <c r="CV2" t="n">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CY2" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="DB2" t="n">
         <v>1.34</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.68</v>
+        <v>3.62</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="DG2" t="n">
         <v>-1</v>
       </c>
       <c r="DH2" t="n">
-        <v>93</v>
+        <v>92.65000000000001</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="DK2" t="n">
-        <v>4.56</v>
+        <v>4.7</v>
       </c>
       <c r="DL2" t="n">
         <v>-1</v>
       </c>
       <c r="DM2" t="n">
-        <v>45.37</v>
+        <v>45</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="DO2" t="n">
         <v>-1</v>
       </c>
       <c r="DP2" t="n">
-        <v>12.18</v>
+        <v>11.94</v>
       </c>
       <c r="DQ2" t="n">
-        <v>17.06</v>
+        <v>16.77</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.43</v>
+        <v>6.41</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.12</v>
+        <v>0.18</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.12</v>
+        <v>0.18</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>46.56</v>
+        <v>46.35</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="DX2" t="n">
-        <v>12.56</v>
+        <v>12.88</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.75</v>
+        <v>8.94</v>
       </c>
       <c r="DZ2" t="n">
-        <v>3.81</v>
+        <v>3.94</v>
       </c>
       <c r="EA2" t="n">
-        <v>21.81</v>
+        <v>22</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.69</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="3">
@@ -1830,7 +1830,7 @@
         <v>15.56</v>
       </c>
       <c r="R3" t="n">
-        <v>7.11</v>
+        <v>7</v>
       </c>
       <c r="S3" t="n">
         <v>1.56</v>
@@ -1863,7 +1863,7 @@
         <v>4.56</v>
       </c>
       <c r="AC3" t="n">
-        <v>18.67</v>
+        <v>19</v>
       </c>
       <c r="AD3" t="n">
         <v>1.38</v>
@@ -2010,13 +2010,13 @@
         <v>3.38</v>
       </c>
       <c r="BZ3" t="n">
-        <v>3.82</v>
+        <v>3.61</v>
       </c>
       <c r="CA3" t="n">
         <v>3.84</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.16</v>
+        <v>4.13</v>
       </c>
       <c r="CC3" t="n">
         <v>4.83</v>
@@ -2082,25 +2082,25 @@
         <v>1.74</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.48</v>
+        <v>2.43</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="DB3" t="n">
         <v>1.24</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="DD3" t="n">
-        <v>2.88</v>
+        <v>2.91</v>
       </c>
       <c r="DE3" t="n">
         <v>0.06</v>
@@ -2142,7 +2142,7 @@
         <v>14.41</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.53</v>
+        <v>7.47</v>
       </c>
       <c r="DS3" t="n">
         <v>0.18</v>
@@ -2169,7 +2169,7 @@
         <v>3.83</v>
       </c>
       <c r="EA3" t="n">
-        <v>18.53</v>
+        <v>18.71</v>
       </c>
       <c r="EB3" t="n">
         <v>1.3</v>
@@ -2185,94 +2185,94 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
         <v>9</v>
       </c>
       <c r="E4" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="F4" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="G4" t="n">
         <v>-1</v>
       </c>
       <c r="H4" t="n">
-        <v>85.56999999999999</v>
+        <v>83.25</v>
       </c>
       <c r="I4" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="J4" t="n">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="K4" t="n">
-        <v>3.57</v>
+        <v>3.5</v>
       </c>
       <c r="L4" t="n">
         <v>-1</v>
       </c>
       <c r="M4" t="n">
-        <v>44.14</v>
+        <v>42.88</v>
       </c>
       <c r="N4" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="O4" t="n">
         <v>-1</v>
       </c>
       <c r="P4" t="n">
-        <v>21.29</v>
+        <v>20.12</v>
       </c>
       <c r="Q4" t="n">
-        <v>12.57</v>
+        <v>12.88</v>
       </c>
       <c r="R4" t="n">
-        <v>6.57</v>
+        <v>7.88</v>
       </c>
       <c r="S4" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="T4" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="U4" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="V4" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>43.43</v>
+        <v>41.25</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="Z4" t="n">
-        <v>12.43</v>
+        <v>12</v>
       </c>
       <c r="AA4" t="n">
-        <v>8.57</v>
+        <v>8.25</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.86</v>
+        <v>3.75</v>
       </c>
       <c r="AC4" t="n">
-        <v>23</v>
+        <v>22.75</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AE4" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AF4" t="n">
         <v>0.22</v>
@@ -2356,31 +2356,31 @@
         <v>3.33</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="BH4" t="n">
-        <v>7.94</v>
+        <v>8.41</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BN4" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="BP4" t="n">
         <v>-1</v>
@@ -2389,37 +2389,37 @@
         <v>-1</v>
       </c>
       <c r="BR4" t="n">
-        <v>75</v>
+        <v>76.47</v>
       </c>
       <c r="BS4" t="n">
-        <v>68.75</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BT4" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BU4" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BV4" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>31.25</v>
+        <v>29.41</v>
       </c>
       <c r="BY4" t="n">
-        <v>2.49</v>
+        <v>2.58</v>
       </c>
       <c r="BZ4" t="n">
-        <v>2.68</v>
+        <v>2.79</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.44</v>
+        <v>3.42</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.48</v>
+        <v>3.45</v>
       </c>
       <c r="CC4" t="n">
         <v>3.37</v>
@@ -2428,61 +2428,61 @@
         <v>3.67</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.96</v>
+        <v>2.99</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="CH4" t="n">
         <v>1.26</v>
       </c>
       <c r="CI4" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.88</v>
+        <v>3.92</v>
       </c>
       <c r="CR4" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="CS4" t="n">
         <v>3.06</v>
       </c>
       <c r="CT4" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="CU4" t="n">
         <v>1.39</v>
       </c>
       <c r="CV4" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CW4" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CX4" t="n">
         <v>1.63</v>
@@ -2497,88 +2497,88 @@
         <v>1.86</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="DD4" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="DG4" t="n">
         <v>-1</v>
       </c>
       <c r="DH4" t="n">
-        <v>89.56</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="DI4" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="DJ4" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="DK4" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="DL4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="DM4" t="n">
+        <v>43</v>
+      </c>
+      <c r="DN4" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="DO4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="DP4" t="n">
+        <v>20.17</v>
+      </c>
+      <c r="DQ4" t="n">
+        <v>13.24</v>
+      </c>
+      <c r="DR4" t="n">
+        <v>7.65</v>
+      </c>
+      <c r="DS4" t="n">
         <v>0.18</v>
       </c>
-      <c r="DJ4" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="DK4" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="DL4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="DM4" t="n">
-        <v>43.56</v>
-      </c>
-      <c r="DN4" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="DO4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="DP4" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="DQ4" t="n">
-        <v>13.13</v>
-      </c>
-      <c r="DR4" t="n">
-        <v>7.06</v>
-      </c>
-      <c r="DS4" t="n">
-        <v>0.19</v>
-      </c>
       <c r="DT4" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>46.12</v>
+        <v>44.94</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DX4" t="n">
-        <v>12.5</v>
+        <v>12.3</v>
       </c>
       <c r="DY4" t="n">
-        <v>8.31</v>
+        <v>8.18</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.19</v>
+        <v>4.12</v>
       </c>
       <c r="EA4" t="n">
-        <v>22</v>
+        <v>21.94</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="EC4" t="n">
-        <v>3.19</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="5">
@@ -2606,7 +2606,7 @@
         <v>-1</v>
       </c>
       <c r="H5" t="n">
-        <v>94.33</v>
+        <v>105.33</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -2621,7 +2621,7 @@
         <v>-1</v>
       </c>
       <c r="M5" t="n">
-        <v>48</v>
+        <v>53.44</v>
       </c>
       <c r="N5" t="n">
         <v>0.67</v>
@@ -2633,7 +2633,7 @@
         <v>11.33</v>
       </c>
       <c r="Q5" t="n">
-        <v>17.56</v>
+        <v>17.67</v>
       </c>
       <c r="R5" t="n">
         <v>8.33</v>
@@ -2672,7 +2672,7 @@
         <v>20.78</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.51</v>
+        <v>1.69</v>
       </c>
       <c r="AE5" t="n">
         <v>1.89</v>
@@ -2822,7 +2822,7 @@
         <v>3.76</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.85</v>
+        <v>3.86</v>
       </c>
       <c r="CC5" t="n">
         <v>2.71</v>
@@ -2882,10 +2882,10 @@
         <v>1.39</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CX5" t="n">
         <v>1.6</v>
@@ -2918,7 +2918,7 @@
         <v>-1</v>
       </c>
       <c r="DH5" t="n">
-        <v>96.53</v>
+        <v>102.35</v>
       </c>
       <c r="DI5" t="n">
         <v>0</v>
@@ -2933,7 +2933,7 @@
         <v>-1</v>
       </c>
       <c r="DM5" t="n">
-        <v>47.06</v>
+        <v>49.94</v>
       </c>
       <c r="DN5" t="n">
         <v>0.59</v>
@@ -2945,7 +2945,7 @@
         <v>11.94</v>
       </c>
       <c r="DQ5" t="n">
-        <v>15.53</v>
+        <v>15.59</v>
       </c>
       <c r="DR5" t="n">
         <v>9.289999999999999</v>
@@ -2978,7 +2978,7 @@
         <v>21.06</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="EC5" t="n">
         <v>2</v>
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" t="n">
         <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -3081,31 +3081,31 @@
         <v>1.56</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AH6" t="n">
         <v>-1</v>
       </c>
       <c r="AI6" t="n">
-        <v>94.43000000000001</v>
+        <v>93.25</v>
       </c>
       <c r="AJ6" t="n">
         <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="AL6" t="n">
-        <v>4.57</v>
+        <v>5</v>
       </c>
       <c r="AM6" t="n">
         <v>-1</v>
       </c>
       <c r="AN6" t="n">
-        <v>48.71</v>
+        <v>48.25</v>
       </c>
       <c r="AO6" t="n">
         <v>1</v>
@@ -3114,79 +3114,79 @@
         <v>-1</v>
       </c>
       <c r="AQ6" t="n">
-        <v>14.57</v>
+        <v>14.38</v>
       </c>
       <c r="AR6" t="n">
-        <v>15.43</v>
+        <v>14.75</v>
       </c>
       <c r="AS6" t="n">
-        <v>6.57</v>
+        <v>6.5</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AX6" t="n">
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>52.71</v>
+        <v>53.25</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>13.43</v>
+        <v>14.5</v>
       </c>
       <c r="BB6" t="n">
-        <v>10.29</v>
+        <v>11.25</v>
       </c>
       <c r="BC6" t="n">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="BD6" t="n">
-        <v>21.29</v>
+        <v>21.12</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="BG6" t="n">
         <v>3</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.19</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="BI6" t="n">
         <v>3</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="BL6" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="BP6" t="n">
         <v>-1</v>
@@ -3195,25 +3195,25 @@
         <v>-1</v>
       </c>
       <c r="BR6" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS6" t="n">
-        <v>75</v>
+        <v>76.47</v>
       </c>
       <c r="BT6" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BU6" t="n">
-        <v>37.5</v>
+        <v>35.29</v>
       </c>
       <c r="BV6" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BW6" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX6" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BY6" t="n">
         <v>1.87</v>
@@ -3222,16 +3222,16 @@
         <v>1.89</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.85</v>
+        <v>3.82</v>
       </c>
       <c r="CB6" t="n">
-        <v>4.05</v>
+        <v>4.02</v>
       </c>
       <c r="CC6" t="n">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="CD6" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="CE6" t="n">
         <v>1.33</v>
@@ -3240,7 +3240,7 @@
         <v>2.58</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="CH6" t="n">
         <v>1.5</v>
@@ -3255,7 +3255,7 @@
         <v>1.45</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CM6" t="n">
         <v>2.57</v>
@@ -3270,7 +3270,7 @@
         <v>1.79</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="CR6" t="n">
         <v>1.35</v>
@@ -3285,10 +3285,10 @@
         <v>1.52</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CX6" t="n">
         <v>1.54</v>
@@ -3297,19 +3297,19 @@
         <v>1.9</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="DA6" t="n">
         <v>1.91</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="DE6" t="n">
         <v>0.06</v>
@@ -3321,22 +3321,22 @@
         <v>-1</v>
       </c>
       <c r="DH6" t="n">
-        <v>98.69</v>
+        <v>97.88</v>
       </c>
       <c r="DI6" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ6" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="DK6" t="n">
-        <v>5.19</v>
+        <v>5.35</v>
       </c>
       <c r="DL6" t="n">
         <v>-1</v>
       </c>
       <c r="DM6" t="n">
-        <v>51.69</v>
+        <v>51.29</v>
       </c>
       <c r="DN6" t="n">
         <v>0.9399999999999999</v>
@@ -3345,46 +3345,46 @@
         <v>-1</v>
       </c>
       <c r="DP6" t="n">
-        <v>13.37</v>
+        <v>13.35</v>
       </c>
       <c r="DQ6" t="n">
-        <v>16.75</v>
+        <v>16.35</v>
       </c>
       <c r="DR6" t="n">
-        <v>5.5</v>
+        <v>5.53</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>55.69</v>
+        <v>55.76</v>
       </c>
       <c r="DW6" t="n">
         <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>15.12</v>
+        <v>15.53</v>
       </c>
       <c r="DY6" t="n">
-        <v>10.5</v>
+        <v>10.94</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.62</v>
+        <v>4.59</v>
       </c>
       <c r="EA6" t="n">
-        <v>21.37</v>
+        <v>21.29</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="EC6" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="7">
@@ -3797,10 +3797,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D8" t="n">
         <v>8</v>
@@ -3809,82 +3809,82 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="G8" t="n">
         <v>-1</v>
       </c>
       <c r="H8" t="n">
-        <v>94.62</v>
+        <v>95.89</v>
       </c>
       <c r="I8" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="J8" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>5.25</v>
+        <v>5.89</v>
       </c>
       <c r="L8" t="n">
         <v>-1</v>
       </c>
       <c r="M8" t="n">
-        <v>50.5</v>
+        <v>52.89</v>
       </c>
       <c r="N8" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="O8" t="n">
         <v>-1</v>
       </c>
       <c r="P8" t="n">
-        <v>14.25</v>
+        <v>13.56</v>
       </c>
       <c r="Q8" t="n">
-        <v>16.25</v>
+        <v>16</v>
       </c>
       <c r="R8" t="n">
-        <v>6.88</v>
+        <v>6.56</v>
       </c>
       <c r="S8" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="T8" t="n">
-        <v>1.75</v>
+        <v>2.11</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>57.88</v>
+        <v>59.11</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="Z8" t="n">
-        <v>18</v>
+        <v>18.78</v>
       </c>
       <c r="AA8" t="n">
-        <v>13.12</v>
+        <v>13.56</v>
       </c>
       <c r="AB8" t="n">
-        <v>4.88</v>
+        <v>5.22</v>
       </c>
       <c r="AC8" t="n">
-        <v>21.25</v>
+        <v>21</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.84</v>
+        <v>1.93</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="AF8" t="n">
         <v>0.25</v>
@@ -3968,31 +3968,31 @@
         <v>1.62</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.44</v>
+        <v>2.59</v>
       </c>
       <c r="BH8" t="n">
-        <v>8.380000000000001</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.44</v>
+        <v>2.59</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.5</v>
+        <v>0.59</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.71</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="BP8" t="n">
         <v>-1</v>
@@ -4001,37 +4001,37 @@
         <v>-1</v>
       </c>
       <c r="BR8" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS8" t="n">
-        <v>75</v>
+        <v>76.47</v>
       </c>
       <c r="BT8" t="n">
-        <v>37.5</v>
+        <v>41.18</v>
       </c>
       <c r="BU8" t="n">
-        <v>12.5</v>
+        <v>17.65</v>
       </c>
       <c r="BV8" t="n">
-        <v>12.5</v>
+        <v>17.65</v>
       </c>
       <c r="BW8" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BX8" t="n">
-        <v>43.75</v>
+        <v>41.18</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="BZ8" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.78</v>
+        <v>3.88</v>
       </c>
       <c r="CB8" t="n">
-        <v>4.04</v>
+        <v>4.13</v>
       </c>
       <c r="CC8" t="n">
         <v>1.95</v>
@@ -4040,28 +4040,28 @@
         <v>1.98</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.73</v>
+        <v>2.71</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.07</v>
+        <v>3.1</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CI8" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CK8" t="n">
         <v>1.49</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CM8" t="n">
         <v>2.47</v>
@@ -4070,13 +4070,13 @@
         <v>1.9</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.11</v>
+        <v>3.08</v>
       </c>
       <c r="CR8" t="n">
         <v>1.42</v>
@@ -4091,10 +4091,10 @@
         <v>1.44</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CX8" t="n">
         <v>1.56</v>
@@ -4103,91 +4103,91 @@
         <v>1.93</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="DA8" t="n">
         <v>1.88</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="DD8" t="n">
-        <v>3.07</v>
+        <v>3.02</v>
       </c>
       <c r="DE8" t="n">
         <v>0.12</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="DG8" t="n">
         <v>-1</v>
       </c>
       <c r="DH8" t="n">
-        <v>92.18000000000001</v>
+        <v>93</v>
       </c>
       <c r="DI8" t="n">
         <v>0.12</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.75</v>
+        <v>5.12</v>
       </c>
       <c r="DL8" t="n">
         <v>-1</v>
       </c>
       <c r="DM8" t="n">
-        <v>44.88</v>
+        <v>46.47</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="DO8" t="n">
         <v>-1</v>
       </c>
       <c r="DP8" t="n">
-        <v>13.93</v>
+        <v>13.59</v>
       </c>
       <c r="DQ8" t="n">
-        <v>17.88</v>
+        <v>17.65</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.69</v>
+        <v>7.47</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>57.38</v>
+        <v>58.06</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DX8" t="n">
-        <v>15.5</v>
+        <v>16.06</v>
       </c>
       <c r="DY8" t="n">
-        <v>10.93</v>
+        <v>11.3</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.56</v>
+        <v>4.76</v>
       </c>
       <c r="EA8" t="n">
-        <v>21.68</v>
+        <v>21.53</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="EC8" t="n">
         <v>2.18</v>
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
         <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E9" t="n">
         <v>0.12</v>
@@ -4290,112 +4290,112 @@
         <v>1.88</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="AH9" t="n">
         <v>-1</v>
       </c>
       <c r="AI9" t="n">
-        <v>77.38</v>
+        <v>74.56</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="AL9" t="n">
-        <v>2.88</v>
+        <v>2.56</v>
       </c>
       <c r="AM9" t="n">
         <v>-1</v>
       </c>
       <c r="AN9" t="n">
-        <v>30.5</v>
+        <v>29.22</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AP9" t="n">
         <v>-1</v>
       </c>
       <c r="AQ9" t="n">
-        <v>15</v>
+        <v>14.89</v>
       </c>
       <c r="AR9" t="n">
-        <v>14.75</v>
+        <v>14.56</v>
       </c>
       <c r="AS9" t="n">
-        <v>7.88</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.75</v>
+        <v>2.11</v>
       </c>
       <c r="AU9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>46.44</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>7.89</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>5.44</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>18.78</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>3</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>9.24</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BO9" t="n">
         <v>1.12</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>48.38</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>8.25</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>5.62</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>9.119999999999999</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>1.06</v>
       </c>
       <c r="BP9" t="n">
         <v>-1</v>
@@ -4407,22 +4407,22 @@
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BT9" t="n">
-        <v>37.5</v>
+        <v>41.18</v>
       </c>
       <c r="BU9" t="n">
-        <v>31.25</v>
+        <v>35.29</v>
       </c>
       <c r="BV9" t="n">
-        <v>18.75</v>
+        <v>23.53</v>
       </c>
       <c r="BW9" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX9" t="n">
-        <v>56.25</v>
+        <v>52.94</v>
       </c>
       <c r="BY9" t="n">
         <v>3.54</v>
@@ -4431,31 +4431,31 @@
         <v>3.82</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.72</v>
+        <v>3.83</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.8</v>
+        <v>3.91</v>
       </c>
       <c r="CC9" t="n">
-        <v>4.88</v>
+        <v>5.27</v>
       </c>
       <c r="CD9" t="n">
-        <v>4.97</v>
+        <v>5.58</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.85</v>
+        <v>2.83</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.96</v>
+        <v>2.99</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CJ9" t="n">
         <v>1.87</v>
@@ -4467,19 +4467,19 @@
         <v>2.05</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.41</v>
+        <v>3.36</v>
       </c>
       <c r="CR9" t="n">
         <v>1.43</v>
@@ -4494,73 +4494,73 @@
         <v>1.41</v>
       </c>
       <c r="CV9" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="CY9" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.26</v>
+        <v>2.29</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.6</v>
+        <v>3.49</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="DG9" t="n">
         <v>-1</v>
       </c>
       <c r="DH9" t="n">
-        <v>79.88</v>
+        <v>78.23999999999999</v>
       </c>
       <c r="DI9" t="n">
         <v>0.12</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="DK9" t="n">
-        <v>3.25</v>
+        <v>3.06</v>
       </c>
       <c r="DL9" t="n">
         <v>-1</v>
       </c>
       <c r="DM9" t="n">
-        <v>34.81</v>
+        <v>33.88</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="DO9" t="n">
         <v>-1</v>
       </c>
       <c r="DP9" t="n">
-        <v>14.56</v>
+        <v>14.53</v>
       </c>
       <c r="DQ9" t="n">
-        <v>14.75</v>
+        <v>14.65</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.5</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="DS9" t="n">
         <v>0.06</v>
@@ -4572,28 +4572,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>47.25</v>
+        <v>46.29</v>
       </c>
       <c r="DW9" t="n">
         <v>0.06</v>
       </c>
       <c r="DX9" t="n">
-        <v>8.82</v>
+        <v>8.59</v>
       </c>
       <c r="DY9" t="n">
-        <v>6.12</v>
+        <v>6</v>
       </c>
       <c r="DZ9" t="n">
-        <v>2.68</v>
+        <v>2.59</v>
       </c>
       <c r="EA9" t="n">
-        <v>19.69</v>
+        <v>19.77</v>
       </c>
       <c r="EB9" t="n">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="10">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C10" t="n">
         <v>8</v>
       </c>
       <c r="D10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E10" t="n">
         <v>0.25</v>
@@ -4693,112 +4693,112 @@
         <v>2.38</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AH10" t="n">
         <v>-1</v>
       </c>
       <c r="AI10" t="n">
-        <v>92.62</v>
+        <v>93.11</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="AL10" t="n">
-        <v>4.5</v>
+        <v>4.44</v>
       </c>
       <c r="AM10" t="n">
         <v>-1</v>
       </c>
       <c r="AN10" t="n">
-        <v>47.5</v>
+        <v>46.44</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AP10" t="n">
         <v>-1</v>
       </c>
       <c r="AQ10" t="n">
-        <v>14.25</v>
+        <v>14.11</v>
       </c>
       <c r="AR10" t="n">
-        <v>15</v>
+        <v>15.11</v>
       </c>
       <c r="AS10" t="n">
-        <v>7.88</v>
+        <v>7.56</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>51.88</v>
+        <v>51.67</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA10" t="n">
-        <v>13</v>
+        <v>13.22</v>
       </c>
       <c r="BB10" t="n">
-        <v>8.619999999999999</v>
+        <v>8.67</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.38</v>
+        <v>4.56</v>
       </c>
       <c r="BD10" t="n">
-        <v>17</v>
+        <v>16.11</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.25</v>
+        <v>3.29</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.119999999999999</v>
+        <v>8.94</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.25</v>
+        <v>3.29</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.38</v>
+        <v>0.47</v>
       </c>
       <c r="BL10" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="BM10" t="n">
         <v>1</v>
       </c>
       <c r="BN10" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="BP10" t="n">
         <v>-1</v>
@@ -4810,22 +4810,22 @@
         <v>100</v>
       </c>
       <c r="BS10" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BT10" t="n">
-        <v>50</v>
+        <v>52.94</v>
       </c>
       <c r="BU10" t="n">
-        <v>31.25</v>
+        <v>35.29</v>
       </c>
       <c r="BV10" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BW10" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BX10" t="n">
-        <v>68.75</v>
+        <v>70.59</v>
       </c>
       <c r="BY10" t="n">
         <v>2.07</v>
@@ -4834,55 +4834,55 @@
         <v>2.27</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.67</v>
+        <v>3.64</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.8</v>
+        <v>3.78</v>
       </c>
       <c r="CC10" t="n">
         <v>2.89</v>
       </c>
       <c r="CD10" t="n">
-        <v>3.23</v>
+        <v>3.19</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="CM10" t="n">
         <v>2.19</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="CR10" t="n">
         <v>1.38</v>
@@ -4903,100 +4903,100 @@
         <v>1.68</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="CY10" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.53</v>
+        <v>2.48</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="DB10" t="n">
         <v>1.25</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.95</v>
+        <v>2.98</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.18</v>
+        <v>0.23</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="DG10" t="n">
         <v>-1</v>
       </c>
       <c r="DH10" t="n">
-        <v>93.12</v>
+        <v>93.34999999999999</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.56</v>
+        <v>2.47</v>
       </c>
       <c r="DK10" t="n">
-        <v>3.75</v>
+        <v>3.76</v>
       </c>
       <c r="DL10" t="n">
         <v>-1</v>
       </c>
       <c r="DM10" t="n">
-        <v>46.56</v>
+        <v>46.05</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.82</v>
+        <v>0.77</v>
       </c>
       <c r="DO10" t="n">
         <v>-1</v>
       </c>
       <c r="DP10" t="n">
-        <v>14.75</v>
+        <v>14.65</v>
       </c>
       <c r="DQ10" t="n">
-        <v>14.44</v>
+        <v>14.53</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.44</v>
+        <v>7.3</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.18</v>
+        <v>0.23</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.18</v>
+        <v>0.23</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>48.06</v>
+        <v>48.18</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX10" t="n">
-        <v>14.12</v>
+        <v>14.18</v>
       </c>
       <c r="DY10" t="n">
-        <v>8.869999999999999</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="DZ10" t="n">
-        <v>5.25</v>
+        <v>5.29</v>
       </c>
       <c r="EA10" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="EB10" t="n">
         <v>1.6</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.44</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="11">
@@ -5532,7 +5532,7 @@
         <v>-1</v>
       </c>
       <c r="AQ12" t="n">
-        <v>16.88</v>
+        <v>17</v>
       </c>
       <c r="AR12" t="n">
         <v>14.12</v>
@@ -5565,10 +5565,10 @@
         <v>10.12</v>
       </c>
       <c r="BB12" t="n">
-        <v>6.88</v>
+        <v>6.75</v>
       </c>
       <c r="BC12" t="n">
-        <v>3.25</v>
+        <v>3.38</v>
       </c>
       <c r="BD12" t="n">
         <v>19.25</v>
@@ -5643,13 +5643,13 @@
         <v>3.98</v>
       </c>
       <c r="CB12" t="n">
-        <v>4.39</v>
+        <v>4.35</v>
       </c>
       <c r="CC12" t="n">
         <v>7.33</v>
       </c>
       <c r="CD12" t="n">
-        <v>8.51</v>
+        <v>7.96</v>
       </c>
       <c r="CE12" t="n">
         <v>1.29</v>
@@ -5703,22 +5703,22 @@
         <v>1.44</v>
       </c>
       <c r="CV12" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="CW12" t="n">
         <v>1.93</v>
       </c>
-      <c r="CW12" t="n">
-        <v>1.94</v>
-      </c>
       <c r="CX12" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.44</v>
+        <v>2.39</v>
       </c>
       <c r="DA12" t="n">
-        <v>2.01</v>
+        <v>1.97</v>
       </c>
       <c r="DB12" t="n">
         <v>1.31</v>
@@ -5727,7 +5727,7 @@
         <v>1.98</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="DE12" t="n">
         <v>0</v>
@@ -5763,7 +5763,7 @@
         <v>-1</v>
       </c>
       <c r="DP12" t="n">
-        <v>17.06</v>
+        <v>17.12</v>
       </c>
       <c r="DQ12" t="n">
         <v>14.23</v>
@@ -5790,10 +5790,10 @@
         <v>11.23</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.3</v>
+        <v>7.24</v>
       </c>
       <c r="DZ12" t="n">
-        <v>3.94</v>
+        <v>4</v>
       </c>
       <c r="EA12" t="n">
         <v>17.83</v>
@@ -5911,7 +5911,7 @@
         <v>-1</v>
       </c>
       <c r="AI13" t="n">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
@@ -5926,7 +5926,7 @@
         <v>-1</v>
       </c>
       <c r="AN13" t="n">
-        <v>36.88</v>
+        <v>43.38</v>
       </c>
       <c r="AO13" t="n">
         <v>0.25</v>
@@ -5938,7 +5938,7 @@
         <v>12.62</v>
       </c>
       <c r="AR13" t="n">
-        <v>15.62</v>
+        <v>16.12</v>
       </c>
       <c r="AS13" t="n">
         <v>9</v>
@@ -5977,7 +5977,7 @@
         <v>22.88</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.07</v>
+        <v>1.31</v>
       </c>
       <c r="BF13" t="n">
         <v>1.88</v>
@@ -6046,13 +6046,13 @@
         <v>4.14</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.4</v>
+        <v>4.41</v>
       </c>
       <c r="CC13" t="n">
         <v>6.6</v>
       </c>
       <c r="CD13" t="n">
-        <v>6.96</v>
+        <v>6.98</v>
       </c>
       <c r="CE13" t="n">
         <v>1.33</v>
@@ -6106,10 +6106,10 @@
         <v>1.56</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CW13" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CX13" t="n">
         <v>1.54</v>
@@ -6142,7 +6142,7 @@
         <v>-1</v>
       </c>
       <c r="DH13" t="n">
-        <v>82.47</v>
+        <v>87.18000000000001</v>
       </c>
       <c r="DI13" t="n">
         <v>0.17</v>
@@ -6157,7 +6157,7 @@
         <v>-1</v>
       </c>
       <c r="DM13" t="n">
-        <v>40.65</v>
+        <v>43.71</v>
       </c>
       <c r="DN13" t="n">
         <v>0.82</v>
@@ -6169,7 +6169,7 @@
         <v>14.64</v>
       </c>
       <c r="DQ13" t="n">
-        <v>15.94</v>
+        <v>16.17</v>
       </c>
       <c r="DR13" t="n">
         <v>8.41</v>
@@ -6202,7 +6202,7 @@
         <v>22.36</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="EC13" t="n">
         <v>2.36</v>
@@ -6215,61 +6215,61 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D14" t="n">
         <v>9</v>
       </c>
       <c r="E14" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F14" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="G14" t="n">
         <v>-1</v>
       </c>
       <c r="H14" t="n">
-        <v>98.56999999999999</v>
+        <v>102.12</v>
       </c>
       <c r="I14" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="J14" t="n">
-        <v>2.86</v>
+        <v>2.75</v>
       </c>
       <c r="K14" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="L14" t="n">
         <v>-1</v>
       </c>
       <c r="M14" t="n">
-        <v>52.86</v>
+        <v>55.5</v>
       </c>
       <c r="N14" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="O14" t="n">
         <v>-1</v>
       </c>
       <c r="P14" t="n">
-        <v>13.71</v>
+        <v>14</v>
       </c>
       <c r="Q14" t="n">
-        <v>17.57</v>
+        <v>17.12</v>
       </c>
       <c r="R14" t="n">
-        <v>5.57</v>
+        <v>5.5</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="T14" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -6281,28 +6281,28 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>52.14</v>
+        <v>51.88</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="Z14" t="n">
-        <v>12.57</v>
+        <v>12.38</v>
       </c>
       <c r="AA14" t="n">
-        <v>8.710000000000001</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="AB14" t="n">
-        <v>3.86</v>
+        <v>3.75</v>
       </c>
       <c r="AC14" t="n">
-        <v>21.29</v>
+        <v>21.38</v>
       </c>
       <c r="AD14" t="n">
         <v>1.45</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -6386,31 +6386,31 @@
         <v>2.33</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.81</v>
+        <v>1.94</v>
       </c>
       <c r="BH14" t="n">
-        <v>7.5</v>
+        <v>7.41</v>
       </c>
       <c r="BI14" t="n">
-        <v>1.81</v>
+        <v>1.94</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.25</v>
+        <v>0.35</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.62</v>
+        <v>0.76</v>
       </c>
       <c r="BP14" t="n">
         <v>-1</v>
@@ -6419,37 +6419,37 @@
         <v>-1</v>
       </c>
       <c r="BR14" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BS14" t="n">
-        <v>43.75</v>
+        <v>47.06</v>
       </c>
       <c r="BT14" t="n">
-        <v>18.75</v>
+        <v>23.53</v>
       </c>
       <c r="BU14" t="n">
-        <v>12.5</v>
+        <v>17.65</v>
       </c>
       <c r="BV14" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BW14" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX14" t="n">
-        <v>37.5</v>
+        <v>41.18</v>
       </c>
       <c r="BY14" t="n">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="BZ14" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.66</v>
+        <v>3.63</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.73</v>
+        <v>3.71</v>
       </c>
       <c r="CC14" t="n">
         <v>4.18</v>
@@ -6461,28 +6461,28 @@
         <v>1.4</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="CG14" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CI14" t="n">
         <v>1.98</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CK14" t="n">
         <v>1.55</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="CN14" t="n">
         <v>1.81</v>
@@ -6494,7 +6494,7 @@
         <v>1.99</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.37</v>
+        <v>3.39</v>
       </c>
       <c r="CR14" t="n">
         <v>1.38</v>
@@ -6509,73 +6509,73 @@
         <v>1.47</v>
       </c>
       <c r="CV14" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CY14" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.29</v>
+        <v>2.26</v>
       </c>
       <c r="DA14" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="DB14" t="n">
         <v>1.34</v>
       </c>
       <c r="DC14" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.63</v>
+        <v>3.6</v>
       </c>
       <c r="DE14" t="n">
         <v>0.06</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="DG14" t="n">
         <v>-1</v>
       </c>
       <c r="DH14" t="n">
-        <v>94.5</v>
+        <v>96.41</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="DK14" t="n">
-        <v>3.94</v>
+        <v>3.82</v>
       </c>
       <c r="DL14" t="n">
         <v>-1</v>
       </c>
       <c r="DM14" t="n">
-        <v>49.88</v>
+        <v>51.3</v>
       </c>
       <c r="DN14" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DO14" t="n">
         <v>-1</v>
       </c>
       <c r="DP14" t="n">
-        <v>14.56</v>
+        <v>14.65</v>
       </c>
       <c r="DQ14" t="n">
-        <v>17.5</v>
+        <v>17.29</v>
       </c>
       <c r="DR14" t="n">
-        <v>6.19</v>
+        <v>6.12</v>
       </c>
       <c r="DS14" t="n">
         <v>0.06</v>
@@ -6587,28 +6587,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>49.87</v>
+        <v>49.88</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX14" t="n">
-        <v>12.19</v>
+        <v>12.12</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.25</v>
+        <v>8.23</v>
       </c>
       <c r="DZ14" t="n">
-        <v>3.94</v>
+        <v>3.88</v>
       </c>
       <c r="EA14" t="n">
-        <v>21.31</v>
+        <v>21.35</v>
       </c>
       <c r="EB14" t="n">
         <v>1.41</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="15">
@@ -6618,13 +6618,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C15" t="n">
         <v>9</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -6711,49 +6711,49 @@
         <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.43</v>
+        <v>1.75</v>
       </c>
       <c r="AH15" t="n">
         <v>-1</v>
       </c>
       <c r="AI15" t="n">
-        <v>83</v>
+        <v>80.88</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.43</v>
+        <v>2.88</v>
       </c>
       <c r="AL15" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AM15" t="n">
         <v>-1</v>
       </c>
       <c r="AN15" t="n">
-        <v>40.43</v>
+        <v>39.62</v>
       </c>
       <c r="AO15" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AP15" t="n">
         <v>-1</v>
       </c>
       <c r="AQ15" t="n">
-        <v>17.29</v>
+        <v>17.75</v>
       </c>
       <c r="AR15" t="n">
-        <v>13.57</v>
+        <v>13.12</v>
       </c>
       <c r="AS15" t="n">
-        <v>8.140000000000001</v>
+        <v>8</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AU15" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AV15" t="n">
         <v>0</v>
@@ -6765,55 +6765,55 @@
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>41.86</v>
+        <v>40.62</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>11.14</v>
+        <v>10.75</v>
       </c>
       <c r="BB15" t="n">
-        <v>8</v>
+        <v>7.75</v>
       </c>
       <c r="BC15" t="n">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="BD15" t="n">
-        <v>16.71</v>
+        <v>17.12</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="BF15" t="n">
-        <v>2.43</v>
+        <v>2.88</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.19</v>
+        <v>2.12</v>
       </c>
       <c r="BH15" t="n">
-        <v>8</v>
+        <v>7.76</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.19</v>
+        <v>2.12</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="BN15" t="n">
         <v>1.12</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="BP15" t="n">
         <v>-1</v>
@@ -6822,25 +6822,25 @@
         <v>-1</v>
       </c>
       <c r="BR15" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BS15" t="n">
-        <v>56.25</v>
+        <v>52.94</v>
       </c>
       <c r="BT15" t="n">
-        <v>37.5</v>
+        <v>35.29</v>
       </c>
       <c r="BU15" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BV15" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW15" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX15" t="n">
-        <v>31.25</v>
+        <v>29.41</v>
       </c>
       <c r="BY15" t="n">
         <v>2.76</v>
@@ -6849,16 +6849,16 @@
         <v>3</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.39</v>
+        <v>3.51</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.59</v>
+        <v>3.7</v>
       </c>
       <c r="CC15" t="n">
-        <v>3.49</v>
+        <v>4.55</v>
       </c>
       <c r="CD15" t="n">
-        <v>3.88</v>
+        <v>4.97</v>
       </c>
       <c r="CE15" t="n">
         <v>1.42</v>
@@ -6873,37 +6873,37 @@
         <v>1.39</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CM15" t="n">
         <v>2.42</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CO15" t="n">
         <v>1.33</v>
       </c>
       <c r="CP15" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.57</v>
+        <v>3.56</v>
       </c>
       <c r="CR15" t="n">
         <v>1.39</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="CT15" t="n">
         <v>3.05</v>
@@ -6912,10 +6912,10 @@
         <v>1.42</v>
       </c>
       <c r="CV15" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="CX15" t="n">
         <v>1.57</v>
@@ -6930,55 +6930,55 @@
         <v>1.86</v>
       </c>
       <c r="DB15" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.73</v>
+        <v>3.69</v>
       </c>
       <c r="DE15" t="n">
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="DG15" t="n">
         <v>-1</v>
       </c>
       <c r="DH15" t="n">
-        <v>85.56</v>
+        <v>84.42</v>
       </c>
       <c r="DI15" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.19</v>
+        <v>2.41</v>
       </c>
       <c r="DK15" t="n">
-        <v>4.69</v>
+        <v>4.47</v>
       </c>
       <c r="DL15" t="n">
         <v>-1</v>
       </c>
       <c r="DM15" t="n">
-        <v>39.81</v>
+        <v>39.47</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.68</v>
+        <v>0.76</v>
       </c>
       <c r="DO15" t="n">
         <v>-1</v>
       </c>
       <c r="DP15" t="n">
-        <v>16.25</v>
+        <v>16.53</v>
       </c>
       <c r="DQ15" t="n">
-        <v>14.13</v>
+        <v>13.88</v>
       </c>
       <c r="DR15" t="n">
-        <v>8.18</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="DS15" t="n">
         <v>0.12</v>
@@ -6990,28 +6990,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>41.31</v>
+        <v>40.76</v>
       </c>
       <c r="DW15" t="n">
         <v>0.06</v>
       </c>
       <c r="DX15" t="n">
-        <v>10.68</v>
+        <v>10.53</v>
       </c>
       <c r="DY15" t="n">
-        <v>7.5</v>
+        <v>7.41</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.18</v>
+        <v>3.12</v>
       </c>
       <c r="EA15" t="n">
-        <v>19.12</v>
+        <v>19.17</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.13</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="16">
@@ -7021,13 +7021,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C16" t="n">
         <v>9</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E16" t="n">
         <v>0.11</v>
@@ -7114,109 +7114,109 @@
         <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AH16" t="n">
         <v>-1</v>
       </c>
       <c r="AI16" t="n">
-        <v>91.29000000000001</v>
+        <v>92.62</v>
       </c>
       <c r="AJ16" t="n">
         <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="AL16" t="n">
-        <v>4.57</v>
+        <v>5.62</v>
       </c>
       <c r="AM16" t="n">
         <v>-1</v>
       </c>
       <c r="AN16" t="n">
-        <v>45.71</v>
+        <v>47.88</v>
       </c>
       <c r="AO16" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AP16" t="n">
         <v>-1</v>
       </c>
       <c r="AQ16" t="n">
-        <v>17.29</v>
+        <v>16.88</v>
       </c>
       <c r="AR16" t="n">
-        <v>16.71</v>
+        <v>16</v>
       </c>
       <c r="AS16" t="n">
-        <v>6.43</v>
+        <v>5.88</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AX16" t="n">
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>61.86</v>
+        <v>63.38</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BA16" t="n">
-        <v>12.43</v>
+        <v>13.25</v>
       </c>
       <c r="BB16" t="n">
-        <v>8.43</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="BC16" t="n">
-        <v>4</v>
+        <v>4.12</v>
       </c>
       <c r="BD16" t="n">
-        <v>18.86</v>
+        <v>19.25</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="BF16" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.88</v>
+        <v>2.76</v>
       </c>
       <c r="BH16" t="n">
-        <v>8.69</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.88</v>
+        <v>2.76</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="BP16" t="n">
         <v>-1</v>
@@ -7228,22 +7228,22 @@
         <v>100</v>
       </c>
       <c r="BS16" t="n">
-        <v>81.25</v>
+        <v>76.47</v>
       </c>
       <c r="BT16" t="n">
-        <v>62.5</v>
+        <v>58.82</v>
       </c>
       <c r="BU16" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BV16" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BW16" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX16" t="n">
-        <v>62.5</v>
+        <v>58.82</v>
       </c>
       <c r="BY16" t="n">
         <v>1.63</v>
@@ -7252,73 +7252,73 @@
         <v>1.66</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.96</v>
+        <v>3.91</v>
       </c>
       <c r="CB16" t="n">
-        <v>4.28</v>
+        <v>4.21</v>
       </c>
       <c r="CC16" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="CD16" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.67</v>
+        <v>2.72</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.1</v>
+        <v>3.06</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CI16" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="CN16" t="n">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.99</v>
+        <v>3.08</v>
       </c>
       <c r="CR16" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="CS16" t="n">
         <v>2.84</v>
       </c>
       <c r="CT16" t="n">
-        <v>3.06</v>
+        <v>2.99</v>
       </c>
       <c r="CU16" t="n">
         <v>1.45</v>
       </c>
       <c r="CV16" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="CX16" t="n">
         <v>1.54</v>
@@ -7333,85 +7333,85 @@
         <v>1.97</v>
       </c>
       <c r="DB16" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="DD16" t="n">
-        <v>3.25</v>
+        <v>3.42</v>
       </c>
       <c r="DE16" t="n">
         <v>0.06</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="DG16" t="n">
         <v>-1</v>
       </c>
       <c r="DH16" t="n">
-        <v>97</v>
+        <v>97.29000000000001</v>
       </c>
       <c r="DI16" t="n">
         <v>0</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="DK16" t="n">
-        <v>4.94</v>
+        <v>5.41</v>
       </c>
       <c r="DL16" t="n">
         <v>-1</v>
       </c>
       <c r="DM16" t="n">
-        <v>48.44</v>
+        <v>49.3</v>
       </c>
       <c r="DN16" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="DO16" t="n">
         <v>-1</v>
       </c>
       <c r="DP16" t="n">
-        <v>16.13</v>
+        <v>16</v>
       </c>
       <c r="DQ16" t="n">
-        <v>16</v>
+        <v>15.7</v>
       </c>
       <c r="DR16" t="n">
-        <v>6.56</v>
+        <v>6.3</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>60.94</v>
+        <v>61.71</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DX16" t="n">
-        <v>12.81</v>
+        <v>13.18</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.81</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="DZ16" t="n">
-        <v>4</v>
+        <v>4.06</v>
       </c>
       <c r="EA16" t="n">
-        <v>21.06</v>
+        <v>21.12</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="EC16" t="n">
         <v>2.06</v>
@@ -7424,94 +7424,94 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D17" t="n">
         <v>9</v>
       </c>
       <c r="E17" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F17" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="G17" t="n">
         <v>-1</v>
       </c>
       <c r="H17" t="n">
-        <v>89.56999999999999</v>
+        <v>92.38</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="K17" t="n">
-        <v>6.57</v>
+        <v>6.12</v>
       </c>
       <c r="L17" t="n">
         <v>-1</v>
       </c>
       <c r="M17" t="n">
-        <v>49.43</v>
+        <v>50.25</v>
       </c>
       <c r="N17" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="O17" t="n">
         <v>-1</v>
       </c>
       <c r="P17" t="n">
-        <v>10</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="Q17" t="n">
-        <v>18.29</v>
+        <v>18.88</v>
       </c>
       <c r="R17" t="n">
-        <v>4.57</v>
+        <v>4.62</v>
       </c>
       <c r="S17" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="T17" t="n">
-        <v>2.57</v>
+        <v>2.38</v>
       </c>
       <c r="U17" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="V17" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>59.86</v>
+        <v>60.88</v>
       </c>
       <c r="Y17" t="n">
         <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>15.29</v>
+        <v>14.38</v>
       </c>
       <c r="AA17" t="n">
-        <v>7.86</v>
+        <v>7.75</v>
       </c>
       <c r="AB17" t="n">
-        <v>7.43</v>
+        <v>6.62</v>
       </c>
       <c r="AC17" t="n">
-        <v>18.43</v>
+        <v>19.25</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.84</v>
+        <v>1.74</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -7595,31 +7595,31 @@
         <v>1.44</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.69</v>
+        <v>2.59</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.81</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.69</v>
+        <v>2.59</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BL17" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="BP17" t="n">
         <v>-1</v>
@@ -7628,37 +7628,37 @@
         <v>-1</v>
       </c>
       <c r="BR17" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS17" t="n">
-        <v>87.5</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BT17" t="n">
-        <v>43.75</v>
+        <v>41.18</v>
       </c>
       <c r="BU17" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BV17" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW17" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX17" t="n">
-        <v>50</v>
+        <v>47.06</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="BZ17" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="CA17" t="n">
-        <v>4.68</v>
+        <v>4.71</v>
       </c>
       <c r="CB17" t="n">
-        <v>4.99</v>
+        <v>5.03</v>
       </c>
       <c r="CC17" t="n">
         <v>1.76</v>
@@ -7670,22 +7670,22 @@
         <v>1.35</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="CG17" t="n">
-        <v>3.22</v>
+        <v>3.19</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="CJ17" t="n">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CL17" t="n">
         <v>1.91</v>
@@ -7700,28 +7700,28 @@
         <v>1.25</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CQ17" t="n">
-        <v>2.96</v>
+        <v>2.99</v>
       </c>
       <c r="CR17" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="CT17" t="n">
-        <v>2.91</v>
+        <v>2.94</v>
       </c>
       <c r="CU17" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CV17" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="CW17" t="n">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="CX17" t="n">
         <v>1.55</v>
@@ -7733,13 +7733,13 @@
         <v>2.42</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="DB17" t="n">
         <v>1.28</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="DD17" t="n">
         <v>3.15</v>
@@ -7754,70 +7754,70 @@
         <v>-1</v>
       </c>
       <c r="DH17" t="n">
-        <v>92.87</v>
+        <v>94</v>
       </c>
       <c r="DI17" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ17" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="DK17" t="n">
-        <v>6.13</v>
+        <v>5.94</v>
       </c>
       <c r="DL17" t="n">
         <v>-1</v>
       </c>
       <c r="DM17" t="n">
-        <v>51.31</v>
+        <v>51.59</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="DO17" t="n">
         <v>-1</v>
       </c>
       <c r="DP17" t="n">
-        <v>9.94</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="DQ17" t="n">
-        <v>20.69</v>
+        <v>20.83</v>
       </c>
       <c r="DR17" t="n">
-        <v>5.81</v>
+        <v>5.76</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>60.44</v>
+        <v>60.89</v>
       </c>
       <c r="DW17" t="n">
         <v>0.06</v>
       </c>
       <c r="DX17" t="n">
-        <v>12.56</v>
+        <v>12.29</v>
       </c>
       <c r="DY17" t="n">
         <v>6.88</v>
       </c>
       <c r="DZ17" t="n">
-        <v>5.69</v>
+        <v>5.41</v>
       </c>
       <c r="EA17" t="n">
-        <v>19.13</v>
+        <v>19.47</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Russian_Premier_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Russian_Premier_League_2025-2026.xlsx
@@ -1824,7 +1824,7 @@
         <v>-1</v>
       </c>
       <c r="P3" t="n">
-        <v>15.11</v>
+        <v>15.22</v>
       </c>
       <c r="Q3" t="n">
         <v>15.56</v>
@@ -2136,7 +2136,7 @@
         <v>-1</v>
       </c>
       <c r="DP3" t="n">
-        <v>15</v>
+        <v>15.06</v>
       </c>
       <c r="DQ3" t="n">
         <v>14.41</v>
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D7" t="n">
         <v>9</v>
@@ -3406,49 +3406,49 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="G7" t="n">
         <v>-1</v>
       </c>
       <c r="H7" t="n">
-        <v>76.86</v>
+        <v>78.38</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="J7" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="K7" t="n">
-        <v>3.86</v>
+        <v>4.12</v>
       </c>
       <c r="L7" t="n">
         <v>-1</v>
       </c>
       <c r="M7" t="n">
-        <v>37.29</v>
+        <v>37.25</v>
       </c>
       <c r="N7" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="O7" t="n">
         <v>-1</v>
       </c>
       <c r="P7" t="n">
-        <v>13.71</v>
+        <v>13.12</v>
       </c>
       <c r="Q7" t="n">
-        <v>14.71</v>
+        <v>15.25</v>
       </c>
       <c r="R7" t="n">
-        <v>7.86</v>
+        <v>7.88</v>
       </c>
       <c r="S7" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="T7" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -3460,28 +3460,28 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>45.43</v>
+        <v>46.5</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>8</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.86</v>
+        <v>6.12</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AC7" t="n">
-        <v>17.86</v>
+        <v>18.75</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.93</v>
+        <v>0.96</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -3565,31 +3565,31 @@
         <v>2.33</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.19</v>
+        <v>3</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.119999999999999</v>
+        <v>8.35</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.19</v>
+        <v>3</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="BL7" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BN7" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="BP7" t="n">
         <v>-1</v>
@@ -3598,37 +3598,37 @@
         <v>-1</v>
       </c>
       <c r="BR7" t="n">
-        <v>93.75</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BS7" t="n">
-        <v>87.5</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BT7" t="n">
-        <v>68.75</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BU7" t="n">
-        <v>37.5</v>
+        <v>35.29</v>
       </c>
       <c r="BV7" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BW7" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BX7" t="n">
-        <v>56.25</v>
+        <v>52.94</v>
       </c>
       <c r="BY7" t="n">
-        <v>4.24</v>
+        <v>4.09</v>
       </c>
       <c r="BZ7" t="n">
-        <v>4.18</v>
+        <v>4.09</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.71</v>
+        <v>3.67</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.92</v>
+        <v>3.86</v>
       </c>
       <c r="CC7" t="n">
         <v>4.89</v>
@@ -3637,61 +3637,61 @@
         <v>5.52</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.88</v>
+        <v>2.93</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.03</v>
+        <v>2.99</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="CJ7" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="CN7" t="n">
         <v>1.87</v>
       </c>
-      <c r="CK7" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="CL7" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="CM7" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="CN7" t="n">
-        <v>1.88</v>
-      </c>
       <c r="CO7" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.99</v>
+        <v>2.03</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.33</v>
+        <v>3.43</v>
       </c>
       <c r="CR7" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="CS7" t="n">
         <v>2.96</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.83</v>
+        <v>2.74</v>
       </c>
       <c r="CU7" t="n">
         <v>1.41</v>
       </c>
       <c r="CV7" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="CX7" t="n">
         <v>1.62</v>
@@ -3706,55 +3706,55 @@
         <v>1.8</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.58</v>
+        <v>3.79</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="DG7" t="n">
         <v>-1</v>
       </c>
       <c r="DH7" t="n">
-        <v>80.69</v>
+        <v>81.18000000000001</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.37</v>
+        <v>2.29</v>
       </c>
       <c r="DK7" t="n">
-        <v>3.13</v>
+        <v>3.29</v>
       </c>
       <c r="DL7" t="n">
         <v>-1</v>
       </c>
       <c r="DM7" t="n">
-        <v>35.25</v>
+        <v>35.35</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="DO7" t="n">
         <v>-1</v>
       </c>
       <c r="DP7" t="n">
-        <v>14.5</v>
+        <v>14.17</v>
       </c>
       <c r="DQ7" t="n">
-        <v>14.63</v>
+        <v>14.88</v>
       </c>
       <c r="DR7" t="n">
-        <v>8.56</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="DS7" t="n">
         <v>0</v>
@@ -3766,28 +3766,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>46.38</v>
+        <v>46.82</v>
       </c>
       <c r="DW7" t="n">
         <v>0.06</v>
       </c>
       <c r="DX7" t="n">
-        <v>8</v>
+        <v>8.18</v>
       </c>
       <c r="DY7" t="n">
-        <v>5.62</v>
+        <v>5.76</v>
       </c>
       <c r="DZ7" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="EA7" t="n">
-        <v>18.5</v>
+        <v>18.88</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.31</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="8">
@@ -3869,19 +3869,19 @@
         <v>0.33</v>
       </c>
       <c r="Z8" t="n">
-        <v>18.78</v>
+        <v>19</v>
       </c>
       <c r="AA8" t="n">
-        <v>13.56</v>
+        <v>13.67</v>
       </c>
       <c r="AB8" t="n">
-        <v>5.22</v>
+        <v>5.33</v>
       </c>
       <c r="AC8" t="n">
         <v>21</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AE8" t="n">
         <v>2.67</v>
@@ -4175,19 +4175,19 @@
         <v>0.23</v>
       </c>
       <c r="DX8" t="n">
-        <v>16.06</v>
+        <v>16.18</v>
       </c>
       <c r="DY8" t="n">
-        <v>11.3</v>
+        <v>11.35</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.76</v>
+        <v>4.82</v>
       </c>
       <c r="EA8" t="n">
         <v>21.53</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="EC8" t="n">
         <v>2.18</v>
@@ -4756,10 +4756,10 @@
         <v>0.11</v>
       </c>
       <c r="BA10" t="n">
-        <v>13.22</v>
+        <v>13.33</v>
       </c>
       <c r="BB10" t="n">
-        <v>8.67</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="BC10" t="n">
         <v>4.56</v>
@@ -4768,7 +4768,7 @@
         <v>16.11</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="BF10" t="n">
         <v>2.33</v>
@@ -4981,10 +4981,10 @@
         <v>0.11</v>
       </c>
       <c r="DX10" t="n">
-        <v>14.18</v>
+        <v>14.23</v>
       </c>
       <c r="DY10" t="n">
-        <v>8.880000000000001</v>
+        <v>8.94</v>
       </c>
       <c r="DZ10" t="n">
         <v>5.29</v>
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C11" t="n">
         <v>8</v>
       </c>
       <c r="D11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E11" t="n">
         <v>0.25</v>
@@ -5099,49 +5099,49 @@
         <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AH11" t="n">
         <v>-1</v>
       </c>
       <c r="AI11" t="n">
-        <v>109.88</v>
+        <v>110.22</v>
       </c>
       <c r="AJ11" t="n">
         <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.5</v>
+        <v>2.22</v>
       </c>
       <c r="AL11" t="n">
-        <v>3.62</v>
+        <v>3.89</v>
       </c>
       <c r="AM11" t="n">
         <v>-1</v>
       </c>
       <c r="AN11" t="n">
-        <v>49.38</v>
+        <v>48.56</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AP11" t="n">
         <v>-1</v>
       </c>
       <c r="AQ11" t="n">
-        <v>13.25</v>
+        <v>13.56</v>
       </c>
       <c r="AR11" t="n">
-        <v>19.75</v>
+        <v>18.67</v>
       </c>
       <c r="AS11" t="n">
-        <v>6.38</v>
+        <v>6.56</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AV11" t="n">
         <v>0</v>
@@ -5153,55 +5153,55 @@
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>48.62</v>
+        <v>48.33</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="BA11" t="n">
-        <v>9.880000000000001</v>
+        <v>10.11</v>
       </c>
       <c r="BB11" t="n">
-        <v>6.88</v>
+        <v>7.33</v>
       </c>
       <c r="BC11" t="n">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="BD11" t="n">
-        <v>23.25</v>
+        <v>23</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="BH11" t="n">
-        <v>7.88</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BK11" t="n">
         <v>0.06</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="BN11" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="BP11" t="n">
         <v>-1</v>
@@ -5210,16 +5210,16 @@
         <v>-1</v>
       </c>
       <c r="BR11" t="n">
-        <v>93.75</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BS11" t="n">
-        <v>62.5</v>
+        <v>58.82</v>
       </c>
       <c r="BT11" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BU11" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BV11" t="n">
         <v>0</v>
@@ -5228,7 +5228,7 @@
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BY11" t="n">
         <v>3.19</v>
@@ -5237,25 +5237,25 @@
         <v>3.34</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.51</v>
+        <v>3.48</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.59</v>
+        <v>3.55</v>
       </c>
       <c r="CC11" t="n">
-        <v>5.65</v>
+        <v>5.29</v>
       </c>
       <c r="CD11" t="n">
-        <v>6.01</v>
+        <v>5.62</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CF11" t="n">
-        <v>3.3</v>
+        <v>3.33</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="CH11" t="n">
         <v>1.33</v>
@@ -5267,34 +5267,34 @@
         <v>2.07</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CO11" t="n">
         <v>1.42</v>
       </c>
       <c r="CP11" t="n">
-        <v>2.26</v>
+        <v>2.29</v>
       </c>
       <c r="CQ11" t="n">
-        <v>4.12</v>
+        <v>4.18</v>
       </c>
       <c r="CR11" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="CS11" t="n">
         <v>3.15</v>
       </c>
       <c r="CT11" t="n">
-        <v>2.73</v>
+        <v>2.68</v>
       </c>
       <c r="CU11" t="n">
         <v>1.37</v>
@@ -5303,7 +5303,7 @@
         <v>1.76</v>
       </c>
       <c r="CW11" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CX11" t="n">
         <v>1.61</v>
@@ -5318,55 +5318,55 @@
         <v>1.85</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="DC11" t="n">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="DD11" t="n">
-        <v>4.24</v>
+        <v>4.4</v>
       </c>
       <c r="DE11" t="n">
         <v>0.12</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="DG11" t="n">
         <v>-1</v>
       </c>
       <c r="DH11" t="n">
-        <v>107.75</v>
+        <v>108.06</v>
       </c>
       <c r="DI11" t="n">
         <v>0</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.19</v>
+        <v>4.29</v>
       </c>
       <c r="DL11" t="n">
         <v>-1</v>
       </c>
       <c r="DM11" t="n">
-        <v>49.06</v>
+        <v>48.65</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="DO11" t="n">
         <v>-1</v>
       </c>
       <c r="DP11" t="n">
-        <v>13.62</v>
+        <v>13.77</v>
       </c>
       <c r="DQ11" t="n">
-        <v>19.31</v>
+        <v>18.77</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.13</v>
+        <v>7.18</v>
       </c>
       <c r="DS11" t="n">
         <v>0</v>
@@ -5378,28 +5378,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>47.81</v>
+        <v>47.7</v>
       </c>
       <c r="DW11" t="n">
         <v>0.12</v>
       </c>
       <c r="DX11" t="n">
-        <v>10.32</v>
+        <v>10.41</v>
       </c>
       <c r="DY11" t="n">
-        <v>7.38</v>
+        <v>7.59</v>
       </c>
       <c r="DZ11" t="n">
-        <v>2.94</v>
+        <v>2.83</v>
       </c>
       <c r="EA11" t="n">
-        <v>24.06</v>
+        <v>23.88</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">

--- a/data/teams/leagues/Averages_Russian_Premier_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Russian_Premier_League_2025-2026.xlsx
@@ -1379,94 +1379,94 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
         <v>9</v>
       </c>
       <c r="E2" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="F2" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="G2" t="n">
         <v>-1</v>
       </c>
       <c r="H2" t="n">
-        <v>92</v>
+        <v>81.78</v>
       </c>
       <c r="I2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="J2" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="K2" t="n">
-        <v>5.62</v>
+        <v>5</v>
       </c>
       <c r="L2" t="n">
         <v>-1</v>
       </c>
       <c r="M2" t="n">
-        <v>48.12</v>
+        <v>42.78</v>
       </c>
       <c r="N2" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="O2" t="n">
         <v>-1</v>
       </c>
       <c r="P2" t="n">
-        <v>9.5</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="Q2" t="n">
-        <v>16.38</v>
+        <v>16.67</v>
       </c>
       <c r="R2" t="n">
-        <v>5.25</v>
+        <v>5.67</v>
       </c>
       <c r="S2" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="T2" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="U2" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="V2" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>46.12</v>
+        <v>46.67</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>15.25</v>
+        <v>14.44</v>
       </c>
       <c r="AA2" t="n">
-        <v>10.25</v>
+        <v>9.67</v>
       </c>
       <c r="AB2" t="n">
-        <v>5</v>
+        <v>4.78</v>
       </c>
       <c r="AC2" t="n">
-        <v>22.5</v>
+        <v>23</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.66</v>
+        <v>1.48</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -1550,31 +1550,31 @@
         <v>1.67</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.71</v>
+        <v>2.61</v>
       </c>
       <c r="BH2" t="n">
-        <v>8.65</v>
+        <v>8.56</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.71</v>
+        <v>2.61</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="BP2" t="n">
         <v>-1</v>
@@ -1586,31 +1586,31 @@
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>82.34999999999999</v>
+        <v>77.78</v>
       </c>
       <c r="BT2" t="n">
-        <v>52.94</v>
+        <v>50</v>
       </c>
       <c r="BU2" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BV2" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BW2" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX2" t="n">
-        <v>58.82</v>
+        <v>55.56</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.71</v>
+        <v>2.63</v>
       </c>
       <c r="BZ2" t="n">
-        <v>2.75</v>
+        <v>2.68</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.49</v>
+        <v>3.5</v>
       </c>
       <c r="CB2" t="n">
         <v>3.57</v>
@@ -1625,16 +1625,16 @@
         <v>1.41</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="CH2" t="n">
         <v>1.4</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CJ2" t="n">
         <v>1.85</v>
@@ -1643,22 +1643,22 @@
         <v>1.48</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="CP2" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.49</v>
+        <v>3.47</v>
       </c>
       <c r="CR2" t="n">
         <v>1.39</v>
@@ -1673,61 +1673,61 @@
         <v>1.42</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CX2" t="n">
         <v>1.57</v>
       </c>
       <c r="CY2" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="CZ2" t="n">
         <v>2.39</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.62</v>
+        <v>3.59</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="DG2" t="n">
         <v>-1</v>
       </c>
       <c r="DH2" t="n">
-        <v>92.65000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="DI2" t="n">
         <v>0.11</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
       <c r="DK2" t="n">
-        <v>4.7</v>
+        <v>4.44</v>
       </c>
       <c r="DL2" t="n">
         <v>-1</v>
       </c>
       <c r="DM2" t="n">
-        <v>45</v>
+        <v>42.5</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DO2" t="n">
         <v>-1</v>
@@ -1736,43 +1736,43 @@
         <v>11.94</v>
       </c>
       <c r="DQ2" t="n">
-        <v>16.77</v>
+        <v>16.89</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.41</v>
+        <v>6.56</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>46.35</v>
+        <v>46.62</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="DX2" t="n">
-        <v>12.88</v>
+        <v>12.61</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.94</v>
+        <v>8.73</v>
       </c>
       <c r="DZ2" t="n">
-        <v>3.94</v>
+        <v>3.89</v>
       </c>
       <c r="EA2" t="n">
-        <v>22</v>
+        <v>22.28</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="3">
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
         <v>9</v>
       </c>
       <c r="D13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E13" t="n">
         <v>0.22</v>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AH13" t="n">
         <v>-1</v>
       </c>
       <c r="AI13" t="n">
-        <v>91</v>
+        <v>80.89</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
@@ -5920,94 +5920,94 @@
         <v>2</v>
       </c>
       <c r="AL13" t="n">
-        <v>5.62</v>
+        <v>5.78</v>
       </c>
       <c r="AM13" t="n">
         <v>-1</v>
       </c>
       <c r="AN13" t="n">
-        <v>43.38</v>
+        <v>38.56</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AP13" t="n">
         <v>-1</v>
       </c>
       <c r="AQ13" t="n">
-        <v>12.62</v>
+        <v>13.33</v>
       </c>
       <c r="AR13" t="n">
-        <v>16.12</v>
+        <v>15.67</v>
       </c>
       <c r="AS13" t="n">
-        <v>9</v>
+        <v>8.56</v>
       </c>
       <c r="AT13" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AU13" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AX13" t="n">
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>47.62</v>
+        <v>47.78</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA13" t="n">
-        <v>10.88</v>
+        <v>11.33</v>
       </c>
       <c r="BB13" t="n">
-        <v>6.62</v>
+        <v>7.22</v>
       </c>
       <c r="BC13" t="n">
-        <v>4.25</v>
+        <v>4.11</v>
       </c>
       <c r="BD13" t="n">
-        <v>22.88</v>
+        <v>22.89</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.31</v>
+        <v>1.16</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="BH13" t="n">
-        <v>10.06</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="BL13" t="n">
         <v>1</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="BP13" t="n">
         <v>-1</v>
@@ -6016,25 +6016,25 @@
         <v>-1</v>
       </c>
       <c r="BR13" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BS13" t="n">
-        <v>64.70999999999999</v>
+        <v>61.11</v>
       </c>
       <c r="BT13" t="n">
-        <v>47.06</v>
+        <v>44.44</v>
       </c>
       <c r="BU13" t="n">
-        <v>41.18</v>
+        <v>38.89</v>
       </c>
       <c r="BV13" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BW13" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX13" t="n">
-        <v>58.82</v>
+        <v>55.56</v>
       </c>
       <c r="BY13" t="n">
         <v>3.67</v>
@@ -6043,28 +6043,28 @@
         <v>4.33</v>
       </c>
       <c r="CA13" t="n">
-        <v>4.14</v>
+        <v>4.12</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.41</v>
+        <v>4.36</v>
       </c>
       <c r="CC13" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="CD13" t="n">
         <v>6.6</v>
-      </c>
-      <c r="CD13" t="n">
-        <v>6.98</v>
       </c>
       <c r="CE13" t="n">
         <v>1.33</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CI13" t="n">
         <v>2.04</v>
@@ -6088,10 +6088,10 @@
         <v>1.24</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="CR13" t="n">
         <v>1.4</v>
@@ -6109,13 +6109,13 @@
         <v>2.11</v>
       </c>
       <c r="CW13" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CX13" t="n">
         <v>1.54</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CZ13" t="n">
         <v>2.42</v>
@@ -6127,52 +6127,52 @@
         <v>1.26</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="DD13" t="n">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="DG13" t="n">
         <v>-1</v>
       </c>
       <c r="DH13" t="n">
-        <v>87.18000000000001</v>
+        <v>82.34</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.35</v>
+        <v>5.44</v>
       </c>
       <c r="DL13" t="n">
         <v>-1</v>
       </c>
       <c r="DM13" t="n">
-        <v>43.71</v>
+        <v>41.28</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="DO13" t="n">
         <v>-1</v>
       </c>
       <c r="DP13" t="n">
-        <v>14.64</v>
+        <v>14.88</v>
       </c>
       <c r="DQ13" t="n">
-        <v>16.17</v>
+        <v>15.94</v>
       </c>
       <c r="DR13" t="n">
-        <v>8.41</v>
+        <v>8.23</v>
       </c>
       <c r="DS13" t="n">
         <v>0.11</v>
@@ -6184,28 +6184,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>48.82</v>
+        <v>48.84</v>
       </c>
       <c r="DW13" t="n">
         <v>0.06</v>
       </c>
       <c r="DX13" t="n">
-        <v>11.18</v>
+        <v>11.38</v>
       </c>
       <c r="DY13" t="n">
-        <v>7.41</v>
+        <v>7.66</v>
       </c>
       <c r="DZ13" t="n">
-        <v>3.76</v>
+        <v>3.72</v>
       </c>
       <c r="EA13" t="n">
-        <v>22.36</v>
+        <v>22.39</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="14">

--- a/data/teams/leagues/Averages_Russian_Premier_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Russian_Premier_League_2025-2026.xlsx
@@ -1397,7 +1397,7 @@
         <v>-1</v>
       </c>
       <c r="H2" t="n">
-        <v>81.78</v>
+        <v>92</v>
       </c>
       <c r="I2" t="n">
         <v>0.11</v>
@@ -1412,7 +1412,7 @@
         <v>-1</v>
       </c>
       <c r="M2" t="n">
-        <v>42.78</v>
+        <v>47.44</v>
       </c>
       <c r="N2" t="n">
         <v>0.22</v>
@@ -1424,7 +1424,7 @@
         <v>9.779999999999999</v>
       </c>
       <c r="Q2" t="n">
-        <v>16.67</v>
+        <v>16.56</v>
       </c>
       <c r="R2" t="n">
         <v>5.67</v>
@@ -1451,10 +1451,10 @@
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>14.44</v>
+        <v>14.56</v>
       </c>
       <c r="AA2" t="n">
-        <v>9.67</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="AB2" t="n">
         <v>4.78</v>
@@ -1463,7 +1463,7 @@
         <v>23</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="AE2" t="n">
         <v>1.78</v>
@@ -1709,7 +1709,7 @@
         <v>-1</v>
       </c>
       <c r="DH2" t="n">
-        <v>87.5</v>
+        <v>92.61</v>
       </c>
       <c r="DI2" t="n">
         <v>0.11</v>
@@ -1724,7 +1724,7 @@
         <v>-1</v>
       </c>
       <c r="DM2" t="n">
-        <v>42.5</v>
+        <v>44.83</v>
       </c>
       <c r="DN2" t="n">
         <v>0.5</v>
@@ -1736,7 +1736,7 @@
         <v>11.94</v>
       </c>
       <c r="DQ2" t="n">
-        <v>16.89</v>
+        <v>16.83</v>
       </c>
       <c r="DR2" t="n">
         <v>6.56</v>
@@ -1757,10 +1757,10 @@
         <v>0.34</v>
       </c>
       <c r="DX2" t="n">
-        <v>12.61</v>
+        <v>12.67</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.73</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="DZ2" t="n">
         <v>3.89</v>
@@ -1769,7 +1769,7 @@
         <v>22.28</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="EC2" t="n">
         <v>1.72</v>
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" t="n">
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1872,112 +1872,112 @@
         <v>1.67</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AH3" t="n">
         <v>-1</v>
       </c>
       <c r="AI3" t="n">
-        <v>86.5</v>
+        <v>85.33</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.25</v>
+        <v>2.56</v>
       </c>
       <c r="AL3" t="n">
-        <v>4.62</v>
+        <v>4.22</v>
       </c>
       <c r="AM3" t="n">
         <v>-1</v>
       </c>
       <c r="AN3" t="n">
-        <v>41</v>
+        <v>40.67</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.75</v>
+        <v>0.89</v>
       </c>
       <c r="AP3" t="n">
         <v>-1</v>
       </c>
       <c r="AQ3" t="n">
-        <v>14.88</v>
+        <v>14.67</v>
       </c>
       <c r="AR3" t="n">
-        <v>13.12</v>
+        <v>13.11</v>
       </c>
       <c r="AS3" t="n">
-        <v>8</v>
+        <v>7.78</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>42.62</v>
+        <v>41.11</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="BA3" t="n">
-        <v>11.12</v>
+        <v>10.56</v>
       </c>
       <c r="BB3" t="n">
-        <v>8.119999999999999</v>
+        <v>7.44</v>
       </c>
       <c r="BC3" t="n">
-        <v>3</v>
+        <v>3.11</v>
       </c>
       <c r="BD3" t="n">
-        <v>18.38</v>
+        <v>17.56</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.71</v>
+        <v>2.67</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.119999999999999</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.71</v>
+        <v>2.67</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.59</v>
+        <v>0.67</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="BP3" t="n">
         <v>-1</v>
@@ -1989,22 +1989,22 @@
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BT3" t="n">
-        <v>52.94</v>
+        <v>50</v>
       </c>
       <c r="BU3" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BV3" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>70.59</v>
+        <v>66.67</v>
       </c>
       <c r="BY3" t="n">
         <v>3.38</v>
@@ -2013,40 +2013,40 @@
         <v>3.61</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.84</v>
+        <v>3.99</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.13</v>
+        <v>4.25</v>
       </c>
       <c r="CC3" t="n">
-        <v>4.83</v>
+        <v>5.75</v>
       </c>
       <c r="CD3" t="n">
-        <v>5.3</v>
+        <v>6.1</v>
       </c>
       <c r="CE3" t="n">
         <v>1.32</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.31</v>
+        <v>3.32</v>
       </c>
       <c r="CH3" t="n">
         <v>1.52</v>
       </c>
       <c r="CI3" t="n">
-        <v>2.12</v>
+        <v>2.09</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="CK3" t="n">
         <v>1.47</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CM3" t="n">
         <v>2.51</v>
@@ -2055,13 +2055,13 @@
         <v>1.93</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="CR3" t="n">
         <v>1.38</v>
@@ -2076,10 +2076,10 @@
         <v>1.47</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="CX3" t="n">
         <v>1.55</v>
@@ -2097,85 +2097,85 @@
         <v>1.24</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="DD3" t="n">
-        <v>2.91</v>
+        <v>2.89</v>
       </c>
       <c r="DE3" t="n">
         <v>0.06</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="DG3" t="n">
         <v>-1</v>
       </c>
       <c r="DH3" t="n">
-        <v>93.47</v>
+        <v>92.5</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.94</v>
+        <v>2.12</v>
       </c>
       <c r="DK3" t="n">
-        <v>4.35</v>
+        <v>4.16</v>
       </c>
       <c r="DL3" t="n">
         <v>-1</v>
       </c>
       <c r="DM3" t="n">
-        <v>45.41</v>
+        <v>45</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.77</v>
+        <v>0.84</v>
       </c>
       <c r="DO3" t="n">
         <v>-1</v>
       </c>
       <c r="DP3" t="n">
-        <v>15.06</v>
+        <v>14.94</v>
       </c>
       <c r="DQ3" t="n">
-        <v>14.41</v>
+        <v>14.34</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.47</v>
+        <v>7.39</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>44.41</v>
+        <v>43.56</v>
       </c>
       <c r="DW3" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DX3" t="n">
-        <v>11.11</v>
+        <v>10.84</v>
       </c>
       <c r="DY3" t="n">
-        <v>7.29</v>
+        <v>7</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.83</v>
+        <v>3.84</v>
       </c>
       <c r="EA3" t="n">
-        <v>18.71</v>
+        <v>18.28</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -2185,94 +2185,94 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" t="n">
         <v>9</v>
       </c>
       <c r="E4" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="F4" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="G4" t="n">
         <v>-1</v>
       </c>
       <c r="H4" t="n">
-        <v>83.25</v>
+        <v>83</v>
       </c>
       <c r="I4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="J4" t="n">
-        <v>3.12</v>
+        <v>2.89</v>
       </c>
       <c r="K4" t="n">
-        <v>3.5</v>
+        <v>3.33</v>
       </c>
       <c r="L4" t="n">
         <v>-1</v>
       </c>
       <c r="M4" t="n">
-        <v>42.88</v>
+        <v>45.67</v>
       </c>
       <c r="N4" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="O4" t="n">
         <v>-1</v>
       </c>
       <c r="P4" t="n">
-        <v>20.12</v>
+        <v>19.44</v>
       </c>
       <c r="Q4" t="n">
-        <v>12.88</v>
+        <v>12.33</v>
       </c>
       <c r="R4" t="n">
-        <v>7.88</v>
+        <v>7.56</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="T4" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="U4" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="V4" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>41.25</v>
+        <v>43.33</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z4" t="n">
-        <v>12</v>
+        <v>12.89</v>
       </c>
       <c r="AA4" t="n">
-        <v>8.25</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="AC4" t="n">
-        <v>22.75</v>
+        <v>22</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.88</v>
+        <v>2.67</v>
       </c>
       <c r="AF4" t="n">
         <v>0.22</v>
@@ -2356,31 +2356,31 @@
         <v>3.33</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="BH4" t="n">
-        <v>8.41</v>
+        <v>8.06</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.35</v>
+        <v>0.44</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.76</v>
+        <v>0.83</v>
       </c>
       <c r="BP4" t="n">
         <v>-1</v>
@@ -2389,37 +2389,37 @@
         <v>-1</v>
       </c>
       <c r="BR4" t="n">
-        <v>76.47</v>
+        <v>77.78</v>
       </c>
       <c r="BS4" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BT4" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BU4" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BV4" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BY4" t="n">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="BZ4" t="n">
-        <v>2.79</v>
+        <v>2.65</v>
       </c>
       <c r="CA4" t="n">
         <v>3.42</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.45</v>
+        <v>3.49</v>
       </c>
       <c r="CC4" t="n">
         <v>3.37</v>
@@ -2428,22 +2428,22 @@
         <v>3.67</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="CI4" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CK4" t="n">
         <v>1.44</v>
@@ -2461,7 +2461,7 @@
         <v>1.32</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CQ4" t="n">
         <v>3.92</v>
@@ -2479,10 +2479,10 @@
         <v>1.39</v>
       </c>
       <c r="CV4" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CW4" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="CX4" t="n">
         <v>1.63</v>
@@ -2497,88 +2497,88 @@
         <v>1.86</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="DD4" t="n">
-        <v>4.4</v>
+        <v>4.37</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="DG4" t="n">
         <v>-1</v>
       </c>
       <c r="DH4" t="n">
-        <v>88.23999999999999</v>
+        <v>87.84</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DJ4" t="n">
-        <v>3.29</v>
+        <v>3.16</v>
       </c>
       <c r="DK4" t="n">
-        <v>3.41</v>
+        <v>3.33</v>
       </c>
       <c r="DL4" t="n">
         <v>-1</v>
       </c>
       <c r="DM4" t="n">
-        <v>43</v>
+        <v>44.39</v>
       </c>
       <c r="DN4" t="n">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="DO4" t="n">
         <v>-1</v>
       </c>
       <c r="DP4" t="n">
-        <v>20.17</v>
+        <v>19.83</v>
       </c>
       <c r="DQ4" t="n">
-        <v>13.24</v>
+        <v>12.94</v>
       </c>
       <c r="DR4" t="n">
-        <v>7.65</v>
+        <v>7.5</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>44.94</v>
+        <v>45.78</v>
       </c>
       <c r="DW4" t="n">
         <v>0.11</v>
       </c>
       <c r="DX4" t="n">
-        <v>12.3</v>
+        <v>12.73</v>
       </c>
       <c r="DY4" t="n">
-        <v>8.18</v>
+        <v>8.5</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.12</v>
+        <v>4.22</v>
       </c>
       <c r="EA4" t="n">
-        <v>21.94</v>
+        <v>21.61</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="EC4" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5" t="n">
         <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E5" t="n">
         <v>0.33</v>
@@ -2681,109 +2681,109 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AH5" t="n">
         <v>-1</v>
       </c>
       <c r="AI5" t="n">
-        <v>99</v>
+        <v>96.44</v>
       </c>
       <c r="AJ5" t="n">
         <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="AL5" t="n">
-        <v>5.5</v>
+        <v>5.44</v>
       </c>
       <c r="AM5" t="n">
         <v>-1</v>
       </c>
       <c r="AN5" t="n">
-        <v>46</v>
+        <v>43.67</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AP5" t="n">
         <v>-1</v>
       </c>
       <c r="AQ5" t="n">
-        <v>12.62</v>
+        <v>12.78</v>
       </c>
       <c r="AR5" t="n">
-        <v>13.25</v>
+        <v>13.11</v>
       </c>
       <c r="AS5" t="n">
-        <v>10.38</v>
+        <v>11.11</v>
       </c>
       <c r="AT5" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AU5" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>53.5</v>
+        <v>52</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="BA5" t="n">
-        <v>12.75</v>
+        <v>12.33</v>
       </c>
       <c r="BB5" t="n">
-        <v>8.619999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.12</v>
+        <v>4</v>
       </c>
       <c r="BD5" t="n">
-        <v>21.38</v>
+        <v>21</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.47</v>
+        <v>2.61</v>
       </c>
       <c r="BH5" t="n">
-        <v>10.47</v>
+        <v>10.67</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.47</v>
+        <v>2.61</v>
       </c>
       <c r="BJ5" t="n">
         <v>1.06</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.59</v>
+        <v>0.67</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.29</v>
+        <v>0.33</v>
       </c>
       <c r="BN5" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="BP5" t="n">
         <v>-1</v>
@@ -2792,25 +2792,25 @@
         <v>-1</v>
       </c>
       <c r="BR5" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS5" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BT5" t="n">
-        <v>41.18</v>
+        <v>44.44</v>
       </c>
       <c r="BU5" t="n">
-        <v>29.41</v>
+        <v>33.33</v>
       </c>
       <c r="BV5" t="n">
-        <v>11.76</v>
+        <v>16.67</v>
       </c>
       <c r="BW5" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX5" t="n">
-        <v>47.06</v>
+        <v>50</v>
       </c>
       <c r="BY5" t="n">
         <v>1.82</v>
@@ -2819,28 +2819,28 @@
         <v>1.9</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.76</v>
+        <v>3.75</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.86</v>
+        <v>3.87</v>
       </c>
       <c r="CC5" t="n">
-        <v>2.71</v>
+        <v>2.96</v>
       </c>
       <c r="CD5" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="CE5" t="n">
         <v>1.38</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CI5" t="n">
         <v>1.96</v>
@@ -2855,31 +2855,31 @@
         <v>1.94</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="CN5" t="n">
         <v>1.88</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.23</v>
+        <v>3.2</v>
       </c>
       <c r="CR5" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CS5" t="n">
-        <v>3.06</v>
+        <v>3.01</v>
       </c>
       <c r="CT5" t="n">
-        <v>2.89</v>
+        <v>2.93</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CV5" t="n">
         <v>2.05</v>
@@ -2888,16 +2888,16 @@
         <v>1.83</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="DB5" t="n">
         <v>1.3</v>
@@ -2909,22 +2909,22 @@
         <v>3.32</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="DG5" t="n">
         <v>-1</v>
       </c>
       <c r="DH5" t="n">
-        <v>102.35</v>
+        <v>100.88</v>
       </c>
       <c r="DI5" t="n">
         <v>0</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="DK5" t="n">
         <v>5</v>
@@ -2933,55 +2933,55 @@
         <v>-1</v>
       </c>
       <c r="DM5" t="n">
-        <v>49.94</v>
+        <v>48.56</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.59</v>
+        <v>0.67</v>
       </c>
       <c r="DO5" t="n">
         <v>-1</v>
       </c>
       <c r="DP5" t="n">
-        <v>11.94</v>
+        <v>12.06</v>
       </c>
       <c r="DQ5" t="n">
-        <v>15.59</v>
+        <v>15.39</v>
       </c>
       <c r="DR5" t="n">
-        <v>9.289999999999999</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>56</v>
+        <v>55.11</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.12</v>
+        <v>0.16</v>
       </c>
       <c r="DX5" t="n">
-        <v>13.71</v>
+        <v>13.44</v>
       </c>
       <c r="DY5" t="n">
-        <v>8.880000000000001</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="DZ5" t="n">
-        <v>4.82</v>
+        <v>4.72</v>
       </c>
       <c r="EA5" t="n">
-        <v>21.06</v>
+        <v>20.89</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="EC5" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="6">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C6" t="n">
         <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -3081,112 +3081,112 @@
         <v>1.56</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AH6" t="n">
         <v>-1</v>
       </c>
       <c r="AI6" t="n">
-        <v>93.25</v>
+        <v>91.33</v>
       </c>
       <c r="AJ6" t="n">
         <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="AL6" t="n">
-        <v>5</v>
+        <v>4.67</v>
       </c>
       <c r="AM6" t="n">
         <v>-1</v>
       </c>
       <c r="AN6" t="n">
-        <v>48.25</v>
+        <v>47.67</v>
       </c>
       <c r="AO6" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>14.89</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>6.44</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>52</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>14</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>10.67</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>22.11</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>9.390000000000001</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="BL6" t="n">
         <v>1</v>
       </c>
-      <c r="AP6" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>14.38</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>14.75</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>53.25</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>11.25</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>21.12</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>3</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>9.529999999999999</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>3</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>1.06</v>
-      </c>
       <c r="BM6" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="BP6" t="n">
         <v>-1</v>
@@ -3195,25 +3195,25 @@
         <v>-1</v>
       </c>
       <c r="BR6" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS6" t="n">
-        <v>76.47</v>
+        <v>77.78</v>
       </c>
       <c r="BT6" t="n">
-        <v>64.70999999999999</v>
+        <v>61.11</v>
       </c>
       <c r="BU6" t="n">
-        <v>35.29</v>
+        <v>33.33</v>
       </c>
       <c r="BV6" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BW6" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX6" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BY6" t="n">
         <v>1.87</v>
@@ -3222,16 +3222,16 @@
         <v>1.89</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.82</v>
+        <v>3.79</v>
       </c>
       <c r="CB6" t="n">
-        <v>4.02</v>
+        <v>4</v>
       </c>
       <c r="CC6" t="n">
-        <v>2.65</v>
+        <v>2.72</v>
       </c>
       <c r="CD6" t="n">
-        <v>2.61</v>
+        <v>2.71</v>
       </c>
       <c r="CE6" t="n">
         <v>1.33</v>
@@ -3240,22 +3240,22 @@
         <v>2.58</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="CH6" t="n">
         <v>1.5</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CJ6" t="n">
         <v>1.7</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CM6" t="n">
         <v>2.57</v>
@@ -3285,7 +3285,7 @@
         <v>1.52</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CW6" t="n">
         <v>1.71</v>
@@ -3315,43 +3315,43 @@
         <v>0.06</v>
       </c>
       <c r="DF6" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="DG6" t="n">
         <v>-1</v>
       </c>
       <c r="DH6" t="n">
-        <v>97.88</v>
+        <v>96.66</v>
       </c>
       <c r="DI6" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ6" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="DK6" t="n">
-        <v>5.35</v>
+        <v>5.17</v>
       </c>
       <c r="DL6" t="n">
         <v>-1</v>
       </c>
       <c r="DM6" t="n">
-        <v>51.29</v>
+        <v>50.84</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="DO6" t="n">
         <v>-1</v>
       </c>
       <c r="DP6" t="n">
-        <v>13.35</v>
+        <v>13.66</v>
       </c>
       <c r="DQ6" t="n">
-        <v>16.35</v>
+        <v>16.89</v>
       </c>
       <c r="DR6" t="n">
-        <v>5.53</v>
+        <v>5.56</v>
       </c>
       <c r="DS6" t="n">
         <v>0.11</v>
@@ -3363,28 +3363,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>55.76</v>
+        <v>55</v>
       </c>
       <c r="DW6" t="n">
         <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>15.53</v>
+        <v>15.22</v>
       </c>
       <c r="DY6" t="n">
-        <v>10.94</v>
+        <v>10.67</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.59</v>
+        <v>4.56</v>
       </c>
       <c r="EA6" t="n">
-        <v>21.29</v>
+        <v>21.78</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="EC6" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7" t="n">
         <v>9</v>
@@ -3406,49 +3406,49 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="G7" t="n">
         <v>-1</v>
       </c>
       <c r="H7" t="n">
-        <v>78.38</v>
+        <v>78.44</v>
       </c>
       <c r="I7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="J7" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>4.12</v>
+        <v>4.33</v>
       </c>
       <c r="L7" t="n">
         <v>-1</v>
       </c>
       <c r="M7" t="n">
-        <v>37.25</v>
+        <v>36.56</v>
       </c>
       <c r="N7" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="O7" t="n">
         <v>-1</v>
       </c>
       <c r="P7" t="n">
-        <v>13.12</v>
+        <v>13.11</v>
       </c>
       <c r="Q7" t="n">
-        <v>15.25</v>
+        <v>15</v>
       </c>
       <c r="R7" t="n">
-        <v>7.88</v>
+        <v>7.67</v>
       </c>
       <c r="S7" t="n">
-        <v>1.88</v>
+        <v>2.11</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -3460,28 +3460,28 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>46.5</v>
+        <v>46.78</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>8.380000000000001</v>
+        <v>8.44</v>
       </c>
       <c r="AA7" t="n">
-        <v>6.12</v>
+        <v>6</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.25</v>
+        <v>2.44</v>
       </c>
       <c r="AC7" t="n">
-        <v>18.75</v>
+        <v>17.44</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -3565,31 +3565,31 @@
         <v>2.33</v>
       </c>
       <c r="BG7" t="n">
-        <v>3</v>
+        <v>3.17</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.35</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="BI7" t="n">
-        <v>3</v>
+        <v>3.17</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.35</v>
+        <v>0.39</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.76</v>
+        <v>0.89</v>
       </c>
       <c r="BL7" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.12</v>
+        <v>1.28</v>
       </c>
       <c r="BP7" t="n">
         <v>-1</v>
@@ -3598,31 +3598,31 @@
         <v>-1</v>
       </c>
       <c r="BR7" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BS7" t="n">
-        <v>82.34999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT7" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BU7" t="n">
-        <v>35.29</v>
+        <v>38.89</v>
       </c>
       <c r="BV7" t="n">
-        <v>17.65</v>
+        <v>22.22</v>
       </c>
       <c r="BW7" t="n">
-        <v>11.76</v>
+        <v>16.67</v>
       </c>
       <c r="BX7" t="n">
-        <v>52.94</v>
+        <v>55.56</v>
       </c>
       <c r="BY7" t="n">
-        <v>4.09</v>
+        <v>4.12</v>
       </c>
       <c r="BZ7" t="n">
-        <v>4.09</v>
+        <v>4.17</v>
       </c>
       <c r="CA7" t="n">
         <v>3.67</v>
@@ -3643,7 +3643,7 @@
         <v>2.93</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="CH7" t="n">
         <v>1.42</v>
@@ -3652,16 +3652,16 @@
         <v>1.91</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="CN7" t="n">
         <v>1.87</v>
@@ -3673,7 +3673,7 @@
         <v>2.03</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.43</v>
+        <v>3.41</v>
       </c>
       <c r="CR7" t="n">
         <v>1.48</v>
@@ -3688,10 +3688,10 @@
         <v>1.41</v>
       </c>
       <c r="CV7" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CX7" t="n">
         <v>1.62</v>
@@ -3700,7 +3700,7 @@
         <v>2.02</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="DA7" t="n">
         <v>1.8</v>
@@ -3709,52 +3709,52 @@
         <v>1.36</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.79</v>
+        <v>3.75</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="DG7" t="n">
         <v>-1</v>
       </c>
       <c r="DH7" t="n">
-        <v>81.18000000000001</v>
+        <v>81.06</v>
       </c>
       <c r="DI7" t="n">
         <v>0.11</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.29</v>
+        <v>2.22</v>
       </c>
       <c r="DK7" t="n">
-        <v>3.29</v>
+        <v>3.44</v>
       </c>
       <c r="DL7" t="n">
         <v>-1</v>
       </c>
       <c r="DM7" t="n">
-        <v>35.35</v>
+        <v>35.12</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="DO7" t="n">
         <v>-1</v>
       </c>
       <c r="DP7" t="n">
-        <v>14.17</v>
+        <v>14.11</v>
       </c>
       <c r="DQ7" t="n">
-        <v>14.88</v>
+        <v>14.78</v>
       </c>
       <c r="DR7" t="n">
-        <v>8.529999999999999</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="DS7" t="n">
         <v>0</v>
@@ -3766,28 +3766,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>46.82</v>
+        <v>46.94</v>
       </c>
       <c r="DW7" t="n">
         <v>0.06</v>
       </c>
       <c r="DX7" t="n">
-        <v>8.18</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="DY7" t="n">
-        <v>5.76</v>
+        <v>5.72</v>
       </c>
       <c r="DZ7" t="n">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="EA7" t="n">
-        <v>18.88</v>
+        <v>18.22</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.23</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="8">
@@ -3797,10 +3797,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D8" t="n">
         <v>8</v>
@@ -3809,82 +3809,82 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="G8" t="n">
         <v>-1</v>
       </c>
       <c r="H8" t="n">
-        <v>95.89</v>
+        <v>96.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="J8" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="K8" t="n">
-        <v>5.89</v>
+        <v>6.2</v>
       </c>
       <c r="L8" t="n">
         <v>-1</v>
       </c>
       <c r="M8" t="n">
-        <v>52.89</v>
+        <v>52.8</v>
       </c>
       <c r="N8" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="O8" t="n">
         <v>-1</v>
       </c>
       <c r="P8" t="n">
-        <v>13.56</v>
+        <v>13.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>16</v>
+        <v>16.1</v>
       </c>
       <c r="R8" t="n">
-        <v>6.56</v>
+        <v>6.4</v>
       </c>
       <c r="S8" t="n">
-        <v>0.78</v>
+        <v>0.9</v>
       </c>
       <c r="T8" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="U8" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V8" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>59.11</v>
+        <v>59.2</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="Z8" t="n">
         <v>19</v>
       </c>
       <c r="AA8" t="n">
-        <v>13.67</v>
+        <v>13.7</v>
       </c>
       <c r="AB8" t="n">
-        <v>5.33</v>
+        <v>5.3</v>
       </c>
       <c r="AC8" t="n">
-        <v>21</v>
+        <v>21.4</v>
       </c>
       <c r="AD8" t="n">
         <v>1.95</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="AF8" t="n">
         <v>0.25</v>
@@ -3968,31 +3968,31 @@
         <v>1.62</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.59</v>
+        <v>2.72</v>
       </c>
       <c r="BH8" t="n">
-        <v>8.529999999999999</v>
+        <v>8.83</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.59</v>
+        <v>2.72</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.71</v>
+        <v>0.78</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="BP8" t="n">
         <v>-1</v>
@@ -4001,34 +4001,34 @@
         <v>-1</v>
       </c>
       <c r="BR8" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS8" t="n">
-        <v>76.47</v>
+        <v>77.78</v>
       </c>
       <c r="BT8" t="n">
-        <v>41.18</v>
+        <v>44.44</v>
       </c>
       <c r="BU8" t="n">
-        <v>17.65</v>
+        <v>22.22</v>
       </c>
       <c r="BV8" t="n">
-        <v>17.65</v>
+        <v>22.22</v>
       </c>
       <c r="BW8" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BX8" t="n">
-        <v>41.18</v>
+        <v>44.44</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="BZ8" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.88</v>
+        <v>3.86</v>
       </c>
       <c r="CB8" t="n">
         <v>4.13</v>
@@ -4043,10 +4043,10 @@
         <v>1.36</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="CH8" t="n">
         <v>1.47</v>
@@ -4055,16 +4055,16 @@
         <v>1.97</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CK8" t="n">
         <v>1.49</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="CN8" t="n">
         <v>1.9</v>
@@ -4073,19 +4073,19 @@
         <v>1.26</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="CR8" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.89</v>
+        <v>2.86</v>
       </c>
       <c r="CT8" t="n">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="CU8" t="n">
         <v>1.44</v>
@@ -4118,46 +4118,46 @@
         <v>3.02</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="DG8" t="n">
         <v>-1</v>
       </c>
       <c r="DH8" t="n">
-        <v>93</v>
+        <v>93.33</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="DK8" t="n">
-        <v>5.12</v>
+        <v>5.33</v>
       </c>
       <c r="DL8" t="n">
         <v>-1</v>
       </c>
       <c r="DM8" t="n">
-        <v>46.47</v>
+        <v>46.78</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="DO8" t="n">
         <v>-1</v>
       </c>
       <c r="DP8" t="n">
-        <v>13.59</v>
+        <v>13.55</v>
       </c>
       <c r="DQ8" t="n">
-        <v>17.65</v>
+        <v>17.61</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.47</v>
+        <v>7.33</v>
       </c>
       <c r="DS8" t="n">
         <v>0.11</v>
@@ -4169,28 +4169,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>58.06</v>
+        <v>58.17</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DX8" t="n">
-        <v>16.18</v>
+        <v>16.33</v>
       </c>
       <c r="DY8" t="n">
-        <v>11.35</v>
+        <v>11.5</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.82</v>
+        <v>4.83</v>
       </c>
       <c r="EA8" t="n">
-        <v>21.53</v>
+        <v>21.72</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="9">
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
         <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E9" t="n">
         <v>0.12</v>
@@ -4290,112 +4290,112 @@
         <v>1.88</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AH9" t="n">
         <v>-1</v>
       </c>
       <c r="AI9" t="n">
-        <v>74.56</v>
+        <v>73.8</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="AL9" t="n">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="AM9" t="n">
         <v>-1</v>
       </c>
       <c r="AN9" t="n">
-        <v>29.22</v>
+        <v>30.1</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AP9" t="n">
         <v>-1</v>
       </c>
       <c r="AQ9" t="n">
-        <v>14.89</v>
+        <v>14.8</v>
       </c>
       <c r="AR9" t="n">
-        <v>14.56</v>
+        <v>13.9</v>
       </c>
       <c r="AS9" t="n">
-        <v>8.220000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AT9" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AU9" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>46.44</v>
+        <v>45.8</v>
       </c>
       <c r="AZ9" t="n">
         <v>0</v>
       </c>
       <c r="BA9" t="n">
-        <v>7.89</v>
+        <v>7.4</v>
       </c>
       <c r="BB9" t="n">
-        <v>5.44</v>
+        <v>5</v>
       </c>
       <c r="BC9" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="BD9" t="n">
-        <v>18.78</v>
+        <v>18.9</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.89</v>
+        <v>0.86</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="BG9" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.24</v>
+        <v>8.83</v>
       </c>
       <c r="BI9" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.59</v>
+        <v>0.67</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BL9" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="BP9" t="n">
         <v>-1</v>
@@ -4407,22 +4407,22 @@
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BT9" t="n">
-        <v>41.18</v>
+        <v>38.89</v>
       </c>
       <c r="BU9" t="n">
-        <v>35.29</v>
+        <v>33.33</v>
       </c>
       <c r="BV9" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BW9" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX9" t="n">
-        <v>52.94</v>
+        <v>50</v>
       </c>
       <c r="BY9" t="n">
         <v>3.54</v>
@@ -4431,40 +4431,40 @@
         <v>3.82</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.83</v>
+        <v>3.8</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.91</v>
+        <v>3.92</v>
       </c>
       <c r="CC9" t="n">
-        <v>5.27</v>
+        <v>5.43</v>
       </c>
       <c r="CD9" t="n">
-        <v>5.58</v>
+        <v>5.78</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.99</v>
+        <v>2.97</v>
       </c>
       <c r="CH9" t="n">
         <v>1.43</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="CK9" t="n">
         <v>1.53</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CM9" t="n">
         <v>2.39</v>
@@ -4476,10 +4476,10 @@
         <v>1.3</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.36</v>
+        <v>3.39</v>
       </c>
       <c r="CR9" t="n">
         <v>1.43</v>
@@ -4494,10 +4494,10 @@
         <v>1.41</v>
       </c>
       <c r="CV9" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="CX9" t="n">
         <v>1.62</v>
@@ -4515,52 +4515,52 @@
         <v>1.32</v>
       </c>
       <c r="DC9" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.49</v>
+        <v>3.54</v>
       </c>
       <c r="DE9" t="n">
         <v>0.11</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="DG9" t="n">
         <v>-1</v>
       </c>
       <c r="DH9" t="n">
-        <v>78.23999999999999</v>
+        <v>77.61</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="DK9" t="n">
-        <v>3.06</v>
+        <v>2.89</v>
       </c>
       <c r="DL9" t="n">
         <v>-1</v>
       </c>
       <c r="DM9" t="n">
-        <v>33.88</v>
+        <v>34.11</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="DO9" t="n">
         <v>-1</v>
       </c>
       <c r="DP9" t="n">
-        <v>14.53</v>
+        <v>14.5</v>
       </c>
       <c r="DQ9" t="n">
-        <v>14.65</v>
+        <v>14.28</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.640000000000001</v>
+        <v>8.83</v>
       </c>
       <c r="DS9" t="n">
         <v>0.06</v>
@@ -4572,28 +4572,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>46.29</v>
+        <v>45.94</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DX9" t="n">
-        <v>8.59</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="DY9" t="n">
-        <v>6</v>
+        <v>5.72</v>
       </c>
       <c r="DZ9" t="n">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="EA9" t="n">
-        <v>19.77</v>
+        <v>19.78</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.41</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="10">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C10" t="n">
         <v>8</v>
       </c>
       <c r="D10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E10" t="n">
         <v>0.25</v>
@@ -4693,100 +4693,100 @@
         <v>2.38</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AH10" t="n">
         <v>-1</v>
       </c>
       <c r="AI10" t="n">
-        <v>93.11</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AL10" t="n">
-        <v>4.44</v>
+        <v>4.1</v>
       </c>
       <c r="AM10" t="n">
         <v>-1</v>
       </c>
       <c r="AN10" t="n">
-        <v>46.44</v>
+        <v>46.8</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AP10" t="n">
         <v>-1</v>
       </c>
       <c r="AQ10" t="n">
-        <v>14.11</v>
+        <v>13.9</v>
       </c>
       <c r="AR10" t="n">
-        <v>15.11</v>
+        <v>15</v>
       </c>
       <c r="AS10" t="n">
-        <v>7.56</v>
+        <v>7.5</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>51.67</v>
+        <v>51.6</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA10" t="n">
-        <v>13.33</v>
+        <v>13.6</v>
       </c>
       <c r="BB10" t="n">
-        <v>8.779999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.56</v>
+        <v>5.1</v>
       </c>
       <c r="BD10" t="n">
-        <v>16.11</v>
+        <v>16.6</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.29</v>
+        <v>3.44</v>
       </c>
       <c r="BH10" t="n">
-        <v>8.94</v>
+        <v>8.83</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.29</v>
+        <v>3.44</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.47</v>
+        <v>0.61</v>
       </c>
       <c r="BL10" t="n">
         <v>1</v>
@@ -4798,7 +4798,7 @@
         <v>2</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="BP10" t="n">
         <v>-1</v>
@@ -4810,22 +4810,22 @@
         <v>100</v>
       </c>
       <c r="BS10" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BT10" t="n">
-        <v>52.94</v>
+        <v>55.56</v>
       </c>
       <c r="BU10" t="n">
-        <v>35.29</v>
+        <v>38.89</v>
       </c>
       <c r="BV10" t="n">
-        <v>23.53</v>
+        <v>27.78</v>
       </c>
       <c r="BW10" t="n">
-        <v>17.65</v>
+        <v>22.22</v>
       </c>
       <c r="BX10" t="n">
-        <v>70.59</v>
+        <v>72.22</v>
       </c>
       <c r="BY10" t="n">
         <v>2.07</v>
@@ -4837,22 +4837,22 @@
         <v>3.64</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.78</v>
+        <v>3.79</v>
       </c>
       <c r="CC10" t="n">
-        <v>2.89</v>
+        <v>2.77</v>
       </c>
       <c r="CD10" t="n">
-        <v>3.19</v>
+        <v>3.04</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="CH10" t="n">
         <v>1.3</v>
@@ -4861,28 +4861,28 @@
         <v>1.9</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="CR10" t="n">
         <v>1.38</v>
@@ -4897,106 +4897,106 @@
         <v>1.47</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CY10" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="DB10" t="n">
         <v>1.25</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.23</v>
+        <v>0.28</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="DG10" t="n">
         <v>-1</v>
       </c>
       <c r="DH10" t="n">
-        <v>93.34999999999999</v>
+        <v>93.89</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.47</v>
+        <v>2.39</v>
       </c>
       <c r="DK10" t="n">
-        <v>3.76</v>
+        <v>3.61</v>
       </c>
       <c r="DL10" t="n">
         <v>-1</v>
       </c>
       <c r="DM10" t="n">
-        <v>46.05</v>
+        <v>46.28</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="DO10" t="n">
         <v>-1</v>
       </c>
       <c r="DP10" t="n">
-        <v>14.65</v>
+        <v>14.5</v>
       </c>
       <c r="DQ10" t="n">
-        <v>14.53</v>
+        <v>14.5</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.3</v>
+        <v>7.28</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.23</v>
+        <v>0.28</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.23</v>
+        <v>0.28</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>48.18</v>
+        <v>48.33</v>
       </c>
       <c r="DW10" t="n">
         <v>0.11</v>
       </c>
       <c r="DX10" t="n">
-        <v>14.23</v>
+        <v>14.33</v>
       </c>
       <c r="DY10" t="n">
-        <v>8.94</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="DZ10" t="n">
-        <v>5.29</v>
+        <v>5.55</v>
       </c>
       <c r="EA10" t="n">
-        <v>17</v>
+        <v>17.22</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="11">
@@ -5006,61 +5006,61 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D11" t="n">
         <v>9</v>
       </c>
       <c r="E11" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="F11" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="G11" t="n">
         <v>-1</v>
       </c>
       <c r="H11" t="n">
-        <v>105.62</v>
+        <v>105.44</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="K11" t="n">
-        <v>4.75</v>
+        <v>4.89</v>
       </c>
       <c r="L11" t="n">
         <v>-1</v>
       </c>
       <c r="M11" t="n">
-        <v>48.75</v>
+        <v>49.78</v>
       </c>
       <c r="N11" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="O11" t="n">
         <v>-1</v>
       </c>
       <c r="P11" t="n">
-        <v>14</v>
+        <v>14.11</v>
       </c>
       <c r="Q11" t="n">
-        <v>18.88</v>
+        <v>19.78</v>
       </c>
       <c r="R11" t="n">
-        <v>7.88</v>
+        <v>7.22</v>
       </c>
       <c r="S11" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="T11" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -5072,28 +5072,28 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>47</v>
+        <v>48.11</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="Z11" t="n">
-        <v>10.75</v>
+        <v>10.67</v>
       </c>
       <c r="AA11" t="n">
-        <v>7.88</v>
+        <v>8</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.88</v>
+        <v>2.67</v>
       </c>
       <c r="AC11" t="n">
-        <v>24.88</v>
+        <v>25.78</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AE11" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -5177,31 +5177,31 @@
         <v>2</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="BH11" t="n">
-        <v>8.119999999999999</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="BN11" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="BP11" t="n">
         <v>-1</v>
@@ -5210,16 +5210,16 @@
         <v>-1</v>
       </c>
       <c r="BR11" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BS11" t="n">
-        <v>58.82</v>
+        <v>55.56</v>
       </c>
       <c r="BT11" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BU11" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BV11" t="n">
         <v>0</v>
@@ -5228,19 +5228,19 @@
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BY11" t="n">
-        <v>3.19</v>
+        <v>3.05</v>
       </c>
       <c r="BZ11" t="n">
-        <v>3.34</v>
+        <v>3.18</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.48</v>
+        <v>3.47</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.55</v>
+        <v>3.54</v>
       </c>
       <c r="CC11" t="n">
         <v>5.29</v>
@@ -5252,40 +5252,40 @@
         <v>1.49</v>
       </c>
       <c r="CF11" t="n">
-        <v>3.33</v>
+        <v>3.35</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CJ11" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CK11" t="n">
         <v>1.55</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="CN11" t="n">
         <v>1.81</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CP11" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="CQ11" t="n">
-        <v>4.18</v>
+        <v>4.23</v>
       </c>
       <c r="CR11" t="n">
         <v>1.5</v>
@@ -5294,79 +5294,79 @@
         <v>3.15</v>
       </c>
       <c r="CT11" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="CU11" t="n">
         <v>1.37</v>
       </c>
       <c r="CV11" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CW11" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="DC11" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="DD11" t="n">
-        <v>4.4</v>
+        <v>4.46</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="DG11" t="n">
         <v>-1</v>
       </c>
       <c r="DH11" t="n">
-        <v>108.06</v>
+        <v>107.83</v>
       </c>
       <c r="DI11" t="n">
         <v>0</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.12</v>
+        <v>2.28</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.29</v>
+        <v>4.39</v>
       </c>
       <c r="DL11" t="n">
         <v>-1</v>
       </c>
       <c r="DM11" t="n">
-        <v>48.65</v>
+        <v>49.17</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.53</v>
+        <v>0.62</v>
       </c>
       <c r="DO11" t="n">
         <v>-1</v>
       </c>
       <c r="DP11" t="n">
-        <v>13.77</v>
+        <v>13.84</v>
       </c>
       <c r="DQ11" t="n">
-        <v>18.77</v>
+        <v>19.23</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.18</v>
+        <v>6.89</v>
       </c>
       <c r="DS11" t="n">
         <v>0</v>
@@ -5378,28 +5378,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>47.7</v>
+        <v>48.22</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.12</v>
+        <v>0.16</v>
       </c>
       <c r="DX11" t="n">
-        <v>10.41</v>
+        <v>10.39</v>
       </c>
       <c r="DY11" t="n">
-        <v>7.59</v>
+        <v>7.66</v>
       </c>
       <c r="DZ11" t="n">
-        <v>2.83</v>
+        <v>2.72</v>
       </c>
       <c r="EA11" t="n">
-        <v>23.88</v>
+        <v>24.39</v>
       </c>
       <c r="EB11" t="n">
         <v>1.21</v>
       </c>
       <c r="EC11" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="12">
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C12" t="n">
         <v>9</v>
       </c>
       <c r="D12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -5502,28 +5502,28 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AH12" t="n">
         <v>-1</v>
       </c>
       <c r="AI12" t="n">
-        <v>75.88</v>
+        <v>76.11</v>
       </c>
       <c r="AJ12" t="n">
         <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.88</v>
+        <v>3.11</v>
       </c>
       <c r="AL12" t="n">
-        <v>4.38</v>
+        <v>4.11</v>
       </c>
       <c r="AM12" t="n">
         <v>-1</v>
       </c>
       <c r="AN12" t="n">
-        <v>31.12</v>
+        <v>32</v>
       </c>
       <c r="AO12" t="n">
         <v>1</v>
@@ -5532,79 +5532,79 @@
         <v>-1</v>
       </c>
       <c r="AQ12" t="n">
-        <v>17</v>
+        <v>17.89</v>
       </c>
       <c r="AR12" t="n">
-        <v>14.12</v>
+        <v>14.67</v>
       </c>
       <c r="AS12" t="n">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>39.22</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="BA12" t="n">
         <v>10</v>
       </c>
-      <c r="AT12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>38.75</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>10.12</v>
-      </c>
       <c r="BB12" t="n">
-        <v>6.75</v>
+        <v>6.67</v>
       </c>
       <c r="BC12" t="n">
-        <v>3.38</v>
+        <v>3.33</v>
       </c>
       <c r="BD12" t="n">
-        <v>19.25</v>
+        <v>18.56</v>
       </c>
       <c r="BE12" t="n">
         <v>1.1</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.62</v>
+        <v>2.89</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.29</v>
+        <v>2.22</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.880000000000001</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.29</v>
+        <v>2.22</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.35</v>
+        <v>0.39</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BP12" t="n">
         <v>-1</v>
@@ -5613,25 +5613,25 @@
         <v>-1</v>
       </c>
       <c r="BR12" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BS12" t="n">
-        <v>76.47</v>
+        <v>72.22</v>
       </c>
       <c r="BT12" t="n">
-        <v>47.06</v>
+        <v>44.44</v>
       </c>
       <c r="BU12" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BV12" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BY12" t="n">
         <v>4.28</v>
@@ -5640,169 +5640,169 @@
         <v>4.56</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.98</v>
+        <v>3.94</v>
       </c>
       <c r="CB12" t="n">
-        <v>4.35</v>
+        <v>4.3</v>
       </c>
       <c r="CC12" t="n">
-        <v>7.33</v>
+        <v>7</v>
       </c>
       <c r="CD12" t="n">
-        <v>7.96</v>
+        <v>7.59</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.61</v>
+        <v>2.67</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.94</v>
+        <v>2.91</v>
       </c>
       <c r="CH12" t="n">
         <v>1.37</v>
       </c>
       <c r="CI12" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="CJ12" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="CK12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="CL12" t="n">
         <v>1.84</v>
       </c>
-      <c r="CJ12" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="CK12" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="CL12" t="n">
-        <v>1.81</v>
-      </c>
       <c r="CM12" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="CN12" t="n">
         <v>1.8</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.99</v>
+        <v>3.11</v>
       </c>
       <c r="CR12" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="CS12" t="n">
         <v>2.88</v>
       </c>
       <c r="CT12" t="n">
-        <v>2.88</v>
+        <v>2.79</v>
       </c>
       <c r="CU12" t="n">
         <v>1.44</v>
       </c>
       <c r="CV12" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="CW12" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="CX12" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="CY12" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="CZ12" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="DA12" t="n">
         <v>1.93</v>
       </c>
-      <c r="CX12" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="CY12" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="CZ12" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="DA12" t="n">
-        <v>1.97</v>
-      </c>
       <c r="DB12" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="DC12" t="n">
-        <v>1.98</v>
+        <v>2.03</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.4</v>
+        <v>3.56</v>
       </c>
       <c r="DE12" t="n">
         <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="DG12" t="n">
         <v>-1</v>
       </c>
       <c r="DH12" t="n">
-        <v>83.59</v>
+        <v>83.28</v>
       </c>
       <c r="DI12" t="n">
         <v>0</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.77</v>
+        <v>2.89</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.18</v>
+        <v>4.06</v>
       </c>
       <c r="DL12" t="n">
         <v>-1</v>
       </c>
       <c r="DM12" t="n">
-        <v>38.76</v>
+        <v>38.78</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="DO12" t="n">
         <v>-1</v>
       </c>
       <c r="DP12" t="n">
-        <v>17.12</v>
+        <v>17.56</v>
       </c>
       <c r="DQ12" t="n">
-        <v>14.23</v>
+        <v>14.5</v>
       </c>
       <c r="DR12" t="n">
-        <v>8.529999999999999</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>43.41</v>
+        <v>43.39</v>
       </c>
       <c r="DW12" t="n">
         <v>0.11</v>
       </c>
       <c r="DX12" t="n">
-        <v>11.23</v>
+        <v>11.11</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.24</v>
+        <v>7.17</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4</v>
+        <v>3.94</v>
       </c>
       <c r="EA12" t="n">
-        <v>17.83</v>
+        <v>17.56</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.59</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="13">
@@ -5911,7 +5911,7 @@
         <v>-1</v>
       </c>
       <c r="AI13" t="n">
-        <v>80.89</v>
+        <v>88.56</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
@@ -5926,7 +5926,7 @@
         <v>-1</v>
       </c>
       <c r="AN13" t="n">
-        <v>38.56</v>
+        <v>43.89</v>
       </c>
       <c r="AO13" t="n">
         <v>0.22</v>
@@ -5938,7 +5938,7 @@
         <v>13.33</v>
       </c>
       <c r="AR13" t="n">
-        <v>15.67</v>
+        <v>15.89</v>
       </c>
       <c r="AS13" t="n">
         <v>8.56</v>
@@ -5965,10 +5965,10 @@
         <v>0.11</v>
       </c>
       <c r="BA13" t="n">
-        <v>11.33</v>
+        <v>11.22</v>
       </c>
       <c r="BB13" t="n">
-        <v>7.22</v>
+        <v>7.11</v>
       </c>
       <c r="BC13" t="n">
         <v>4.11</v>
@@ -5977,7 +5977,7 @@
         <v>22.89</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.16</v>
+        <v>1.32</v>
       </c>
       <c r="BF13" t="n">
         <v>1.89</v>
@@ -6142,7 +6142,7 @@
         <v>-1</v>
       </c>
       <c r="DH13" t="n">
-        <v>82.34</v>
+        <v>86.17</v>
       </c>
       <c r="DI13" t="n">
         <v>0.16</v>
@@ -6157,7 +6157,7 @@
         <v>-1</v>
       </c>
       <c r="DM13" t="n">
-        <v>41.28</v>
+        <v>43.94</v>
       </c>
       <c r="DN13" t="n">
         <v>0.78</v>
@@ -6169,7 +6169,7 @@
         <v>14.88</v>
       </c>
       <c r="DQ13" t="n">
-        <v>15.94</v>
+        <v>16.06</v>
       </c>
       <c r="DR13" t="n">
         <v>8.23</v>
@@ -6190,10 +6190,10 @@
         <v>0.06</v>
       </c>
       <c r="DX13" t="n">
-        <v>11.38</v>
+        <v>11.33</v>
       </c>
       <c r="DY13" t="n">
-        <v>7.66</v>
+        <v>7.61</v>
       </c>
       <c r="DZ13" t="n">
         <v>3.72</v>
@@ -6202,7 +6202,7 @@
         <v>22.39</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="EC13" t="n">
         <v>2.34</v>
@@ -6215,94 +6215,94 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D14" t="n">
         <v>9</v>
       </c>
       <c r="E14" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F14" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="G14" t="n">
         <v>-1</v>
       </c>
       <c r="H14" t="n">
-        <v>102.12</v>
+        <v>102.56</v>
       </c>
       <c r="I14" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="J14" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="K14" t="n">
-        <v>3.75</v>
+        <v>4.22</v>
       </c>
       <c r="L14" t="n">
         <v>-1</v>
       </c>
       <c r="M14" t="n">
-        <v>55.5</v>
+        <v>56.11</v>
       </c>
       <c r="N14" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="O14" t="n">
         <v>-1</v>
       </c>
       <c r="P14" t="n">
-        <v>14</v>
+        <v>14.33</v>
       </c>
       <c r="Q14" t="n">
-        <v>17.12</v>
+        <v>17.56</v>
       </c>
       <c r="R14" t="n">
-        <v>5.5</v>
+        <v>5.78</v>
       </c>
       <c r="S14" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="T14" t="n">
-        <v>0.75</v>
+        <v>0.89</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>51.88</v>
+        <v>52.22</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="Z14" t="n">
-        <v>12.38</v>
+        <v>13</v>
       </c>
       <c r="AA14" t="n">
-        <v>8.619999999999999</v>
+        <v>9.44</v>
       </c>
       <c r="AB14" t="n">
-        <v>3.75</v>
+        <v>3.56</v>
       </c>
       <c r="AC14" t="n">
-        <v>21.38</v>
+        <v>21.11</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -6389,28 +6389,28 @@
         <v>1.94</v>
       </c>
       <c r="BH14" t="n">
-        <v>7.41</v>
+        <v>7.61</v>
       </c>
       <c r="BI14" t="n">
         <v>1.94</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.53</v>
+        <v>0.61</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="BP14" t="n">
         <v>-1</v>
@@ -6419,37 +6419,37 @@
         <v>-1</v>
       </c>
       <c r="BR14" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BS14" t="n">
-        <v>47.06</v>
+        <v>50</v>
       </c>
       <c r="BT14" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BU14" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BV14" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BW14" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX14" t="n">
-        <v>41.18</v>
+        <v>38.89</v>
       </c>
       <c r="BY14" t="n">
-        <v>2.37</v>
+        <v>2.34</v>
       </c>
       <c r="BZ14" t="n">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.63</v>
+        <v>3.59</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.71</v>
+        <v>3.68</v>
       </c>
       <c r="CC14" t="n">
         <v>4.18</v>
@@ -6461,40 +6461,40 @@
         <v>1.4</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.99</v>
+        <v>2.97</v>
       </c>
       <c r="CH14" t="n">
         <v>1.42</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.39</v>
+        <v>3.45</v>
       </c>
       <c r="CR14" t="n">
         <v>1.38</v>
@@ -6509,10 +6509,10 @@
         <v>1.47</v>
       </c>
       <c r="CV14" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="CX14" t="n">
         <v>1.63</v>
@@ -6539,76 +6539,76 @@
         <v>0.06</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="DG14" t="n">
         <v>-1</v>
       </c>
       <c r="DH14" t="n">
-        <v>96.41</v>
+        <v>96.94</v>
       </c>
       <c r="DI14" t="n">
         <v>0.11</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="DK14" t="n">
-        <v>3.82</v>
+        <v>4.06</v>
       </c>
       <c r="DL14" t="n">
         <v>-1</v>
       </c>
       <c r="DM14" t="n">
-        <v>51.3</v>
+        <v>51.84</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="DO14" t="n">
         <v>-1</v>
       </c>
       <c r="DP14" t="n">
-        <v>14.65</v>
+        <v>14.78</v>
       </c>
       <c r="DQ14" t="n">
-        <v>17.29</v>
+        <v>17.5</v>
       </c>
       <c r="DR14" t="n">
-        <v>6.12</v>
+        <v>6.22</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>49.88</v>
+        <v>50.16</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.12</v>
+        <v>0.16</v>
       </c>
       <c r="DX14" t="n">
-        <v>12.12</v>
+        <v>12.44</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.23</v>
+        <v>8.66</v>
       </c>
       <c r="DZ14" t="n">
-        <v>3.88</v>
+        <v>3.78</v>
       </c>
       <c r="EA14" t="n">
-        <v>21.35</v>
+        <v>21.22</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="15">
@@ -6618,13 +6618,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C15" t="n">
         <v>9</v>
       </c>
       <c r="D15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -6711,49 +6711,49 @@
         <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AH15" t="n">
         <v>-1</v>
       </c>
       <c r="AI15" t="n">
-        <v>80.88</v>
+        <v>79.78</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AL15" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AM15" t="n">
         <v>-1</v>
       </c>
       <c r="AN15" t="n">
-        <v>39.62</v>
+        <v>37.78</v>
       </c>
       <c r="AO15" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AP15" t="n">
         <v>-1</v>
       </c>
       <c r="AQ15" t="n">
-        <v>17.75</v>
+        <v>17.89</v>
       </c>
       <c r="AR15" t="n">
-        <v>13.12</v>
+        <v>13.67</v>
       </c>
       <c r="AS15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AV15" t="n">
         <v>0</v>
@@ -6765,55 +6765,55 @@
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>40.62</v>
+        <v>41.11</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>10.75</v>
+        <v>10.56</v>
       </c>
       <c r="BB15" t="n">
-        <v>7.75</v>
+        <v>7.78</v>
       </c>
       <c r="BC15" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>16.89</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BF15" t="n">
         <v>3</v>
       </c>
-      <c r="BD15" t="n">
-        <v>17.12</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>2.88</v>
-      </c>
       <c r="BG15" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="BH15" t="n">
-        <v>7.76</v>
+        <v>7.94</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.71</v>
+        <v>0.78</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="BO15" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BP15" t="n">
         <v>-1</v>
@@ -6822,25 +6822,25 @@
         <v>-1</v>
       </c>
       <c r="BR15" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BS15" t="n">
-        <v>52.94</v>
+        <v>55.56</v>
       </c>
       <c r="BT15" t="n">
-        <v>35.29</v>
+        <v>33.33</v>
       </c>
       <c r="BU15" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BV15" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BW15" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX15" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BY15" t="n">
         <v>2.76</v>
@@ -6849,55 +6849,55 @@
         <v>3</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.51</v>
+        <v>3.47</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.7</v>
+        <v>3.67</v>
       </c>
       <c r="CC15" t="n">
-        <v>4.55</v>
+        <v>4.42</v>
       </c>
       <c r="CD15" t="n">
-        <v>4.97</v>
+        <v>4.84</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.99</v>
+        <v>3.01</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.42</v>
+        <v>2.39</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="CO15" t="n">
         <v>1.33</v>
       </c>
       <c r="CP15" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.56</v>
+        <v>3.61</v>
       </c>
       <c r="CR15" t="n">
         <v>1.39</v>
@@ -6912,10 +6912,10 @@
         <v>1.42</v>
       </c>
       <c r="CV15" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="CX15" t="n">
         <v>1.57</v>
@@ -6942,76 +6942,76 @@
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="DG15" t="n">
         <v>-1</v>
       </c>
       <c r="DH15" t="n">
-        <v>84.42</v>
+        <v>83.67</v>
       </c>
       <c r="DI15" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="DK15" t="n">
-        <v>4.47</v>
+        <v>4.39</v>
       </c>
       <c r="DL15" t="n">
         <v>-1</v>
       </c>
       <c r="DM15" t="n">
-        <v>39.47</v>
+        <v>38.56</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.76</v>
+        <v>0.83</v>
       </c>
       <c r="DO15" t="n">
         <v>-1</v>
       </c>
       <c r="DP15" t="n">
-        <v>16.53</v>
+        <v>16.67</v>
       </c>
       <c r="DQ15" t="n">
-        <v>13.88</v>
+        <v>14.12</v>
       </c>
       <c r="DR15" t="n">
-        <v>8.119999999999999</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>40.76</v>
+        <v>41</v>
       </c>
       <c r="DW15" t="n">
         <v>0.06</v>
       </c>
       <c r="DX15" t="n">
-        <v>10.53</v>
+        <v>10.44</v>
       </c>
       <c r="DY15" t="n">
-        <v>7.41</v>
+        <v>7.44</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="EA15" t="n">
-        <v>19.17</v>
+        <v>18.94</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="16">
@@ -7021,94 +7021,94 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D16" t="n">
         <v>8</v>
       </c>
       <c r="E16" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F16" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="G16" t="n">
         <v>-1</v>
       </c>
       <c r="H16" t="n">
-        <v>101.44</v>
+        <v>100.4</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="K16" t="n">
-        <v>5.22</v>
+        <v>5.2</v>
       </c>
       <c r="L16" t="n">
         <v>-1</v>
       </c>
       <c r="M16" t="n">
-        <v>50.56</v>
+        <v>50.1</v>
       </c>
       <c r="N16" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="O16" t="n">
         <v>-1</v>
       </c>
       <c r="P16" t="n">
-        <v>15.22</v>
+        <v>15.6</v>
       </c>
       <c r="Q16" t="n">
-        <v>15.44</v>
+        <v>16.3</v>
       </c>
       <c r="R16" t="n">
-        <v>6.67</v>
+        <v>6.8</v>
       </c>
       <c r="S16" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="T16" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="U16" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="V16" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>60.22</v>
+        <v>60</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="Z16" t="n">
-        <v>13.11</v>
+        <v>12.6</v>
       </c>
       <c r="AA16" t="n">
-        <v>9.109999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="AB16" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="AC16" t="n">
-        <v>22.78</v>
+        <v>22.8</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -7192,31 +7192,31 @@
         <v>2.38</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="BH16" t="n">
-        <v>9.119999999999999</v>
+        <v>9</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="BP16" t="n">
         <v>-1</v>
@@ -7228,34 +7228,34 @@
         <v>100</v>
       </c>
       <c r="BS16" t="n">
-        <v>76.47</v>
+        <v>77.78</v>
       </c>
       <c r="BT16" t="n">
-        <v>58.82</v>
+        <v>55.56</v>
       </c>
       <c r="BU16" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BV16" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BW16" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX16" t="n">
-        <v>58.82</v>
+        <v>61.11</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="BZ16" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.91</v>
+        <v>3.87</v>
       </c>
       <c r="CB16" t="n">
-        <v>4.21</v>
+        <v>4.18</v>
       </c>
       <c r="CC16" t="n">
         <v>2.33</v>
@@ -7267,19 +7267,19 @@
         <v>1.37</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="CH16" t="n">
         <v>1.47</v>
       </c>
       <c r="CI16" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CK16" t="n">
         <v>1.44</v>
@@ -7297,10 +7297,10 @@
         <v>1.26</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CQ16" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="CR16" t="n">
         <v>1.41</v>
@@ -7315,10 +7315,10 @@
         <v>1.45</v>
       </c>
       <c r="CV16" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CX16" t="n">
         <v>1.54</v>
@@ -7345,73 +7345,73 @@
         <v>0.06</v>
       </c>
       <c r="DF16" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="DG16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="DH16" t="n">
+        <v>96.94</v>
+      </c>
+      <c r="DI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ16" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="DK16" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="DL16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="DM16" t="n">
+        <v>49.11</v>
+      </c>
+      <c r="DN16" t="n">
         <v>1.11</v>
       </c>
-      <c r="DG16" t="n">
-        <v>-1</v>
-      </c>
-      <c r="DH16" t="n">
-        <v>97.29000000000001</v>
-      </c>
-      <c r="DI16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ16" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="DK16" t="n">
-        <v>5.41</v>
-      </c>
-      <c r="DL16" t="n">
-        <v>-1</v>
-      </c>
-      <c r="DM16" t="n">
-        <v>49.3</v>
-      </c>
-      <c r="DN16" t="n">
-        <v>1.18</v>
-      </c>
       <c r="DO16" t="n">
         <v>-1</v>
       </c>
       <c r="DP16" t="n">
-        <v>16</v>
+        <v>16.17</v>
       </c>
       <c r="DQ16" t="n">
-        <v>15.7</v>
+        <v>16.17</v>
       </c>
       <c r="DR16" t="n">
-        <v>6.3</v>
+        <v>6.39</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>61.71</v>
+        <v>61.5</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DX16" t="n">
-        <v>13.18</v>
+        <v>12.89</v>
       </c>
       <c r="DY16" t="n">
-        <v>9.109999999999999</v>
+        <v>9</v>
       </c>
       <c r="DZ16" t="n">
-        <v>4.06</v>
+        <v>3.89</v>
       </c>
       <c r="EA16" t="n">
-        <v>21.12</v>
+        <v>21.22</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="EC16" t="n">
         <v>2.06</v>
@@ -7424,94 +7424,94 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D17" t="n">
         <v>9</v>
       </c>
       <c r="E17" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F17" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="G17" t="n">
         <v>-1</v>
       </c>
       <c r="H17" t="n">
-        <v>92.38</v>
+        <v>92</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="K17" t="n">
-        <v>6.12</v>
+        <v>5.89</v>
       </c>
       <c r="L17" t="n">
         <v>-1</v>
       </c>
       <c r="M17" t="n">
-        <v>50.25</v>
+        <v>51</v>
       </c>
       <c r="N17" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="O17" t="n">
         <v>-1</v>
       </c>
       <c r="P17" t="n">
-        <v>9.880000000000001</v>
+        <v>9.44</v>
       </c>
       <c r="Q17" t="n">
-        <v>18.88</v>
+        <v>18.67</v>
       </c>
       <c r="R17" t="n">
-        <v>4.62</v>
+        <v>4.78</v>
       </c>
       <c r="S17" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="U17" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="V17" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>60.88</v>
+        <v>62</v>
       </c>
       <c r="Y17" t="n">
         <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>14.38</v>
+        <v>14.44</v>
       </c>
       <c r="AA17" t="n">
-        <v>7.75</v>
+        <v>7.89</v>
       </c>
       <c r="AB17" t="n">
-        <v>6.62</v>
+        <v>6.56</v>
       </c>
       <c r="AC17" t="n">
-        <v>19.25</v>
+        <v>18.78</v>
       </c>
       <c r="AD17" t="n">
         <v>1.74</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -7595,31 +7595,31 @@
         <v>1.44</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.470000000000001</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.59</v>
+        <v>0.67</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="BP17" t="n">
         <v>-1</v>
@@ -7628,37 +7628,37 @@
         <v>-1</v>
       </c>
       <c r="BR17" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS17" t="n">
-        <v>82.34999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT17" t="n">
-        <v>41.18</v>
+        <v>38.89</v>
       </c>
       <c r="BU17" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BV17" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BW17" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX17" t="n">
-        <v>47.06</v>
+        <v>44.44</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="BZ17" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CA17" t="n">
-        <v>4.71</v>
+        <v>4.82</v>
       </c>
       <c r="CB17" t="n">
-        <v>5.03</v>
+        <v>5.1</v>
       </c>
       <c r="CC17" t="n">
         <v>1.76</v>
@@ -7670,25 +7670,25 @@
         <v>1.35</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.69</v>
+        <v>2.67</v>
       </c>
       <c r="CG17" t="n">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="CH17" t="n">
         <v>1.49</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="CJ17" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CK17" t="n">
         <v>1.45</v>
       </c>
       <c r="CL17" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CM17" t="n">
         <v>2.61</v>
@@ -7700,10 +7700,10 @@
         <v>1.25</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CQ17" t="n">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="CR17" t="n">
         <v>1.42</v>
@@ -7718,10 +7718,10 @@
         <v>1.51</v>
       </c>
       <c r="CV17" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CW17" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CX17" t="n">
         <v>1.55</v>
@@ -7739,85 +7739,85 @@
         <v>1.28</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.15</v>
+        <v>3.12</v>
       </c>
       <c r="DE17" t="n">
         <v>0.06</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="DG17" t="n">
         <v>-1</v>
       </c>
       <c r="DH17" t="n">
-        <v>94</v>
+        <v>93.72</v>
       </c>
       <c r="DI17" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ17" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.94</v>
+        <v>5.84</v>
       </c>
       <c r="DL17" t="n">
         <v>-1</v>
       </c>
       <c r="DM17" t="n">
-        <v>51.59</v>
+        <v>51.89</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DO17" t="n">
         <v>-1</v>
       </c>
       <c r="DP17" t="n">
-        <v>9.890000000000001</v>
+        <v>9.66</v>
       </c>
       <c r="DQ17" t="n">
-        <v>20.83</v>
+        <v>20.62</v>
       </c>
       <c r="DR17" t="n">
-        <v>5.76</v>
+        <v>5.78</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>60.89</v>
+        <v>61.44</v>
       </c>
       <c r="DW17" t="n">
         <v>0.06</v>
       </c>
       <c r="DX17" t="n">
-        <v>12.29</v>
+        <v>12.44</v>
       </c>
       <c r="DY17" t="n">
-        <v>6.88</v>
+        <v>7</v>
       </c>
       <c r="DZ17" t="n">
-        <v>5.41</v>
+        <v>5.44</v>
       </c>
       <c r="EA17" t="n">
-        <v>19.47</v>
+        <v>19.23</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Russian_Premier_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Russian_Premier_League_2025-2026.xlsx
@@ -1911,7 +1911,7 @@
         <v>13.11</v>
       </c>
       <c r="AS3" t="n">
-        <v>7.78</v>
+        <v>7.89</v>
       </c>
       <c r="AT3" t="n">
         <v>1.33</v>
@@ -1944,7 +1944,7 @@
         <v>3.11</v>
       </c>
       <c r="BD3" t="n">
-        <v>17.56</v>
+        <v>17.67</v>
       </c>
       <c r="BE3" t="n">
         <v>1.18</v>
@@ -2142,7 +2142,7 @@
         <v>14.34</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.39</v>
+        <v>7.44</v>
       </c>
       <c r="DS3" t="n">
         <v>0.16</v>
@@ -2169,7 +2169,7 @@
         <v>3.84</v>
       </c>
       <c r="EA3" t="n">
-        <v>18.28</v>
+        <v>18.34</v>
       </c>
       <c r="EB3" t="n">
         <v>1.28</v>
@@ -2717,7 +2717,7 @@
         <v>13.11</v>
       </c>
       <c r="AS5" t="n">
-        <v>11.11</v>
+        <v>11</v>
       </c>
       <c r="AT5" t="n">
         <v>1.22</v>
@@ -2735,7 +2735,7 @@
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>52</v>
+        <v>51.89</v>
       </c>
       <c r="AZ5" t="n">
         <v>0.33</v>
@@ -2948,7 +2948,7 @@
         <v>15.39</v>
       </c>
       <c r="DR5" t="n">
-        <v>9.720000000000001</v>
+        <v>9.66</v>
       </c>
       <c r="DS5" t="n">
         <v>0.28</v>
@@ -2960,7 +2960,7 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>55.11</v>
+        <v>55.06</v>
       </c>
       <c r="DW5" t="n">
         <v>0.16</v>
@@ -3839,7 +3839,7 @@
         <v>-1</v>
       </c>
       <c r="P8" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="Q8" t="n">
         <v>16.1</v>
@@ -3863,25 +3863,25 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>59.2</v>
+        <v>59.3</v>
       </c>
       <c r="Y8" t="n">
         <v>0.3</v>
       </c>
       <c r="Z8" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="AA8" t="n">
         <v>13.7</v>
       </c>
       <c r="AB8" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AC8" t="n">
         <v>21.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AE8" t="n">
         <v>2.6</v>
@@ -4151,7 +4151,7 @@
         <v>-1</v>
       </c>
       <c r="DP8" t="n">
-        <v>13.55</v>
+        <v>13.61</v>
       </c>
       <c r="DQ8" t="n">
         <v>17.61</v>
@@ -4169,25 +4169,25 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>58.17</v>
+        <v>58.22</v>
       </c>
       <c r="DW8" t="n">
         <v>0.22</v>
       </c>
       <c r="DX8" t="n">
-        <v>16.33</v>
+        <v>16.28</v>
       </c>
       <c r="DY8" t="n">
         <v>11.5</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.83</v>
+        <v>4.78</v>
       </c>
       <c r="EA8" t="n">
         <v>21.72</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="EC8" t="n">
         <v>2.16</v>
@@ -7102,7 +7102,7 @@
         <v>3.7</v>
       </c>
       <c r="AC16" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="AD16" t="n">
         <v>1.42</v>
@@ -7408,7 +7408,7 @@
         <v>3.89</v>
       </c>
       <c r="EA16" t="n">
-        <v>21.22</v>
+        <v>21.28</v>
       </c>
       <c r="EB16" t="n">
         <v>1.44</v>
@@ -7496,19 +7496,19 @@
         <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>14.44</v>
+        <v>14.56</v>
       </c>
       <c r="AA17" t="n">
-        <v>7.89</v>
+        <v>8</v>
       </c>
       <c r="AB17" t="n">
         <v>6.56</v>
       </c>
       <c r="AC17" t="n">
-        <v>18.78</v>
+        <v>18.89</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AE17" t="n">
         <v>1.44</v>
@@ -7802,16 +7802,16 @@
         <v>0.06</v>
       </c>
       <c r="DX17" t="n">
-        <v>12.44</v>
+        <v>12.5</v>
       </c>
       <c r="DY17" t="n">
-        <v>7</v>
+        <v>7.06</v>
       </c>
       <c r="DZ17" t="n">
         <v>5.44</v>
       </c>
       <c r="EA17" t="n">
-        <v>19.23</v>
+        <v>19.28</v>
       </c>
       <c r="EB17" t="n">
         <v>1.55</v>

--- a/data/teams/leagues/Averages_Russian_Premier_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Russian_Premier_League_2025-2026.xlsx
@@ -1445,25 +1445,25 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>46.67</v>
+        <v>46.78</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>14.56</v>
+        <v>14.33</v>
       </c>
       <c r="AA2" t="n">
-        <v>9.779999999999999</v>
+        <v>9.56</v>
       </c>
       <c r="AB2" t="n">
         <v>4.78</v>
       </c>
       <c r="AC2" t="n">
-        <v>23</v>
+        <v>23.11</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AE2" t="n">
         <v>1.78</v>
@@ -1526,7 +1526,7 @@
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>46.56</v>
+        <v>46.33</v>
       </c>
       <c r="AZ2" t="n">
         <v>0.67</v>
@@ -1535,16 +1535,16 @@
         <v>10.78</v>
       </c>
       <c r="BB2" t="n">
-        <v>7.78</v>
+        <v>7.89</v>
       </c>
       <c r="BC2" t="n">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="BD2" t="n">
         <v>21.56</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="BF2" t="n">
         <v>1.67</v>
@@ -1751,25 +1751,25 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>46.62</v>
+        <v>46.56</v>
       </c>
       <c r="DW2" t="n">
         <v>0.34</v>
       </c>
       <c r="DX2" t="n">
-        <v>12.67</v>
+        <v>12.56</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.779999999999999</v>
+        <v>8.73</v>
       </c>
       <c r="DZ2" t="n">
-        <v>3.89</v>
+        <v>3.84</v>
       </c>
       <c r="EA2" t="n">
-        <v>22.28</v>
+        <v>22.33</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="EC2" t="n">
         <v>1.72</v>
@@ -1875,7 +1875,7 @@
         <v>0.11</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="AH3" t="n">
         <v>-1</v>
@@ -1887,7 +1887,7 @@
         <v>0.11</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.56</v>
+        <v>2.44</v>
       </c>
       <c r="AL3" t="n">
         <v>4.22</v>
@@ -1929,7 +1929,7 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>41.11</v>
+        <v>41.22</v>
       </c>
       <c r="AZ3" t="n">
         <v>0.11</v>
@@ -1950,7 +1950,7 @@
         <v>1.18</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.33</v>
+        <v>2.22</v>
       </c>
       <c r="BG3" t="n">
         <v>2.67</v>
@@ -2106,7 +2106,7 @@
         <v>0.06</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="DG3" t="n">
         <v>-1</v>
@@ -2118,7 +2118,7 @@
         <v>0.16</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="DK3" t="n">
         <v>4.16</v>
@@ -2154,7 +2154,7 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>43.56</v>
+        <v>43.61</v>
       </c>
       <c r="DW3" t="n">
         <v>0.06</v>
@@ -2175,7 +2175,7 @@
         <v>1.28</v>
       </c>
       <c r="EC3" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="4">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>43.33</v>
+        <v>43.22</v>
       </c>
       <c r="Y4" t="n">
         <v>0.11</v>
@@ -2338,10 +2338,10 @@
         <v>0.11</v>
       </c>
       <c r="BA4" t="n">
-        <v>12.56</v>
+        <v>12.67</v>
       </c>
       <c r="BB4" t="n">
-        <v>8.109999999999999</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="BC4" t="n">
         <v>4.44</v>
@@ -2557,16 +2557,16 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>45.78</v>
+        <v>45.72</v>
       </c>
       <c r="DW4" t="n">
         <v>0.11</v>
       </c>
       <c r="DX4" t="n">
-        <v>12.73</v>
+        <v>12.78</v>
       </c>
       <c r="DY4" t="n">
-        <v>8.5</v>
+        <v>8.56</v>
       </c>
       <c r="DZ4" t="n">
         <v>4.22</v>
@@ -2660,10 +2660,10 @@
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>14.56</v>
+        <v>14.44</v>
       </c>
       <c r="AA5" t="n">
-        <v>9.109999999999999</v>
+        <v>9</v>
       </c>
       <c r="AB5" t="n">
         <v>5.44</v>
@@ -2672,7 +2672,7 @@
         <v>20.78</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AE5" t="n">
         <v>1.89</v>
@@ -2735,16 +2735,16 @@
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>51.89</v>
+        <v>52</v>
       </c>
       <c r="AZ5" t="n">
         <v>0.33</v>
       </c>
       <c r="BA5" t="n">
-        <v>12.33</v>
+        <v>12.22</v>
       </c>
       <c r="BB5" t="n">
-        <v>8.33</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="BC5" t="n">
         <v>4</v>
@@ -2753,7 +2753,7 @@
         <v>21</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="BF5" t="n">
         <v>2.22</v>
@@ -2960,16 +2960,16 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>55.06</v>
+        <v>55.11</v>
       </c>
       <c r="DW5" t="n">
         <v>0.16</v>
       </c>
       <c r="DX5" t="n">
-        <v>13.44</v>
+        <v>13.33</v>
       </c>
       <c r="DY5" t="n">
-        <v>8.720000000000001</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="DZ5" t="n">
         <v>4.72</v>
@@ -2978,7 +2978,7 @@
         <v>20.89</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="EC5" t="n">
         <v>2.05</v>
@@ -3018,7 +3018,7 @@
         <v>1.56</v>
       </c>
       <c r="K6" t="n">
-        <v>5.67</v>
+        <v>6.11</v>
       </c>
       <c r="L6" t="n">
         <v>-1</v>
@@ -3033,7 +3033,7 @@
         <v>-1</v>
       </c>
       <c r="P6" t="n">
-        <v>12.44</v>
+        <v>12.78</v>
       </c>
       <c r="Q6" t="n">
         <v>17.78</v>
@@ -3057,25 +3057,25 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>58</v>
+        <v>57.89</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>16.44</v>
+        <v>17.11</v>
       </c>
       <c r="AA6" t="n">
-        <v>10.67</v>
+        <v>11.22</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.78</v>
+        <v>5.89</v>
       </c>
       <c r="AC6" t="n">
-        <v>21.44</v>
+        <v>21.67</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AE6" t="n">
         <v>1.56</v>
@@ -3144,19 +3144,19 @@
         <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>14</v>
+        <v>14.33</v>
       </c>
       <c r="BB6" t="n">
-        <v>10.67</v>
+        <v>10.78</v>
       </c>
       <c r="BC6" t="n">
-        <v>3.33</v>
+        <v>3.56</v>
       </c>
       <c r="BD6" t="n">
         <v>22.11</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="BF6" t="n">
         <v>2.44</v>
@@ -3165,7 +3165,7 @@
         <v>2.94</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.390000000000001</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="BI6" t="n">
         <v>2.94</v>
@@ -3330,7 +3330,7 @@
         <v>2</v>
       </c>
       <c r="DK6" t="n">
-        <v>5.17</v>
+        <v>5.39</v>
       </c>
       <c r="DL6" t="n">
         <v>-1</v>
@@ -3345,7 +3345,7 @@
         <v>-1</v>
       </c>
       <c r="DP6" t="n">
-        <v>13.66</v>
+        <v>13.84</v>
       </c>
       <c r="DQ6" t="n">
         <v>16.89</v>
@@ -3363,25 +3363,25 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>55</v>
+        <v>54.94</v>
       </c>
       <c r="DW6" t="n">
         <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>15.22</v>
+        <v>15.72</v>
       </c>
       <c r="DY6" t="n">
-        <v>10.67</v>
+        <v>11</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.56</v>
+        <v>4.72</v>
       </c>
       <c r="EA6" t="n">
-        <v>21.78</v>
+        <v>21.89</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="EC6" t="n">
         <v>2</v>
@@ -3475,7 +3475,7 @@
         <v>2.44</v>
       </c>
       <c r="AC7" t="n">
-        <v>17.44</v>
+        <v>17.56</v>
       </c>
       <c r="AD7" t="n">
         <v>0.97</v>
@@ -3487,7 +3487,7 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="AH7" t="n">
         <v>-1</v>
@@ -3499,7 +3499,7 @@
         <v>0.11</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.44</v>
+        <v>2.56</v>
       </c>
       <c r="AL7" t="n">
         <v>2.56</v>
@@ -3541,7 +3541,7 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>47.11</v>
+        <v>47</v>
       </c>
       <c r="AZ7" t="n">
         <v>0.11</v>
@@ -3562,7 +3562,7 @@
         <v>0.93</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.33</v>
+        <v>2.44</v>
       </c>
       <c r="BG7" t="n">
         <v>3.17</v>
@@ -3718,7 +3718,7 @@
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="DG7" t="n">
         <v>-1</v>
@@ -3730,7 +3730,7 @@
         <v>0.11</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="DK7" t="n">
         <v>3.44</v>
@@ -3766,7 +3766,7 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>46.94</v>
+        <v>46.89</v>
       </c>
       <c r="DW7" t="n">
         <v>0.06</v>
@@ -3781,13 +3781,13 @@
         <v>2.5</v>
       </c>
       <c r="EA7" t="n">
-        <v>18.22</v>
+        <v>18.28</v>
       </c>
       <c r="EB7" t="n">
         <v>0.95</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="8">
@@ -3890,7 +3890,7 @@
         <v>0.25</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AH8" t="n">
         <v>-1</v>
@@ -3902,7 +3902,7 @@
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AL8" t="n">
         <v>4.25</v>
@@ -3950,10 +3950,10 @@
         <v>0.12</v>
       </c>
       <c r="BA8" t="n">
-        <v>13</v>
+        <v>12.88</v>
       </c>
       <c r="BB8" t="n">
-        <v>8.75</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="BC8" t="n">
         <v>4.25</v>
@@ -3965,7 +3965,7 @@
         <v>1.4</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="BG8" t="n">
         <v>2.72</v>
@@ -4121,7 +4121,7 @@
         <v>0.11</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="DG8" t="n">
         <v>-1</v>
@@ -4133,7 +4133,7 @@
         <v>0.11</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="DK8" t="n">
         <v>5.33</v>
@@ -4175,10 +4175,10 @@
         <v>0.22</v>
       </c>
       <c r="DX8" t="n">
-        <v>16.28</v>
+        <v>16.22</v>
       </c>
       <c r="DY8" t="n">
-        <v>11.5</v>
+        <v>11.44</v>
       </c>
       <c r="DZ8" t="n">
         <v>4.78</v>
@@ -4190,7 +4190,7 @@
         <v>1.69</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="9">
@@ -4323,7 +4323,7 @@
         <v>-1</v>
       </c>
       <c r="AQ9" t="n">
-        <v>14.8</v>
+        <v>14.7</v>
       </c>
       <c r="AR9" t="n">
         <v>13.9</v>
@@ -4353,19 +4353,19 @@
         <v>0</v>
       </c>
       <c r="BA9" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BB9" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BC9" t="n">
         <v>2.4</v>
       </c>
       <c r="BD9" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="BF9" t="n">
         <v>2.9</v>
@@ -4554,7 +4554,7 @@
         <v>-1</v>
       </c>
       <c r="DP9" t="n">
-        <v>14.5</v>
+        <v>14.44</v>
       </c>
       <c r="DQ9" t="n">
         <v>14.28</v>
@@ -4578,16 +4578,16 @@
         <v>0.05</v>
       </c>
       <c r="DX9" t="n">
-        <v>8.279999999999999</v>
+        <v>8.17</v>
       </c>
       <c r="DY9" t="n">
-        <v>5.72</v>
+        <v>5.61</v>
       </c>
       <c r="DZ9" t="n">
         <v>2.56</v>
       </c>
       <c r="EA9" t="n">
-        <v>19.78</v>
+        <v>19.72</v>
       </c>
       <c r="EB9" t="n">
         <v>0.95</v>
@@ -4726,7 +4726,7 @@
         <v>-1</v>
       </c>
       <c r="AQ10" t="n">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="AR10" t="n">
         <v>15</v>
@@ -4756,19 +4756,19 @@
         <v>0.1</v>
       </c>
       <c r="BA10" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="BB10" t="n">
         <v>8.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BD10" t="n">
         <v>16.6</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="BF10" t="n">
         <v>2.2</v>
@@ -4957,7 +4957,7 @@
         <v>-1</v>
       </c>
       <c r="DP10" t="n">
-        <v>14.5</v>
+        <v>14.56</v>
       </c>
       <c r="DQ10" t="n">
         <v>14.5</v>
@@ -4981,19 +4981,19 @@
         <v>0.11</v>
       </c>
       <c r="DX10" t="n">
-        <v>14.33</v>
+        <v>14.39</v>
       </c>
       <c r="DY10" t="n">
         <v>8.779999999999999</v>
       </c>
       <c r="DZ10" t="n">
-        <v>5.55</v>
+        <v>5.61</v>
       </c>
       <c r="EA10" t="n">
         <v>17.22</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="EC10" t="n">
         <v>2.28</v>
@@ -5018,7 +5018,7 @@
         <v>0.22</v>
       </c>
       <c r="F11" t="n">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="G11" t="n">
         <v>-1</v>
@@ -5030,7 +5030,7 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>2.33</v>
+        <v>2.44</v>
       </c>
       <c r="K11" t="n">
         <v>4.89</v>
@@ -5087,13 +5087,13 @@
         <v>2.67</v>
       </c>
       <c r="AC11" t="n">
-        <v>25.78</v>
+        <v>25.67</v>
       </c>
       <c r="AD11" t="n">
         <v>1.23</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.11</v>
+        <v>2.22</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
         <v>18.67</v>
       </c>
       <c r="AS11" t="n">
-        <v>6.56</v>
+        <v>6.67</v>
       </c>
       <c r="AT11" t="n">
         <v>1.67</v>
@@ -5153,7 +5153,7 @@
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>48.33</v>
+        <v>48.44</v>
       </c>
       <c r="AZ11" t="n">
         <v>0.22</v>
@@ -5180,7 +5180,7 @@
         <v>1.61</v>
       </c>
       <c r="BH11" t="n">
-        <v>8.109999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BI11" t="n">
         <v>1.61</v>
@@ -5330,7 +5330,7 @@
         <v>0.11</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="DG11" t="n">
         <v>-1</v>
@@ -5342,7 +5342,7 @@
         <v>0</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.28</v>
+        <v>2.33</v>
       </c>
       <c r="DK11" t="n">
         <v>4.39</v>
@@ -5366,7 +5366,7 @@
         <v>19.23</v>
       </c>
       <c r="DR11" t="n">
-        <v>6.89</v>
+        <v>6.94</v>
       </c>
       <c r="DS11" t="n">
         <v>0</v>
@@ -5378,7 +5378,7 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>48.22</v>
+        <v>48.28</v>
       </c>
       <c r="DW11" t="n">
         <v>0.16</v>
@@ -5393,13 +5393,13 @@
         <v>2.72</v>
       </c>
       <c r="EA11" t="n">
-        <v>24.39</v>
+        <v>24.34</v>
       </c>
       <c r="EB11" t="n">
         <v>1.21</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="12">
@@ -5451,7 +5451,7 @@
         <v>-1</v>
       </c>
       <c r="P12" t="n">
-        <v>17.22</v>
+        <v>17.11</v>
       </c>
       <c r="Q12" t="n">
         <v>14.33</v>
@@ -5475,16 +5475,16 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>47.56</v>
+        <v>47.33</v>
       </c>
       <c r="Y12" t="n">
         <v>0.11</v>
       </c>
       <c r="Z12" t="n">
-        <v>12.22</v>
+        <v>12.33</v>
       </c>
       <c r="AA12" t="n">
-        <v>7.67</v>
+        <v>7.78</v>
       </c>
       <c r="AB12" t="n">
         <v>4.56</v>
@@ -5493,7 +5493,7 @@
         <v>16.56</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AE12" t="n">
         <v>2.56</v>
@@ -5562,10 +5562,10 @@
         <v>0.11</v>
       </c>
       <c r="BA12" t="n">
-        <v>10</v>
+        <v>10.11</v>
       </c>
       <c r="BB12" t="n">
-        <v>6.67</v>
+        <v>6.78</v>
       </c>
       <c r="BC12" t="n">
         <v>3.33</v>
@@ -5574,7 +5574,7 @@
         <v>18.56</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="BF12" t="n">
         <v>2.89</v>
@@ -5763,7 +5763,7 @@
         <v>-1</v>
       </c>
       <c r="DP12" t="n">
-        <v>17.56</v>
+        <v>17.5</v>
       </c>
       <c r="DQ12" t="n">
         <v>14.5</v>
@@ -5781,16 +5781,16 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>43.39</v>
+        <v>43.28</v>
       </c>
       <c r="DW12" t="n">
         <v>0.11</v>
       </c>
       <c r="DX12" t="n">
-        <v>11.11</v>
+        <v>11.22</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.17</v>
+        <v>7.28</v>
       </c>
       <c r="DZ12" t="n">
         <v>3.94</v>
@@ -5799,7 +5799,7 @@
         <v>17.56</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="EC12" t="n">
         <v>2.72</v>
@@ -5884,10 +5884,10 @@
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>11.44</v>
+        <v>11.56</v>
       </c>
       <c r="AA13" t="n">
-        <v>8.109999999999999</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="AB13" t="n">
         <v>3.33</v>
@@ -5935,7 +5935,7 @@
         <v>-1</v>
       </c>
       <c r="AQ13" t="n">
-        <v>13.33</v>
+        <v>13.44</v>
       </c>
       <c r="AR13" t="n">
         <v>15.89</v>
@@ -5965,19 +5965,19 @@
         <v>0.11</v>
       </c>
       <c r="BA13" t="n">
-        <v>11.22</v>
+        <v>11.56</v>
       </c>
       <c r="BB13" t="n">
-        <v>7.11</v>
+        <v>7.44</v>
       </c>
       <c r="BC13" t="n">
         <v>4.11</v>
       </c>
       <c r="BD13" t="n">
-        <v>22.89</v>
+        <v>23</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="BF13" t="n">
         <v>1.89</v>
@@ -6166,7 +6166,7 @@
         <v>-1</v>
       </c>
       <c r="DP13" t="n">
-        <v>14.88</v>
+        <v>14.94</v>
       </c>
       <c r="DQ13" t="n">
         <v>16.06</v>
@@ -6190,19 +6190,19 @@
         <v>0.06</v>
       </c>
       <c r="DX13" t="n">
-        <v>11.33</v>
+        <v>11.56</v>
       </c>
       <c r="DY13" t="n">
-        <v>7.61</v>
+        <v>7.83</v>
       </c>
       <c r="DZ13" t="n">
         <v>3.72</v>
       </c>
       <c r="EA13" t="n">
-        <v>22.39</v>
+        <v>22.44</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="EC13" t="n">
         <v>2.34</v>
@@ -6287,10 +6287,10 @@
         <v>0.33</v>
       </c>
       <c r="Z14" t="n">
-        <v>13</v>
+        <v>13.22</v>
       </c>
       <c r="AA14" t="n">
-        <v>9.44</v>
+        <v>9.67</v>
       </c>
       <c r="AB14" t="n">
         <v>3.56</v>
@@ -6299,7 +6299,7 @@
         <v>21.11</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AE14" t="n">
         <v>2.44</v>
@@ -6338,7 +6338,7 @@
         <v>-1</v>
       </c>
       <c r="AQ14" t="n">
-        <v>15.22</v>
+        <v>15.33</v>
       </c>
       <c r="AR14" t="n">
         <v>17.44</v>
@@ -6368,10 +6368,10 @@
         <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>11.89</v>
+        <v>11.78</v>
       </c>
       <c r="BB14" t="n">
-        <v>7.89</v>
+        <v>7.78</v>
       </c>
       <c r="BC14" t="n">
         <v>4</v>
@@ -6380,7 +6380,7 @@
         <v>21.33</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="BF14" t="n">
         <v>2.33</v>
@@ -6569,7 +6569,7 @@
         <v>-1</v>
       </c>
       <c r="DP14" t="n">
-        <v>14.78</v>
+        <v>14.83</v>
       </c>
       <c r="DQ14" t="n">
         <v>17.5</v>
@@ -6593,10 +6593,10 @@
         <v>0.16</v>
       </c>
       <c r="DX14" t="n">
-        <v>12.44</v>
+        <v>12.5</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.66</v>
+        <v>8.73</v>
       </c>
       <c r="DZ14" t="n">
         <v>3.78</v>
@@ -6684,7 +6684,7 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>40.89</v>
+        <v>41.11</v>
       </c>
       <c r="Y15" t="n">
         <v>0.11</v>
@@ -6699,7 +6699,7 @@
         <v>3.22</v>
       </c>
       <c r="AC15" t="n">
-        <v>21</v>
+        <v>21.11</v>
       </c>
       <c r="AD15" t="n">
         <v>1.17</v>
@@ -6765,7 +6765,7 @@
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>41.11</v>
+        <v>41.22</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
@@ -6990,7 +6990,7 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>41</v>
+        <v>41.16</v>
       </c>
       <c r="DW15" t="n">
         <v>0.06</v>
@@ -7005,7 +7005,7 @@
         <v>3</v>
       </c>
       <c r="EA15" t="n">
-        <v>18.94</v>
+        <v>19</v>
       </c>
       <c r="EB15" t="n">
         <v>1.16</v>
@@ -7087,7 +7087,7 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>60</v>
+        <v>59.9</v>
       </c>
       <c r="Y16" t="n">
         <v>0.3</v>
@@ -7102,7 +7102,7 @@
         <v>3.7</v>
       </c>
       <c r="AC16" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="AD16" t="n">
         <v>1.42</v>
@@ -7168,7 +7168,7 @@
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>63.38</v>
+        <v>63.5</v>
       </c>
       <c r="AZ16" t="n">
         <v>0.12</v>
@@ -7408,7 +7408,7 @@
         <v>3.89</v>
       </c>
       <c r="EA16" t="n">
-        <v>21.28</v>
+        <v>21.33</v>
       </c>
       <c r="EB16" t="n">
         <v>1.44</v>
@@ -7472,7 +7472,7 @@
         <v>18.67</v>
       </c>
       <c r="R17" t="n">
-        <v>4.78</v>
+        <v>4.67</v>
       </c>
       <c r="S17" t="n">
         <v>0.5600000000000001</v>
@@ -7496,19 +7496,19 @@
         <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>14.56</v>
+        <v>14.67</v>
       </c>
       <c r="AA17" t="n">
         <v>8</v>
       </c>
       <c r="AB17" t="n">
-        <v>6.56</v>
+        <v>6.67</v>
       </c>
       <c r="AC17" t="n">
         <v>18.89</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AE17" t="n">
         <v>1.44</v>
@@ -7784,7 +7784,7 @@
         <v>20.62</v>
       </c>
       <c r="DR17" t="n">
-        <v>5.78</v>
+        <v>5.72</v>
       </c>
       <c r="DS17" t="n">
         <v>0.33</v>
@@ -7802,19 +7802,19 @@
         <v>0.06</v>
       </c>
       <c r="DX17" t="n">
-        <v>12.5</v>
+        <v>12.56</v>
       </c>
       <c r="DY17" t="n">
         <v>7.06</v>
       </c>
       <c r="DZ17" t="n">
-        <v>5.44</v>
+        <v>5.5</v>
       </c>
       <c r="EA17" t="n">
         <v>19.28</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="EC17" t="n">
         <v>1.44</v>

--- a/data/teams/leagues/Averages_Russian_Premier_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Russian_Premier_League_2025-2026.xlsx
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" t="n">
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1872,112 +1872,112 @@
         <v>1.67</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AH3" t="n">
         <v>-1</v>
       </c>
       <c r="AI3" t="n">
-        <v>85.33</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="AL3" t="n">
-        <v>4.22</v>
+        <v>4.3</v>
       </c>
       <c r="AM3" t="n">
         <v>-1</v>
       </c>
       <c r="AN3" t="n">
-        <v>40.67</v>
+        <v>38.7</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AP3" t="n">
         <v>-1</v>
       </c>
       <c r="AQ3" t="n">
-        <v>14.67</v>
+        <v>14.9</v>
       </c>
       <c r="AR3" t="n">
-        <v>13.11</v>
+        <v>13.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>7.89</v>
+        <v>8.4</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>41.22</v>
+        <v>41.9</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA3" t="n">
-        <v>10.56</v>
+        <v>10.6</v>
       </c>
       <c r="BB3" t="n">
-        <v>7.44</v>
+        <v>7.3</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.11</v>
+        <v>3.3</v>
       </c>
       <c r="BD3" t="n">
-        <v>17.67</v>
+        <v>17.1</v>
       </c>
       <c r="BE3" t="n">
         <v>1.18</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.67</v>
+        <v>2.63</v>
       </c>
       <c r="BH3" t="n">
         <v>8.890000000000001</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.67</v>
+        <v>2.63</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="BP3" t="n">
         <v>-1</v>
@@ -1989,22 +1989,22 @@
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>88.89</v>
+        <v>89.47</v>
       </c>
       <c r="BT3" t="n">
-        <v>50</v>
+        <v>47.37</v>
       </c>
       <c r="BU3" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BV3" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>66.67</v>
+        <v>63.16</v>
       </c>
       <c r="BY3" t="n">
         <v>3.38</v>
@@ -2013,55 +2013,55 @@
         <v>3.61</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.99</v>
+        <v>3.96</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.25</v>
+        <v>4.22</v>
       </c>
       <c r="CC3" t="n">
-        <v>5.75</v>
+        <v>5.48</v>
       </c>
       <c r="CD3" t="n">
-        <v>6.1</v>
+        <v>5.82</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CI3" t="n">
         <v>2.09</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="CN3" t="n">
         <v>1.93</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="CR3" t="n">
         <v>1.38</v>
@@ -2076,10 +2076,10 @@
         <v>1.47</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CX3" t="n">
         <v>1.55</v>
@@ -2103,7 +2103,7 @@
         <v>2.89</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DF3" t="n">
         <v>1.16</v>
@@ -2112,22 +2112,22 @@
         <v>-1</v>
       </c>
       <c r="DH3" t="n">
-        <v>92.5</v>
+        <v>91.48</v>
       </c>
       <c r="DI3" t="n">
         <v>0.16</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="DK3" t="n">
-        <v>4.16</v>
+        <v>4.21</v>
       </c>
       <c r="DL3" t="n">
         <v>-1</v>
       </c>
       <c r="DM3" t="n">
-        <v>45</v>
+        <v>43.74</v>
       </c>
       <c r="DN3" t="n">
         <v>0.84</v>
@@ -2136,13 +2136,13 @@
         <v>-1</v>
       </c>
       <c r="DP3" t="n">
-        <v>14.94</v>
+        <v>15.05</v>
       </c>
       <c r="DQ3" t="n">
-        <v>14.34</v>
+        <v>14.48</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.44</v>
+        <v>7.74</v>
       </c>
       <c r="DS3" t="n">
         <v>0.16</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>43.61</v>
+        <v>43.84</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DX3" t="n">
         <v>10.84</v>
       </c>
       <c r="DY3" t="n">
-        <v>7</v>
+        <v>6.95</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.84</v>
+        <v>3.9</v>
       </c>
       <c r="EA3" t="n">
-        <v>18.34</v>
+        <v>18</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="4">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4" t="n">
         <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E4" t="n">
         <v>0.33</v>
@@ -2275,112 +2275,112 @@
         <v>2.67</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AH4" t="n">
         <v>-1</v>
       </c>
       <c r="AI4" t="n">
-        <v>92.67</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AK4" t="n">
-        <v>3.44</v>
+        <v>3.4</v>
       </c>
       <c r="AL4" t="n">
-        <v>3.33</v>
+        <v>3.5</v>
       </c>
       <c r="AM4" t="n">
         <v>-1</v>
       </c>
       <c r="AN4" t="n">
-        <v>43.11</v>
+        <v>43.4</v>
       </c>
       <c r="AO4" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AP4" t="n">
         <v>-1</v>
       </c>
       <c r="AQ4" t="n">
-        <v>20.22</v>
+        <v>19.4</v>
       </c>
       <c r="AR4" t="n">
-        <v>13.56</v>
+        <v>13.1</v>
       </c>
       <c r="AS4" t="n">
-        <v>7.44</v>
+        <v>7.8</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>48.22</v>
+        <v>47.1</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA4" t="n">
-        <v>12.67</v>
+        <v>12.2</v>
       </c>
       <c r="BB4" t="n">
-        <v>8.220000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.44</v>
+        <v>4.1</v>
       </c>
       <c r="BD4" t="n">
-        <v>21.22</v>
+        <v>20.8</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="BF4" t="n">
-        <v>3.33</v>
+        <v>3.3</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="BH4" t="n">
-        <v>8.06</v>
+        <v>8.26</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BN4" t="n">
         <v>0.89</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="BP4" t="n">
         <v>-1</v>
@@ -2389,25 +2389,25 @@
         <v>-1</v>
       </c>
       <c r="BR4" t="n">
-        <v>77.78</v>
+        <v>78.95</v>
       </c>
       <c r="BS4" t="n">
-        <v>66.67</v>
+        <v>63.16</v>
       </c>
       <c r="BT4" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BU4" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BV4" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>27.78</v>
+        <v>26.32</v>
       </c>
       <c r="BY4" t="n">
         <v>2.46</v>
@@ -2419,22 +2419,22 @@
         <v>3.42</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.49</v>
+        <v>3.51</v>
       </c>
       <c r="CC4" t="n">
-        <v>3.37</v>
+        <v>3.71</v>
       </c>
       <c r="CD4" t="n">
-        <v>3.67</v>
+        <v>4</v>
       </c>
       <c r="CE4" t="n">
         <v>1.39</v>
       </c>
       <c r="CF4" t="n">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="CH4" t="n">
         <v>1.27</v>
@@ -2443,46 +2443,46 @@
         <v>1.67</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="CN4" t="n">
         <v>1.76</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.92</v>
+        <v>3.95</v>
       </c>
       <c r="CR4" t="n">
         <v>1.47</v>
       </c>
       <c r="CS4" t="n">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
       <c r="CT4" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CV4" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CW4" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CX4" t="n">
         <v>1.63</v>
@@ -2506,76 +2506,76 @@
         <v>4.37</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="DG4" t="n">
         <v>-1</v>
       </c>
       <c r="DH4" t="n">
-        <v>87.84</v>
+        <v>88.31999999999999</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="DJ4" t="n">
         <v>3.16</v>
       </c>
       <c r="DK4" t="n">
-        <v>3.33</v>
+        <v>3.42</v>
       </c>
       <c r="DL4" t="n">
         <v>-1</v>
       </c>
       <c r="DM4" t="n">
-        <v>44.39</v>
+        <v>44.48</v>
       </c>
       <c r="DN4" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="DO4" t="n">
         <v>-1</v>
       </c>
       <c r="DP4" t="n">
-        <v>19.83</v>
+        <v>19.42</v>
       </c>
       <c r="DQ4" t="n">
-        <v>12.94</v>
+        <v>12.74</v>
       </c>
       <c r="DR4" t="n">
-        <v>7.5</v>
+        <v>7.69</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>45.72</v>
+        <v>45.26</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX4" t="n">
-        <v>12.78</v>
+        <v>12.53</v>
       </c>
       <c r="DY4" t="n">
-        <v>8.56</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.22</v>
+        <v>4.05</v>
       </c>
       <c r="EA4" t="n">
-        <v>21.61</v>
+        <v>21.37</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="EC4" t="n">
         <v>3</v>
@@ -3797,94 +3797,94 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D8" t="n">
         <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="G8" t="n">
         <v>-1</v>
       </c>
       <c r="H8" t="n">
-        <v>96.2</v>
+        <v>96.09</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="J8" t="n">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="K8" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="L8" t="n">
         <v>-1</v>
       </c>
       <c r="M8" t="n">
-        <v>52.8</v>
+        <v>52.45</v>
       </c>
       <c r="N8" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="O8" t="n">
         <v>-1</v>
       </c>
       <c r="P8" t="n">
-        <v>13.6</v>
+        <v>13.82</v>
       </c>
       <c r="Q8" t="n">
-        <v>16.1</v>
+        <v>15.82</v>
       </c>
       <c r="R8" t="n">
-        <v>6.4</v>
+        <v>6.36</v>
       </c>
       <c r="S8" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="T8" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="V8" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>59.3</v>
+        <v>59.73</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="Z8" t="n">
-        <v>18.9</v>
+        <v>18.91</v>
       </c>
       <c r="AA8" t="n">
-        <v>13.7</v>
+        <v>13.64</v>
       </c>
       <c r="AB8" t="n">
-        <v>5.2</v>
+        <v>5.27</v>
       </c>
       <c r="AC8" t="n">
-        <v>21.4</v>
+        <v>20.73</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="AF8" t="n">
         <v>0.25</v>
@@ -3968,31 +3968,31 @@
         <v>1.75</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="BH8" t="n">
-        <v>8.83</v>
+        <v>8.84</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="BP8" t="n">
         <v>-1</v>
@@ -4001,37 +4001,37 @@
         <v>-1</v>
       </c>
       <c r="BR8" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS8" t="n">
-        <v>77.78</v>
+        <v>78.95</v>
       </c>
       <c r="BT8" t="n">
-        <v>44.44</v>
+        <v>47.37</v>
       </c>
       <c r="BU8" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BV8" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BW8" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BX8" t="n">
-        <v>44.44</v>
+        <v>47.37</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="BZ8" t="n">
         <v>1.71</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.86</v>
+        <v>3.88</v>
       </c>
       <c r="CB8" t="n">
-        <v>4.13</v>
+        <v>4.12</v>
       </c>
       <c r="CC8" t="n">
         <v>1.95</v>
@@ -4046,7 +4046,7 @@
         <v>2.7</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="CH8" t="n">
         <v>1.47</v>
@@ -4055,19 +4055,19 @@
         <v>1.97</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CO8" t="n">
         <v>1.26</v>
@@ -4079,34 +4079,34 @@
         <v>3.06</v>
       </c>
       <c r="CR8" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="CT8" t="n">
-        <v>2.97</v>
+        <v>3.01</v>
       </c>
       <c r="CU8" t="n">
         <v>1.44</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CW8" t="n">
         <v>1.86</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="DB8" t="n">
         <v>1.26</v>
@@ -4115,82 +4115,82 @@
         <v>1.83</v>
       </c>
       <c r="DD8" t="n">
-        <v>3.02</v>
+        <v>3.03</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="DG8" t="n">
         <v>-1</v>
       </c>
       <c r="DH8" t="n">
-        <v>93.33</v>
+        <v>93.42</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="DK8" t="n">
-        <v>5.33</v>
+        <v>5.26</v>
       </c>
       <c r="DL8" t="n">
         <v>-1</v>
       </c>
       <c r="DM8" t="n">
-        <v>46.78</v>
+        <v>46.89</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="DO8" t="n">
         <v>-1</v>
       </c>
       <c r="DP8" t="n">
-        <v>13.61</v>
+        <v>13.74</v>
       </c>
       <c r="DQ8" t="n">
-        <v>17.61</v>
+        <v>17.37</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.33</v>
+        <v>7.26</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.11</v>
+        <v>0.15</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.11</v>
+        <v>0.15</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>58.22</v>
+        <v>58.53</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DX8" t="n">
-        <v>16.22</v>
+        <v>16.37</v>
       </c>
       <c r="DY8" t="n">
-        <v>11.44</v>
+        <v>11.53</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.78</v>
+        <v>4.84</v>
       </c>
       <c r="EA8" t="n">
-        <v>21.72</v>
+        <v>21.32</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="9">
@@ -4603,31 +4603,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D10" t="n">
         <v>10</v>
       </c>
       <c r="E10" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="F10" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="G10" t="n">
         <v>-1</v>
       </c>
       <c r="H10" t="n">
-        <v>93.62</v>
+        <v>94.22</v>
       </c>
       <c r="I10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="J10" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="K10" t="n">
         <v>3</v>
@@ -4636,61 +4636,61 @@
         <v>-1</v>
       </c>
       <c r="M10" t="n">
-        <v>45.62</v>
+        <v>45.89</v>
       </c>
       <c r="N10" t="n">
-        <v>0.75</v>
+        <v>0.89</v>
       </c>
       <c r="O10" t="n">
         <v>-1</v>
       </c>
       <c r="P10" t="n">
-        <v>15.25</v>
+        <v>15.11</v>
       </c>
       <c r="Q10" t="n">
-        <v>13.88</v>
+        <v>14.22</v>
       </c>
       <c r="R10" t="n">
-        <v>7</v>
+        <v>6.89</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="U10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="V10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>44.25</v>
+        <v>45.22</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="Z10" t="n">
-        <v>15.25</v>
+        <v>14.78</v>
       </c>
       <c r="AA10" t="n">
-        <v>9.119999999999999</v>
+        <v>8.67</v>
       </c>
       <c r="AB10" t="n">
-        <v>6.12</v>
+        <v>6.11</v>
       </c>
       <c r="AC10" t="n">
-        <v>18</v>
+        <v>18.44</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="AF10" t="n">
         <v>0.3</v>
@@ -4774,19 +4774,19 @@
         <v>2.2</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.44</v>
+        <v>3.42</v>
       </c>
       <c r="BH10" t="n">
-        <v>8.83</v>
+        <v>8.74</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.44</v>
+        <v>3.42</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BL10" t="n">
         <v>1</v>
@@ -4798,7 +4798,7 @@
         <v>2</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="BP10" t="n">
         <v>-1</v>
@@ -4810,34 +4810,34 @@
         <v>100</v>
       </c>
       <c r="BS10" t="n">
-        <v>88.89</v>
+        <v>89.47</v>
       </c>
       <c r="BT10" t="n">
-        <v>55.56</v>
+        <v>57.89</v>
       </c>
       <c r="BU10" t="n">
-        <v>38.89</v>
+        <v>36.84</v>
       </c>
       <c r="BV10" t="n">
-        <v>27.78</v>
+        <v>26.32</v>
       </c>
       <c r="BW10" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BX10" t="n">
-        <v>72.22</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="BY10" t="n">
-        <v>2.07</v>
+        <v>2.01</v>
       </c>
       <c r="BZ10" t="n">
-        <v>2.27</v>
+        <v>2.18</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.64</v>
+        <v>3.69</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.79</v>
+        <v>3.83</v>
       </c>
       <c r="CC10" t="n">
         <v>2.77</v>
@@ -4846,49 +4846,49 @@
         <v>3.04</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="CG10" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="CH10" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="CI10" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="CN10" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="CO10" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="CP10" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="CQ10" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="CR10" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="CS10" t="n">
         <v>2.74</v>
-      </c>
-      <c r="CH10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="CI10" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="CJ10" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="CK10" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="CL10" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="CM10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="CN10" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="CO10" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="CP10" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="CQ10" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="CR10" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="CS10" t="n">
-        <v>2.73</v>
       </c>
       <c r="CT10" t="n">
         <v>3.12</v>
@@ -4897,10 +4897,10 @@
         <v>1.47</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="CX10" t="n">
         <v>1.54</v>
@@ -4912,91 +4912,91 @@
         <v>2.46</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="DC10" t="n">
         <v>1.82</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="DG10" t="n">
         <v>-1</v>
       </c>
       <c r="DH10" t="n">
-        <v>93.89</v>
+        <v>94.16</v>
       </c>
       <c r="DI10" t="n">
         <v>0.16</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="DK10" t="n">
-        <v>3.61</v>
+        <v>3.58</v>
       </c>
       <c r="DL10" t="n">
         <v>-1</v>
       </c>
       <c r="DM10" t="n">
-        <v>46.28</v>
+        <v>46.37</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.78</v>
+        <v>0.84</v>
       </c>
       <c r="DO10" t="n">
         <v>-1</v>
       </c>
       <c r="DP10" t="n">
-        <v>14.56</v>
+        <v>14.53</v>
       </c>
       <c r="DQ10" t="n">
-        <v>14.5</v>
+        <v>14.63</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.28</v>
+        <v>7.21</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>48.33</v>
+        <v>48.58</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="DX10" t="n">
-        <v>14.39</v>
+        <v>14.21</v>
       </c>
       <c r="DY10" t="n">
-        <v>8.779999999999999</v>
+        <v>8.58</v>
       </c>
       <c r="DZ10" t="n">
-        <v>5.61</v>
+        <v>5.63</v>
       </c>
       <c r="EA10" t="n">
-        <v>17.22</v>
+        <v>17.47</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.28</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="11">
@@ -5006,94 +5006,94 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D11" t="n">
         <v>9</v>
       </c>
       <c r="E11" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="F11" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="G11" t="n">
         <v>-1</v>
       </c>
       <c r="H11" t="n">
-        <v>105.44</v>
+        <v>106</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="K11" t="n">
-        <v>4.89</v>
+        <v>5</v>
       </c>
       <c r="L11" t="n">
         <v>-1</v>
       </c>
       <c r="M11" t="n">
-        <v>49.78</v>
+        <v>50.8</v>
       </c>
       <c r="N11" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="O11" t="n">
         <v>-1</v>
       </c>
       <c r="P11" t="n">
-        <v>14.11</v>
+        <v>13.9</v>
       </c>
       <c r="Q11" t="n">
-        <v>19.78</v>
+        <v>19.3</v>
       </c>
       <c r="R11" t="n">
-        <v>7.22</v>
+        <v>7</v>
       </c>
       <c r="S11" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="T11" t="n">
-        <v>0.67</v>
+        <v>0.8</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>48.11</v>
+        <v>49.3</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z11" t="n">
-        <v>10.67</v>
+        <v>10.6</v>
       </c>
       <c r="AA11" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AC11" t="n">
-        <v>25.67</v>
+        <v>26.6</v>
       </c>
       <c r="AD11" t="n">
         <v>1.23</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -5177,31 +5177,31 @@
         <v>2</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="BH11" t="n">
-        <v>8.33</v>
+        <v>8.26</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="BN11" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.78</v>
+        <v>0.84</v>
       </c>
       <c r="BP11" t="n">
         <v>-1</v>
@@ -5210,16 +5210,16 @@
         <v>-1</v>
       </c>
       <c r="BR11" t="n">
-        <v>88.89</v>
+        <v>89.47</v>
       </c>
       <c r="BS11" t="n">
-        <v>55.56</v>
+        <v>57.89</v>
       </c>
       <c r="BT11" t="n">
-        <v>11.11</v>
+        <v>15.79</v>
       </c>
       <c r="BU11" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BV11" t="n">
         <v>0</v>
@@ -5228,19 +5228,19 @@
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>22.22</v>
+        <v>26.32</v>
       </c>
       <c r="BY11" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BZ11" t="n">
-        <v>3.18</v>
+        <v>3.12</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.47</v>
+        <v>3.43</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="CC11" t="n">
         <v>5.29</v>
@@ -5249,43 +5249,43 @@
         <v>5.62</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CF11" t="n">
-        <v>3.35</v>
+        <v>3.39</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="CH11" t="n">
         <v>1.32</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CJ11" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CP11" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="CQ11" t="n">
-        <v>4.23</v>
+        <v>4.31</v>
       </c>
       <c r="CR11" t="n">
         <v>1.5</v>
@@ -5300,106 +5300,106 @@
         <v>1.37</v>
       </c>
       <c r="CV11" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CW11" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.28</v>
+        <v>2.23</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="DC11" t="n">
-        <v>2.36</v>
+        <v>2.43</v>
       </c>
       <c r="DD11" t="n">
-        <v>4.46</v>
+        <v>4.65</v>
       </c>
       <c r="DE11" t="n">
         <v>0.11</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="DG11" t="n">
         <v>-1</v>
       </c>
       <c r="DH11" t="n">
-        <v>107.83</v>
+        <v>108</v>
       </c>
       <c r="DI11" t="n">
         <v>0</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.33</v>
+        <v>2.21</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.39</v>
+        <v>4.47</v>
       </c>
       <c r="DL11" t="n">
         <v>-1</v>
       </c>
       <c r="DM11" t="n">
-        <v>49.17</v>
+        <v>49.74</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.62</v>
+        <v>0.58</v>
       </c>
       <c r="DO11" t="n">
         <v>-1</v>
       </c>
       <c r="DP11" t="n">
-        <v>13.84</v>
+        <v>13.74</v>
       </c>
       <c r="DQ11" t="n">
-        <v>19.23</v>
+        <v>19</v>
       </c>
       <c r="DR11" t="n">
-        <v>6.94</v>
+        <v>6.84</v>
       </c>
       <c r="DS11" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="DT11" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>48.28</v>
+        <v>48.89</v>
       </c>
       <c r="DW11" t="n">
         <v>0.16</v>
       </c>
       <c r="DX11" t="n">
-        <v>10.39</v>
+        <v>10.37</v>
       </c>
       <c r="DY11" t="n">
-        <v>7.66</v>
+        <v>7.63</v>
       </c>
       <c r="DZ11" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="EA11" t="n">
-        <v>24.34</v>
+        <v>24.89</v>
       </c>
       <c r="EB11" t="n">
         <v>1.21</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C12" t="n">
         <v>9</v>
       </c>
       <c r="D12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -5508,103 +5508,103 @@
         <v>-1</v>
       </c>
       <c r="AI12" t="n">
-        <v>76.11</v>
+        <v>77.2</v>
       </c>
       <c r="AJ12" t="n">
         <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>3.11</v>
+        <v>3</v>
       </c>
       <c r="AL12" t="n">
-        <v>4.11</v>
+        <v>4.1</v>
       </c>
       <c r="AM12" t="n">
         <v>-1</v>
       </c>
       <c r="AN12" t="n">
-        <v>32</v>
+        <v>32.9</v>
       </c>
       <c r="AO12" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AP12" t="n">
         <v>-1</v>
       </c>
       <c r="AQ12" t="n">
-        <v>17.89</v>
+        <v>17.7</v>
       </c>
       <c r="AR12" t="n">
-        <v>14.67</v>
+        <v>14.7</v>
       </c>
       <c r="AS12" t="n">
-        <v>9.220000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AX12" t="n">
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>39.22</v>
+        <v>40</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA12" t="n">
-        <v>10.11</v>
+        <v>10.5</v>
       </c>
       <c r="BB12" t="n">
-        <v>6.78</v>
+        <v>7</v>
       </c>
       <c r="BC12" t="n">
-        <v>3.33</v>
+        <v>3.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>18.56</v>
+        <v>18.5</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.779999999999999</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="BL12" t="n">
         <v>0.89</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="BP12" t="n">
         <v>-1</v>
@@ -5613,25 +5613,25 @@
         <v>-1</v>
       </c>
       <c r="BR12" t="n">
-        <v>88.89</v>
+        <v>89.47</v>
       </c>
       <c r="BS12" t="n">
-        <v>72.22</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="BT12" t="n">
-        <v>44.44</v>
+        <v>47.37</v>
       </c>
       <c r="BU12" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BV12" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>27.78</v>
+        <v>31.58</v>
       </c>
       <c r="BY12" t="n">
         <v>4.28</v>
@@ -5640,46 +5640,46 @@
         <v>4.56</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.94</v>
+        <v>3.98</v>
       </c>
       <c r="CB12" t="n">
-        <v>4.3</v>
+        <v>4.31</v>
       </c>
       <c r="CC12" t="n">
-        <v>7</v>
+        <v>6.98</v>
       </c>
       <c r="CD12" t="n">
-        <v>7.59</v>
+        <v>7.51</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CF12" t="n">
         <v>2.67</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="CH12" t="n">
         <v>1.37</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="CK12" t="n">
         <v>1.4</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CO12" t="n">
         <v>1.21</v>
@@ -5688,46 +5688,46 @@
         <v>1.85</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.11</v>
+        <v>3.09</v>
       </c>
       <c r="CR12" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="CT12" t="n">
-        <v>2.79</v>
+        <v>2.85</v>
       </c>
       <c r="CU12" t="n">
         <v>1.44</v>
       </c>
       <c r="CV12" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CW12" t="n">
         <v>1.96</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CY12" t="n">
         <v>1.89</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="DA12" t="n">
         <v>1.93</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.56</v>
+        <v>3.53</v>
       </c>
       <c r="DE12" t="n">
         <v>0</v>
@@ -5739,70 +5739,70 @@
         <v>-1</v>
       </c>
       <c r="DH12" t="n">
-        <v>83.28</v>
+        <v>83.47</v>
       </c>
       <c r="DI12" t="n">
         <v>0</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.89</v>
+        <v>2.84</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.06</v>
+        <v>4.05</v>
       </c>
       <c r="DL12" t="n">
         <v>-1</v>
       </c>
       <c r="DM12" t="n">
-        <v>38.78</v>
+        <v>38.9</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.84</v>
+        <v>0.79</v>
       </c>
       <c r="DO12" t="n">
         <v>-1</v>
       </c>
       <c r="DP12" t="n">
-        <v>17.5</v>
+        <v>17.42</v>
       </c>
       <c r="DQ12" t="n">
-        <v>14.5</v>
+        <v>14.52</v>
       </c>
       <c r="DR12" t="n">
-        <v>8.220000000000001</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>43.28</v>
+        <v>43.47</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX12" t="n">
-        <v>11.22</v>
+        <v>11.37</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.28</v>
+        <v>7.37</v>
       </c>
       <c r="DZ12" t="n">
-        <v>3.94</v>
+        <v>4</v>
       </c>
       <c r="EA12" t="n">
-        <v>17.56</v>
+        <v>17.58</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.72</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="13">
@@ -5812,94 +5812,94 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D13" t="n">
         <v>9</v>
       </c>
       <c r="E13" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="F13" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="G13" t="n">
         <v>-1</v>
       </c>
       <c r="H13" t="n">
-        <v>83.78</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="J13" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="K13" t="n">
-        <v>5.11</v>
+        <v>5</v>
       </c>
       <c r="L13" t="n">
         <v>-1</v>
       </c>
       <c r="M13" t="n">
-        <v>44</v>
+        <v>43.5</v>
       </c>
       <c r="N13" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="O13" t="n">
         <v>-1</v>
       </c>
       <c r="P13" t="n">
-        <v>16.44</v>
+        <v>16.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>16.22</v>
+        <v>16.6</v>
       </c>
       <c r="R13" t="n">
-        <v>7.89</v>
+        <v>7.6</v>
       </c>
       <c r="S13" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="T13" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="U13" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="V13" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>49.89</v>
+        <v>50.1</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>11.56</v>
+        <v>12.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>8.220000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AB13" t="n">
-        <v>3.33</v>
+        <v>3.7</v>
       </c>
       <c r="AC13" t="n">
-        <v>21.89</v>
+        <v>21.1</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -5983,31 +5983,31 @@
         <v>1.89</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.890000000000001</v>
+        <v>9.84</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="BL13" t="n">
         <v>1</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="BP13" t="n">
         <v>-1</v>
@@ -6016,37 +6016,37 @@
         <v>-1</v>
       </c>
       <c r="BR13" t="n">
-        <v>88.89</v>
+        <v>89.47</v>
       </c>
       <c r="BS13" t="n">
-        <v>61.11</v>
+        <v>63.16</v>
       </c>
       <c r="BT13" t="n">
-        <v>44.44</v>
+        <v>42.11</v>
       </c>
       <c r="BU13" t="n">
-        <v>38.89</v>
+        <v>36.84</v>
       </c>
       <c r="BV13" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BW13" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX13" t="n">
-        <v>55.56</v>
+        <v>52.63</v>
       </c>
       <c r="BY13" t="n">
-        <v>3.67</v>
+        <v>3.52</v>
       </c>
       <c r="BZ13" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="CB13" t="n">
         <v>4.33</v>
-      </c>
-      <c r="CA13" t="n">
-        <v>4.12</v>
-      </c>
-      <c r="CB13" t="n">
-        <v>4.36</v>
       </c>
       <c r="CC13" t="n">
         <v>6.29</v>
@@ -6055,19 +6055,19 @@
         <v>6.6</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CF13" t="n">
         <v>2.61</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="CH13" t="n">
         <v>1.51</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CJ13" t="n">
         <v>1.77</v>
@@ -6076,13 +6076,13 @@
         <v>1.38</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="CN13" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CO13" t="n">
         <v>1.24</v>
@@ -6091,7 +6091,7 @@
         <v>1.8</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="CR13" t="n">
         <v>1.4</v>
@@ -6106,7 +6106,7 @@
         <v>1.56</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CW13" t="n">
         <v>1.78</v>
@@ -6127,85 +6127,85 @@
         <v>1.26</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="DD13" t="n">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
       <c r="DE13" t="n">
         <v>0.11</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="DG13" t="n">
         <v>-1</v>
       </c>
       <c r="DH13" t="n">
-        <v>86.17</v>
+        <v>86.37</v>
       </c>
       <c r="DI13" t="n">
         <v>0.16</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.44</v>
+        <v>5.37</v>
       </c>
       <c r="DL13" t="n">
         <v>-1</v>
       </c>
       <c r="DM13" t="n">
-        <v>43.94</v>
+        <v>43.68</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="DO13" t="n">
         <v>-1</v>
       </c>
       <c r="DP13" t="n">
-        <v>14.94</v>
+        <v>14.89</v>
       </c>
       <c r="DQ13" t="n">
-        <v>16.06</v>
+        <v>16.26</v>
       </c>
       <c r="DR13" t="n">
-        <v>8.23</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>48.84</v>
+        <v>49</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DX13" t="n">
-        <v>11.56</v>
+        <v>12.05</v>
       </c>
       <c r="DY13" t="n">
-        <v>7.83</v>
+        <v>8.16</v>
       </c>
       <c r="DZ13" t="n">
-        <v>3.72</v>
+        <v>3.89</v>
       </c>
       <c r="EA13" t="n">
-        <v>22.44</v>
+        <v>22</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="14">
@@ -6215,13 +6215,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C14" t="n">
         <v>9</v>
       </c>
       <c r="D14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E14" t="n">
         <v>0.11</v>
@@ -6308,109 +6308,109 @@
         <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AH14" t="n">
         <v>-1</v>
       </c>
       <c r="AI14" t="n">
-        <v>91.33</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="AL14" t="n">
-        <v>3.89</v>
+        <v>4</v>
       </c>
       <c r="AM14" t="n">
         <v>-1</v>
       </c>
       <c r="AN14" t="n">
-        <v>47.56</v>
+        <v>46.6</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="AP14" t="n">
         <v>-1</v>
       </c>
       <c r="AQ14" t="n">
-        <v>15.33</v>
+        <v>15.3</v>
       </c>
       <c r="AR14" t="n">
-        <v>17.44</v>
+        <v>17.2</v>
       </c>
       <c r="AS14" t="n">
-        <v>6.67</v>
+        <v>6.8</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="AX14" t="n">
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>48.11</v>
+        <v>46.9</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="BA14" t="n">
-        <v>11.78</v>
+        <v>11.9</v>
       </c>
       <c r="BB14" t="n">
-        <v>7.78</v>
+        <v>7.9</v>
       </c>
       <c r="BC14" t="n">
         <v>4</v>
       </c>
       <c r="BD14" t="n">
-        <v>21.33</v>
+        <v>21</v>
       </c>
       <c r="BE14" t="n">
         <v>1.37</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="BH14" t="n">
-        <v>7.61</v>
+        <v>7.68</v>
       </c>
       <c r="BI14" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.33</v>
+        <v>0.37</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.72</v>
+        <v>0.79</v>
       </c>
       <c r="BP14" t="n">
         <v>-1</v>
@@ -6419,25 +6419,25 @@
         <v>-1</v>
       </c>
       <c r="BR14" t="n">
-        <v>88.89</v>
+        <v>89.47</v>
       </c>
       <c r="BS14" t="n">
-        <v>50</v>
+        <v>52.63</v>
       </c>
       <c r="BT14" t="n">
-        <v>22.22</v>
+        <v>26.32</v>
       </c>
       <c r="BU14" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BV14" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BW14" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX14" t="n">
-        <v>38.89</v>
+        <v>42.11</v>
       </c>
       <c r="BY14" t="n">
         <v>2.34</v>
@@ -6446,34 +6446,34 @@
         <v>2.41</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.59</v>
+        <v>3.63</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.68</v>
+        <v>3.7</v>
       </c>
       <c r="CC14" t="n">
-        <v>4.18</v>
+        <v>4.29</v>
       </c>
       <c r="CD14" t="n">
-        <v>4.25</v>
+        <v>4.37</v>
       </c>
       <c r="CE14" t="n">
         <v>1.4</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="CH14" t="n">
         <v>1.42</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CK14" t="n">
         <v>1.57</v>
@@ -6482,7 +6482,7 @@
         <v>2.16</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="CN14" t="n">
         <v>1.79</v>
@@ -6491,22 +6491,22 @@
         <v>1.31</v>
       </c>
       <c r="CP14" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.45</v>
+        <v>3.43</v>
       </c>
       <c r="CR14" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CS14" t="n">
         <v>2.76</v>
       </c>
       <c r="CT14" t="n">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="CU14" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CV14" t="n">
         <v>1.97</v>
@@ -6515,100 +6515,100 @@
         <v>1.92</v>
       </c>
       <c r="CX14" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="CY14" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="CZ14" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="DA14" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="DB14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DC14" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="DD14" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="DE14" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="DF14" t="n">
         <v>1.63</v>
       </c>
-      <c r="CY14" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="CZ14" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="DA14" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="DB14" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="DC14" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="DD14" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="DE14" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="DF14" t="n">
-        <v>1.66</v>
-      </c>
       <c r="DG14" t="n">
         <v>-1</v>
       </c>
       <c r="DH14" t="n">
-        <v>96.94</v>
+        <v>96.16</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="DK14" t="n">
-        <v>4.06</v>
+        <v>4.1</v>
       </c>
       <c r="DL14" t="n">
         <v>-1</v>
       </c>
       <c r="DM14" t="n">
-        <v>51.84</v>
+        <v>51.1</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="DO14" t="n">
         <v>-1</v>
       </c>
       <c r="DP14" t="n">
-        <v>14.83</v>
+        <v>14.84</v>
       </c>
       <c r="DQ14" t="n">
-        <v>17.5</v>
+        <v>17.37</v>
       </c>
       <c r="DR14" t="n">
-        <v>6.22</v>
+        <v>6.32</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>50.16</v>
+        <v>49.42</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="DX14" t="n">
-        <v>12.5</v>
+        <v>12.53</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.73</v>
+        <v>8.74</v>
       </c>
       <c r="DZ14" t="n">
-        <v>3.78</v>
+        <v>3.79</v>
       </c>
       <c r="EA14" t="n">
-        <v>21.22</v>
+        <v>21.05</v>
       </c>
       <c r="EB14" t="n">
         <v>1.43</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="15">
@@ -6618,13 +6618,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C15" t="n">
         <v>9</v>
       </c>
       <c r="D15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -6711,49 +6711,49 @@
         <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AH15" t="n">
         <v>-1</v>
       </c>
       <c r="AI15" t="n">
-        <v>79.78</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="AK15" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AL15" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="AM15" t="n">
         <v>-1</v>
       </c>
       <c r="AN15" t="n">
-        <v>37.78</v>
+        <v>36.6</v>
       </c>
       <c r="AO15" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AP15" t="n">
         <v>-1</v>
       </c>
       <c r="AQ15" t="n">
-        <v>17.89</v>
+        <v>17.5</v>
       </c>
       <c r="AR15" t="n">
-        <v>13.67</v>
+        <v>13.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AV15" t="n">
         <v>0</v>
@@ -6765,55 +6765,55 @@
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>41.22</v>
+        <v>41.1</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>10.56</v>
+        <v>10.2</v>
       </c>
       <c r="BB15" t="n">
-        <v>7.78</v>
+        <v>7.6</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.78</v>
+        <v>2.6</v>
       </c>
       <c r="BD15" t="n">
-        <v>16.89</v>
+        <v>18.2</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="BF15" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.11</v>
+        <v>2.16</v>
       </c>
       <c r="BH15" t="n">
-        <v>7.94</v>
+        <v>7.89</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.11</v>
+        <v>2.16</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="BO15" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="BP15" t="n">
         <v>-1</v>
@@ -6822,25 +6822,25 @@
         <v>-1</v>
       </c>
       <c r="BR15" t="n">
-        <v>88.89</v>
+        <v>89.47</v>
       </c>
       <c r="BS15" t="n">
-        <v>55.56</v>
+        <v>57.89</v>
       </c>
       <c r="BT15" t="n">
-        <v>33.33</v>
+        <v>36.84</v>
       </c>
       <c r="BU15" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BV15" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BW15" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX15" t="n">
-        <v>27.78</v>
+        <v>31.58</v>
       </c>
       <c r="BY15" t="n">
         <v>2.76</v>
@@ -6849,55 +6849,55 @@
         <v>3</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.47</v>
+        <v>3.44</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.67</v>
+        <v>3.63</v>
       </c>
       <c r="CC15" t="n">
-        <v>4.42</v>
+        <v>4.29</v>
       </c>
       <c r="CD15" t="n">
-        <v>4.84</v>
+        <v>4.7</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CF15" t="n">
-        <v>3.01</v>
+        <v>3.07</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="CL15" t="n">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.39</v>
+        <v>2.36</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="CP15" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.61</v>
+        <v>3.72</v>
       </c>
       <c r="CR15" t="n">
         <v>1.39</v>
@@ -6912,106 +6912,106 @@
         <v>1.42</v>
       </c>
       <c r="CV15" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="CX15" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="CY15" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="DB15" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.69</v>
+        <v>3.91</v>
       </c>
       <c r="DE15" t="n">
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="DG15" t="n">
         <v>-1</v>
       </c>
       <c r="DH15" t="n">
-        <v>83.67</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="DK15" t="n">
-        <v>4.39</v>
+        <v>4.21</v>
       </c>
       <c r="DL15" t="n">
         <v>-1</v>
       </c>
       <c r="DM15" t="n">
-        <v>38.56</v>
+        <v>37.89</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.83</v>
+        <v>0.95</v>
       </c>
       <c r="DO15" t="n">
         <v>-1</v>
       </c>
       <c r="DP15" t="n">
-        <v>16.67</v>
+        <v>16.52</v>
       </c>
       <c r="DQ15" t="n">
-        <v>14.12</v>
+        <v>14</v>
       </c>
       <c r="DR15" t="n">
-        <v>8.609999999999999</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>41.16</v>
+        <v>41.1</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DX15" t="n">
-        <v>10.44</v>
+        <v>10.26</v>
       </c>
       <c r="DY15" t="n">
-        <v>7.44</v>
+        <v>7.37</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="EA15" t="n">
-        <v>19</v>
+        <v>19.58</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.44</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="16">
@@ -7424,16 +7424,16 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D17" t="n">
         <v>9</v>
       </c>
       <c r="E17" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F17" t="n">
         <v>1</v>
@@ -7442,76 +7442,76 @@
         <v>-1</v>
       </c>
       <c r="H17" t="n">
-        <v>92</v>
+        <v>92.8</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="K17" t="n">
-        <v>5.89</v>
+        <v>6</v>
       </c>
       <c r="L17" t="n">
         <v>-1</v>
       </c>
       <c r="M17" t="n">
-        <v>51</v>
+        <v>50.6</v>
       </c>
       <c r="N17" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="O17" t="n">
         <v>-1</v>
       </c>
       <c r="P17" t="n">
-        <v>9.44</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Q17" t="n">
-        <v>18.67</v>
+        <v>18.5</v>
       </c>
       <c r="R17" t="n">
-        <v>4.67</v>
+        <v>4.8</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="T17" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="U17" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="V17" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>62</v>
+        <v>62.1</v>
       </c>
       <c r="Y17" t="n">
         <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>14.67</v>
+        <v>14.9</v>
       </c>
       <c r="AA17" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AB17" t="n">
-        <v>6.67</v>
+        <v>6.3</v>
       </c>
       <c r="AC17" t="n">
-        <v>18.89</v>
+        <v>19.7</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -7595,31 +7595,31 @@
         <v>1.44</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.56</v>
+        <v>2.47</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.220000000000001</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.56</v>
+        <v>2.47</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="BL17" t="n">
         <v>0.89</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="BP17" t="n">
         <v>-1</v>
@@ -7628,37 +7628,37 @@
         <v>-1</v>
       </c>
       <c r="BR17" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS17" t="n">
-        <v>83.33</v>
+        <v>78.95</v>
       </c>
       <c r="BT17" t="n">
-        <v>38.89</v>
+        <v>36.84</v>
       </c>
       <c r="BU17" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BV17" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BW17" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX17" t="n">
-        <v>44.44</v>
+        <v>42.11</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="BZ17" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="CA17" t="n">
-        <v>4.82</v>
+        <v>4.75</v>
       </c>
       <c r="CB17" t="n">
-        <v>5.1</v>
+        <v>5.04</v>
       </c>
       <c r="CC17" t="n">
         <v>1.76</v>
@@ -7667,61 +7667,61 @@
         <v>1.81</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="CG17" t="n">
-        <v>3.2</v>
+        <v>3.16</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CJ17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CL17" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.61</v>
+        <v>2.58</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="CO17" t="n">
         <v>1.25</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="CQ17" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="CR17" t="n">
         <v>1.42</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.79</v>
+        <v>2.83</v>
       </c>
       <c r="CT17" t="n">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="CU17" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="CV17" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CW17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CX17" t="n">
         <v>1.55</v>
@@ -7745,7 +7745,7 @@
         <v>3.12</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DF17" t="n">
         <v>1</v>
@@ -7754,70 +7754,70 @@
         <v>-1</v>
       </c>
       <c r="DH17" t="n">
-        <v>93.72</v>
+        <v>94.05</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DJ17" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.84</v>
+        <v>5.9</v>
       </c>
       <c r="DL17" t="n">
         <v>-1</v>
       </c>
       <c r="DM17" t="n">
-        <v>51.89</v>
+        <v>51.63</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="DO17" t="n">
         <v>-1</v>
       </c>
       <c r="DP17" t="n">
-        <v>9.66</v>
+        <v>9.58</v>
       </c>
       <c r="DQ17" t="n">
-        <v>20.62</v>
+        <v>20.42</v>
       </c>
       <c r="DR17" t="n">
-        <v>5.72</v>
+        <v>5.74</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>61.44</v>
+        <v>61.53</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DX17" t="n">
-        <v>12.56</v>
+        <v>12.79</v>
       </c>
       <c r="DY17" t="n">
-        <v>7.06</v>
+        <v>7.42</v>
       </c>
       <c r="DZ17" t="n">
-        <v>5.5</v>
+        <v>5.37</v>
       </c>
       <c r="EA17" t="n">
-        <v>19.28</v>
+        <v>19.69</v>
       </c>
       <c r="EB17" t="n">
         <v>1.56</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Russian_Premier_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Russian_Premier_League_2025-2026.xlsx
@@ -1379,31 +1379,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
         <v>9</v>
       </c>
       <c r="E2" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="F2" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="G2" t="n">
         <v>-1</v>
       </c>
       <c r="H2" t="n">
-        <v>92</v>
+        <v>89.7</v>
       </c>
       <c r="I2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="J2" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="K2" t="n">
         <v>5</v>
@@ -1412,61 +1412,61 @@
         <v>-1</v>
       </c>
       <c r="M2" t="n">
-        <v>47.44</v>
+        <v>45.7</v>
       </c>
       <c r="N2" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="O2" t="n">
         <v>-1</v>
       </c>
       <c r="P2" t="n">
-        <v>9.779999999999999</v>
+        <v>10.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>16.56</v>
+        <v>16.2</v>
       </c>
       <c r="R2" t="n">
-        <v>5.67</v>
+        <v>6.1</v>
       </c>
       <c r="S2" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="T2" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="U2" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="V2" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>46.78</v>
+        <v>45.6</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>14.33</v>
+        <v>14.6</v>
       </c>
       <c r="AA2" t="n">
-        <v>9.56</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.78</v>
+        <v>4.9</v>
       </c>
       <c r="AC2" t="n">
-        <v>23.11</v>
+        <v>21.1</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -1550,31 +1550,31 @@
         <v>1.67</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.61</v>
+        <v>2.53</v>
       </c>
       <c r="BH2" t="n">
-        <v>8.56</v>
+        <v>8.74</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.61</v>
+        <v>2.53</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="BP2" t="n">
         <v>-1</v>
@@ -1586,34 +1586,34 @@
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>77.78</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="BT2" t="n">
-        <v>50</v>
+        <v>47.37</v>
       </c>
       <c r="BU2" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BV2" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BW2" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX2" t="n">
-        <v>55.56</v>
+        <v>52.63</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.63</v>
+        <v>2.69</v>
       </c>
       <c r="BZ2" t="n">
-        <v>2.68</v>
+        <v>2.71</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.5</v>
+        <v>3.49</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.57</v>
+        <v>3.56</v>
       </c>
       <c r="CC2" t="n">
         <v>3.38</v>
@@ -1634,16 +1634,16 @@
         <v>1.4</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CJ2" t="n">
         <v>1.85</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CM2" t="n">
         <v>2.5</v>
@@ -1655,10 +1655,10 @@
         <v>1.32</v>
       </c>
       <c r="CP2" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.47</v>
+        <v>3.48</v>
       </c>
       <c r="CR2" t="n">
         <v>1.39</v>
@@ -1676,19 +1676,19 @@
         <v>2.02</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CY2" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="CZ2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="DA2" t="n">
         <v>1.91</v>
-      </c>
-      <c r="CZ2" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="DA2" t="n">
-        <v>1.9</v>
       </c>
       <c r="DB2" t="n">
         <v>1.33</v>
@@ -1700,46 +1700,46 @@
         <v>3.59</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="DG2" t="n">
         <v>-1</v>
       </c>
       <c r="DH2" t="n">
-        <v>92.61</v>
+        <v>91.37</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="DK2" t="n">
-        <v>4.44</v>
+        <v>4.47</v>
       </c>
       <c r="DL2" t="n">
         <v>-1</v>
       </c>
       <c r="DM2" t="n">
-        <v>44.83</v>
+        <v>44.05</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DO2" t="n">
         <v>-1</v>
       </c>
       <c r="DP2" t="n">
-        <v>11.94</v>
+        <v>12.05</v>
       </c>
       <c r="DQ2" t="n">
-        <v>16.83</v>
+        <v>16.63</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.56</v>
+        <v>6.73</v>
       </c>
       <c r="DS2" t="n">
         <v>0.16</v>
@@ -1751,28 +1751,28 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>46.56</v>
+        <v>45.95</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.34</v>
+        <v>0.32</v>
       </c>
       <c r="DX2" t="n">
-        <v>12.56</v>
+        <v>12.79</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.73</v>
+        <v>8.84</v>
       </c>
       <c r="DZ2" t="n">
-        <v>3.84</v>
+        <v>3.95</v>
       </c>
       <c r="EA2" t="n">
-        <v>22.33</v>
+        <v>21.32</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="3">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C5" t="n">
         <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
         <v>0.33</v>
@@ -2681,109 +2681,109 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AH5" t="n">
         <v>-1</v>
       </c>
       <c r="AI5" t="n">
-        <v>96.44</v>
+        <v>97.8</v>
       </c>
       <c r="AJ5" t="n">
         <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.67</v>
+        <v>2.4</v>
       </c>
       <c r="AL5" t="n">
-        <v>5.44</v>
+        <v>5.6</v>
       </c>
       <c r="AM5" t="n">
         <v>-1</v>
       </c>
       <c r="AN5" t="n">
-        <v>43.67</v>
+        <v>45.3</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AP5" t="n">
         <v>-1</v>
       </c>
       <c r="AQ5" t="n">
-        <v>12.78</v>
+        <v>12.8</v>
       </c>
       <c r="AR5" t="n">
-        <v>13.11</v>
+        <v>13.6</v>
       </c>
       <c r="AS5" t="n">
-        <v>11</v>
+        <v>10.2</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>52</v>
+        <v>53.3</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="BA5" t="n">
-        <v>12.22</v>
+        <v>13.1</v>
       </c>
       <c r="BB5" t="n">
-        <v>8.220000000000001</v>
+        <v>9</v>
       </c>
       <c r="BC5" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BD5" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.61</v>
+        <v>2.53</v>
       </c>
       <c r="BH5" t="n">
-        <v>10.67</v>
+        <v>10.74</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.61</v>
+        <v>2.53</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="BN5" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="BP5" t="n">
         <v>-1</v>
@@ -2792,25 +2792,25 @@
         <v>-1</v>
       </c>
       <c r="BR5" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS5" t="n">
-        <v>66.67</v>
+        <v>63.16</v>
       </c>
       <c r="BT5" t="n">
-        <v>44.44</v>
+        <v>42.11</v>
       </c>
       <c r="BU5" t="n">
-        <v>33.33</v>
+        <v>31.58</v>
       </c>
       <c r="BV5" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BW5" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX5" t="n">
-        <v>50</v>
+        <v>47.37</v>
       </c>
       <c r="BY5" t="n">
         <v>1.82</v>
@@ -2819,43 +2819,43 @@
         <v>1.9</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.75</v>
+        <v>3.73</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.87</v>
+        <v>3.84</v>
       </c>
       <c r="CC5" t="n">
-        <v>2.96</v>
+        <v>2.91</v>
       </c>
       <c r="CD5" t="n">
-        <v>3.2</v>
+        <v>3.13</v>
       </c>
       <c r="CE5" t="n">
         <v>1.38</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.02</v>
+        <v>3.01</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CI5" t="n">
         <v>1.96</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CK5" t="n">
         <v>1.49</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="CN5" t="n">
         <v>1.88</v>
@@ -2864,10 +2864,10 @@
         <v>1.27</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="CR5" t="n">
         <v>1.42</v>
@@ -2882,106 +2882,106 @@
         <v>1.4</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CW5" t="n">
         <v>1.83</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="DB5" t="n">
         <v>1.3</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.32</v>
+        <v>3.34</v>
       </c>
       <c r="DE5" t="n">
         <v>0.16</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="DG5" t="n">
         <v>-1</v>
       </c>
       <c r="DH5" t="n">
-        <v>100.88</v>
+        <v>101.37</v>
       </c>
       <c r="DI5" t="n">
         <v>0</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="DK5" t="n">
-        <v>5</v>
+        <v>5.11</v>
       </c>
       <c r="DL5" t="n">
         <v>-1</v>
       </c>
       <c r="DM5" t="n">
-        <v>48.56</v>
+        <v>49.16</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="DO5" t="n">
         <v>-1</v>
       </c>
       <c r="DP5" t="n">
-        <v>12.06</v>
+        <v>12.1</v>
       </c>
       <c r="DQ5" t="n">
-        <v>15.39</v>
+        <v>15.53</v>
       </c>
       <c r="DR5" t="n">
-        <v>9.66</v>
+        <v>9.31</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>55.11</v>
+        <v>55.63</v>
       </c>
       <c r="DW5" t="n">
         <v>0.16</v>
       </c>
       <c r="DX5" t="n">
-        <v>13.33</v>
+        <v>13.73</v>
       </c>
       <c r="DY5" t="n">
-        <v>8.609999999999999</v>
+        <v>9</v>
       </c>
       <c r="DZ5" t="n">
-        <v>4.72</v>
+        <v>4.73</v>
       </c>
       <c r="EA5" t="n">
-        <v>20.89</v>
+        <v>20.95</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="6">
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D6" t="n">
         <v>9</v>
@@ -3003,82 +3003,82 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="G6" t="n">
         <v>-1</v>
       </c>
       <c r="H6" t="n">
-        <v>102</v>
+        <v>101.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="J6" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="K6" t="n">
-        <v>6.11</v>
+        <v>5.8</v>
       </c>
       <c r="L6" t="n">
         <v>-1</v>
       </c>
       <c r="M6" t="n">
-        <v>54</v>
+        <v>53.5</v>
       </c>
       <c r="N6" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="O6" t="n">
         <v>-1</v>
       </c>
       <c r="P6" t="n">
-        <v>12.78</v>
+        <v>12.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>17.78</v>
+        <v>17.7</v>
       </c>
       <c r="R6" t="n">
-        <v>4.67</v>
+        <v>4.9</v>
       </c>
       <c r="S6" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="T6" t="n">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="U6" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="V6" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>57.89</v>
+        <v>57.3</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>17.11</v>
+        <v>16.7</v>
       </c>
       <c r="AA6" t="n">
-        <v>11.22</v>
+        <v>10.9</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.89</v>
+        <v>5.8</v>
       </c>
       <c r="AC6" t="n">
-        <v>21.67</v>
+        <v>20.7</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AF6" t="n">
         <v>0.11</v>
@@ -3162,31 +3162,31 @@
         <v>2.44</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.609999999999999</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.68</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="BL6" t="n">
         <v>1</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="BP6" t="n">
         <v>-1</v>
@@ -3195,37 +3195,37 @@
         <v>-1</v>
       </c>
       <c r="BR6" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS6" t="n">
-        <v>77.78</v>
+        <v>78.95</v>
       </c>
       <c r="BT6" t="n">
-        <v>61.11</v>
+        <v>63.16</v>
       </c>
       <c r="BU6" t="n">
-        <v>33.33</v>
+        <v>36.84</v>
       </c>
       <c r="BV6" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BW6" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX6" t="n">
-        <v>66.67</v>
+        <v>63.16</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="BZ6" t="n">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.79</v>
+        <v>3.87</v>
       </c>
       <c r="CB6" t="n">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="CC6" t="n">
         <v>2.72</v>
@@ -3237,16 +3237,16 @@
         <v>1.33</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="CH6" t="n">
         <v>1.5</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CJ6" t="n">
         <v>1.7</v>
@@ -3255,7 +3255,7 @@
         <v>1.44</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CM6" t="n">
         <v>2.57</v>
@@ -3267,28 +3267,28 @@
         <v>1.23</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.85</v>
+        <v>2.83</v>
       </c>
       <c r="CR6" t="n">
         <v>1.35</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.59</v>
+        <v>2.55</v>
       </c>
       <c r="CT6" t="n">
         <v>3.22</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CX6" t="n">
         <v>1.54</v>
@@ -3306,85 +3306,85 @@
         <v>1.26</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.07</v>
+        <v>3.03</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="DG6" t="n">
         <v>-1</v>
       </c>
       <c r="DH6" t="n">
-        <v>96.66</v>
+        <v>96.52</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="DK6" t="n">
-        <v>5.39</v>
+        <v>5.26</v>
       </c>
       <c r="DL6" t="n">
         <v>-1</v>
       </c>
       <c r="DM6" t="n">
-        <v>50.84</v>
+        <v>50.74</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="DO6" t="n">
         <v>-1</v>
       </c>
       <c r="DP6" t="n">
-        <v>13.84</v>
+        <v>13.53</v>
       </c>
       <c r="DQ6" t="n">
         <v>16.89</v>
       </c>
       <c r="DR6" t="n">
-        <v>5.56</v>
+        <v>5.63</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>54.94</v>
+        <v>54.79</v>
       </c>
       <c r="DW6" t="n">
         <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>15.72</v>
+        <v>15.58</v>
       </c>
       <c r="DY6" t="n">
-        <v>11</v>
+        <v>10.84</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.72</v>
+        <v>4.74</v>
       </c>
       <c r="EA6" t="n">
-        <v>21.89</v>
+        <v>21.37</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="EC6" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="7">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D7" t="n">
         <v>9</v>
@@ -3406,82 +3406,82 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="G7" t="n">
         <v>-1</v>
       </c>
       <c r="H7" t="n">
-        <v>78.44</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="K7" t="n">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="L7" t="n">
         <v>-1</v>
       </c>
       <c r="M7" t="n">
-        <v>36.56</v>
+        <v>36</v>
       </c>
       <c r="N7" t="n">
-        <v>0.78</v>
+        <v>0.9</v>
       </c>
       <c r="O7" t="n">
         <v>-1</v>
       </c>
       <c r="P7" t="n">
-        <v>13.11</v>
+        <v>13.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>15</v>
+        <v>14.4</v>
       </c>
       <c r="R7" t="n">
-        <v>7.67</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="S7" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="T7" t="n">
-        <v>0.67</v>
+        <v>0.8</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>46.78</v>
+        <v>46</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>8.44</v>
+        <v>8.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="AC7" t="n">
-        <v>17.56</v>
+        <v>16.9</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="AE7" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -3565,31 +3565,31 @@
         <v>2.44</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.17</v>
+        <v>3.26</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.279999999999999</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.17</v>
+        <v>3.26</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="BK7" t="n">
         <v>0.89</v>
       </c>
       <c r="BL7" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.72</v>
+        <v>0.79</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="BP7" t="n">
         <v>-1</v>
@@ -3598,37 +3598,37 @@
         <v>-1</v>
       </c>
       <c r="BR7" t="n">
-        <v>88.89</v>
+        <v>89.47</v>
       </c>
       <c r="BS7" t="n">
-        <v>83.33</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BT7" t="n">
-        <v>66.67</v>
+        <v>68.42</v>
       </c>
       <c r="BU7" t="n">
-        <v>38.89</v>
+        <v>42.11</v>
       </c>
       <c r="BV7" t="n">
-        <v>22.22</v>
+        <v>26.32</v>
       </c>
       <c r="BW7" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BX7" t="n">
-        <v>55.56</v>
+        <v>57.89</v>
       </c>
       <c r="BY7" t="n">
-        <v>4.12</v>
+        <v>4.28</v>
       </c>
       <c r="BZ7" t="n">
-        <v>4.17</v>
+        <v>4.42</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.67</v>
+        <v>3.68</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.86</v>
+        <v>3.89</v>
       </c>
       <c r="CC7" t="n">
         <v>4.89</v>
@@ -3640,7 +3640,7 @@
         <v>1.4</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="CG7" t="n">
         <v>3</v>
@@ -3649,28 +3649,28 @@
         <v>1.42</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CK7" t="n">
         <v>1.51</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CM7" t="n">
         <v>2.43</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CO7" t="n">
         <v>1.3</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CQ7" t="n">
         <v>3.41</v>
@@ -3688,106 +3688,106 @@
         <v>1.41</v>
       </c>
       <c r="CV7" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CY7" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.75</v>
+        <v>3.72</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="DG7" t="n">
         <v>-1</v>
       </c>
       <c r="DH7" t="n">
-        <v>81.06</v>
+        <v>80.37</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.28</v>
+        <v>2.42</v>
       </c>
       <c r="DK7" t="n">
-        <v>3.44</v>
+        <v>3.48</v>
       </c>
       <c r="DL7" t="n">
         <v>-1</v>
       </c>
       <c r="DM7" t="n">
-        <v>35.12</v>
+        <v>34.9</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.84</v>
+        <v>0.9</v>
       </c>
       <c r="DO7" t="n">
         <v>-1</v>
       </c>
       <c r="DP7" t="n">
-        <v>14.11</v>
+        <v>14.16</v>
       </c>
       <c r="DQ7" t="n">
-        <v>14.78</v>
+        <v>14.48</v>
       </c>
       <c r="DR7" t="n">
-        <v>8.390000000000001</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="DS7" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="DT7" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>46.89</v>
+        <v>46.47</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DX7" t="n">
-        <v>8.220000000000001</v>
+        <v>8.26</v>
       </c>
       <c r="DY7" t="n">
-        <v>5.72</v>
+        <v>5.68</v>
       </c>
       <c r="DZ7" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="EA7" t="n">
-        <v>18.28</v>
+        <v>17.89</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.22</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="8">
@@ -3815,7 +3815,7 @@
         <v>-1</v>
       </c>
       <c r="H8" t="n">
-        <v>96.09</v>
+        <v>95.45</v>
       </c>
       <c r="I8" t="n">
         <v>0.18</v>
@@ -3842,7 +3842,7 @@
         <v>13.82</v>
       </c>
       <c r="Q8" t="n">
-        <v>15.82</v>
+        <v>16.09</v>
       </c>
       <c r="R8" t="n">
         <v>6.36</v>
@@ -3863,16 +3863,16 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>59.73</v>
+        <v>59.82</v>
       </c>
       <c r="Y8" t="n">
         <v>0.27</v>
       </c>
       <c r="Z8" t="n">
-        <v>18.91</v>
+        <v>19</v>
       </c>
       <c r="AA8" t="n">
-        <v>13.64</v>
+        <v>13.73</v>
       </c>
       <c r="AB8" t="n">
         <v>5.27</v>
@@ -4127,7 +4127,7 @@
         <v>-1</v>
       </c>
       <c r="DH8" t="n">
-        <v>93.42</v>
+        <v>93.05</v>
       </c>
       <c r="DI8" t="n">
         <v>0.1</v>
@@ -4154,7 +4154,7 @@
         <v>13.74</v>
       </c>
       <c r="DQ8" t="n">
-        <v>17.37</v>
+        <v>17.53</v>
       </c>
       <c r="DR8" t="n">
         <v>7.26</v>
@@ -4169,16 +4169,16 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>58.53</v>
+        <v>58.58</v>
       </c>
       <c r="DW8" t="n">
         <v>0.21</v>
       </c>
       <c r="DX8" t="n">
-        <v>16.37</v>
+        <v>16.42</v>
       </c>
       <c r="DY8" t="n">
-        <v>11.53</v>
+        <v>11.58</v>
       </c>
       <c r="DZ8" t="n">
         <v>4.84</v>
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
         <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E9" t="n">
         <v>0.12</v>
@@ -4290,112 +4290,112 @@
         <v>1.88</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AH9" t="n">
         <v>-1</v>
       </c>
       <c r="AI9" t="n">
-        <v>73.8</v>
+        <v>75</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="AL9" t="n">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="AM9" t="n">
         <v>-1</v>
       </c>
       <c r="AN9" t="n">
-        <v>30.1</v>
+        <v>30</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.7</v>
+        <v>0.82</v>
       </c>
       <c r="AP9" t="n">
         <v>-1</v>
       </c>
       <c r="AQ9" t="n">
-        <v>14.7</v>
+        <v>14.64</v>
       </c>
       <c r="AR9" t="n">
-        <v>13.9</v>
+        <v>13.82</v>
       </c>
       <c r="AS9" t="n">
-        <v>8.6</v>
+        <v>8.27</v>
       </c>
       <c r="AT9" t="n">
-        <v>2.1</v>
+        <v>2.27</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>45.8</v>
+        <v>46</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="BA9" t="n">
-        <v>7.2</v>
+        <v>7.18</v>
       </c>
       <c r="BB9" t="n">
-        <v>4.8</v>
+        <v>4.91</v>
       </c>
       <c r="BC9" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="BD9" t="n">
-        <v>18.8</v>
+        <v>18.91</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.85</v>
+        <v>0.84</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="BH9" t="n">
-        <v>8.83</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.67</v>
+        <v>0.79</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BL9" t="n">
         <v>1.11</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="BP9" t="n">
         <v>-1</v>
@@ -4407,22 +4407,22 @@
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BT9" t="n">
-        <v>38.89</v>
+        <v>42.11</v>
       </c>
       <c r="BU9" t="n">
-        <v>33.33</v>
+        <v>36.84</v>
       </c>
       <c r="BV9" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BW9" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX9" t="n">
-        <v>50</v>
+        <v>47.37</v>
       </c>
       <c r="BY9" t="n">
         <v>3.54</v>
@@ -4431,43 +4431,43 @@
         <v>3.82</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.8</v>
+        <v>3.88</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.92</v>
+        <v>3.98</v>
       </c>
       <c r="CC9" t="n">
-        <v>5.43</v>
+        <v>5.61</v>
       </c>
       <c r="CD9" t="n">
-        <v>5.78</v>
+        <v>5.9</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.85</v>
+        <v>2.82</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.97</v>
+        <v>3.01</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CI9" t="n">
         <v>1.93</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CL9" t="n">
         <v>2.04</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="CN9" t="n">
         <v>1.85</v>
@@ -4476,22 +4476,22 @@
         <v>1.3</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.39</v>
+        <v>3.34</v>
       </c>
       <c r="CR9" t="n">
         <v>1.43</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.98</v>
+        <v>2.89</v>
       </c>
       <c r="CT9" t="n">
         <v>2.93</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="CV9" t="n">
         <v>1.94</v>
@@ -4512,88 +4512,88 @@
         <v>1.81</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.54</v>
+        <v>3.46</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="DG9" t="n">
         <v>-1</v>
       </c>
       <c r="DH9" t="n">
-        <v>77.61</v>
+        <v>78.11</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="DK9" t="n">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="DL9" t="n">
         <v>-1</v>
       </c>
       <c r="DM9" t="n">
-        <v>34.11</v>
+        <v>33.84</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.61</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DO9" t="n">
         <v>-1</v>
       </c>
       <c r="DP9" t="n">
-        <v>14.44</v>
+        <v>14.42</v>
       </c>
       <c r="DQ9" t="n">
-        <v>14.28</v>
+        <v>14.21</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.83</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>45.94</v>
+        <v>46.05</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="DX9" t="n">
-        <v>8.17</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="DY9" t="n">
-        <v>5.61</v>
+        <v>5.63</v>
       </c>
       <c r="DZ9" t="n">
-        <v>2.56</v>
+        <v>2.47</v>
       </c>
       <c r="EA9" t="n">
-        <v>19.72</v>
+        <v>19.74</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.95</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="10">
@@ -4777,7 +4777,7 @@
         <v>3.42</v>
       </c>
       <c r="BH10" t="n">
-        <v>8.74</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="BI10" t="n">
         <v>3.42</v>
@@ -5517,7 +5517,7 @@
         <v>3</v>
       </c>
       <c r="AL12" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AM12" t="n">
         <v>-1</v>
@@ -5583,7 +5583,7 @@
         <v>2.26</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.630000000000001</v>
+        <v>9.68</v>
       </c>
       <c r="BI12" t="n">
         <v>2.26</v>
@@ -5748,7 +5748,7 @@
         <v>2.84</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.05</v>
+        <v>4.11</v>
       </c>
       <c r="DL12" t="n">
         <v>-1</v>
@@ -6308,19 +6308,19 @@
         <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AH14" t="n">
         <v>-1</v>
       </c>
       <c r="AI14" t="n">
-        <v>90.40000000000001</v>
+        <v>89.8</v>
       </c>
       <c r="AJ14" t="n">
         <v>0.2</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AL14" t="n">
         <v>4</v>
@@ -6341,7 +6341,7 @@
         <v>15.3</v>
       </c>
       <c r="AR14" t="n">
-        <v>17.2</v>
+        <v>17.5</v>
       </c>
       <c r="AS14" t="n">
         <v>6.8</v>
@@ -6362,16 +6362,16 @@
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>46.9</v>
+        <v>46.8</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="BA14" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="BB14" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="BC14" t="n">
         <v>4</v>
@@ -6380,7 +6380,7 @@
         <v>21</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="BF14" t="n">
         <v>2.4</v>
@@ -6539,19 +6539,19 @@
         <v>0.05</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="DG14" t="n">
         <v>-1</v>
       </c>
       <c r="DH14" t="n">
-        <v>96.16</v>
+        <v>95.84</v>
       </c>
       <c r="DI14" t="n">
         <v>0.16</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.63</v>
+        <v>2.74</v>
       </c>
       <c r="DK14" t="n">
         <v>4.1</v>
@@ -6572,7 +6572,7 @@
         <v>14.84</v>
       </c>
       <c r="DQ14" t="n">
-        <v>17.37</v>
+        <v>17.53</v>
       </c>
       <c r="DR14" t="n">
         <v>6.32</v>
@@ -6587,16 +6587,16 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>49.42</v>
+        <v>49.37</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.21</v>
+        <v>0.26</v>
       </c>
       <c r="DX14" t="n">
-        <v>12.53</v>
+        <v>12.58</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.74</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="DZ14" t="n">
         <v>3.79</v>
@@ -7021,13 +7021,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C16" t="n">
         <v>10</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E16" t="n">
         <v>0.1</v>
@@ -7114,109 +7114,109 @@
         <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.12</v>
+        <v>1.33</v>
       </c>
       <c r="AH16" t="n">
         <v>-1</v>
       </c>
       <c r="AI16" t="n">
-        <v>92.62</v>
+        <v>94.22</v>
       </c>
       <c r="AJ16" t="n">
         <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AL16" t="n">
-        <v>5.62</v>
+        <v>5.67</v>
       </c>
       <c r="AM16" t="n">
         <v>-1</v>
       </c>
       <c r="AN16" t="n">
-        <v>47.88</v>
+        <v>49.56</v>
       </c>
       <c r="AO16" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AP16" t="n">
         <v>-1</v>
       </c>
       <c r="AQ16" t="n">
-        <v>16.88</v>
+        <v>16</v>
       </c>
       <c r="AR16" t="n">
         <v>16</v>
       </c>
       <c r="AS16" t="n">
-        <v>5.88</v>
+        <v>5.89</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="AX16" t="n">
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>63.5</v>
+        <v>63.22</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA16" t="n">
-        <v>13.25</v>
+        <v>13.56</v>
       </c>
       <c r="BB16" t="n">
-        <v>9.119999999999999</v>
+        <v>9.33</v>
       </c>
       <c r="BC16" t="n">
-        <v>4.12</v>
+        <v>4.22</v>
       </c>
       <c r="BD16" t="n">
-        <v>19.25</v>
+        <v>19.22</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="BF16" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.72</v>
+        <v>2.84</v>
       </c>
       <c r="BH16" t="n">
-        <v>9</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.72</v>
+        <v>2.84</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.72</v>
+        <v>0.79</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.78</v>
+        <v>0.84</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="BP16" t="n">
         <v>-1</v>
@@ -7228,22 +7228,22 @@
         <v>100</v>
       </c>
       <c r="BS16" t="n">
-        <v>77.78</v>
+        <v>78.95</v>
       </c>
       <c r="BT16" t="n">
-        <v>55.56</v>
+        <v>57.89</v>
       </c>
       <c r="BU16" t="n">
-        <v>22.22</v>
+        <v>26.32</v>
       </c>
       <c r="BV16" t="n">
-        <v>11.11</v>
+        <v>15.79</v>
       </c>
       <c r="BW16" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX16" t="n">
-        <v>61.11</v>
+        <v>63.16</v>
       </c>
       <c r="BY16" t="n">
         <v>1.68</v>
@@ -7252,16 +7252,16 @@
         <v>1.7</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.87</v>
+        <v>3.88</v>
       </c>
       <c r="CB16" t="n">
-        <v>4.18</v>
+        <v>4.19</v>
       </c>
       <c r="CC16" t="n">
-        <v>2.33</v>
+        <v>2.24</v>
       </c>
       <c r="CD16" t="n">
-        <v>2.41</v>
+        <v>2.31</v>
       </c>
       <c r="CE16" t="n">
         <v>1.37</v>
@@ -7273,34 +7273,34 @@
         <v>3.05</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CI16" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="CJ16" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="CK16" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="CL16" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="CM16" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="CN16" t="n">
         <v>1.98</v>
-      </c>
-      <c r="CJ16" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="CK16" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="CL16" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="CM16" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="CN16" t="n">
-        <v>1.99</v>
       </c>
       <c r="CO16" t="n">
         <v>1.26</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CQ16" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="CR16" t="n">
         <v>1.41</v>
@@ -7315,106 +7315,106 @@
         <v>1.45</v>
       </c>
       <c r="CV16" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CX16" t="n">
         <v>1.54</v>
       </c>
       <c r="CY16" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="DA16" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="DB16" t="n">
         <v>1.31</v>
       </c>
       <c r="DC16" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="DD16" t="n">
-        <v>3.42</v>
+        <v>3.41</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="DG16" t="n">
         <v>-1</v>
       </c>
       <c r="DH16" t="n">
-        <v>96.94</v>
+        <v>97.47</v>
       </c>
       <c r="DI16" t="n">
         <v>0</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="DK16" t="n">
-        <v>5.39</v>
+        <v>5.42</v>
       </c>
       <c r="DL16" t="n">
         <v>-1</v>
       </c>
       <c r="DM16" t="n">
-        <v>49.11</v>
+        <v>49.84</v>
       </c>
       <c r="DN16" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="DO16" t="n">
         <v>-1</v>
       </c>
       <c r="DP16" t="n">
-        <v>16.17</v>
+        <v>15.79</v>
       </c>
       <c r="DQ16" t="n">
-        <v>16.17</v>
+        <v>16.16</v>
       </c>
       <c r="DR16" t="n">
-        <v>6.39</v>
+        <v>6.37</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>61.5</v>
+        <v>61.47</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DX16" t="n">
-        <v>12.89</v>
+        <v>13.05</v>
       </c>
       <c r="DY16" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="DZ16" t="n">
-        <v>3.89</v>
+        <v>3.95</v>
       </c>
       <c r="EA16" t="n">
-        <v>21.33</v>
+        <v>21.21</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="17">

--- a/data/teams/leagues/Averages_Russian_Premier_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Russian_Premier_League_2025-2026.xlsx
@@ -3869,19 +3869,19 @@
         <v>0.27</v>
       </c>
       <c r="Z8" t="n">
-        <v>19</v>
+        <v>19.09</v>
       </c>
       <c r="AA8" t="n">
         <v>13.73</v>
       </c>
       <c r="AB8" t="n">
-        <v>5.27</v>
+        <v>5.36</v>
       </c>
       <c r="AC8" t="n">
         <v>20.73</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AE8" t="n">
         <v>2.55</v>
@@ -4175,19 +4175,19 @@
         <v>0.21</v>
       </c>
       <c r="DX8" t="n">
-        <v>16.42</v>
+        <v>16.48</v>
       </c>
       <c r="DY8" t="n">
         <v>11.58</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.84</v>
+        <v>4.89</v>
       </c>
       <c r="EA8" t="n">
         <v>21.32</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="EC8" t="n">
         <v>2.21</v>
@@ -6368,10 +6368,10 @@
         <v>0.2</v>
       </c>
       <c r="BA14" t="n">
-        <v>12</v>
+        <v>11.8</v>
       </c>
       <c r="BB14" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BC14" t="n">
         <v>4</v>
@@ -6380,7 +6380,7 @@
         <v>21</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="BF14" t="n">
         <v>2.4</v>
@@ -6593,10 +6593,10 @@
         <v>0.26</v>
       </c>
       <c r="DX14" t="n">
-        <v>12.58</v>
+        <v>12.47</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.789999999999999</v>
+        <v>8.69</v>
       </c>
       <c r="DZ14" t="n">
         <v>3.79</v>
@@ -6605,7 +6605,7 @@
         <v>21.05</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="EC14" t="n">
         <v>2.42</v>

--- a/data/teams/leagues/Averages_Russian_Premier_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Russian_Premier_League_2025-2026.xlsx
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C4" t="n">
         <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E4" t="n">
         <v>0.33</v>
@@ -2275,112 +2275,112 @@
         <v>2.67</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AG4" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>93.81999999999999</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>42.82</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>19.27</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>12.73</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>47.45</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>11.73</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>7.64</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>20.82</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="BG4" t="n">
         <v>1.7</v>
       </c>
-      <c r="AH4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>93.09999999999999</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>43.4</v>
-      </c>
-      <c r="AO4" t="n">
+      <c r="BH4" t="n">
+        <v>8.15</v>
+      </c>
+      <c r="BI4" t="n">
         <v>1.7</v>
       </c>
-      <c r="AP4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AT4" t="n">
+      <c r="BJ4" t="n">
         <v>0.4</v>
       </c>
-      <c r="AU4" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>47.1</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>8.26</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>0.42</v>
-      </c>
       <c r="BK4" t="n">
-        <v>0.37</v>
+        <v>0.4</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.42</v>
+        <v>0.45</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BP4" t="n">
         <v>-1</v>
@@ -2389,25 +2389,25 @@
         <v>-1</v>
       </c>
       <c r="BR4" t="n">
-        <v>78.95</v>
+        <v>80</v>
       </c>
       <c r="BS4" t="n">
-        <v>63.16</v>
+        <v>65</v>
       </c>
       <c r="BT4" t="n">
-        <v>15.79</v>
+        <v>15</v>
       </c>
       <c r="BU4" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BV4" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>26.32</v>
+        <v>30</v>
       </c>
       <c r="BY4" t="n">
         <v>2.46</v>
@@ -2416,25 +2416,25 @@
         <v>2.65</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.51</v>
+        <v>3.49</v>
       </c>
       <c r="CC4" t="n">
-        <v>3.71</v>
+        <v>3.61</v>
       </c>
       <c r="CD4" t="n">
-        <v>4</v>
+        <v>3.89</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CF4" t="n">
-        <v>3.02</v>
+        <v>3.05</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="CH4" t="n">
         <v>1.27</v>
@@ -2446,25 +2446,25 @@
         <v>1.94</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.95</v>
+        <v>3.99</v>
       </c>
       <c r="CR4" t="n">
         <v>1.47</v>
@@ -2485,100 +2485,100 @@
         <v>2.11</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="DD4" t="n">
-        <v>4.37</v>
+        <v>4.45</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="DG4" t="n">
         <v>-1</v>
       </c>
       <c r="DH4" t="n">
-        <v>88.31999999999999</v>
+        <v>88.95</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DJ4" t="n">
-        <v>3.16</v>
+        <v>3.2</v>
       </c>
       <c r="DK4" t="n">
-        <v>3.42</v>
+        <v>3.35</v>
       </c>
       <c r="DL4" t="n">
         <v>-1</v>
       </c>
       <c r="DM4" t="n">
-        <v>44.48</v>
+        <v>44.1</v>
       </c>
       <c r="DN4" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="DO4" t="n">
         <v>-1</v>
       </c>
       <c r="DP4" t="n">
-        <v>19.42</v>
+        <v>19.35</v>
       </c>
       <c r="DQ4" t="n">
-        <v>12.74</v>
+        <v>12.55</v>
       </c>
       <c r="DR4" t="n">
-        <v>7.69</v>
+        <v>7.8</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>45.26</v>
+        <v>45.55</v>
       </c>
       <c r="DW4" t="n">
         <v>0.1</v>
       </c>
       <c r="DX4" t="n">
-        <v>12.53</v>
+        <v>12.25</v>
       </c>
       <c r="DY4" t="n">
-        <v>8.470000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="DZ4" t="n">
         <v>4.05</v>
       </c>
       <c r="EA4" t="n">
-        <v>21.37</v>
+        <v>21.35</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="EC4" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
     </row>
     <row r="5">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" t="n">
         <v>10</v>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3487,109 +3487,109 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AH7" t="n">
         <v>-1</v>
       </c>
       <c r="AI7" t="n">
-        <v>83.67</v>
+        <v>84.3</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="AL7" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="AM7" t="n">
         <v>-1</v>
       </c>
       <c r="AN7" t="n">
-        <v>33.67</v>
+        <v>33.1</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AP7" t="n">
         <v>-1</v>
       </c>
       <c r="AQ7" t="n">
-        <v>15.11</v>
+        <v>15.1</v>
       </c>
       <c r="AR7" t="n">
-        <v>14.56</v>
+        <v>14.1</v>
       </c>
       <c r="AS7" t="n">
-        <v>9.109999999999999</v>
+        <v>9</v>
       </c>
       <c r="AT7" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AX7" t="n">
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>47</v>
+        <v>47.3</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA7" t="n">
-        <v>8</v>
+        <v>7.7</v>
       </c>
       <c r="BB7" t="n">
-        <v>5.44</v>
+        <v>5.1</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="BD7" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.369999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.37</v>
+        <v>0.4</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.89</v>
+        <v>0.85</v>
       </c>
       <c r="BL7" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BN7" t="n">
         <v>2</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="BP7" t="n">
         <v>-1</v>
@@ -3598,25 +3598,25 @@
         <v>-1</v>
       </c>
       <c r="BR7" t="n">
-        <v>89.47</v>
+        <v>90</v>
       </c>
       <c r="BS7" t="n">
-        <v>84.20999999999999</v>
+        <v>85</v>
       </c>
       <c r="BT7" t="n">
-        <v>68.42</v>
+        <v>70</v>
       </c>
       <c r="BU7" t="n">
-        <v>42.11</v>
+        <v>40</v>
       </c>
       <c r="BV7" t="n">
-        <v>26.32</v>
+        <v>25</v>
       </c>
       <c r="BW7" t="n">
-        <v>15.79</v>
+        <v>15</v>
       </c>
       <c r="BX7" t="n">
-        <v>57.89</v>
+        <v>60</v>
       </c>
       <c r="BY7" t="n">
         <v>4.28</v>
@@ -3625,25 +3625,25 @@
         <v>4.42</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.68</v>
+        <v>3.65</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.89</v>
+        <v>3.85</v>
       </c>
       <c r="CC7" t="n">
-        <v>4.89</v>
+        <v>4.7</v>
       </c>
       <c r="CD7" t="n">
-        <v>5.52</v>
+        <v>5.33</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="CG7" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="CH7" t="n">
         <v>1.42</v>
@@ -3658,22 +3658,22 @@
         <v>1.51</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="CN7" t="n">
         <v>1.86</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.41</v>
+        <v>3.43</v>
       </c>
       <c r="CR7" t="n">
         <v>1.48</v>
@@ -3697,7 +3697,7 @@
         <v>1.61</v>
       </c>
       <c r="CY7" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CZ7" t="n">
         <v>2.29</v>
@@ -3706,88 +3706,88 @@
         <v>1.81</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.72</v>
+        <v>3.75</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="DG7" t="n">
         <v>-1</v>
       </c>
       <c r="DH7" t="n">
-        <v>80.37</v>
+        <v>80.84999999999999</v>
       </c>
       <c r="DI7" t="n">
         <v>0.1</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.42</v>
+        <v>2.35</v>
       </c>
       <c r="DK7" t="n">
-        <v>3.48</v>
+        <v>3.35</v>
       </c>
       <c r="DL7" t="n">
         <v>-1</v>
       </c>
       <c r="DM7" t="n">
-        <v>34.9</v>
+        <v>34.55</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="DO7" t="n">
         <v>-1</v>
       </c>
       <c r="DP7" t="n">
-        <v>14.16</v>
+        <v>14.2</v>
       </c>
       <c r="DQ7" t="n">
-        <v>14.48</v>
+        <v>14.25</v>
       </c>
       <c r="DR7" t="n">
-        <v>8.890000000000001</v>
+        <v>8.85</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>46.47</v>
+        <v>46.65</v>
       </c>
       <c r="DW7" t="n">
         <v>0.05</v>
       </c>
       <c r="DX7" t="n">
-        <v>8.26</v>
+        <v>8.1</v>
       </c>
       <c r="DY7" t="n">
-        <v>5.68</v>
+        <v>5.5</v>
       </c>
       <c r="DZ7" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="EA7" t="n">
-        <v>17.89</v>
+        <v>17.7</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="8">
@@ -5409,10 +5409,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D12" t="n">
         <v>10</v>
@@ -5421,49 +5421,49 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="G12" t="n">
         <v>-1</v>
       </c>
       <c r="H12" t="n">
-        <v>90.44</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="K12" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="L12" t="n">
         <v>-1</v>
       </c>
       <c r="M12" t="n">
-        <v>45.56</v>
+        <v>47.2</v>
       </c>
       <c r="N12" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="O12" t="n">
         <v>-1</v>
       </c>
       <c r="P12" t="n">
-        <v>17.11</v>
+        <v>16.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>14.33</v>
+        <v>14.4</v>
       </c>
       <c r="R12" t="n">
-        <v>7.22</v>
+        <v>7.1</v>
       </c>
       <c r="S12" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T12" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -5475,28 +5475,28 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>47.33</v>
+        <v>47.6</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z12" t="n">
-        <v>12.33</v>
+        <v>13</v>
       </c>
       <c r="AA12" t="n">
-        <v>7.78</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AB12" t="n">
-        <v>4.56</v>
+        <v>4.7</v>
       </c>
       <c r="AC12" t="n">
-        <v>16.56</v>
+        <v>18.3</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -5580,31 +5580,31 @@
         <v>2.8</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.68</v>
+        <v>9.65</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="BP12" t="n">
         <v>-1</v>
@@ -5613,37 +5613,37 @@
         <v>-1</v>
       </c>
       <c r="BR12" t="n">
-        <v>89.47</v>
+        <v>90</v>
       </c>
       <c r="BS12" t="n">
-        <v>73.68000000000001</v>
+        <v>75</v>
       </c>
       <c r="BT12" t="n">
-        <v>47.37</v>
+        <v>50</v>
       </c>
       <c r="BU12" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BV12" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>31.58</v>
+        <v>35</v>
       </c>
       <c r="BY12" t="n">
-        <v>4.28</v>
+        <v>4.06</v>
       </c>
       <c r="BZ12" t="n">
-        <v>4.56</v>
+        <v>4.34</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.98</v>
+        <v>3.93</v>
       </c>
       <c r="CB12" t="n">
-        <v>4.31</v>
+        <v>4.25</v>
       </c>
       <c r="CC12" t="n">
         <v>6.98</v>
@@ -5652,13 +5652,13 @@
         <v>7.51</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.92</v>
+        <v>2.89</v>
       </c>
       <c r="CH12" t="n">
         <v>1.37</v>
@@ -5673,7 +5673,7 @@
         <v>1.4</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="CM12" t="n">
         <v>2.36</v>
@@ -5682,13 +5682,13 @@
         <v>1.81</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.09</v>
+        <v>3.14</v>
       </c>
       <c r="CR12" t="n">
         <v>1.45</v>
@@ -5712,97 +5712,97 @@
         <v>1.57</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.53</v>
+        <v>3.58</v>
       </c>
       <c r="DE12" t="n">
         <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="DG12" t="n">
         <v>-1</v>
       </c>
       <c r="DH12" t="n">
-        <v>83.47</v>
+        <v>85.65000000000001</v>
       </c>
       <c r="DI12" t="n">
         <v>0</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.11</v>
+        <v>4.3</v>
       </c>
       <c r="DL12" t="n">
         <v>-1</v>
       </c>
       <c r="DM12" t="n">
-        <v>38.9</v>
+        <v>40.05</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="DO12" t="n">
         <v>-1</v>
       </c>
       <c r="DP12" t="n">
-        <v>17.42</v>
+        <v>17.1</v>
       </c>
       <c r="DQ12" t="n">
-        <v>14.52</v>
+        <v>14.55</v>
       </c>
       <c r="DR12" t="n">
-        <v>8.210000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>43.47</v>
+        <v>43.8</v>
       </c>
       <c r="DW12" t="n">
         <v>0.1</v>
       </c>
       <c r="DX12" t="n">
-        <v>11.37</v>
+        <v>11.75</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.37</v>
+        <v>7.65</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="EA12" t="n">
-        <v>17.58</v>
+        <v>18.4</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="13">
@@ -6215,94 +6215,94 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D14" t="n">
         <v>10</v>
       </c>
       <c r="E14" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F14" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="G14" t="n">
         <v>-1</v>
       </c>
       <c r="H14" t="n">
-        <v>102.56</v>
+        <v>102.6</v>
       </c>
       <c r="I14" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="J14" t="n">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="K14" t="n">
-        <v>4.22</v>
+        <v>4.2</v>
       </c>
       <c r="L14" t="n">
         <v>-1</v>
       </c>
       <c r="M14" t="n">
-        <v>56.11</v>
+        <v>56</v>
       </c>
       <c r="N14" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="O14" t="n">
         <v>-1</v>
       </c>
       <c r="P14" t="n">
-        <v>14.33</v>
+        <v>13.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>17.56</v>
+        <v>17.5</v>
       </c>
       <c r="R14" t="n">
-        <v>5.78</v>
+        <v>5.8</v>
       </c>
       <c r="S14" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="T14" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="U14" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V14" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>52.22</v>
+        <v>51.9</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>13.22</v>
+        <v>13.4</v>
       </c>
       <c r="AA14" t="n">
-        <v>9.67</v>
+        <v>9.9</v>
       </c>
       <c r="AB14" t="n">
-        <v>3.56</v>
+        <v>3.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>21.11</v>
+        <v>21.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -6389,28 +6389,28 @@
         <v>2</v>
       </c>
       <c r="BH14" t="n">
-        <v>7.68</v>
+        <v>7.6</v>
       </c>
       <c r="BI14" t="n">
         <v>2</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.37</v>
+        <v>0.4</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BP14" t="n">
         <v>-1</v>
@@ -6419,37 +6419,37 @@
         <v>-1</v>
       </c>
       <c r="BR14" t="n">
-        <v>89.47</v>
+        <v>90</v>
       </c>
       <c r="BS14" t="n">
-        <v>52.63</v>
+        <v>55</v>
       </c>
       <c r="BT14" t="n">
-        <v>26.32</v>
+        <v>25</v>
       </c>
       <c r="BU14" t="n">
-        <v>15.79</v>
+        <v>15</v>
       </c>
       <c r="BV14" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BW14" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX14" t="n">
-        <v>42.11</v>
+        <v>45</v>
       </c>
       <c r="BY14" t="n">
-        <v>2.34</v>
+        <v>2.39</v>
       </c>
       <c r="BZ14" t="n">
-        <v>2.41</v>
+        <v>2.45</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.63</v>
+        <v>3.59</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.7</v>
+        <v>3.66</v>
       </c>
       <c r="CC14" t="n">
         <v>4.29</v>
@@ -6458,43 +6458,43 @@
         <v>4.37</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.96</v>
+        <v>2.93</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CL14" t="n">
         <v>2.16</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CP14" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.43</v>
+        <v>3.49</v>
       </c>
       <c r="CR14" t="n">
         <v>1.37</v>
@@ -6509,49 +6509,49 @@
         <v>1.46</v>
       </c>
       <c r="CV14" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="CY14" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.24</v>
+        <v>2.21</v>
       </c>
       <c r="DA14" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="DB14" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="DC14" t="n">
-        <v>2.04</v>
+        <v>2.09</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.56</v>
+        <v>3.7</v>
       </c>
       <c r="DE14" t="n">
         <v>0.05</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="DG14" t="n">
         <v>-1</v>
       </c>
       <c r="DH14" t="n">
-        <v>95.84</v>
+        <v>96.2</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.74</v>
+        <v>2.6</v>
       </c>
       <c r="DK14" t="n">
         <v>4.1</v>
@@ -6560,55 +6560,55 @@
         <v>-1</v>
       </c>
       <c r="DM14" t="n">
-        <v>51.1</v>
+        <v>51.3</v>
       </c>
       <c r="DN14" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="DO14" t="n">
         <v>-1</v>
       </c>
       <c r="DP14" t="n">
-        <v>14.84</v>
+        <v>14.55</v>
       </c>
       <c r="DQ14" t="n">
-        <v>17.53</v>
+        <v>17.5</v>
       </c>
       <c r="DR14" t="n">
-        <v>6.32</v>
+        <v>6.3</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>49.37</v>
+        <v>49.35</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DX14" t="n">
-        <v>12.47</v>
+        <v>12.6</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.69</v>
+        <v>8.85</v>
       </c>
       <c r="DZ14" t="n">
-        <v>3.79</v>
+        <v>3.75</v>
       </c>
       <c r="EA14" t="n">
-        <v>21.05</v>
+        <v>21.2</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="15">

--- a/data/teams/leagues/Averages_Russian_Premier_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Russian_Premier_League_2025-2026.xlsx
@@ -645,7 +645,7 @@
     <col width="9.6" customWidth="1" min="73" max="73"/>
     <col width="9.6" customWidth="1" min="74" max="74"/>
     <col width="9.6" customWidth="1" min="75" max="75"/>
-    <col width="8.4" customWidth="1" min="76" max="76"/>
+    <col width="7.199999999999999" customWidth="1" min="76" max="76"/>
     <col width="18" customWidth="1" min="77" max="77"/>
     <col width="27.6" customWidth="1" min="78" max="78"/>
     <col width="18" customWidth="1" min="79" max="79"/>
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C2" t="n">
         <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" t="n">
         <v>0.3</v>
@@ -1472,109 +1472,109 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AH2" t="n">
         <v>-1</v>
       </c>
       <c r="AI2" t="n">
-        <v>93.22</v>
+        <v>92</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.78</v>
+        <v>2.6</v>
       </c>
       <c r="AL2" t="n">
-        <v>3.89</v>
+        <v>3.9</v>
       </c>
       <c r="AM2" t="n">
         <v>-1</v>
       </c>
       <c r="AN2" t="n">
-        <v>42.22</v>
+        <v>41.5</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AP2" t="n">
         <v>-1</v>
       </c>
       <c r="AQ2" t="n">
-        <v>14.11</v>
+        <v>13.8</v>
       </c>
       <c r="AR2" t="n">
-        <v>17.11</v>
+        <v>17.9</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.44</v>
+        <v>7.3</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>46.33</v>
+        <v>45.8</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="BA2" t="n">
-        <v>10.78</v>
+        <v>10.3</v>
       </c>
       <c r="BB2" t="n">
-        <v>7.89</v>
+        <v>7.4</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="BD2" t="n">
-        <v>21.56</v>
+        <v>21.4</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.53</v>
+        <v>2.6</v>
       </c>
       <c r="BH2" t="n">
-        <v>8.74</v>
+        <v>8.85</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.53</v>
+        <v>2.6</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.47</v>
+        <v>0.55</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="BP2" t="n">
         <v>-1</v>
@@ -1586,22 +1586,22 @@
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>73.68000000000001</v>
+        <v>75</v>
       </c>
       <c r="BT2" t="n">
-        <v>47.37</v>
+        <v>50</v>
       </c>
       <c r="BU2" t="n">
-        <v>21.05</v>
+        <v>25</v>
       </c>
       <c r="BV2" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BW2" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX2" t="n">
-        <v>52.63</v>
+        <v>55</v>
       </c>
       <c r="BY2" t="n">
         <v>2.69</v>
@@ -1610,169 +1610,169 @@
         <v>2.71</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.49</v>
+        <v>3.51</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.56</v>
+        <v>3.59</v>
       </c>
       <c r="CC2" t="n">
-        <v>3.38</v>
+        <v>3.51</v>
       </c>
       <c r="CD2" t="n">
-        <v>3.46</v>
+        <v>3.62</v>
       </c>
       <c r="CE2" t="n">
         <v>1.41</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.95</v>
+        <v>2.93</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="CH2" t="n">
         <v>1.4</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CM2" t="n">
         <v>2.5</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CO2" t="n">
         <v>1.32</v>
       </c>
       <c r="CP2" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="CV2" t="n">
         <v>2.04</v>
       </c>
-      <c r="CQ2" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="CR2" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="CS2" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="CT2" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="CU2" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="CV2" t="n">
-        <v>2.02</v>
-      </c>
       <c r="CW2" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CX2" t="n">
         <v>1.56</v>
       </c>
       <c r="CY2" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CZ2" t="n">
         <v>2.4</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.59</v>
+        <v>3.53</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="DG2" t="n">
         <v>-1</v>
       </c>
       <c r="DH2" t="n">
-        <v>91.37</v>
+        <v>90.84999999999999</v>
       </c>
       <c r="DI2" t="n">
         <v>0.1</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="DK2" t="n">
-        <v>4.47</v>
+        <v>4.45</v>
       </c>
       <c r="DL2" t="n">
         <v>-1</v>
       </c>
       <c r="DM2" t="n">
-        <v>44.05</v>
+        <v>43.6</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="DO2" t="n">
         <v>-1</v>
       </c>
       <c r="DP2" t="n">
-        <v>12.05</v>
+        <v>12</v>
       </c>
       <c r="DQ2" t="n">
-        <v>16.63</v>
+        <v>17.05</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.73</v>
+        <v>6.7</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>45.95</v>
+        <v>45.7</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="DX2" t="n">
-        <v>12.79</v>
+        <v>12.45</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.84</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="DZ2" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="EA2" t="n">
-        <v>21.32</v>
+        <v>21.25</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="3">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C3" t="n">
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1872,112 +1872,112 @@
         <v>1.67</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG3" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>83.55</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>39</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>13.36</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>8.359999999999999</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>41.27</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>10.55</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>7.18</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>16.64</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>8.949999999999999</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BN3" t="n">
         <v>1.4</v>
       </c>
-      <c r="AH3" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>84.09999999999999</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>38.7</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>41.9</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>8.890000000000001</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>1.32</v>
-      </c>
       <c r="BO3" t="n">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="BP3" t="n">
         <v>-1</v>
@@ -1989,22 +1989,22 @@
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>89.47</v>
+        <v>90</v>
       </c>
       <c r="BT3" t="n">
-        <v>47.37</v>
+        <v>50</v>
       </c>
       <c r="BU3" t="n">
-        <v>21.05</v>
+        <v>25</v>
       </c>
       <c r="BV3" t="n">
-        <v>5.26</v>
+        <v>10</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BX3" t="n">
-        <v>63.16</v>
+        <v>65</v>
       </c>
       <c r="BY3" t="n">
         <v>3.38</v>
@@ -2013,34 +2013,34 @@
         <v>3.61</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.96</v>
+        <v>4</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.22</v>
+        <v>4.28</v>
       </c>
       <c r="CC3" t="n">
-        <v>5.48</v>
+        <v>5.69</v>
       </c>
       <c r="CD3" t="n">
-        <v>5.82</v>
+        <v>6.02</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.3</v>
+        <v>3.31</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CI3" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CK3" t="n">
         <v>1.46</v>
@@ -2052,34 +2052,34 @@
         <v>2.52</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CO3" t="n">
         <v>1.22</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.83</v>
+        <v>2.81</v>
       </c>
       <c r="CR3" t="n">
         <v>1.38</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.76</v>
+        <v>2.71</v>
       </c>
       <c r="CT3" t="n">
         <v>3.11</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CX3" t="n">
         <v>1.55</v>
@@ -2106,73 +2106,73 @@
         <v>0.05</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="DG3" t="n">
         <v>-1</v>
       </c>
       <c r="DH3" t="n">
-        <v>91.48</v>
+        <v>90.8</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="DJ3" t="n">
         <v>2.05</v>
       </c>
       <c r="DK3" t="n">
-        <v>4.21</v>
+        <v>4.05</v>
       </c>
       <c r="DL3" t="n">
         <v>-1</v>
       </c>
       <c r="DM3" t="n">
-        <v>43.74</v>
+        <v>43.65</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="DO3" t="n">
         <v>-1</v>
       </c>
       <c r="DP3" t="n">
-        <v>15.05</v>
+        <v>15.1</v>
       </c>
       <c r="DQ3" t="n">
-        <v>14.48</v>
+        <v>14.35</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.74</v>
+        <v>7.75</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>43.84</v>
+        <v>43.4</v>
       </c>
       <c r="DW3" t="n">
         <v>0.05</v>
       </c>
       <c r="DX3" t="n">
-        <v>10.84</v>
+        <v>10.8</v>
       </c>
       <c r="DY3" t="n">
-        <v>6.95</v>
+        <v>6.9</v>
       </c>
       <c r="DZ3" t="n">
         <v>3.9</v>
       </c>
       <c r="EA3" t="n">
-        <v>18</v>
+        <v>17.7</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="EC3" t="n">
         <v>1.95</v>
@@ -2299,7 +2299,7 @@
         <v>-1</v>
       </c>
       <c r="AN4" t="n">
-        <v>42.82</v>
+        <v>43</v>
       </c>
       <c r="AO4" t="n">
         <v>1.64</v>
@@ -2311,7 +2311,7 @@
         <v>19.27</v>
       </c>
       <c r="AR4" t="n">
-        <v>12.73</v>
+        <v>12.82</v>
       </c>
       <c r="AS4" t="n">
         <v>8</v>
@@ -2332,16 +2332,16 @@
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>47.45</v>
+        <v>47.36</v>
       </c>
       <c r="AZ4" t="n">
         <v>0.09</v>
       </c>
       <c r="BA4" t="n">
-        <v>11.73</v>
+        <v>11.91</v>
       </c>
       <c r="BB4" t="n">
-        <v>7.64</v>
+        <v>7.82</v>
       </c>
       <c r="BC4" t="n">
         <v>4.09</v>
@@ -2350,7 +2350,7 @@
         <v>20.82</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="BF4" t="n">
         <v>3.36</v>
@@ -2425,7 +2425,7 @@
         <v>3.61</v>
       </c>
       <c r="CD4" t="n">
-        <v>3.89</v>
+        <v>3.9</v>
       </c>
       <c r="CE4" t="n">
         <v>1.4</v>
@@ -2500,10 +2500,10 @@
         <v>1.43</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="DD4" t="n">
-        <v>4.45</v>
+        <v>4.46</v>
       </c>
       <c r="DE4" t="n">
         <v>0.25</v>
@@ -2530,7 +2530,7 @@
         <v>-1</v>
       </c>
       <c r="DM4" t="n">
-        <v>44.1</v>
+        <v>44.2</v>
       </c>
       <c r="DN4" t="n">
         <v>1.35</v>
@@ -2542,7 +2542,7 @@
         <v>19.35</v>
       </c>
       <c r="DQ4" t="n">
-        <v>12.55</v>
+        <v>12.6</v>
       </c>
       <c r="DR4" t="n">
         <v>7.8</v>
@@ -2557,16 +2557,16 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>45.55</v>
+        <v>45.5</v>
       </c>
       <c r="DW4" t="n">
         <v>0.1</v>
       </c>
       <c r="DX4" t="n">
-        <v>12.25</v>
+        <v>12.35</v>
       </c>
       <c r="DY4" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="DZ4" t="n">
         <v>4.05</v>
@@ -2588,94 +2588,94 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
         <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="F5" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="G5" t="n">
         <v>-1</v>
       </c>
       <c r="H5" t="n">
-        <v>105.33</v>
+        <v>105.4</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="K5" t="n">
-        <v>4.56</v>
+        <v>4.9</v>
       </c>
       <c r="L5" t="n">
         <v>-1</v>
       </c>
       <c r="M5" t="n">
-        <v>53.44</v>
+        <v>53</v>
       </c>
       <c r="N5" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="O5" t="n">
         <v>-1</v>
       </c>
       <c r="P5" t="n">
-        <v>11.33</v>
+        <v>11</v>
       </c>
       <c r="Q5" t="n">
-        <v>17.67</v>
+        <v>17.5</v>
       </c>
       <c r="R5" t="n">
-        <v>8.33</v>
+        <v>8.4</v>
       </c>
       <c r="S5" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="U5" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="V5" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>58.22</v>
+        <v>58</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="Z5" t="n">
-        <v>14.44</v>
+        <v>14.3</v>
       </c>
       <c r="AA5" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.44</v>
+        <v>5.2</v>
       </c>
       <c r="AC5" t="n">
-        <v>20.78</v>
+        <v>20.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -2759,31 +2759,31 @@
         <v>2</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.53</v>
+        <v>2.65</v>
       </c>
       <c r="BH5" t="n">
-        <v>10.74</v>
+        <v>11.05</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.53</v>
+        <v>2.65</v>
       </c>
       <c r="BJ5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BN5" t="n">
         <v>1.05</v>
       </c>
-      <c r="BK5" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>0.95</v>
-      </c>
       <c r="BO5" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="BP5" t="n">
         <v>-1</v>
@@ -2792,34 +2792,34 @@
         <v>-1</v>
       </c>
       <c r="BR5" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS5" t="n">
-        <v>63.16</v>
+        <v>65</v>
       </c>
       <c r="BT5" t="n">
-        <v>42.11</v>
+        <v>45</v>
       </c>
       <c r="BU5" t="n">
-        <v>31.58</v>
+        <v>35</v>
       </c>
       <c r="BV5" t="n">
-        <v>15.79</v>
+        <v>20</v>
       </c>
       <c r="BW5" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX5" t="n">
-        <v>47.37</v>
+        <v>50</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.73</v>
+        <v>3.72</v>
       </c>
       <c r="CB5" t="n">
         <v>3.84</v>
@@ -2834,40 +2834,40 @@
         <v>1.38</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="CH5" t="n">
         <v>1.45</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CM5" t="n">
         <v>2.46</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CO5" t="n">
         <v>1.27</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.22</v>
+        <v>3.19</v>
       </c>
       <c r="CR5" t="n">
         <v>1.42</v>
@@ -2882,106 +2882,106 @@
         <v>1.4</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="DG5" t="n">
         <v>-1</v>
       </c>
       <c r="DH5" t="n">
-        <v>101.37</v>
+        <v>101.6</v>
       </c>
       <c r="DI5" t="n">
         <v>0</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.11</v>
+        <v>5.25</v>
       </c>
       <c r="DL5" t="n">
         <v>-1</v>
       </c>
       <c r="DM5" t="n">
-        <v>49.16</v>
+        <v>49.15</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="DO5" t="n">
         <v>-1</v>
       </c>
       <c r="DP5" t="n">
-        <v>12.1</v>
+        <v>11.9</v>
       </c>
       <c r="DQ5" t="n">
-        <v>15.53</v>
+        <v>15.55</v>
       </c>
       <c r="DR5" t="n">
-        <v>9.31</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>55.63</v>
+        <v>55.65</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="DX5" t="n">
-        <v>13.73</v>
+        <v>13.7</v>
       </c>
       <c r="DY5" t="n">
-        <v>9</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="DZ5" t="n">
-        <v>4.73</v>
+        <v>4.65</v>
       </c>
       <c r="EA5" t="n">
-        <v>20.95</v>
+        <v>20.75</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="6">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C6" t="n">
         <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -3081,112 +3081,112 @@
         <v>1.5</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AH6" t="n">
         <v>-1</v>
       </c>
       <c r="AI6" t="n">
-        <v>91.33</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="AJ6" t="n">
         <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="AL6" t="n">
-        <v>4.67</v>
+        <v>5.1</v>
       </c>
       <c r="AM6" t="n">
         <v>-1</v>
       </c>
       <c r="AN6" t="n">
-        <v>47.67</v>
+        <v>47.8</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AP6" t="n">
         <v>-1</v>
       </c>
       <c r="AQ6" t="n">
-        <v>14.89</v>
+        <v>14.9</v>
       </c>
       <c r="AR6" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="AS6" t="n">
-        <v>6.44</v>
+        <v>6.3</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.11</v>
+        <v>1.4</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AX6" t="n">
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>52</v>
+        <v>51.2</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>14.33</v>
+        <v>15.3</v>
       </c>
       <c r="BB6" t="n">
-        <v>10.78</v>
+        <v>11.4</v>
       </c>
       <c r="BC6" t="n">
-        <v>3.56</v>
+        <v>3.9</v>
       </c>
       <c r="BD6" t="n">
-        <v>22.11</v>
+        <v>21.1</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="BG6" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.529999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="BI6" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.74</v>
+        <v>0.8</v>
       </c>
       <c r="BL6" t="n">
         <v>1</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.58</v>
+        <v>0.65</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="BP6" t="n">
         <v>-1</v>
@@ -3195,25 +3195,25 @@
         <v>-1</v>
       </c>
       <c r="BR6" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS6" t="n">
-        <v>78.95</v>
+        <v>80</v>
       </c>
       <c r="BT6" t="n">
-        <v>63.16</v>
+        <v>65</v>
       </c>
       <c r="BU6" t="n">
-        <v>36.84</v>
+        <v>40</v>
       </c>
       <c r="BV6" t="n">
-        <v>10.53</v>
+        <v>15</v>
       </c>
       <c r="BW6" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX6" t="n">
-        <v>63.16</v>
+        <v>65</v>
       </c>
       <c r="BY6" t="n">
         <v>1.82</v>
@@ -3222,16 +3222,16 @@
         <v>1.84</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.87</v>
+        <v>3.84</v>
       </c>
       <c r="CB6" t="n">
-        <v>4.05</v>
+        <v>4.03</v>
       </c>
       <c r="CC6" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="CD6" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="CE6" t="n">
         <v>1.33</v>
@@ -3240,22 +3240,22 @@
         <v>2.57</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="CH6" t="n">
         <v>1.5</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CK6" t="n">
         <v>1.44</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CM6" t="n">
         <v>2.57</v>
@@ -3267,10 +3267,10 @@
         <v>1.23</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.83</v>
+        <v>2.81</v>
       </c>
       <c r="CR6" t="n">
         <v>1.35</v>
@@ -3285,31 +3285,31 @@
         <v>1.53</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.03</v>
+        <v>3.01</v>
       </c>
       <c r="DE6" t="n">
         <v>0.05</v>
@@ -3321,7 +3321,7 @@
         <v>-1</v>
       </c>
       <c r="DH6" t="n">
-        <v>96.52</v>
+        <v>95.8</v>
       </c>
       <c r="DI6" t="n">
         <v>0.05</v>
@@ -3330,13 +3330,13 @@
         <v>1.95</v>
       </c>
       <c r="DK6" t="n">
-        <v>5.26</v>
+        <v>5.45</v>
       </c>
       <c r="DL6" t="n">
         <v>-1</v>
       </c>
       <c r="DM6" t="n">
-        <v>50.74</v>
+        <v>50.65</v>
       </c>
       <c r="DN6" t="n">
         <v>0.9</v>
@@ -3345,43 +3345,43 @@
         <v>-1</v>
       </c>
       <c r="DP6" t="n">
-        <v>13.53</v>
+        <v>13.6</v>
       </c>
       <c r="DQ6" t="n">
-        <v>16.89</v>
+        <v>16.5</v>
       </c>
       <c r="DR6" t="n">
-        <v>5.63</v>
+        <v>5.6</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>54.79</v>
+        <v>54.25</v>
       </c>
       <c r="DW6" t="n">
         <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>15.58</v>
+        <v>16</v>
       </c>
       <c r="DY6" t="n">
-        <v>10.84</v>
+        <v>11.15</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.74</v>
+        <v>4.85</v>
       </c>
       <c r="EA6" t="n">
-        <v>21.37</v>
+        <v>20.9</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="EC6" t="n">
         <v>1.95</v>
@@ -3493,7 +3493,7 @@
         <v>-1</v>
       </c>
       <c r="AI7" t="n">
-        <v>84.3</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="AJ7" t="n">
         <v>0.1</v>
@@ -3520,10 +3520,10 @@
         <v>15.1</v>
       </c>
       <c r="AR7" t="n">
-        <v>14.1</v>
+        <v>14.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="AT7" t="n">
         <v>2.4</v>
@@ -3628,13 +3628,13 @@
         <v>3.65</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.85</v>
+        <v>3.86</v>
       </c>
       <c r="CC7" t="n">
         <v>4.7</v>
       </c>
       <c r="CD7" t="n">
-        <v>5.33</v>
+        <v>5.31</v>
       </c>
       <c r="CE7" t="n">
         <v>1.41</v>
@@ -3697,7 +3697,7 @@
         <v>1.61</v>
       </c>
       <c r="CY7" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CZ7" t="n">
         <v>2.29</v>
@@ -3724,7 +3724,7 @@
         <v>-1</v>
       </c>
       <c r="DH7" t="n">
-        <v>80.84999999999999</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="DI7" t="n">
         <v>0.1</v>
@@ -3751,10 +3751,10 @@
         <v>14.2</v>
       </c>
       <c r="DQ7" t="n">
-        <v>14.25</v>
+        <v>14.45</v>
       </c>
       <c r="DR7" t="n">
-        <v>8.85</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="DS7" t="n">
         <v>0.1</v>
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C8" t="n">
         <v>11</v>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E8" t="n">
         <v>0.09</v>
@@ -3887,112 +3887,112 @@
         <v>2.55</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AH8" t="n">
         <v>-1</v>
       </c>
       <c r="AI8" t="n">
-        <v>89.75</v>
+        <v>90.33</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AL8" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="AM8" t="n">
         <v>-1</v>
       </c>
       <c r="AN8" t="n">
-        <v>39.25</v>
+        <v>38.22</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AP8" t="n">
         <v>-1</v>
       </c>
       <c r="AQ8" t="n">
-        <v>13.62</v>
+        <v>14.44</v>
       </c>
       <c r="AR8" t="n">
-        <v>19.5</v>
+        <v>19.44</v>
       </c>
       <c r="AS8" t="n">
-        <v>8.5</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.38</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>56.88</v>
+        <v>57.44</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA8" t="n">
-        <v>12.88</v>
+        <v>12.22</v>
       </c>
       <c r="BB8" t="n">
-        <v>8.619999999999999</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.25</v>
+        <v>4.11</v>
       </c>
       <c r="BD8" t="n">
-        <v>22.12</v>
+        <v>21.33</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="BH8" t="n">
-        <v>8.84</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="BP8" t="n">
         <v>-1</v>
@@ -4001,25 +4001,25 @@
         <v>-1</v>
       </c>
       <c r="BR8" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS8" t="n">
-        <v>78.95</v>
+        <v>80</v>
       </c>
       <c r="BT8" t="n">
-        <v>47.37</v>
+        <v>50</v>
       </c>
       <c r="BU8" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BV8" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BW8" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BX8" t="n">
-        <v>47.37</v>
+        <v>50</v>
       </c>
       <c r="BY8" t="n">
         <v>1.72</v>
@@ -4028,55 +4028,55 @@
         <v>1.71</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.88</v>
+        <v>3.86</v>
       </c>
       <c r="CB8" t="n">
-        <v>4.12</v>
+        <v>4.1</v>
       </c>
       <c r="CC8" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="CD8" t="n">
         <v>1.95</v>
       </c>
-      <c r="CD8" t="n">
-        <v>1.98</v>
-      </c>
       <c r="CE8" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.1</v>
+        <v>3.07</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CI8" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.46</v>
+        <v>2.43</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="CO8" t="n">
         <v>1.26</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.06</v>
+        <v>3.12</v>
       </c>
       <c r="CR8" t="n">
         <v>1.4</v>
@@ -4091,73 +4091,73 @@
         <v>1.44</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="CW8" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="CX8" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="CY8" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="CZ8" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="DA8" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="DB8" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="DC8" t="n">
         <v>1.86</v>
       </c>
-      <c r="CX8" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="CY8" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="CZ8" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="DA8" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="DB8" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="DC8" t="n">
-        <v>1.83</v>
-      </c>
       <c r="DD8" t="n">
-        <v>3.03</v>
+        <v>3.1</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.69</v>
+        <v>1.6</v>
       </c>
       <c r="DG8" t="n">
         <v>-1</v>
       </c>
       <c r="DH8" t="n">
-        <v>93.05</v>
+        <v>93.15000000000001</v>
       </c>
       <c r="DI8" t="n">
         <v>0.1</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.47</v>
+        <v>2.35</v>
       </c>
       <c r="DK8" t="n">
-        <v>5.26</v>
+        <v>5.1</v>
       </c>
       <c r="DL8" t="n">
         <v>-1</v>
       </c>
       <c r="DM8" t="n">
-        <v>46.89</v>
+        <v>46.05</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="DO8" t="n">
         <v>-1</v>
       </c>
       <c r="DP8" t="n">
-        <v>13.74</v>
+        <v>14.1</v>
       </c>
       <c r="DQ8" t="n">
-        <v>17.53</v>
+        <v>17.6</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.26</v>
+        <v>7.15</v>
       </c>
       <c r="DS8" t="n">
         <v>0.15</v>
@@ -4169,28 +4169,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>58.58</v>
+        <v>58.75</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DX8" t="n">
-        <v>16.48</v>
+        <v>16</v>
       </c>
       <c r="DY8" t="n">
-        <v>11.58</v>
+        <v>11.2</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.89</v>
+        <v>4.8</v>
       </c>
       <c r="EA8" t="n">
-        <v>21.32</v>
+        <v>21</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.21</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="9">
@@ -4200,61 +4200,61 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D9" t="n">
         <v>11</v>
       </c>
       <c r="E9" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="F9" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="G9" t="n">
         <v>-1</v>
       </c>
       <c r="H9" t="n">
-        <v>82.38</v>
+        <v>83.78</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="K9" t="n">
-        <v>3.62</v>
+        <v>3.89</v>
       </c>
       <c r="L9" t="n">
         <v>-1</v>
       </c>
       <c r="M9" t="n">
-        <v>39.12</v>
+        <v>38.67</v>
       </c>
       <c r="N9" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="O9" t="n">
         <v>-1</v>
       </c>
       <c r="P9" t="n">
-        <v>14.12</v>
+        <v>14.33</v>
       </c>
       <c r="Q9" t="n">
-        <v>14.75</v>
+        <v>14.67</v>
       </c>
       <c r="R9" t="n">
-        <v>9.119999999999999</v>
+        <v>8.56</v>
       </c>
       <c r="S9" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="T9" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -4266,28 +4266,28 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>46.12</v>
+        <v>46.11</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z9" t="n">
-        <v>9.380000000000001</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="AA9" t="n">
-        <v>6.62</v>
+        <v>6.33</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.75</v>
+        <v>2.89</v>
       </c>
       <c r="AC9" t="n">
-        <v>20.88</v>
+        <v>20.78</v>
       </c>
       <c r="AD9" t="n">
         <v>1.07</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AF9" t="n">
         <v>0.09</v>
@@ -4371,31 +4371,31 @@
         <v>2.82</v>
       </c>
       <c r="BG9" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="BH9" t="n">
-        <v>8.789999999999999</v>
+        <v>9</v>
       </c>
       <c r="BI9" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.79</v>
+        <v>0.85</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="BL9" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="BP9" t="n">
         <v>-1</v>
@@ -4407,34 +4407,34 @@
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BT9" t="n">
-        <v>42.11</v>
+        <v>40</v>
       </c>
       <c r="BU9" t="n">
-        <v>36.84</v>
+        <v>35</v>
       </c>
       <c r="BV9" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BW9" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX9" t="n">
-        <v>47.37</v>
+        <v>45</v>
       </c>
       <c r="BY9" t="n">
-        <v>3.54</v>
+        <v>3.45</v>
       </c>
       <c r="BZ9" t="n">
-        <v>3.82</v>
+        <v>3.71</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.88</v>
+        <v>3.83</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.98</v>
+        <v>3.92</v>
       </c>
       <c r="CC9" t="n">
         <v>5.61</v>
@@ -4443,43 +4443,43 @@
         <v>5.9</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.01</v>
+        <v>2.97</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.34</v>
+        <v>3.45</v>
       </c>
       <c r="CR9" t="n">
         <v>1.43</v>
@@ -4494,10 +4494,10 @@
         <v>1.44</v>
       </c>
       <c r="CV9" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="CX9" t="n">
         <v>1.62</v>
@@ -4512,55 +4512,55 @@
         <v>1.81</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.99</v>
+        <v>2.07</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.46</v>
+        <v>3.69</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="DG9" t="n">
         <v>-1</v>
       </c>
       <c r="DH9" t="n">
-        <v>78.11</v>
+        <v>78.95</v>
       </c>
       <c r="DI9" t="n">
         <v>0.1</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.53</v>
+        <v>2.45</v>
       </c>
       <c r="DK9" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="DL9" t="n">
         <v>-1</v>
       </c>
       <c r="DM9" t="n">
-        <v>33.84</v>
+        <v>33.9</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="DO9" t="n">
         <v>-1</v>
       </c>
       <c r="DP9" t="n">
-        <v>14.42</v>
+        <v>14.5</v>
       </c>
       <c r="DQ9" t="n">
-        <v>14.21</v>
+        <v>14.2</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.630000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="DS9" t="n">
         <v>0.05</v>
@@ -4578,22 +4578,22 @@
         <v>0.1</v>
       </c>
       <c r="DX9" t="n">
-        <v>8.109999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="DY9" t="n">
-        <v>5.63</v>
+        <v>5.55</v>
       </c>
       <c r="DZ9" t="n">
-        <v>2.47</v>
+        <v>2.55</v>
       </c>
       <c r="EA9" t="n">
-        <v>19.74</v>
+        <v>19.75</v>
       </c>
       <c r="EB9" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.42</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="10">
@@ -4603,94 +4603,94 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D10" t="n">
         <v>10</v>
       </c>
       <c r="E10" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="F10" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="G10" t="n">
         <v>-1</v>
       </c>
       <c r="H10" t="n">
-        <v>94.22</v>
+        <v>93.8</v>
       </c>
       <c r="I10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="J10" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="K10" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="L10" t="n">
         <v>-1</v>
       </c>
       <c r="M10" t="n">
-        <v>45.89</v>
+        <v>47.2</v>
       </c>
       <c r="N10" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="O10" t="n">
         <v>-1</v>
       </c>
       <c r="P10" t="n">
-        <v>15.11</v>
+        <v>16</v>
       </c>
       <c r="Q10" t="n">
-        <v>14.22</v>
+        <v>13.8</v>
       </c>
       <c r="R10" t="n">
-        <v>6.89</v>
+        <v>6.6</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="T10" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="U10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>45.22</v>
+        <v>46.6</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="Z10" t="n">
-        <v>14.78</v>
+        <v>14.4</v>
       </c>
       <c r="AA10" t="n">
-        <v>8.67</v>
+        <v>8.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>6.11</v>
+        <v>5.9</v>
       </c>
       <c r="AC10" t="n">
-        <v>18.44</v>
+        <v>19</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="AF10" t="n">
         <v>0.3</v>
@@ -4774,31 +4774,31 @@
         <v>2.2</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.42</v>
+        <v>3.45</v>
       </c>
       <c r="BH10" t="n">
-        <v>8.789999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.42</v>
+        <v>3.45</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.58</v>
+        <v>0.65</v>
       </c>
       <c r="BL10" t="n">
         <v>1</v>
       </c>
       <c r="BM10" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BN10" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="BP10" t="n">
         <v>-1</v>
@@ -4810,34 +4810,34 @@
         <v>100</v>
       </c>
       <c r="BS10" t="n">
-        <v>89.47</v>
+        <v>90</v>
       </c>
       <c r="BT10" t="n">
-        <v>57.89</v>
+        <v>60</v>
       </c>
       <c r="BU10" t="n">
-        <v>36.84</v>
+        <v>40</v>
       </c>
       <c r="BV10" t="n">
-        <v>26.32</v>
+        <v>25</v>
       </c>
       <c r="BW10" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BX10" t="n">
-        <v>73.68000000000001</v>
+        <v>75</v>
       </c>
       <c r="BY10" t="n">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="BZ10" t="n">
-        <v>2.18</v>
+        <v>2.13</v>
       </c>
       <c r="CA10" t="n">
         <v>3.69</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.83</v>
+        <v>3.84</v>
       </c>
       <c r="CC10" t="n">
         <v>2.77</v>
@@ -4849,25 +4849,25 @@
         <v>1.22</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CJ10" t="n">
         <v>1.55</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CM10" t="n">
         <v>2.22</v>
@@ -4879,7 +4879,7 @@
         <v>1.11</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CQ10" t="n">
         <v>2.66</v>
@@ -4888,16 +4888,16 @@
         <v>1.37</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.74</v>
+        <v>2.71</v>
       </c>
       <c r="CT10" t="n">
-        <v>3.12</v>
+        <v>3.15</v>
       </c>
       <c r="CU10" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="CW10" t="n">
         <v>1.71</v>
@@ -4909,94 +4909,94 @@
         <v>1.9</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="DD10" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="DG10" t="n">
         <v>-1</v>
       </c>
       <c r="DH10" t="n">
-        <v>94.16</v>
+        <v>93.95</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="DK10" t="n">
-        <v>3.58</v>
+        <v>3.75</v>
       </c>
       <c r="DL10" t="n">
         <v>-1</v>
       </c>
       <c r="DM10" t="n">
-        <v>46.37</v>
+        <v>47</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="DO10" t="n">
         <v>-1</v>
       </c>
       <c r="DP10" t="n">
-        <v>14.53</v>
+        <v>15</v>
       </c>
       <c r="DQ10" t="n">
-        <v>14.63</v>
+        <v>14.4</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.21</v>
+        <v>7.05</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>48.58</v>
+        <v>49.1</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DX10" t="n">
-        <v>14.21</v>
+        <v>14.05</v>
       </c>
       <c r="DY10" t="n">
-        <v>8.58</v>
+        <v>8.5</v>
       </c>
       <c r="DZ10" t="n">
-        <v>5.63</v>
+        <v>5.55</v>
       </c>
       <c r="EA10" t="n">
-        <v>17.47</v>
+        <v>17.8</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="11">
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C11" t="n">
         <v>10</v>
       </c>
       <c r="D11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E11" t="n">
         <v>0.2</v>
@@ -5099,49 +5099,49 @@
         <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AH11" t="n">
         <v>-1</v>
       </c>
       <c r="AI11" t="n">
-        <v>110.22</v>
+        <v>109.8</v>
       </c>
       <c r="AJ11" t="n">
         <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AL11" t="n">
-        <v>3.89</v>
+        <v>4.2</v>
       </c>
       <c r="AM11" t="n">
         <v>-1</v>
       </c>
       <c r="AN11" t="n">
-        <v>48.56</v>
+        <v>47.2</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="AP11" t="n">
         <v>-1</v>
       </c>
       <c r="AQ11" t="n">
-        <v>13.56</v>
+        <v>13.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>18.67</v>
+        <v>18.8</v>
       </c>
       <c r="AS11" t="n">
-        <v>6.67</v>
+        <v>6.7</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AV11" t="n">
         <v>0</v>
@@ -5153,55 +5153,55 @@
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>48.44</v>
+        <v>49</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="BA11" t="n">
-        <v>10.11</v>
+        <v>10</v>
       </c>
       <c r="BB11" t="n">
-        <v>7.33</v>
+        <v>7.2</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="BD11" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="BF11" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="BH11" t="n">
-        <v>8.26</v>
+        <v>8.5</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.68</v>
+        <v>0.75</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="BN11" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.84</v>
+        <v>0.9</v>
       </c>
       <c r="BP11" t="n">
         <v>-1</v>
@@ -5210,16 +5210,16 @@
         <v>-1</v>
       </c>
       <c r="BR11" t="n">
-        <v>89.47</v>
+        <v>90</v>
       </c>
       <c r="BS11" t="n">
-        <v>57.89</v>
+        <v>60</v>
       </c>
       <c r="BT11" t="n">
-        <v>15.79</v>
+        <v>15</v>
       </c>
       <c r="BU11" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BV11" t="n">
         <v>0</v>
@@ -5228,7 +5228,7 @@
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>26.32</v>
+        <v>25</v>
       </c>
       <c r="BY11" t="n">
         <v>3</v>
@@ -5237,55 +5237,55 @@
         <v>3.12</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.43</v>
+        <v>3.41</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.5</v>
+        <v>3.47</v>
       </c>
       <c r="CC11" t="n">
-        <v>5.29</v>
+        <v>5.02</v>
       </c>
       <c r="CD11" t="n">
-        <v>5.62</v>
+        <v>5.36</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CF11" t="n">
-        <v>3.39</v>
+        <v>3.42</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="CI11" t="n">
         <v>1.73</v>
       </c>
       <c r="CJ11" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="CP11" t="n">
-        <v>2.35</v>
+        <v>2.39</v>
       </c>
       <c r="CQ11" t="n">
-        <v>4.31</v>
+        <v>4.37</v>
       </c>
       <c r="CR11" t="n">
         <v>1.5</v>
@@ -5300,10 +5300,10 @@
         <v>1.37</v>
       </c>
       <c r="CV11" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CW11" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="CX11" t="n">
         <v>1.66</v>
@@ -5318,88 +5318,88 @@
         <v>1.79</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="DC11" t="n">
-        <v>2.43</v>
+        <v>2.47</v>
       </c>
       <c r="DD11" t="n">
-        <v>4.65</v>
+        <v>4.76</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="DG11" t="n">
         <v>-1</v>
       </c>
       <c r="DH11" t="n">
-        <v>108</v>
+        <v>107.9</v>
       </c>
       <c r="DI11" t="n">
         <v>0</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.47</v>
+        <v>4.6</v>
       </c>
       <c r="DL11" t="n">
         <v>-1</v>
       </c>
       <c r="DM11" t="n">
-        <v>49.74</v>
+        <v>49</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="DO11" t="n">
         <v>-1</v>
       </c>
       <c r="DP11" t="n">
-        <v>13.74</v>
+        <v>13.7</v>
       </c>
       <c r="DQ11" t="n">
-        <v>19</v>
+        <v>19.05</v>
       </c>
       <c r="DR11" t="n">
-        <v>6.84</v>
+        <v>6.85</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>48.89</v>
+        <v>49.15</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DX11" t="n">
-        <v>10.37</v>
+        <v>10.3</v>
       </c>
       <c r="DY11" t="n">
-        <v>7.63</v>
+        <v>7.55</v>
       </c>
       <c r="DZ11" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="EA11" t="n">
-        <v>24.89</v>
+        <v>24.85</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="EC11" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="12">
@@ -5427,7 +5427,7 @@
         <v>-1</v>
       </c>
       <c r="H12" t="n">
-        <v>94.09999999999999</v>
+        <v>92.7</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -5454,7 +5454,7 @@
         <v>16.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="R12" t="n">
         <v>7.1</v>
@@ -5481,19 +5481,19 @@
         <v>0.1</v>
       </c>
       <c r="Z12" t="n">
-        <v>13</v>
+        <v>12.9</v>
       </c>
       <c r="AA12" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="AB12" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AC12" t="n">
         <v>18.3</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AE12" t="n">
         <v>2.5</v>
@@ -5715,7 +5715,7 @@
         <v>1.9</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="DA12" t="n">
         <v>1.92</v>
@@ -5739,7 +5739,7 @@
         <v>-1</v>
       </c>
       <c r="DH12" t="n">
-        <v>85.65000000000001</v>
+        <v>84.95</v>
       </c>
       <c r="DI12" t="n">
         <v>0</v>
@@ -5766,7 +5766,7 @@
         <v>17.1</v>
       </c>
       <c r="DQ12" t="n">
-        <v>14.55</v>
+        <v>14.6</v>
       </c>
       <c r="DR12" t="n">
         <v>8.1</v>
@@ -5787,13 +5787,13 @@
         <v>0.1</v>
       </c>
       <c r="DX12" t="n">
-        <v>11.75</v>
+        <v>11.7</v>
       </c>
       <c r="DY12" t="n">
         <v>7.65</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="EA12" t="n">
         <v>18.4</v>
@@ -5812,94 +5812,94 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D13" t="n">
         <v>9</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="F13" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="G13" t="n">
         <v>-1</v>
       </c>
       <c r="H13" t="n">
-        <v>84.40000000000001</v>
+        <v>83.18000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="J13" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="K13" t="n">
-        <v>5</v>
+        <v>5.27</v>
       </c>
       <c r="L13" t="n">
         <v>-1</v>
       </c>
       <c r="M13" t="n">
-        <v>43.5</v>
+        <v>43.27</v>
       </c>
       <c r="N13" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="O13" t="n">
         <v>-1</v>
       </c>
       <c r="P13" t="n">
-        <v>16.2</v>
+        <v>16.36</v>
       </c>
       <c r="Q13" t="n">
-        <v>16.6</v>
+        <v>15.64</v>
       </c>
       <c r="R13" t="n">
-        <v>7.6</v>
+        <v>7.82</v>
       </c>
       <c r="S13" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="T13" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>50.1</v>
+        <v>49</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>12.5</v>
+        <v>12.73</v>
       </c>
       <c r="AA13" t="n">
-        <v>8.800000000000001</v>
+        <v>8.91</v>
       </c>
       <c r="AB13" t="n">
-        <v>3.7</v>
+        <v>3.82</v>
       </c>
       <c r="AC13" t="n">
-        <v>21.1</v>
+        <v>20.18</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -5983,31 +5983,31 @@
         <v>1.89</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.84</v>
+        <v>10</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.26</v>
+        <v>0.3</v>
       </c>
       <c r="BL13" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BP13" t="n">
         <v>-1</v>
@@ -6016,37 +6016,37 @@
         <v>-1</v>
       </c>
       <c r="BR13" t="n">
-        <v>89.47</v>
+        <v>90</v>
       </c>
       <c r="BS13" t="n">
-        <v>63.16</v>
+        <v>65</v>
       </c>
       <c r="BT13" t="n">
-        <v>42.11</v>
+        <v>45</v>
       </c>
       <c r="BU13" t="n">
-        <v>36.84</v>
+        <v>35</v>
       </c>
       <c r="BV13" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BW13" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX13" t="n">
-        <v>52.63</v>
+        <v>55</v>
       </c>
       <c r="BY13" t="n">
-        <v>3.52</v>
+        <v>3.85</v>
       </c>
       <c r="BZ13" t="n">
-        <v>4.12</v>
+        <v>4.42</v>
       </c>
       <c r="CA13" t="n">
-        <v>4.09</v>
+        <v>4.1</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.33</v>
+        <v>4.35</v>
       </c>
       <c r="CC13" t="n">
         <v>6.29</v>
@@ -6061,28 +6061,28 @@
         <v>2.61</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="CH13" t="n">
         <v>1.51</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CL13" t="n">
         <v>1.8</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="CN13" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CO13" t="n">
         <v>1.24</v>
@@ -6106,22 +6106,22 @@
         <v>1.56</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CW13" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CX13" t="n">
         <v>1.54</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="DA13" t="n">
-        <v>2.12</v>
+        <v>2.09</v>
       </c>
       <c r="DB13" t="n">
         <v>1.26</v>
@@ -6133,79 +6133,79 @@
         <v>3.04</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="DG13" t="n">
         <v>-1</v>
       </c>
       <c r="DH13" t="n">
-        <v>86.37</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.37</v>
+        <v>5.5</v>
       </c>
       <c r="DL13" t="n">
         <v>-1</v>
       </c>
       <c r="DM13" t="n">
-        <v>43.68</v>
+        <v>43.55</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="DO13" t="n">
         <v>-1</v>
       </c>
       <c r="DP13" t="n">
-        <v>14.89</v>
+        <v>15.05</v>
       </c>
       <c r="DQ13" t="n">
-        <v>16.26</v>
+        <v>15.75</v>
       </c>
       <c r="DR13" t="n">
-        <v>8.050000000000001</v>
+        <v>8.15</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>49</v>
+        <v>48.45</v>
       </c>
       <c r="DW13" t="n">
         <v>0.05</v>
       </c>
       <c r="DX13" t="n">
-        <v>12.05</v>
+        <v>12.2</v>
       </c>
       <c r="DY13" t="n">
-        <v>8.16</v>
+        <v>8.25</v>
       </c>
       <c r="DZ13" t="n">
-        <v>3.89</v>
+        <v>3.95</v>
       </c>
       <c r="EA13" t="n">
-        <v>22</v>
+        <v>21.45</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="14">
@@ -6233,7 +6233,7 @@
         <v>-1</v>
       </c>
       <c r="H14" t="n">
-        <v>102.6</v>
+        <v>102.2</v>
       </c>
       <c r="I14" t="n">
         <v>0.1</v>
@@ -6248,7 +6248,7 @@
         <v>-1</v>
       </c>
       <c r="M14" t="n">
-        <v>56</v>
+        <v>56.3</v>
       </c>
       <c r="N14" t="n">
         <v>0.8</v>
@@ -6260,7 +6260,7 @@
         <v>13.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>17.5</v>
+        <v>17.8</v>
       </c>
       <c r="R14" t="n">
         <v>5.8</v>
@@ -6281,25 +6281,25 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>51.9</v>
+        <v>52</v>
       </c>
       <c r="Y14" t="n">
         <v>0.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>13.4</v>
+        <v>13.6</v>
       </c>
       <c r="AA14" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="AB14" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AC14" t="n">
-        <v>21.4</v>
+        <v>21.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AE14" t="n">
         <v>2.2</v>
@@ -6512,7 +6512,7 @@
         <v>1.96</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CX14" t="n">
         <v>1.66</v>
@@ -6530,10 +6530,10 @@
         <v>1.35</v>
       </c>
       <c r="DC14" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.7</v>
+        <v>3.72</v>
       </c>
       <c r="DE14" t="n">
         <v>0.05</v>
@@ -6545,7 +6545,7 @@
         <v>-1</v>
       </c>
       <c r="DH14" t="n">
-        <v>96.2</v>
+        <v>96</v>
       </c>
       <c r="DI14" t="n">
         <v>0.15</v>
@@ -6560,7 +6560,7 @@
         <v>-1</v>
       </c>
       <c r="DM14" t="n">
-        <v>51.3</v>
+        <v>51.45</v>
       </c>
       <c r="DN14" t="n">
         <v>0.95</v>
@@ -6572,7 +6572,7 @@
         <v>14.55</v>
       </c>
       <c r="DQ14" t="n">
-        <v>17.5</v>
+        <v>17.65</v>
       </c>
       <c r="DR14" t="n">
         <v>6.3</v>
@@ -6587,25 +6587,25 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>49.35</v>
+        <v>49.4</v>
       </c>
       <c r="DW14" t="n">
         <v>0.25</v>
       </c>
       <c r="DX14" t="n">
-        <v>12.6</v>
+        <v>12.7</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.85</v>
+        <v>8.9</v>
       </c>
       <c r="DZ14" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="EA14" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="EC14" t="n">
         <v>2.3</v>
@@ -6618,10 +6618,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D15" t="n">
         <v>10</v>
@@ -6630,82 +6630,82 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="G15" t="n">
         <v>-1</v>
       </c>
       <c r="H15" t="n">
-        <v>87.56</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>38.4</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P15" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AE15" t="n">
         <v>2</v>
-      </c>
-      <c r="K15" t="n">
-        <v>4.44</v>
-      </c>
-      <c r="L15" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M15" t="n">
-        <v>39.33</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="O15" t="n">
-        <v>-1</v>
-      </c>
-      <c r="P15" t="n">
-        <v>15.44</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>14.56</v>
-      </c>
-      <c r="R15" t="n">
-        <v>8.220000000000001</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>41.11</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>10.33</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>7.11</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>21.11</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.89</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -6789,28 +6789,28 @@
         <v>3.1</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="BH15" t="n">
-        <v>7.89</v>
+        <v>7.65</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.37</v>
+        <v>0.4</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="BO15" t="n">
         <v>1</v>
@@ -6822,31 +6822,31 @@
         <v>-1</v>
       </c>
       <c r="BR15" t="n">
-        <v>89.47</v>
+        <v>90</v>
       </c>
       <c r="BS15" t="n">
-        <v>57.89</v>
+        <v>60</v>
       </c>
       <c r="BT15" t="n">
-        <v>36.84</v>
+        <v>40</v>
       </c>
       <c r="BU15" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BV15" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BW15" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX15" t="n">
-        <v>31.58</v>
+        <v>35</v>
       </c>
       <c r="BY15" t="n">
-        <v>2.76</v>
+        <v>2.98</v>
       </c>
       <c r="BZ15" t="n">
-        <v>3</v>
+        <v>3.29</v>
       </c>
       <c r="CA15" t="n">
         <v>3.44</v>
@@ -6864,40 +6864,40 @@
         <v>1.44</v>
       </c>
       <c r="CF15" t="n">
-        <v>3.07</v>
+        <v>3.09</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="CH15" t="n">
         <v>1.37</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CL15" t="n">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="CO15" t="n">
         <v>1.35</v>
       </c>
       <c r="CP15" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.72</v>
+        <v>3.75</v>
       </c>
       <c r="CR15" t="n">
         <v>1.39</v>
@@ -6912,58 +6912,58 @@
         <v>1.42</v>
       </c>
       <c r="CV15" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="CX15" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="CY15" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="DB15" t="n">
         <v>1.37</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.91</v>
+        <v>3.93</v>
       </c>
       <c r="DE15" t="n">
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="DG15" t="n">
         <v>-1</v>
       </c>
       <c r="DH15" t="n">
-        <v>83.90000000000001</v>
+        <v>84.5</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="DK15" t="n">
-        <v>4.21</v>
+        <v>4.05</v>
       </c>
       <c r="DL15" t="n">
         <v>-1</v>
       </c>
       <c r="DM15" t="n">
-        <v>37.89</v>
+        <v>37.5</v>
       </c>
       <c r="DN15" t="n">
         <v>0.95</v>
@@ -6972,13 +6972,13 @@
         <v>-1</v>
       </c>
       <c r="DP15" t="n">
-        <v>16.52</v>
+        <v>16.55</v>
       </c>
       <c r="DQ15" t="n">
-        <v>14</v>
+        <v>14.6</v>
       </c>
       <c r="DR15" t="n">
-        <v>8.470000000000001</v>
+        <v>8.15</v>
       </c>
       <c r="DS15" t="n">
         <v>0.1</v>
@@ -6990,28 +6990,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>41.1</v>
+        <v>40.95</v>
       </c>
       <c r="DW15" t="n">
         <v>0.05</v>
       </c>
       <c r="DX15" t="n">
-        <v>10.26</v>
+        <v>10.1</v>
       </c>
       <c r="DY15" t="n">
-        <v>7.37</v>
+        <v>7.15</v>
       </c>
       <c r="DZ15" t="n">
-        <v>2.89</v>
+        <v>2.95</v>
       </c>
       <c r="EA15" t="n">
-        <v>19.58</v>
+        <v>19.45</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="16">
@@ -7021,94 +7021,94 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D16" t="n">
         <v>9</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="G16" t="n">
         <v>-1</v>
       </c>
       <c r="H16" t="n">
-        <v>100.4</v>
+        <v>100.64</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="K16" t="n">
-        <v>5.2</v>
+        <v>5.55</v>
       </c>
       <c r="L16" t="n">
         <v>-1</v>
       </c>
       <c r="M16" t="n">
-        <v>50.1</v>
+        <v>50.45</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="O16" t="n">
         <v>-1</v>
       </c>
       <c r="P16" t="n">
-        <v>15.6</v>
+        <v>15.36</v>
       </c>
       <c r="Q16" t="n">
-        <v>16.3</v>
+        <v>16.27</v>
       </c>
       <c r="R16" t="n">
-        <v>6.8</v>
+        <v>6.73</v>
       </c>
       <c r="S16" t="n">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="T16" t="n">
-        <v>1.4</v>
+        <v>1.64</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="V16" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>59.9</v>
+        <v>60.36</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="Z16" t="n">
-        <v>12.6</v>
+        <v>12.82</v>
       </c>
       <c r="AA16" t="n">
-        <v>8.9</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="AB16" t="n">
-        <v>3.7</v>
+        <v>4.18</v>
       </c>
       <c r="AC16" t="n">
-        <v>23</v>
+        <v>22.09</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -7192,31 +7192,31 @@
         <v>2.44</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.84</v>
+        <v>3.05</v>
       </c>
       <c r="BH16" t="n">
-        <v>9.050000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.84</v>
+        <v>3.05</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.79</v>
+        <v>0.9</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.42</v>
+        <v>0.45</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.84</v>
+        <v>0.9</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.21</v>
+        <v>1.35</v>
       </c>
       <c r="BP16" t="n">
         <v>-1</v>
@@ -7228,34 +7228,34 @@
         <v>100</v>
       </c>
       <c r="BS16" t="n">
-        <v>78.95</v>
+        <v>80</v>
       </c>
       <c r="BT16" t="n">
-        <v>57.89</v>
+        <v>60</v>
       </c>
       <c r="BU16" t="n">
-        <v>26.32</v>
+        <v>30</v>
       </c>
       <c r="BV16" t="n">
-        <v>15.79</v>
+        <v>20</v>
       </c>
       <c r="BW16" t="n">
-        <v>5.26</v>
+        <v>10</v>
       </c>
       <c r="BX16" t="n">
-        <v>63.16</v>
+        <v>65</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="BZ16" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.88</v>
+        <v>3.92</v>
       </c>
       <c r="CB16" t="n">
-        <v>4.19</v>
+        <v>4.25</v>
       </c>
       <c r="CC16" t="n">
         <v>2.24</v>
@@ -7267,13 +7267,13 @@
         <v>1.37</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CI16" t="n">
         <v>1.96</v>
@@ -7282,7 +7282,7 @@
         <v>1.85</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CL16" t="n">
         <v>1.91</v>
@@ -7297,28 +7297,28 @@
         <v>1.26</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="CQ16" t="n">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="CR16" t="n">
         <v>1.41</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="CT16" t="n">
         <v>2.99</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CV16" t="n">
         <v>1.98</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CX16" t="n">
         <v>1.54</v>
@@ -7345,73 +7345,73 @@
         <v>0.05</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="DG16" t="n">
         <v>-1</v>
       </c>
       <c r="DH16" t="n">
-        <v>97.47</v>
+        <v>97.75</v>
       </c>
       <c r="DI16" t="n">
         <v>0</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="DK16" t="n">
-        <v>5.42</v>
+        <v>5.6</v>
       </c>
       <c r="DL16" t="n">
         <v>-1</v>
       </c>
       <c r="DM16" t="n">
-        <v>49.84</v>
+        <v>50.05</v>
       </c>
       <c r="DN16" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="DO16" t="n">
         <v>-1</v>
       </c>
       <c r="DP16" t="n">
-        <v>15.79</v>
+        <v>15.65</v>
       </c>
       <c r="DQ16" t="n">
-        <v>16.16</v>
+        <v>16.15</v>
       </c>
       <c r="DR16" t="n">
-        <v>6.37</v>
+        <v>6.35</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>61.47</v>
+        <v>61.65</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DX16" t="n">
-        <v>13.05</v>
+        <v>13.15</v>
       </c>
       <c r="DY16" t="n">
-        <v>9.1</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="DZ16" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="EA16" t="n">
-        <v>21.21</v>
+        <v>20.8</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="EC16" t="n">
         <v>2.1</v>
@@ -7424,13 +7424,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C17" t="n">
         <v>10</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E17" t="n">
         <v>0.1</v>
@@ -7517,106 +7517,106 @@
         <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AH17" t="n">
         <v>-1</v>
       </c>
       <c r="AI17" t="n">
-        <v>95.44</v>
+        <v>92.8</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AL17" t="n">
-        <v>5.78</v>
+        <v>5.7</v>
       </c>
       <c r="AM17" t="n">
         <v>-1</v>
       </c>
       <c r="AN17" t="n">
-        <v>52.78</v>
+        <v>51.6</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AP17" t="n">
         <v>-1</v>
       </c>
       <c r="AQ17" t="n">
-        <v>9.890000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>22.56</v>
+        <v>22.2</v>
       </c>
       <c r="AS17" t="n">
-        <v>6.78</v>
+        <v>7</v>
       </c>
       <c r="AT17" t="n">
-        <v>0.78</v>
+        <v>0.9</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AX17" t="n">
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>60.89</v>
+        <v>61</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA17" t="n">
-        <v>10.44</v>
+        <v>11.2</v>
       </c>
       <c r="BB17" t="n">
-        <v>6.11</v>
+        <v>6.8</v>
       </c>
       <c r="BC17" t="n">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="BD17" t="n">
-        <v>19.67</v>
+        <v>19</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.369999999999999</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.42</v>
+        <v>0.45</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.89</v>
+        <v>0.95</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="BO17" t="n">
         <v>1.05</v>
@@ -7628,25 +7628,25 @@
         <v>-1</v>
       </c>
       <c r="BR17" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS17" t="n">
-        <v>78.95</v>
+        <v>80</v>
       </c>
       <c r="BT17" t="n">
-        <v>36.84</v>
+        <v>40</v>
       </c>
       <c r="BU17" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BV17" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BW17" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX17" t="n">
-        <v>42.11</v>
+        <v>45</v>
       </c>
       <c r="BY17" t="n">
         <v>1.37</v>
@@ -7655,22 +7655,22 @@
         <v>1.39</v>
       </c>
       <c r="CA17" t="n">
-        <v>4.75</v>
+        <v>4.73</v>
       </c>
       <c r="CB17" t="n">
-        <v>5.04</v>
+        <v>5.02</v>
       </c>
       <c r="CC17" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="CD17" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="CE17" t="n">
         <v>1.36</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="CG17" t="n">
         <v>3.16</v>
@@ -7691,7 +7691,7 @@
         <v>1.93</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="CN17" t="n">
         <v>1.94</v>
@@ -7727,7 +7727,7 @@
         <v>1.55</v>
       </c>
       <c r="CY17" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CZ17" t="n">
         <v>2.42</v>
@@ -7736,88 +7736,88 @@
         <v>1.93</v>
       </c>
       <c r="DB17" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="DE17" t="n">
         <v>0.05</v>
       </c>
       <c r="DF17" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="DG17" t="n">
         <v>-1</v>
       </c>
       <c r="DH17" t="n">
-        <v>94.05</v>
+        <v>92.8</v>
       </c>
       <c r="DI17" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ17" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="DK17" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="DL17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="DM17" t="n">
+        <v>51.1</v>
+      </c>
+      <c r="DN17" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="DO17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="DP17" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="DQ17" t="n">
+        <v>20.35</v>
+      </c>
+      <c r="DR17" t="n">
         <v>5.9</v>
       </c>
-      <c r="DL17" t="n">
-        <v>-1</v>
-      </c>
-      <c r="DM17" t="n">
-        <v>51.63</v>
-      </c>
-      <c r="DN17" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="DO17" t="n">
-        <v>-1</v>
-      </c>
-      <c r="DP17" t="n">
-        <v>9.58</v>
-      </c>
-      <c r="DQ17" t="n">
-        <v>20.42</v>
-      </c>
-      <c r="DR17" t="n">
-        <v>5.74</v>
-      </c>
       <c r="DS17" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>61.53</v>
+        <v>61.55</v>
       </c>
       <c r="DW17" t="n">
         <v>0.05</v>
       </c>
       <c r="DX17" t="n">
-        <v>12.79</v>
+        <v>13.05</v>
       </c>
       <c r="DY17" t="n">
-        <v>7.42</v>
+        <v>7.7</v>
       </c>
       <c r="DZ17" t="n">
-        <v>5.37</v>
+        <v>5.35</v>
       </c>
       <c r="EA17" t="n">
-        <v>19.69</v>
+        <v>19.35</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Russian_Premier_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Russian_Premier_League_2025-2026.xlsx
@@ -1881,7 +1881,7 @@
         <v>-1</v>
       </c>
       <c r="AI3" t="n">
-        <v>83.55</v>
+        <v>83.09</v>
       </c>
       <c r="AJ3" t="n">
         <v>0.18</v>
@@ -1908,7 +1908,7 @@
         <v>15</v>
       </c>
       <c r="AR3" t="n">
-        <v>13.36</v>
+        <v>13.82</v>
       </c>
       <c r="AS3" t="n">
         <v>8.359999999999999</v>
@@ -2112,7 +2112,7 @@
         <v>-1</v>
       </c>
       <c r="DH3" t="n">
-        <v>90.8</v>
+        <v>90.55</v>
       </c>
       <c r="DI3" t="n">
         <v>0.2</v>
@@ -2139,7 +2139,7 @@
         <v>15.1</v>
       </c>
       <c r="DQ3" t="n">
-        <v>14.35</v>
+        <v>14.6</v>
       </c>
       <c r="DR3" t="n">
         <v>7.75</v>
@@ -4266,7 +4266,7 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>46.11</v>
+        <v>46</v>
       </c>
       <c r="Y9" t="n">
         <v>0.11</v>
@@ -4572,7 +4572,7 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>46.05</v>
+        <v>46</v>
       </c>
       <c r="DW9" t="n">
         <v>0.1</v>
@@ -5153,7 +5153,7 @@
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>49</v>
+        <v>49.1</v>
       </c>
       <c r="AZ11" t="n">
         <v>0.2</v>
@@ -5378,7 +5378,7 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>49.15</v>
+        <v>49.2</v>
       </c>
       <c r="DW11" t="n">
         <v>0.15</v>
@@ -7039,7 +7039,7 @@
         <v>-1</v>
       </c>
       <c r="H16" t="n">
-        <v>100.64</v>
+        <v>100</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -7093,10 +7093,10 @@
         <v>0.27</v>
       </c>
       <c r="Z16" t="n">
-        <v>12.82</v>
+        <v>12.91</v>
       </c>
       <c r="AA16" t="n">
-        <v>8.640000000000001</v>
+        <v>8.73</v>
       </c>
       <c r="AB16" t="n">
         <v>4.18</v>
@@ -7105,7 +7105,7 @@
         <v>22.09</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AE16" t="n">
         <v>1.82</v>
@@ -7351,7 +7351,7 @@
         <v>-1</v>
       </c>
       <c r="DH16" t="n">
-        <v>97.75</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="DI16" t="n">
         <v>0</v>
@@ -7399,10 +7399,10 @@
         <v>0.2</v>
       </c>
       <c r="DX16" t="n">
-        <v>13.15</v>
+        <v>13.2</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.949999999999999</v>
+        <v>9</v>
       </c>
       <c r="DZ16" t="n">
         <v>4.2</v>
@@ -7577,10 +7577,10 @@
         <v>0.1</v>
       </c>
       <c r="BA17" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="BB17" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="BC17" t="n">
         <v>4.4</v>
@@ -7589,7 +7589,7 @@
         <v>19</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="BF17" t="n">
         <v>1.3</v>
@@ -7802,10 +7802,10 @@
         <v>0.05</v>
       </c>
       <c r="DX17" t="n">
-        <v>13.05</v>
+        <v>13.1</v>
       </c>
       <c r="DY17" t="n">
-        <v>7.7</v>
+        <v>7.75</v>
       </c>
       <c r="DZ17" t="n">
         <v>5.35</v>
@@ -7814,7 +7814,7 @@
         <v>19.35</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="EC17" t="n">
         <v>1.35</v>

--- a/data/teams/leagues/Averages_Russian_Premier_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Russian_Premier_League_2025-2026.xlsx
@@ -645,7 +645,7 @@
     <col width="9.6" customWidth="1" min="73" max="73"/>
     <col width="9.6" customWidth="1" min="74" max="74"/>
     <col width="9.6" customWidth="1" min="75" max="75"/>
-    <col width="7.199999999999999" customWidth="1" min="76" max="76"/>
+    <col width="8.4" customWidth="1" min="76" max="76"/>
     <col width="18" customWidth="1" min="77" max="77"/>
     <col width="27.6" customWidth="1" min="78" max="78"/>
     <col width="18" customWidth="1" min="79" max="79"/>
@@ -5006,91 +5006,91 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D11" t="n">
         <v>10</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="F11" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="G11" t="n">
         <v>-1</v>
       </c>
       <c r="H11" t="n">
-        <v>106</v>
+        <v>103.45</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="K11" t="n">
-        <v>5</v>
+        <v>5.09</v>
       </c>
       <c r="L11" t="n">
         <v>-1</v>
       </c>
       <c r="M11" t="n">
-        <v>50.8</v>
+        <v>50.64</v>
       </c>
       <c r="N11" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="O11" t="n">
         <v>-1</v>
       </c>
       <c r="P11" t="n">
-        <v>13.9</v>
+        <v>13.82</v>
       </c>
       <c r="Q11" t="n">
-        <v>19.3</v>
+        <v>18.82</v>
       </c>
       <c r="R11" t="n">
         <v>7</v>
       </c>
       <c r="S11" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="T11" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="V11" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>49.3</v>
+        <v>49</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z11" t="n">
-        <v>10.6</v>
+        <v>10.73</v>
       </c>
       <c r="AA11" t="n">
-        <v>7.9</v>
+        <v>7.91</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="AC11" t="n">
-        <v>26.6</v>
+        <v>26.18</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AE11" t="n">
         <v>2</v>
@@ -5177,28 +5177,28 @@
         <v>1.9</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="BH11" t="n">
-        <v>8.5</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="BN11" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="BO11" t="n">
         <v>0.9</v>
@@ -5210,16 +5210,16 @@
         <v>-1</v>
       </c>
       <c r="BR11" t="n">
-        <v>90</v>
+        <v>90.48</v>
       </c>
       <c r="BS11" t="n">
-        <v>60</v>
+        <v>57.14</v>
       </c>
       <c r="BT11" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BU11" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BV11" t="n">
         <v>0</v>
@@ -5228,19 +5228,19 @@
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>25</v>
+        <v>23.81</v>
       </c>
       <c r="BY11" t="n">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="BZ11" t="n">
-        <v>3.12</v>
+        <v>3.04</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.41</v>
+        <v>3.39</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.47</v>
+        <v>3.46</v>
       </c>
       <c r="CC11" t="n">
         <v>5.02</v>
@@ -5252,10 +5252,10 @@
         <v>1.51</v>
       </c>
       <c r="CF11" t="n">
-        <v>3.42</v>
+        <v>3.43</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="CH11" t="n">
         <v>1.31</v>
@@ -5270,7 +5270,7 @@
         <v>1.57</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CM11" t="n">
         <v>2.28</v>
@@ -5285,7 +5285,7 @@
         <v>2.39</v>
       </c>
       <c r="CQ11" t="n">
-        <v>4.37</v>
+        <v>4.4</v>
       </c>
       <c r="CR11" t="n">
         <v>1.5</v>
@@ -5318,34 +5318,34 @@
         <v>1.79</v>
       </c>
       <c r="DB11" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="DC11" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="DD11" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="DE11" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="DF11" t="n">
         <v>1.47</v>
       </c>
-      <c r="DC11" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="DD11" t="n">
-        <v>4.76</v>
-      </c>
-      <c r="DE11" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="DF11" t="n">
-        <v>1.5</v>
-      </c>
       <c r="DG11" t="n">
         <v>-1</v>
       </c>
       <c r="DH11" t="n">
-        <v>107.9</v>
+        <v>106.47</v>
       </c>
       <c r="DI11" t="n">
         <v>0</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.6</v>
+        <v>4.67</v>
       </c>
       <c r="DL11" t="n">
         <v>-1</v>
@@ -5354,49 +5354,49 @@
         <v>49</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="DO11" t="n">
         <v>-1</v>
       </c>
       <c r="DP11" t="n">
-        <v>13.7</v>
+        <v>13.67</v>
       </c>
       <c r="DQ11" t="n">
-        <v>19.05</v>
+        <v>18.81</v>
       </c>
       <c r="DR11" t="n">
-        <v>6.85</v>
+        <v>6.86</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>49.2</v>
+        <v>49.05</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX11" t="n">
-        <v>10.3</v>
+        <v>10.38</v>
       </c>
       <c r="DY11" t="n">
-        <v>7.55</v>
+        <v>7.57</v>
       </c>
       <c r="DZ11" t="n">
-        <v>2.75</v>
+        <v>2.81</v>
       </c>
       <c r="EA11" t="n">
-        <v>24.85</v>
+        <v>24.71</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="EC11" t="n">
         <v>1.95</v>
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C13" t="n">
         <v>11</v>
       </c>
       <c r="D13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E13" t="n">
         <v>0.18</v>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AH13" t="n">
         <v>-1</v>
       </c>
       <c r="AI13" t="n">
-        <v>88.56</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
@@ -5920,94 +5920,94 @@
         <v>2</v>
       </c>
       <c r="AL13" t="n">
-        <v>5.78</v>
+        <v>5.7</v>
       </c>
       <c r="AM13" t="n">
         <v>-1</v>
       </c>
       <c r="AN13" t="n">
-        <v>43.89</v>
+        <v>44.2</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AP13" t="n">
         <v>-1</v>
       </c>
       <c r="AQ13" t="n">
-        <v>13.44</v>
+        <v>13.4</v>
       </c>
       <c r="AR13" t="n">
-        <v>15.89</v>
+        <v>16.1</v>
       </c>
       <c r="AS13" t="n">
-        <v>8.56</v>
+        <v>8.4</v>
       </c>
       <c r="AT13" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AX13" t="n">
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>47.78</v>
+        <v>48.4</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA13" t="n">
-        <v>11.56</v>
+        <v>11.2</v>
       </c>
       <c r="BB13" t="n">
-        <v>7.44</v>
+        <v>7.2</v>
       </c>
       <c r="BC13" t="n">
-        <v>4.11</v>
+        <v>4</v>
       </c>
       <c r="BD13" t="n">
-        <v>23</v>
+        <v>22.8</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.55</v>
+        <v>2.48</v>
       </c>
       <c r="BH13" t="n">
-        <v>10</v>
+        <v>10.05</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.55</v>
+        <v>2.48</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="BL13" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BP13" t="n">
         <v>-1</v>
@@ -6016,25 +6016,25 @@
         <v>-1</v>
       </c>
       <c r="BR13" t="n">
-        <v>90</v>
+        <v>90.48</v>
       </c>
       <c r="BS13" t="n">
-        <v>65</v>
+        <v>61.9</v>
       </c>
       <c r="BT13" t="n">
-        <v>45</v>
+        <v>42.86</v>
       </c>
       <c r="BU13" t="n">
-        <v>35</v>
+        <v>33.33</v>
       </c>
       <c r="BV13" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BW13" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX13" t="n">
-        <v>55</v>
+        <v>52.38</v>
       </c>
       <c r="BY13" t="n">
         <v>3.85</v>
@@ -6043,55 +6043,55 @@
         <v>4.42</v>
       </c>
       <c r="CA13" t="n">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.35</v>
+        <v>4.29</v>
       </c>
       <c r="CC13" t="n">
-        <v>6.29</v>
+        <v>5.98</v>
       </c>
       <c r="CD13" t="n">
-        <v>6.6</v>
+        <v>6.31</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.61</v>
+        <v>2.66</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.2</v>
+        <v>3.16</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="CN13" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.91</v>
+        <v>3.01</v>
       </c>
       <c r="CR13" t="n">
         <v>1.4</v>
@@ -6106,10 +6106,10 @@
         <v>1.56</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="CW13" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="CX13" t="n">
         <v>1.54</v>
@@ -6124,88 +6124,88 @@
         <v>2.09</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="DD13" t="n">
-        <v>3.04</v>
+        <v>3.16</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="DG13" t="n">
         <v>-1</v>
       </c>
       <c r="DH13" t="n">
-        <v>85.59999999999999</v>
+        <v>85.67</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.5</v>
+        <v>5.47</v>
       </c>
       <c r="DL13" t="n">
         <v>-1</v>
       </c>
       <c r="DM13" t="n">
-        <v>43.55</v>
+        <v>43.71</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="DO13" t="n">
         <v>-1</v>
       </c>
       <c r="DP13" t="n">
-        <v>15.05</v>
+        <v>14.95</v>
       </c>
       <c r="DQ13" t="n">
-        <v>15.75</v>
+        <v>15.86</v>
       </c>
       <c r="DR13" t="n">
-        <v>8.15</v>
+        <v>8.1</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>48.45</v>
+        <v>48.71</v>
       </c>
       <c r="DW13" t="n">
         <v>0.05</v>
       </c>
       <c r="DX13" t="n">
-        <v>12.2</v>
+        <v>12</v>
       </c>
       <c r="DY13" t="n">
-        <v>8.25</v>
+        <v>8.1</v>
       </c>
       <c r="DZ13" t="n">
-        <v>3.95</v>
+        <v>3.91</v>
       </c>
       <c r="EA13" t="n">
-        <v>21.45</v>
+        <v>21.43</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="14">

--- a/data/teams/leagues/Averages_Russian_Premier_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Russian_Premier_League_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C2" t="n">
         <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" t="n">
         <v>0.3</v>
@@ -1472,109 +1472,109 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AH2" t="n">
         <v>-1</v>
       </c>
       <c r="AI2" t="n">
-        <v>92</v>
+        <v>90.36</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.6</v>
+        <v>2.73</v>
       </c>
       <c r="AL2" t="n">
-        <v>3.9</v>
+        <v>3.82</v>
       </c>
       <c r="AM2" t="n">
         <v>-1</v>
       </c>
       <c r="AN2" t="n">
-        <v>41.5</v>
+        <v>40.73</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.7</v>
+        <v>0.82</v>
       </c>
       <c r="AP2" t="n">
         <v>-1</v>
       </c>
       <c r="AQ2" t="n">
-        <v>13.8</v>
+        <v>13.64</v>
       </c>
       <c r="AR2" t="n">
-        <v>17.9</v>
+        <v>18.09</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.3</v>
+        <v>7.82</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AU2" t="n">
         <v>1</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>45.8</v>
+        <v>45.55</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="BA2" t="n">
-        <v>10.3</v>
+        <v>10.45</v>
       </c>
       <c r="BB2" t="n">
-        <v>7.4</v>
+        <v>7.55</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="BD2" t="n">
-        <v>21.4</v>
+        <v>20.82</v>
       </c>
       <c r="BE2" t="n">
         <v>1.16</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="BH2" t="n">
-        <v>8.85</v>
+        <v>8.76</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="BP2" t="n">
         <v>-1</v>
@@ -1586,22 +1586,22 @@
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>75</v>
+        <v>76.19</v>
       </c>
       <c r="BT2" t="n">
-        <v>50</v>
+        <v>47.62</v>
       </c>
       <c r="BU2" t="n">
-        <v>25</v>
+        <v>23.81</v>
       </c>
       <c r="BV2" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BW2" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX2" t="n">
-        <v>55</v>
+        <v>57.14</v>
       </c>
       <c r="BY2" t="n">
         <v>2.69</v>
@@ -1610,16 +1610,16 @@
         <v>2.71</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.51</v>
+        <v>3.5</v>
       </c>
       <c r="CB2" t="n">
         <v>3.59</v>
       </c>
       <c r="CC2" t="n">
-        <v>3.51</v>
+        <v>3.42</v>
       </c>
       <c r="CD2" t="n">
-        <v>3.62</v>
+        <v>3.5</v>
       </c>
       <c r="CE2" t="n">
         <v>1.41</v>
@@ -1631,22 +1631,22 @@
         <v>2.85</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CK2" t="n">
         <v>1.48</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="CN2" t="n">
         <v>1.94</v>
@@ -1658,7 +1658,7 @@
         <v>2.02</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.44</v>
+        <v>3.43</v>
       </c>
       <c r="CR2" t="n">
         <v>1.38</v>
@@ -1673,10 +1673,10 @@
         <v>1.43</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CX2" t="n">
         <v>1.56</v>
@@ -1697,37 +1697,37 @@
         <v>2.02</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.53</v>
+        <v>3.51</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="DG2" t="n">
         <v>-1</v>
       </c>
       <c r="DH2" t="n">
-        <v>90.84999999999999</v>
+        <v>90.05</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="DK2" t="n">
-        <v>4.45</v>
+        <v>4.38</v>
       </c>
       <c r="DL2" t="n">
         <v>-1</v>
       </c>
       <c r="DM2" t="n">
-        <v>43.6</v>
+        <v>43.1</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.45</v>
+        <v>0.52</v>
       </c>
       <c r="DO2" t="n">
         <v>-1</v>
@@ -1736,43 +1736,43 @@
         <v>12</v>
       </c>
       <c r="DQ2" t="n">
-        <v>17.05</v>
+        <v>17.19</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>45.7</v>
+        <v>45.57</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.3</v>
+        <v>0.34</v>
       </c>
       <c r="DX2" t="n">
-        <v>12.45</v>
+        <v>12.43</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.550000000000001</v>
+        <v>8.57</v>
       </c>
       <c r="DZ2" t="n">
-        <v>3.9</v>
+        <v>3.86</v>
       </c>
       <c r="EA2" t="n">
-        <v>21.25</v>
+        <v>20.95</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="3">
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" t="n">
         <v>11</v>
@@ -1794,82 +1794,82 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="G3" t="n">
         <v>-1</v>
       </c>
       <c r="H3" t="n">
-        <v>99.67</v>
+        <v>101</v>
       </c>
       <c r="I3" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="J3" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="K3" t="n">
-        <v>4.11</v>
+        <v>4.1</v>
       </c>
       <c r="L3" t="n">
         <v>-1</v>
       </c>
       <c r="M3" t="n">
-        <v>49.33</v>
+        <v>51.5</v>
       </c>
       <c r="N3" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="O3" t="n">
         <v>-1</v>
       </c>
       <c r="P3" t="n">
-        <v>15.22</v>
+        <v>15.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>15.56</v>
+        <v>15.4</v>
       </c>
       <c r="R3" t="n">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="S3" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="T3" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="U3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>46</v>
+        <v>47.1</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>11.11</v>
+        <v>11.7</v>
       </c>
       <c r="AA3" t="n">
-        <v>6.56</v>
+        <v>7.2</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.56</v>
+        <v>4.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>19</v>
+        <v>18.8</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AF3" t="n">
         <v>0.09</v>
@@ -1953,31 +1953,31 @@
         <v>2.18</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="BH3" t="n">
-        <v>8.949999999999999</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="BP3" t="n">
         <v>-1</v>
@@ -1989,34 +1989,34 @@
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>90</v>
+        <v>90.48</v>
       </c>
       <c r="BT3" t="n">
-        <v>50</v>
+        <v>47.62</v>
       </c>
       <c r="BU3" t="n">
-        <v>25</v>
+        <v>23.81</v>
       </c>
       <c r="BV3" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BW3" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX3" t="n">
-        <v>65</v>
+        <v>66.67</v>
       </c>
       <c r="BY3" t="n">
-        <v>3.38</v>
+        <v>3.32</v>
       </c>
       <c r="BZ3" t="n">
-        <v>3.61</v>
+        <v>3.56</v>
       </c>
       <c r="CA3" t="n">
-        <v>4</v>
+        <v>3.97</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.28</v>
+        <v>4.24</v>
       </c>
       <c r="CC3" t="n">
         <v>5.69</v>
@@ -2025,16 +2025,16 @@
         <v>6.02</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.31</v>
+        <v>3.29</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CI3" t="n">
         <v>2.08</v>
@@ -2046,22 +2046,22 @@
         <v>1.46</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CO3" t="n">
         <v>1.22</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="CR3" t="n">
         <v>1.38</v>
@@ -2076,49 +2076,49 @@
         <v>1.49</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CX3" t="n">
         <v>1.55</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="DB3" t="n">
         <v>1.24</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="DD3" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="DE3" t="n">
         <v>0.05</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="DG3" t="n">
         <v>-1</v>
       </c>
       <c r="DH3" t="n">
-        <v>90.55</v>
+        <v>91.62</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="DK3" t="n">
         <v>4.05</v>
@@ -2127,55 +2127,55 @@
         <v>-1</v>
       </c>
       <c r="DM3" t="n">
-        <v>43.65</v>
+        <v>44.95</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="DO3" t="n">
         <v>-1</v>
       </c>
       <c r="DP3" t="n">
-        <v>15.1</v>
+        <v>15.14</v>
       </c>
       <c r="DQ3" t="n">
-        <v>14.6</v>
+        <v>14.57</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.75</v>
+        <v>7.86</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>43.4</v>
+        <v>44.05</v>
       </c>
       <c r="DW3" t="n">
         <v>0.05</v>
       </c>
       <c r="DX3" t="n">
-        <v>10.8</v>
+        <v>11.1</v>
       </c>
       <c r="DY3" t="n">
-        <v>6.9</v>
+        <v>7.19</v>
       </c>
       <c r="DZ3" t="n">
         <v>3.9</v>
       </c>
       <c r="EA3" t="n">
-        <v>17.7</v>
+        <v>17.67</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="4">
@@ -2185,40 +2185,40 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
         <v>11</v>
       </c>
       <c r="E4" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="F4" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="G4" t="n">
         <v>-1</v>
       </c>
       <c r="H4" t="n">
-        <v>83</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="J4" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="K4" t="n">
-        <v>3.33</v>
+        <v>3.5</v>
       </c>
       <c r="L4" t="n">
         <v>-1</v>
       </c>
       <c r="M4" t="n">
-        <v>45.67</v>
+        <v>45.6</v>
       </c>
       <c r="N4" t="n">
         <v>1</v>
@@ -2227,52 +2227,52 @@
         <v>-1</v>
       </c>
       <c r="P4" t="n">
-        <v>19.44</v>
+        <v>19.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>12.33</v>
+        <v>12.1</v>
       </c>
       <c r="R4" t="n">
-        <v>7.56</v>
+        <v>7.6</v>
       </c>
       <c r="S4" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="T4" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="U4" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="V4" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>43.22</v>
+        <v>42.7</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z4" t="n">
-        <v>12.89</v>
+        <v>12.6</v>
       </c>
       <c r="AA4" t="n">
-        <v>8.890000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="AB4" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AC4" t="n">
-        <v>22</v>
+        <v>21.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AF4" t="n">
         <v>0.18</v>
@@ -2356,31 +2356,31 @@
         <v>3.36</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="BH4" t="n">
-        <v>8.15</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BN4" t="n">
         <v>0.9</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="BP4" t="n">
         <v>-1</v>
@@ -2389,25 +2389,25 @@
         <v>-1</v>
       </c>
       <c r="BR4" t="n">
-        <v>80</v>
+        <v>80.95</v>
       </c>
       <c r="BS4" t="n">
-        <v>65</v>
+        <v>61.9</v>
       </c>
       <c r="BT4" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BU4" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BV4" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>30</v>
+        <v>28.57</v>
       </c>
       <c r="BY4" t="n">
         <v>2.46</v>
@@ -2416,10 +2416,10 @@
         <v>2.65</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.49</v>
+        <v>3.48</v>
       </c>
       <c r="CC4" t="n">
         <v>3.61</v>
@@ -2428,10 +2428,10 @@
         <v>3.9</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CF4" t="n">
-        <v>3.05</v>
+        <v>3.07</v>
       </c>
       <c r="CG4" t="n">
         <v>2.53</v>
@@ -2443,13 +2443,13 @@
         <v>1.67</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CK4" t="n">
         <v>1.47</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CM4" t="n">
         <v>2.27</v>
@@ -2461,10 +2461,10 @@
         <v>1.34</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.99</v>
+        <v>4.01</v>
       </c>
       <c r="CR4" t="n">
         <v>1.47</v>
@@ -2485,16 +2485,16 @@
         <v>2.11</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CY4" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="DB4" t="n">
         <v>1.43</v>
@@ -2503,76 +2503,76 @@
         <v>2.37</v>
       </c>
       <c r="DD4" t="n">
-        <v>4.46</v>
+        <v>4.47</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="DG4" t="n">
         <v>-1</v>
       </c>
       <c r="DH4" t="n">
-        <v>88.95</v>
+        <v>88.86</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DJ4" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="DK4" t="n">
-        <v>3.35</v>
+        <v>3.43</v>
       </c>
       <c r="DL4" t="n">
         <v>-1</v>
       </c>
       <c r="DM4" t="n">
-        <v>44.2</v>
+        <v>44.24</v>
       </c>
       <c r="DN4" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="DO4" t="n">
         <v>-1</v>
       </c>
       <c r="DP4" t="n">
-        <v>19.35</v>
+        <v>19.52</v>
       </c>
       <c r="DQ4" t="n">
-        <v>12.6</v>
+        <v>12.48</v>
       </c>
       <c r="DR4" t="n">
-        <v>7.8</v>
+        <v>7.81</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>45.5</v>
+        <v>45.14</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX4" t="n">
-        <v>12.35</v>
+        <v>12.24</v>
       </c>
       <c r="DY4" t="n">
-        <v>8.300000000000001</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.05</v>
+        <v>4.09</v>
       </c>
       <c r="EA4" t="n">
-        <v>21.35</v>
+        <v>21.14</v>
       </c>
       <c r="EB4" t="n">
         <v>1.38</v>
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C5" t="n">
         <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E5" t="n">
         <v>0.3</v>
@@ -2681,76 +2681,76 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AH5" t="n">
         <v>-1</v>
       </c>
       <c r="AI5" t="n">
-        <v>97.8</v>
+        <v>98.91</v>
       </c>
       <c r="AJ5" t="n">
         <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="AL5" t="n">
-        <v>5.6</v>
+        <v>5.64</v>
       </c>
       <c r="AM5" t="n">
         <v>-1</v>
       </c>
       <c r="AN5" t="n">
-        <v>45.3</v>
+        <v>46.27</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AP5" t="n">
         <v>-1</v>
       </c>
       <c r="AQ5" t="n">
-        <v>12.8</v>
+        <v>12.55</v>
       </c>
       <c r="AR5" t="n">
-        <v>13.6</v>
+        <v>14.55</v>
       </c>
       <c r="AS5" t="n">
-        <v>10.2</v>
+        <v>9.73</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AU5" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>53.3</v>
+        <v>54.09</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="BA5" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="BB5" t="n">
-        <v>9</v>
+        <v>8.91</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.1</v>
+        <v>4.09</v>
       </c>
       <c r="BD5" t="n">
-        <v>21.1</v>
+        <v>22.09</v>
       </c>
       <c r="BE5" t="n">
         <v>1.45</v>
@@ -2759,31 +2759,31 @@
         <v>2</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.65</v>
+        <v>2.57</v>
       </c>
       <c r="BH5" t="n">
         <v>11.05</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.65</v>
+        <v>2.57</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BN5" t="n">
         <v>1.05</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="BP5" t="n">
         <v>-1</v>
@@ -2792,25 +2792,25 @@
         <v>-1</v>
       </c>
       <c r="BR5" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS5" t="n">
-        <v>65</v>
+        <v>61.9</v>
       </c>
       <c r="BT5" t="n">
-        <v>45</v>
+        <v>42.86</v>
       </c>
       <c r="BU5" t="n">
-        <v>35</v>
+        <v>33.33</v>
       </c>
       <c r="BV5" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BW5" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX5" t="n">
-        <v>50</v>
+        <v>47.62</v>
       </c>
       <c r="BY5" t="n">
         <v>1.86</v>
@@ -2819,40 +2819,40 @@
         <v>1.94</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.72</v>
+        <v>3.69</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.84</v>
+        <v>3.81</v>
       </c>
       <c r="CC5" t="n">
-        <v>2.91</v>
+        <v>2.89</v>
       </c>
       <c r="CD5" t="n">
-        <v>3.13</v>
+        <v>3.11</v>
       </c>
       <c r="CE5" t="n">
         <v>1.38</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.76</v>
+        <v>2.79</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.02</v>
+        <v>2.99</v>
       </c>
       <c r="CH5" t="n">
         <v>1.45</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="CM5" t="n">
         <v>2.46</v>
@@ -2861,13 +2861,13 @@
         <v>1.89</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.19</v>
+        <v>3.25</v>
       </c>
       <c r="CR5" t="n">
         <v>1.42</v>
@@ -2882,10 +2882,10 @@
         <v>1.4</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CX5" t="n">
         <v>1.57</v>
@@ -2894,94 +2894,94 @@
         <v>1.94</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="DA5" t="n">
         <v>1.87</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.3</v>
+        <v>3.37</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="DG5" t="n">
         <v>-1</v>
       </c>
       <c r="DH5" t="n">
-        <v>101.6</v>
+        <v>102</v>
       </c>
       <c r="DI5" t="n">
         <v>0</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.25</v>
+        <v>5.29</v>
       </c>
       <c r="DL5" t="n">
         <v>-1</v>
       </c>
       <c r="DM5" t="n">
-        <v>49.15</v>
+        <v>49.47</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="DO5" t="n">
         <v>-1</v>
       </c>
       <c r="DP5" t="n">
-        <v>11.9</v>
+        <v>11.81</v>
       </c>
       <c r="DQ5" t="n">
-        <v>15.55</v>
+        <v>15.95</v>
       </c>
       <c r="DR5" t="n">
-        <v>9.300000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>55.65</v>
+        <v>55.95</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DX5" t="n">
-        <v>13.7</v>
+        <v>13.62</v>
       </c>
       <c r="DY5" t="n">
-        <v>9.050000000000001</v>
+        <v>9</v>
       </c>
       <c r="DZ5" t="n">
-        <v>4.65</v>
+        <v>4.62</v>
       </c>
       <c r="EA5" t="n">
-        <v>20.75</v>
+        <v>21.29</v>
       </c>
       <c r="EB5" t="n">
         <v>1.55</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="6">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C6" t="n">
         <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -3081,112 +3081,112 @@
         <v>1.5</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AH6" t="n">
         <v>-1</v>
       </c>
       <c r="AI6" t="n">
-        <v>90.40000000000001</v>
+        <v>91</v>
       </c>
       <c r="AJ6" t="n">
         <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.4</v>
+        <v>2.64</v>
       </c>
       <c r="AL6" t="n">
-        <v>5.1</v>
+        <v>5.27</v>
       </c>
       <c r="AM6" t="n">
         <v>-1</v>
       </c>
       <c r="AN6" t="n">
-        <v>47.8</v>
+        <v>49</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AP6" t="n">
         <v>-1</v>
       </c>
       <c r="AQ6" t="n">
-        <v>14.9</v>
+        <v>14.55</v>
       </c>
       <c r="AR6" t="n">
-        <v>15.3</v>
+        <v>15.36</v>
       </c>
       <c r="AS6" t="n">
-        <v>6.3</v>
+        <v>6.36</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AX6" t="n">
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>51.2</v>
+        <v>51.91</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="BA6" t="n">
-        <v>15.3</v>
+        <v>15.45</v>
       </c>
       <c r="BB6" t="n">
-        <v>11.4</v>
+        <v>11.64</v>
       </c>
       <c r="BC6" t="n">
-        <v>3.9</v>
+        <v>3.82</v>
       </c>
       <c r="BD6" t="n">
-        <v>21.1</v>
+        <v>20.55</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="BG6" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.9</v>
+        <v>10.1</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BL6" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="BP6" t="n">
         <v>-1</v>
@@ -3195,25 +3195,25 @@
         <v>-1</v>
       </c>
       <c r="BR6" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS6" t="n">
-        <v>80</v>
+        <v>76.19</v>
       </c>
       <c r="BT6" t="n">
-        <v>65</v>
+        <v>61.9</v>
       </c>
       <c r="BU6" t="n">
-        <v>40</v>
+        <v>38.1</v>
       </c>
       <c r="BV6" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BW6" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX6" t="n">
-        <v>65</v>
+        <v>61.9</v>
       </c>
       <c r="BY6" t="n">
         <v>1.82</v>
@@ -3222,16 +3222,16 @@
         <v>1.84</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.84</v>
+        <v>3.81</v>
       </c>
       <c r="CB6" t="n">
-        <v>4.03</v>
+        <v>4</v>
       </c>
       <c r="CC6" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="CD6" t="n">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="CE6" t="n">
         <v>1.33</v>
@@ -3252,37 +3252,37 @@
         <v>1.69</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CO6" t="n">
         <v>1.23</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="CR6" t="n">
         <v>1.35</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.55</v>
+        <v>2.59</v>
       </c>
       <c r="CT6" t="n">
         <v>3.22</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CV6" t="n">
         <v>2.22</v>
@@ -3291,100 +3291,100 @@
         <v>1.71</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="DE6" t="n">
         <v>0.05</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="DG6" t="n">
         <v>-1</v>
       </c>
       <c r="DH6" t="n">
-        <v>95.8</v>
+        <v>95.86</v>
       </c>
       <c r="DI6" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ6" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="DK6" t="n">
-        <v>5.45</v>
+        <v>5.52</v>
       </c>
       <c r="DL6" t="n">
         <v>-1</v>
       </c>
       <c r="DM6" t="n">
-        <v>50.65</v>
+        <v>51.14</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="DO6" t="n">
         <v>-1</v>
       </c>
       <c r="DP6" t="n">
-        <v>13.6</v>
+        <v>13.48</v>
       </c>
       <c r="DQ6" t="n">
-        <v>16.5</v>
+        <v>16.47</v>
       </c>
       <c r="DR6" t="n">
-        <v>5.6</v>
+        <v>5.66</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>54.25</v>
+        <v>54.48</v>
       </c>
       <c r="DW6" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="DX6" t="n">
-        <v>16</v>
+        <v>16.05</v>
       </c>
       <c r="DY6" t="n">
-        <v>11.15</v>
+        <v>11.29</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.85</v>
+        <v>4.76</v>
       </c>
       <c r="EA6" t="n">
-        <v>20.9</v>
+        <v>20.62</v>
       </c>
       <c r="EB6" t="n">
         <v>1.72</v>
       </c>
       <c r="EC6" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="7">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D7" t="n">
         <v>10</v>
@@ -3406,82 +3406,82 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="G7" t="n">
         <v>-1</v>
       </c>
       <c r="H7" t="n">
-        <v>77.40000000000001</v>
+        <v>77.55</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J7" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="K7" t="n">
-        <v>4.3</v>
+        <v>4.27</v>
       </c>
       <c r="L7" t="n">
         <v>-1</v>
       </c>
       <c r="M7" t="n">
-        <v>36</v>
+        <v>36.64</v>
       </c>
       <c r="N7" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="O7" t="n">
         <v>-1</v>
       </c>
       <c r="P7" t="n">
-        <v>13.3</v>
+        <v>13.73</v>
       </c>
       <c r="Q7" t="n">
-        <v>14.4</v>
+        <v>14.36</v>
       </c>
       <c r="R7" t="n">
-        <v>8.699999999999999</v>
+        <v>8.73</v>
       </c>
       <c r="S7" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="T7" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="V7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>46</v>
+        <v>44.91</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>8.5</v>
+        <v>8.18</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.9</v>
+        <v>5.64</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="AC7" t="n">
-        <v>16.9</v>
+        <v>17.36</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -3565,31 +3565,31 @@
         <v>2.3</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.4</v>
+        <v>8.67</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="BL7" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BN7" t="n">
         <v>2</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="BP7" t="n">
         <v>-1</v>
@@ -3598,37 +3598,37 @@
         <v>-1</v>
       </c>
       <c r="BR7" t="n">
-        <v>90</v>
+        <v>90.48</v>
       </c>
       <c r="BS7" t="n">
-        <v>85</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT7" t="n">
-        <v>70</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BU7" t="n">
-        <v>40</v>
+        <v>38.1</v>
       </c>
       <c r="BV7" t="n">
-        <v>25</v>
+        <v>23.81</v>
       </c>
       <c r="BW7" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BX7" t="n">
-        <v>60</v>
+        <v>61.9</v>
       </c>
       <c r="BY7" t="n">
-        <v>4.28</v>
+        <v>4.69</v>
       </c>
       <c r="BZ7" t="n">
-        <v>4.42</v>
+        <v>4.92</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.65</v>
+        <v>3.69</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.86</v>
+        <v>3.94</v>
       </c>
       <c r="CC7" t="n">
         <v>4.7</v>
@@ -3637,22 +3637,22 @@
         <v>5.31</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.97</v>
+        <v>2.98</v>
       </c>
       <c r="CH7" t="n">
         <v>1.42</v>
       </c>
       <c r="CI7" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="CJ7" t="n">
         <v>1.9</v>
-      </c>
-      <c r="CJ7" t="n">
-        <v>1.89</v>
       </c>
       <c r="CK7" t="n">
         <v>1.51</v>
@@ -3661,19 +3661,19 @@
         <v>2.03</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="CN7" t="n">
         <v>1.86</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.43</v>
+        <v>3.4</v>
       </c>
       <c r="CR7" t="n">
         <v>1.48</v>
@@ -3688,22 +3688,22 @@
         <v>1.41</v>
       </c>
       <c r="CV7" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CY7" t="n">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="DB7" t="n">
         <v>1.36</v>
@@ -3718,76 +3718,76 @@
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="DG7" t="n">
         <v>-1</v>
       </c>
       <c r="DH7" t="n">
-        <v>80.40000000000001</v>
+        <v>80.34</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="DK7" t="n">
-        <v>3.35</v>
+        <v>3.38</v>
       </c>
       <c r="DL7" t="n">
         <v>-1</v>
       </c>
       <c r="DM7" t="n">
-        <v>34.55</v>
+        <v>34.95</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="DO7" t="n">
         <v>-1</v>
       </c>
       <c r="DP7" t="n">
-        <v>14.2</v>
+        <v>14.38</v>
       </c>
       <c r="DQ7" t="n">
-        <v>14.45</v>
+        <v>14.43</v>
       </c>
       <c r="DR7" t="n">
-        <v>8.800000000000001</v>
+        <v>8.81</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>46.65</v>
+        <v>46.05</v>
       </c>
       <c r="DW7" t="n">
         <v>0.05</v>
       </c>
       <c r="DX7" t="n">
-        <v>8.1</v>
+        <v>7.95</v>
       </c>
       <c r="DY7" t="n">
-        <v>5.5</v>
+        <v>5.38</v>
       </c>
       <c r="DZ7" t="n">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="EA7" t="n">
-        <v>17.7</v>
+        <v>17.9</v>
       </c>
       <c r="EB7" t="n">
         <v>0.95</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="8">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C8" t="n">
         <v>11</v>
       </c>
       <c r="D8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E8" t="n">
         <v>0.09</v>
@@ -3887,112 +3887,112 @@
         <v>2.55</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AH8" t="n">
         <v>-1</v>
       </c>
       <c r="AI8" t="n">
-        <v>90.33</v>
+        <v>90.3</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AL8" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="AM8" t="n">
         <v>-1</v>
       </c>
       <c r="AN8" t="n">
-        <v>38.22</v>
+        <v>39.7</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.44</v>
+        <v>0.6</v>
       </c>
       <c r="AP8" t="n">
         <v>-1</v>
       </c>
       <c r="AQ8" t="n">
-        <v>14.44</v>
+        <v>14.1</v>
       </c>
       <c r="AR8" t="n">
-        <v>19.44</v>
+        <v>19.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>8.109999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>57.44</v>
+        <v>58.3</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA8" t="n">
-        <v>12.22</v>
+        <v>13.5</v>
       </c>
       <c r="BB8" t="n">
-        <v>8.109999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.11</v>
+        <v>4.7</v>
       </c>
       <c r="BD8" t="n">
-        <v>21.33</v>
+        <v>20.6</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.34</v>
+        <v>1.47</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="BH8" t="n">
-        <v>8.550000000000001</v>
+        <v>8.81</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="BP8" t="n">
         <v>-1</v>
@@ -4001,25 +4001,25 @@
         <v>-1</v>
       </c>
       <c r="BR8" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS8" t="n">
-        <v>80</v>
+        <v>80.95</v>
       </c>
       <c r="BT8" t="n">
-        <v>50</v>
+        <v>52.38</v>
       </c>
       <c r="BU8" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BV8" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BW8" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BX8" t="n">
-        <v>50</v>
+        <v>52.38</v>
       </c>
       <c r="BY8" t="n">
         <v>1.72</v>
@@ -4028,22 +4028,22 @@
         <v>1.71</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.86</v>
+        <v>3.9</v>
       </c>
       <c r="CB8" t="n">
-        <v>4.1</v>
+        <v>4.16</v>
       </c>
       <c r="CC8" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="CD8" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="CE8" t="n">
         <v>1.37</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="CG8" t="n">
         <v>3.07</v>
@@ -4052,10 +4052,10 @@
         <v>1.46</v>
       </c>
       <c r="CI8" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CK8" t="n">
         <v>1.51</v>
@@ -4064,7 +4064,7 @@
         <v>2</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="CN8" t="n">
         <v>1.87</v>
@@ -4073,10 +4073,10 @@
         <v>1.26</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="CR8" t="n">
         <v>1.4</v>
@@ -4091,19 +4091,19 @@
         <v>1.44</v>
       </c>
       <c r="CV8" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="DA8" t="n">
         <v>1.84</v>
@@ -4118,79 +4118,79 @@
         <v>3.1</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="DG8" t="n">
         <v>-1</v>
       </c>
       <c r="DH8" t="n">
-        <v>93.15000000000001</v>
+        <v>93</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="DK8" t="n">
-        <v>5.1</v>
+        <v>5.33</v>
       </c>
       <c r="DL8" t="n">
         <v>-1</v>
       </c>
       <c r="DM8" t="n">
-        <v>46.05</v>
+        <v>46.38</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.7</v>
+        <v>0.76</v>
       </c>
       <c r="DO8" t="n">
         <v>-1</v>
       </c>
       <c r="DP8" t="n">
-        <v>14.1</v>
+        <v>13.95</v>
       </c>
       <c r="DQ8" t="n">
-        <v>17.6</v>
+        <v>17.71</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.15</v>
+        <v>7.05</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>58.75</v>
+        <v>59.1</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DX8" t="n">
-        <v>16</v>
+        <v>16.43</v>
       </c>
       <c r="DY8" t="n">
-        <v>11.2</v>
+        <v>11.38</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.8</v>
+        <v>5.05</v>
       </c>
       <c r="EA8" t="n">
-        <v>21</v>
+        <v>20.67</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="9">
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
         <v>9</v>
       </c>
       <c r="D9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E9" t="n">
         <v>0.22</v>
@@ -4290,85 +4290,85 @@
         <v>1.78</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AH9" t="n">
         <v>-1</v>
       </c>
       <c r="AI9" t="n">
-        <v>75</v>
+        <v>77.67</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.91</v>
+        <v>2.83</v>
       </c>
       <c r="AL9" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AM9" t="n">
         <v>-1</v>
       </c>
       <c r="AN9" t="n">
-        <v>30</v>
+        <v>31.42</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AP9" t="n">
         <v>-1</v>
       </c>
       <c r="AQ9" t="n">
-        <v>14.64</v>
+        <v>15.08</v>
       </c>
       <c r="AR9" t="n">
-        <v>13.82</v>
+        <v>13.33</v>
       </c>
       <c r="AS9" t="n">
-        <v>8.27</v>
+        <v>7.92</v>
       </c>
       <c r="AT9" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>46</v>
+        <v>46.75</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="BA9" t="n">
-        <v>7.18</v>
+        <v>7.42</v>
       </c>
       <c r="BB9" t="n">
-        <v>4.91</v>
+        <v>5.08</v>
       </c>
       <c r="BC9" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="BD9" t="n">
-        <v>18.91</v>
+        <v>18.67</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.84</v>
+        <v>0.87</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="BG9" t="n">
         <v>2.95</v>
@@ -4380,22 +4380,22 @@
         <v>2.95</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BL9" t="n">
         <v>1.05</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="BP9" t="n">
         <v>-1</v>
@@ -4407,22 +4407,22 @@
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BT9" t="n">
-        <v>40</v>
+        <v>42.86</v>
       </c>
       <c r="BU9" t="n">
-        <v>35</v>
+        <v>33.33</v>
       </c>
       <c r="BV9" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BW9" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX9" t="n">
-        <v>45</v>
+        <v>42.86</v>
       </c>
       <c r="BY9" t="n">
         <v>3.45</v>
@@ -4431,28 +4431,28 @@
         <v>3.71</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.83</v>
+        <v>3.79</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.92</v>
+        <v>3.89</v>
       </c>
       <c r="CC9" t="n">
-        <v>5.61</v>
+        <v>5.4</v>
       </c>
       <c r="CD9" t="n">
-        <v>5.9</v>
+        <v>5.71</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CI9" t="n">
         <v>1.91</v>
@@ -4467,7 +4467,7 @@
         <v>2.07</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="CN9" t="n">
         <v>1.84</v>
@@ -4476,25 +4476,25 @@
         <v>1.32</v>
       </c>
       <c r="CP9" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.45</v>
+        <v>3.48</v>
       </c>
       <c r="CR9" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.89</v>
+        <v>2.95</v>
       </c>
       <c r="CT9" t="n">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="CV9" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CW9" t="n">
         <v>1.96</v>
@@ -4515,52 +4515,52 @@
         <v>1.34</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.69</v>
+        <v>3.74</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="DG9" t="n">
         <v>-1</v>
       </c>
       <c r="DH9" t="n">
-        <v>78.95</v>
+        <v>80.29000000000001</v>
       </c>
       <c r="DI9" t="n">
         <v>0.1</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="DK9" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="DL9" t="n">
         <v>-1</v>
       </c>
       <c r="DM9" t="n">
-        <v>33.9</v>
+        <v>34.53</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="DO9" t="n">
         <v>-1</v>
       </c>
       <c r="DP9" t="n">
-        <v>14.5</v>
+        <v>14.76</v>
       </c>
       <c r="DQ9" t="n">
-        <v>14.2</v>
+        <v>13.9</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.4</v>
+        <v>8.19</v>
       </c>
       <c r="DS9" t="n">
         <v>0.05</v>
@@ -4572,28 +4572,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>46</v>
+        <v>46.43</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX9" t="n">
-        <v>8.1</v>
+        <v>8.19</v>
       </c>
       <c r="DY9" t="n">
-        <v>5.55</v>
+        <v>5.62</v>
       </c>
       <c r="DZ9" t="n">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="EA9" t="n">
-        <v>19.75</v>
+        <v>19.57</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.96</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="10">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C10" t="n">
         <v>10</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E10" t="n">
         <v>0.2</v>
@@ -4693,112 +4693,112 @@
         <v>2.2</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AH10" t="n">
         <v>-1</v>
       </c>
       <c r="AI10" t="n">
-        <v>94.09999999999999</v>
+        <v>94.45</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.3</v>
+        <v>2.64</v>
       </c>
       <c r="AL10" t="n">
-        <v>4.1</v>
+        <v>4.09</v>
       </c>
       <c r="AM10" t="n">
         <v>-1</v>
       </c>
       <c r="AN10" t="n">
-        <v>46.8</v>
+        <v>46.18</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.8</v>
+        <v>0.91</v>
       </c>
       <c r="AP10" t="n">
         <v>-1</v>
       </c>
       <c r="AQ10" t="n">
-        <v>14</v>
+        <v>14.55</v>
       </c>
       <c r="AR10" t="n">
-        <v>15</v>
+        <v>14.91</v>
       </c>
       <c r="AS10" t="n">
-        <v>7.5</v>
+        <v>7.27</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AU10" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>51.6</v>
+        <v>51.55</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="BA10" t="n">
-        <v>13.7</v>
+        <v>13.09</v>
       </c>
       <c r="BB10" t="n">
-        <v>8.5</v>
+        <v>8.18</v>
       </c>
       <c r="BC10" t="n">
-        <v>5.2</v>
+        <v>4.91</v>
       </c>
       <c r="BD10" t="n">
-        <v>16.6</v>
+        <v>17.27</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.45</v>
+        <v>3.43</v>
       </c>
       <c r="BH10" t="n">
-        <v>8.9</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.45</v>
+        <v>3.43</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BL10" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="BN10" t="n">
         <v>1.95</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="BP10" t="n">
         <v>-1</v>
@@ -4810,22 +4810,22 @@
         <v>100</v>
       </c>
       <c r="BS10" t="n">
-        <v>90</v>
+        <v>90.48</v>
       </c>
       <c r="BT10" t="n">
-        <v>60</v>
+        <v>61.9</v>
       </c>
       <c r="BU10" t="n">
-        <v>40</v>
+        <v>38.1</v>
       </c>
       <c r="BV10" t="n">
-        <v>25</v>
+        <v>23.81</v>
       </c>
       <c r="BW10" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BX10" t="n">
-        <v>75</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BY10" t="n">
         <v>1.98</v>
@@ -4834,25 +4834,25 @@
         <v>2.13</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.69</v>
+        <v>3.67</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.84</v>
+        <v>3.82</v>
       </c>
       <c r="CC10" t="n">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="CD10" t="n">
-        <v>3.04</v>
+        <v>2.96</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.43</v>
+        <v>2.47</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="CH10" t="n">
         <v>1.32</v>
@@ -4861,28 +4861,28 @@
         <v>1.9</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CN10" t="n">
         <v>1.71</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.66</v>
+        <v>2.73</v>
       </c>
       <c r="CR10" t="n">
         <v>1.37</v>
@@ -4897,10 +4897,10 @@
         <v>1.48</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="CX10" t="n">
         <v>1.54</v>
@@ -4915,88 +4915,88 @@
         <v>1.91</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.98</v>
+        <v>3.06</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="DG10" t="n">
         <v>-1</v>
       </c>
       <c r="DH10" t="n">
-        <v>93.95</v>
+        <v>94.14</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.35</v>
+        <v>2.53</v>
       </c>
       <c r="DK10" t="n">
-        <v>3.75</v>
+        <v>3.76</v>
       </c>
       <c r="DL10" t="n">
         <v>-1</v>
       </c>
       <c r="DM10" t="n">
-        <v>47</v>
+        <v>46.67</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.8</v>
+        <v>0.86</v>
       </c>
       <c r="DO10" t="n">
         <v>-1</v>
       </c>
       <c r="DP10" t="n">
-        <v>15</v>
+        <v>15.24</v>
       </c>
       <c r="DQ10" t="n">
-        <v>14.4</v>
+        <v>14.38</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.05</v>
+        <v>6.95</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>49.1</v>
+        <v>49.19</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="DX10" t="n">
-        <v>14.05</v>
+        <v>13.71</v>
       </c>
       <c r="DY10" t="n">
-        <v>8.5</v>
+        <v>8.33</v>
       </c>
       <c r="DZ10" t="n">
-        <v>5.55</v>
+        <v>5.38</v>
       </c>
       <c r="EA10" t="n">
-        <v>17.8</v>
+        <v>18.09</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="11">
@@ -5054,7 +5054,7 @@
         <v>18.82</v>
       </c>
       <c r="R11" t="n">
-        <v>7</v>
+        <v>7.18</v>
       </c>
       <c r="S11" t="n">
         <v>0.64</v>
@@ -5072,22 +5072,22 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>49</v>
+        <v>49.09</v>
       </c>
       <c r="Y11" t="n">
         <v>0.09</v>
       </c>
       <c r="Z11" t="n">
-        <v>10.73</v>
+        <v>10.82</v>
       </c>
       <c r="AA11" t="n">
-        <v>7.91</v>
+        <v>8</v>
       </c>
       <c r="AB11" t="n">
         <v>2.82</v>
       </c>
       <c r="AC11" t="n">
-        <v>26.18</v>
+        <v>26.27</v>
       </c>
       <c r="AD11" t="n">
         <v>1.25</v>
@@ -5180,7 +5180,7 @@
         <v>1.67</v>
       </c>
       <c r="BH11" t="n">
-        <v>8.619999999999999</v>
+        <v>8.67</v>
       </c>
       <c r="BI11" t="n">
         <v>1.67</v>
@@ -5366,7 +5366,7 @@
         <v>18.81</v>
       </c>
       <c r="DR11" t="n">
-        <v>6.86</v>
+        <v>6.95</v>
       </c>
       <c r="DS11" t="n">
         <v>0.09</v>
@@ -5378,22 +5378,22 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>49.05</v>
+        <v>49.09</v>
       </c>
       <c r="DW11" t="n">
         <v>0.14</v>
       </c>
       <c r="DX11" t="n">
-        <v>10.38</v>
+        <v>10.43</v>
       </c>
       <c r="DY11" t="n">
-        <v>7.57</v>
+        <v>7.62</v>
       </c>
       <c r="DZ11" t="n">
         <v>2.81</v>
       </c>
       <c r="EA11" t="n">
-        <v>24.71</v>
+        <v>24.76</v>
       </c>
       <c r="EB11" t="n">
         <v>1.22</v>
@@ -5409,10 +5409,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D12" t="n">
         <v>10</v>
@@ -5421,82 +5421,82 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="G12" t="n">
         <v>-1</v>
       </c>
       <c r="H12" t="n">
-        <v>92.7</v>
+        <v>91.36</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="K12" t="n">
-        <v>4.4</v>
+        <v>4.64</v>
       </c>
       <c r="L12" t="n">
         <v>-1</v>
       </c>
       <c r="M12" t="n">
-        <v>47.2</v>
+        <v>46.27</v>
       </c>
       <c r="N12" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="O12" t="n">
         <v>-1</v>
       </c>
       <c r="P12" t="n">
-        <v>16.5</v>
+        <v>15.64</v>
       </c>
       <c r="Q12" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="R12" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="S12" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="T12" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>47.6</v>
+        <v>47.36</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z12" t="n">
-        <v>12.9</v>
+        <v>13.18</v>
       </c>
       <c r="AA12" t="n">
-        <v>8.300000000000001</v>
+        <v>8.18</v>
       </c>
       <c r="AB12" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AC12" t="n">
-        <v>18.3</v>
+        <v>18.18</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -5580,31 +5580,31 @@
         <v>2.8</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.65</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="BL12" t="n">
         <v>0.9</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="BP12" t="n">
         <v>-1</v>
@@ -5613,37 +5613,37 @@
         <v>-1</v>
       </c>
       <c r="BR12" t="n">
-        <v>90</v>
+        <v>90.48</v>
       </c>
       <c r="BS12" t="n">
-        <v>75</v>
+        <v>76.19</v>
       </c>
       <c r="BT12" t="n">
-        <v>50</v>
+        <v>52.38</v>
       </c>
       <c r="BU12" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BV12" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>35</v>
+        <v>33.33</v>
       </c>
       <c r="BY12" t="n">
-        <v>4.06</v>
+        <v>3.9</v>
       </c>
       <c r="BZ12" t="n">
-        <v>4.34</v>
+        <v>4.15</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.93</v>
+        <v>3.89</v>
       </c>
       <c r="CB12" t="n">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="CC12" t="n">
         <v>6.98</v>
@@ -5652,13 +5652,13 @@
         <v>7.51</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="CH12" t="n">
         <v>1.37</v>
@@ -5667,40 +5667,40 @@
         <v>1.82</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="CN12" t="n">
         <v>1.81</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.14</v>
+        <v>3.18</v>
       </c>
       <c r="CR12" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.86</v>
+        <v>2.96</v>
       </c>
       <c r="CT12" t="n">
-        <v>2.85</v>
+        <v>2.82</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="CV12" t="n">
         <v>1.91</v>
@@ -5709,100 +5709,100 @@
         <v>1.96</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.58</v>
+        <v>3.64</v>
       </c>
       <c r="DE12" t="n">
         <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="DG12" t="n">
         <v>-1</v>
       </c>
       <c r="DH12" t="n">
-        <v>84.95</v>
+        <v>84.62</v>
       </c>
       <c r="DI12" t="n">
         <v>0</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.8</v>
+        <v>2.71</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.3</v>
+        <v>4.43</v>
       </c>
       <c r="DL12" t="n">
         <v>-1</v>
       </c>
       <c r="DM12" t="n">
-        <v>40.05</v>
+        <v>39.9</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="DO12" t="n">
         <v>-1</v>
       </c>
       <c r="DP12" t="n">
-        <v>17.1</v>
+        <v>16.62</v>
       </c>
       <c r="DQ12" t="n">
-        <v>14.6</v>
+        <v>14.86</v>
       </c>
       <c r="DR12" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>43.8</v>
+        <v>43.86</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX12" t="n">
-        <v>11.7</v>
+        <v>11.9</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.65</v>
+        <v>7.62</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.05</v>
+        <v>4.29</v>
       </c>
       <c r="EA12" t="n">
-        <v>18.4</v>
+        <v>18.33</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.65</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="13">
@@ -5920,7 +5920,7 @@
         <v>2</v>
       </c>
       <c r="AL13" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AM13" t="n">
         <v>-1</v>
@@ -5941,7 +5941,7 @@
         <v>16.1</v>
       </c>
       <c r="AS13" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="AT13" t="n">
         <v>1.9</v>
@@ -5959,25 +5959,25 @@
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>48.4</v>
+        <v>48.3</v>
       </c>
       <c r="AZ13" t="n">
         <v>0.1</v>
       </c>
       <c r="BA13" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="BB13" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="BC13" t="n">
         <v>4</v>
       </c>
       <c r="BD13" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="BF13" t="n">
         <v>1.9</v>
@@ -5986,7 +5986,7 @@
         <v>2.48</v>
       </c>
       <c r="BH13" t="n">
-        <v>10.05</v>
+        <v>10.1</v>
       </c>
       <c r="BI13" t="n">
         <v>2.48</v>
@@ -6151,7 +6151,7 @@
         <v>2.34</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.47</v>
+        <v>5.52</v>
       </c>
       <c r="DL13" t="n">
         <v>-1</v>
@@ -6172,7 +6172,7 @@
         <v>15.86</v>
       </c>
       <c r="DR13" t="n">
-        <v>8.1</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="DS13" t="n">
         <v>0.14</v>
@@ -6184,22 +6184,22 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>48.71</v>
+        <v>48.67</v>
       </c>
       <c r="DW13" t="n">
         <v>0.05</v>
       </c>
       <c r="DX13" t="n">
-        <v>12</v>
+        <v>12.05</v>
       </c>
       <c r="DY13" t="n">
-        <v>8.1</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="DZ13" t="n">
         <v>3.91</v>
       </c>
       <c r="EA13" t="n">
-        <v>21.43</v>
+        <v>21.48</v>
       </c>
       <c r="EB13" t="n">
         <v>1.35</v>
@@ -6215,94 +6215,94 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D14" t="n">
         <v>10</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F14" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="G14" t="n">
         <v>-1</v>
       </c>
       <c r="H14" t="n">
-        <v>102.2</v>
+        <v>99.09</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J14" t="n">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="K14" t="n">
-        <v>4.2</v>
+        <v>4.45</v>
       </c>
       <c r="L14" t="n">
         <v>-1</v>
       </c>
       <c r="M14" t="n">
-        <v>56.3</v>
+        <v>54.45</v>
       </c>
       <c r="N14" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="O14" t="n">
         <v>-1</v>
       </c>
       <c r="P14" t="n">
-        <v>13.8</v>
+        <v>13.82</v>
       </c>
       <c r="Q14" t="n">
-        <v>17.8</v>
+        <v>17.45</v>
       </c>
       <c r="R14" t="n">
-        <v>5.8</v>
+        <v>6.09</v>
       </c>
       <c r="S14" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="T14" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="V14" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="Z14" t="n">
-        <v>13.6</v>
+        <v>13.73</v>
       </c>
       <c r="AA14" t="n">
-        <v>10</v>
+        <v>9.91</v>
       </c>
       <c r="AB14" t="n">
-        <v>3.6</v>
+        <v>3.82</v>
       </c>
       <c r="AC14" t="n">
-        <v>21.6</v>
+        <v>21.09</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -6386,31 +6386,31 @@
         <v>2.4</v>
       </c>
       <c r="BG14" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="BH14" t="n">
-        <v>7.6</v>
+        <v>7.9</v>
       </c>
       <c r="BI14" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.4</v>
+        <v>0.43</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BP14" t="n">
         <v>-1</v>
@@ -6419,37 +6419,37 @@
         <v>-1</v>
       </c>
       <c r="BR14" t="n">
-        <v>90</v>
+        <v>90.48</v>
       </c>
       <c r="BS14" t="n">
-        <v>55</v>
+        <v>52.38</v>
       </c>
       <c r="BT14" t="n">
-        <v>25</v>
+        <v>23.81</v>
       </c>
       <c r="BU14" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BV14" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BW14" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX14" t="n">
-        <v>45</v>
+        <v>42.86</v>
       </c>
       <c r="BY14" t="n">
-        <v>2.39</v>
+        <v>2.43</v>
       </c>
       <c r="BZ14" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.59</v>
+        <v>3.57</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.66</v>
+        <v>3.65</v>
       </c>
       <c r="CC14" t="n">
         <v>4.29</v>
@@ -6461,10 +6461,10 @@
         <v>1.41</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="CH14" t="n">
         <v>1.41</v>
@@ -6473,16 +6473,16 @@
         <v>1.95</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CK14" t="n">
         <v>1.58</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CN14" t="n">
         <v>1.78</v>
@@ -6494,7 +6494,7 @@
         <v>2.03</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.49</v>
+        <v>3.47</v>
       </c>
       <c r="CR14" t="n">
         <v>1.37</v>
@@ -6503,25 +6503,25 @@
         <v>2.76</v>
       </c>
       <c r="CT14" t="n">
-        <v>3.12</v>
+        <v>3.14</v>
       </c>
       <c r="CU14" t="n">
         <v>1.46</v>
       </c>
       <c r="CV14" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="CX14" t="n">
         <v>1.66</v>
       </c>
       <c r="CY14" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="DA14" t="n">
         <v>1.75</v>
@@ -6530,85 +6530,85 @@
         <v>1.35</v>
       </c>
       <c r="DC14" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.72</v>
+        <v>3.68</v>
       </c>
       <c r="DE14" t="n">
         <v>0.05</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="DG14" t="n">
         <v>-1</v>
       </c>
       <c r="DH14" t="n">
-        <v>96</v>
+        <v>94.67</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="DK14" t="n">
-        <v>4.1</v>
+        <v>4.24</v>
       </c>
       <c r="DL14" t="n">
         <v>-1</v>
       </c>
       <c r="DM14" t="n">
-        <v>51.45</v>
+        <v>50.71</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.95</v>
+        <v>1.05</v>
       </c>
       <c r="DO14" t="n">
         <v>-1</v>
       </c>
       <c r="DP14" t="n">
-        <v>14.55</v>
+        <v>14.52</v>
       </c>
       <c r="DQ14" t="n">
-        <v>17.65</v>
+        <v>17.47</v>
       </c>
       <c r="DR14" t="n">
-        <v>6.3</v>
+        <v>6.43</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>49.4</v>
+        <v>49</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.25</v>
+        <v>0.28</v>
       </c>
       <c r="DX14" t="n">
-        <v>12.7</v>
+        <v>12.81</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.9</v>
+        <v>8.91</v>
       </c>
       <c r="DZ14" t="n">
-        <v>3.8</v>
+        <v>3.91</v>
       </c>
       <c r="EA14" t="n">
-        <v>21.3</v>
+        <v>21.05</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="15">
@@ -6618,10 +6618,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D15" t="n">
         <v>10</v>
@@ -6630,82 +6630,82 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="G15" t="n">
         <v>-1</v>
       </c>
       <c r="H15" t="n">
-        <v>88.40000000000001</v>
+        <v>88.64</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="K15" t="n">
-        <v>4.1</v>
+        <v>4.09</v>
       </c>
       <c r="L15" t="n">
         <v>-1</v>
       </c>
       <c r="M15" t="n">
-        <v>38.4</v>
+        <v>38.18</v>
       </c>
       <c r="N15" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="O15" t="n">
         <v>-1</v>
       </c>
       <c r="P15" t="n">
-        <v>15.6</v>
+        <v>15.45</v>
       </c>
       <c r="Q15" t="n">
-        <v>15.7</v>
+        <v>16.45</v>
       </c>
       <c r="R15" t="n">
-        <v>7.6</v>
+        <v>7.73</v>
       </c>
       <c r="S15" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="T15" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>40.8</v>
+        <v>41.55</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z15" t="n">
-        <v>10</v>
+        <v>10.27</v>
       </c>
       <c r="AA15" t="n">
-        <v>6.7</v>
+        <v>6.91</v>
       </c>
       <c r="AB15" t="n">
-        <v>3.3</v>
+        <v>3.36</v>
       </c>
       <c r="AC15" t="n">
-        <v>20.7</v>
+        <v>20.82</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AE15" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -6789,28 +6789,28 @@
         <v>3.1</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="BH15" t="n">
-        <v>7.65</v>
+        <v>7.67</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.8</v>
+        <v>0.86</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="BO15" t="n">
         <v>1</v>
@@ -6822,37 +6822,37 @@
         <v>-1</v>
       </c>
       <c r="BR15" t="n">
-        <v>90</v>
+        <v>90.48</v>
       </c>
       <c r="BS15" t="n">
-        <v>60</v>
+        <v>61.9</v>
       </c>
       <c r="BT15" t="n">
-        <v>40</v>
+        <v>42.86</v>
       </c>
       <c r="BU15" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BV15" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BW15" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX15" t="n">
-        <v>35</v>
+        <v>33.33</v>
       </c>
       <c r="BY15" t="n">
-        <v>2.98</v>
+        <v>3.01</v>
       </c>
       <c r="BZ15" t="n">
-        <v>3.29</v>
+        <v>3.34</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.44</v>
+        <v>3.43</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.63</v>
+        <v>3.61</v>
       </c>
       <c r="CC15" t="n">
         <v>4.29</v>
@@ -6861,13 +6861,13 @@
         <v>4.7</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CF15" t="n">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="CH15" t="n">
         <v>1.37</v>
@@ -6879,16 +6879,16 @@
         <v>1.93</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CL15" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CO15" t="n">
         <v>1.35</v>
@@ -6897,7 +6897,7 @@
         <v>2.17</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.75</v>
+        <v>3.77</v>
       </c>
       <c r="CR15" t="n">
         <v>1.39</v>
@@ -6924,37 +6924,37 @@
         <v>2.04</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="DA15" t="n">
         <v>1.8</v>
       </c>
       <c r="DB15" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.93</v>
+        <v>3.95</v>
       </c>
       <c r="DE15" t="n">
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="DG15" t="n">
         <v>-1</v>
       </c>
       <c r="DH15" t="n">
-        <v>84.5</v>
+        <v>84.81</v>
       </c>
       <c r="DI15" t="n">
         <v>0.1</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="DK15" t="n">
         <v>4.05</v>
@@ -6963,55 +6963,55 @@
         <v>-1</v>
       </c>
       <c r="DM15" t="n">
-        <v>37.5</v>
+        <v>37.43</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="DO15" t="n">
         <v>-1</v>
       </c>
       <c r="DP15" t="n">
-        <v>16.55</v>
+        <v>16.43</v>
       </c>
       <c r="DQ15" t="n">
-        <v>14.6</v>
+        <v>15.05</v>
       </c>
       <c r="DR15" t="n">
-        <v>8.15</v>
+        <v>8.19</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>40.95</v>
+        <v>41.34</v>
       </c>
       <c r="DW15" t="n">
         <v>0.05</v>
       </c>
       <c r="DX15" t="n">
-        <v>10.1</v>
+        <v>10.24</v>
       </c>
       <c r="DY15" t="n">
-        <v>7.15</v>
+        <v>7.24</v>
       </c>
       <c r="DZ15" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="EA15" t="n">
-        <v>19.45</v>
+        <v>19.57</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.55</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="16">
@@ -7021,13 +7021,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C16" t="n">
         <v>11</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E16" t="n">
         <v>0.09</v>
@@ -7114,109 +7114,109 @@
         <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AH16" t="n">
         <v>-1</v>
       </c>
       <c r="AI16" t="n">
-        <v>94.22</v>
+        <v>94.3</v>
       </c>
       <c r="AJ16" t="n">
         <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="AL16" t="n">
-        <v>5.67</v>
+        <v>5.6</v>
       </c>
       <c r="AM16" t="n">
         <v>-1</v>
       </c>
       <c r="AN16" t="n">
-        <v>49.56</v>
+        <v>50.3</v>
       </c>
       <c r="AO16" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AP16" t="n">
         <v>-1</v>
       </c>
       <c r="AQ16" t="n">
-        <v>16</v>
+        <v>16.4</v>
       </c>
       <c r="AR16" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="AS16" t="n">
-        <v>5.89</v>
+        <v>5.8</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AX16" t="n">
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>63.22</v>
+        <v>62.4</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA16" t="n">
-        <v>13.56</v>
+        <v>13.1</v>
       </c>
       <c r="BB16" t="n">
-        <v>9.33</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="BC16" t="n">
-        <v>4.22</v>
+        <v>3.8</v>
       </c>
       <c r="BD16" t="n">
-        <v>19.22</v>
+        <v>19.6</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="BF16" t="n">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="BG16" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BH16" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BJ16" t="n">
         <v>0.9</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="BP16" t="n">
         <v>-1</v>
@@ -7228,22 +7228,22 @@
         <v>100</v>
       </c>
       <c r="BS16" t="n">
-        <v>80</v>
+        <v>80.95</v>
       </c>
       <c r="BT16" t="n">
-        <v>60</v>
+        <v>57.14</v>
       </c>
       <c r="BU16" t="n">
-        <v>30</v>
+        <v>28.57</v>
       </c>
       <c r="BV16" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BW16" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BX16" t="n">
-        <v>65</v>
+        <v>61.9</v>
       </c>
       <c r="BY16" t="n">
         <v>1.65</v>
@@ -7252,22 +7252,22 @@
         <v>1.67</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.92</v>
+        <v>3.9</v>
       </c>
       <c r="CB16" t="n">
-        <v>4.25</v>
+        <v>4.22</v>
       </c>
       <c r="CC16" t="n">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="CD16" t="n">
-        <v>2.31</v>
+        <v>2.48</v>
       </c>
       <c r="CE16" t="n">
         <v>1.37</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="CG16" t="n">
         <v>3.08</v>
@@ -7282,34 +7282,34 @@
         <v>1.85</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="CN16" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CO16" t="n">
         <v>1.26</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CQ16" t="n">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="CR16" t="n">
         <v>1.41</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="CT16" t="n">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="CU16" t="n">
         <v>1.46</v>
@@ -7321,22 +7321,22 @@
         <v>1.9</v>
       </c>
       <c r="CX16" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CY16" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="DA16" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="DB16" t="n">
         <v>1.31</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="DD16" t="n">
         <v>3.41</v>
@@ -7345,76 +7345,76 @@
         <v>0.05</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="DG16" t="n">
         <v>-1</v>
       </c>
       <c r="DH16" t="n">
-        <v>97.40000000000001</v>
+        <v>97.29000000000001</v>
       </c>
       <c r="DI16" t="n">
         <v>0</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.4</v>
+        <v>2.47</v>
       </c>
       <c r="DK16" t="n">
-        <v>5.6</v>
+        <v>5.57</v>
       </c>
       <c r="DL16" t="n">
         <v>-1</v>
       </c>
       <c r="DM16" t="n">
-        <v>50.05</v>
+        <v>50.38</v>
       </c>
       <c r="DN16" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="DO16" t="n">
         <v>-1</v>
       </c>
       <c r="DP16" t="n">
-        <v>15.65</v>
+        <v>15.86</v>
       </c>
       <c r="DQ16" t="n">
-        <v>16.15</v>
+        <v>15.81</v>
       </c>
       <c r="DR16" t="n">
-        <v>6.35</v>
+        <v>6.29</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>61.65</v>
+        <v>61.33</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DX16" t="n">
-        <v>13.2</v>
+        <v>13</v>
       </c>
       <c r="DY16" t="n">
         <v>9</v>
       </c>
       <c r="DZ16" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="EA16" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="17">
@@ -7424,94 +7424,94 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D17" t="n">
         <v>10</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="G17" t="n">
         <v>-1</v>
       </c>
       <c r="H17" t="n">
-        <v>92.8</v>
+        <v>92.09</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="K17" t="n">
-        <v>6</v>
+        <v>5.64</v>
       </c>
       <c r="L17" t="n">
         <v>-1</v>
       </c>
       <c r="M17" t="n">
-        <v>50.6</v>
+        <v>49.18</v>
       </c>
       <c r="N17" t="n">
-        <v>0.4</v>
+        <v>0.55</v>
       </c>
       <c r="O17" t="n">
         <v>-1</v>
       </c>
       <c r="P17" t="n">
-        <v>9.300000000000001</v>
+        <v>9.09</v>
       </c>
       <c r="Q17" t="n">
-        <v>18.5</v>
+        <v>18.36</v>
       </c>
       <c r="R17" t="n">
-        <v>4.8</v>
+        <v>5.27</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="T17" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3</v>
+        <v>0.45</v>
       </c>
       <c r="V17" t="n">
-        <v>0.3</v>
+        <v>0.45</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>62.1</v>
+        <v>60.55</v>
       </c>
       <c r="Y17" t="n">
         <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>14.9</v>
+        <v>14.55</v>
       </c>
       <c r="AA17" t="n">
-        <v>8.6</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="AB17" t="n">
-        <v>6.3</v>
+        <v>6.09</v>
       </c>
       <c r="AC17" t="n">
-        <v>19.7</v>
+        <v>19.27</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -7595,28 +7595,28 @@
         <v>1.3</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.550000000000001</v>
+        <v>9.43</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BL17" t="n">
         <v>0.95</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="BO17" t="n">
         <v>1.05</v>
@@ -7628,37 +7628,37 @@
         <v>-1</v>
       </c>
       <c r="BR17" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS17" t="n">
-        <v>80</v>
+        <v>80.95</v>
       </c>
       <c r="BT17" t="n">
-        <v>40</v>
+        <v>38.1</v>
       </c>
       <c r="BU17" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BV17" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BW17" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX17" t="n">
-        <v>45</v>
+        <v>42.86</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="BZ17" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="CA17" t="n">
-        <v>4.73</v>
+        <v>4.67</v>
       </c>
       <c r="CB17" t="n">
-        <v>5.02</v>
+        <v>4.95</v>
       </c>
       <c r="CC17" t="n">
         <v>1.72</v>
@@ -7670,154 +7670,154 @@
         <v>1.36</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="CG17" t="n">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="CH17" t="n">
         <v>1.48</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="CJ17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CL17" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="CN17" t="n">
         <v>1.94</v>
       </c>
       <c r="CO17" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="CP17" t="n">
         <v>1.88</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="CR17" t="n">
         <v>1.42</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="CT17" t="n">
         <v>2.93</v>
       </c>
       <c r="CU17" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CV17" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CW17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CY17" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="DB17" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.11</v>
+        <v>3.13</v>
       </c>
       <c r="DE17" t="n">
         <v>0.05</v>
       </c>
       <c r="DF17" t="n">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="DG17" t="n">
         <v>-1</v>
       </c>
       <c r="DH17" t="n">
-        <v>92.8</v>
+        <v>92.43000000000001</v>
       </c>
       <c r="DI17" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ17" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.85</v>
+        <v>5.67</v>
       </c>
       <c r="DL17" t="n">
         <v>-1</v>
       </c>
       <c r="DM17" t="n">
-        <v>51.1</v>
+        <v>50.33</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.45</v>
+        <v>0.53</v>
       </c>
       <c r="DO17" t="n">
         <v>-1</v>
       </c>
       <c r="DP17" t="n">
-        <v>9.4</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="DQ17" t="n">
-        <v>20.35</v>
+        <v>20.19</v>
       </c>
       <c r="DR17" t="n">
-        <v>5.9</v>
+        <v>6.09</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.3</v>
+        <v>0.38</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.3</v>
+        <v>0.38</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>61.55</v>
+        <v>60.76</v>
       </c>
       <c r="DW17" t="n">
         <v>0.05</v>
       </c>
       <c r="DX17" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="DY17" t="n">
-        <v>7.75</v>
+        <v>7.71</v>
       </c>
       <c r="DZ17" t="n">
-        <v>5.35</v>
+        <v>5.29</v>
       </c>
       <c r="EA17" t="n">
-        <v>19.35</v>
+        <v>19.14</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Russian_Premier_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Russian_Premier_League_2025-2026.xlsx
@@ -1379,94 +1379,94 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" t="n">
         <v>11</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="F2" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="G2" t="n">
         <v>-1</v>
       </c>
       <c r="H2" t="n">
-        <v>89.7</v>
+        <v>90</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J2" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="K2" t="n">
-        <v>5</v>
+        <v>4.91</v>
       </c>
       <c r="L2" t="n">
         <v>-1</v>
       </c>
       <c r="M2" t="n">
-        <v>45.7</v>
+        <v>44.82</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="O2" t="n">
         <v>-1</v>
       </c>
       <c r="P2" t="n">
-        <v>10.2</v>
+        <v>10.64</v>
       </c>
       <c r="Q2" t="n">
-        <v>16.2</v>
+        <v>16.45</v>
       </c>
       <c r="R2" t="n">
-        <v>6.1</v>
+        <v>6.09</v>
       </c>
       <c r="S2" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="T2" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="V2" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>45.6</v>
+        <v>46.36</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>14.6</v>
+        <v>13.91</v>
       </c>
       <c r="AA2" t="n">
-        <v>9.699999999999999</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.9</v>
+        <v>4.55</v>
       </c>
       <c r="AC2" t="n">
-        <v>21.1</v>
+        <v>21.45</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.59</v>
+        <v>1.52</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -1550,31 +1550,31 @@
         <v>1.73</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="BH2" t="n">
-        <v>8.76</v>
+        <v>8.68</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="BP2" t="n">
         <v>-1</v>
@@ -1586,34 +1586,34 @@
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>76.19</v>
+        <v>72.73</v>
       </c>
       <c r="BT2" t="n">
-        <v>47.62</v>
+        <v>45.45</v>
       </c>
       <c r="BU2" t="n">
-        <v>23.81</v>
+        <v>22.73</v>
       </c>
       <c r="BV2" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BW2" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX2" t="n">
-        <v>57.14</v>
+        <v>54.55</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.69</v>
+        <v>2.66</v>
       </c>
       <c r="BZ2" t="n">
-        <v>2.71</v>
+        <v>2.67</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.5</v>
+        <v>3.49</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.59</v>
+        <v>3.58</v>
       </c>
       <c r="CC2" t="n">
         <v>3.42</v>
@@ -1625,40 +1625,40 @@
         <v>1.41</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CJ2" t="n">
         <v>1.83</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CL2" t="n">
         <v>1.89</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="CO2" t="n">
         <v>1.32</v>
       </c>
       <c r="CP2" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.43</v>
+        <v>3.46</v>
       </c>
       <c r="CR2" t="n">
         <v>1.38</v>
@@ -1673,10 +1673,10 @@
         <v>1.43</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CX2" t="n">
         <v>1.56</v>
@@ -1694,85 +1694,85 @@
         <v>1.32</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.51</v>
+        <v>3.54</v>
       </c>
       <c r="DE2" t="n">
         <v>0.14</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="DG2" t="n">
         <v>-1</v>
       </c>
       <c r="DH2" t="n">
-        <v>90.05</v>
+        <v>90.18000000000001</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="DK2" t="n">
-        <v>4.38</v>
+        <v>4.36</v>
       </c>
       <c r="DL2" t="n">
         <v>-1</v>
       </c>
       <c r="DM2" t="n">
-        <v>43.1</v>
+        <v>42.78</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="DO2" t="n">
         <v>-1</v>
       </c>
       <c r="DP2" t="n">
-        <v>12</v>
+        <v>12.14</v>
       </c>
       <c r="DQ2" t="n">
-        <v>17.19</v>
+        <v>17.27</v>
       </c>
       <c r="DR2" t="n">
-        <v>7</v>
+        <v>6.95</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>45.57</v>
+        <v>45.96</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.34</v>
+        <v>0.32</v>
       </c>
       <c r="DX2" t="n">
-        <v>12.43</v>
+        <v>12.18</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.57</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="DZ2" t="n">
-        <v>3.86</v>
+        <v>3.73</v>
       </c>
       <c r="EA2" t="n">
-        <v>20.95</v>
+        <v>21.14</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="3">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C3" t="n">
         <v>10</v>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1872,112 +1872,112 @@
         <v>1.6</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AH3" t="n">
         <v>-1</v>
       </c>
       <c r="AI3" t="n">
-        <v>83.09</v>
+        <v>81.83</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="AL3" t="n">
-        <v>4</v>
+        <v>3.83</v>
       </c>
       <c r="AM3" t="n">
         <v>-1</v>
       </c>
       <c r="AN3" t="n">
-        <v>39</v>
+        <v>38.92</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AP3" t="n">
         <v>-1</v>
       </c>
       <c r="AQ3" t="n">
-        <v>15</v>
+        <v>14.58</v>
       </c>
       <c r="AR3" t="n">
-        <v>13.82</v>
+        <v>14.08</v>
       </c>
       <c r="AS3" t="n">
-        <v>8.359999999999999</v>
+        <v>8.17</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.64</v>
+        <v>1.92</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>41.27</v>
+        <v>41.08</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="BA3" t="n">
-        <v>10.55</v>
+        <v>10.5</v>
       </c>
       <c r="BB3" t="n">
-        <v>7.18</v>
+        <v>7.08</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.36</v>
+        <v>3.42</v>
       </c>
       <c r="BD3" t="n">
-        <v>16.64</v>
+        <v>17</v>
       </c>
       <c r="BE3" t="n">
         <v>1.19</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.81</v>
+        <v>2.95</v>
       </c>
       <c r="BH3" t="n">
-        <v>8.859999999999999</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.81</v>
+        <v>2.95</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.76</v>
+        <v>0.95</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.43</v>
+        <v>1.64</v>
       </c>
       <c r="BP3" t="n">
         <v>-1</v>
@@ -1989,22 +1989,22 @@
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>90.48</v>
+        <v>90.91</v>
       </c>
       <c r="BT3" t="n">
-        <v>47.62</v>
+        <v>50</v>
       </c>
       <c r="BU3" t="n">
-        <v>23.81</v>
+        <v>27.27</v>
       </c>
       <c r="BV3" t="n">
-        <v>9.52</v>
+        <v>13.64</v>
       </c>
       <c r="BW3" t="n">
-        <v>4.76</v>
+        <v>9.09</v>
       </c>
       <c r="BX3" t="n">
-        <v>66.67</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BY3" t="n">
         <v>3.32</v>
@@ -2013,43 +2013,43 @@
         <v>3.56</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.97</v>
+        <v>3.99</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.24</v>
+        <v>4.29</v>
       </c>
       <c r="CC3" t="n">
-        <v>5.69</v>
+        <v>5.73</v>
       </c>
       <c r="CD3" t="n">
-        <v>6.02</v>
+        <v>6.14</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.29</v>
+        <v>3.3</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CI3" t="n">
         <v>2.08</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="CN3" t="n">
         <v>1.93</v>
@@ -2058,10 +2058,10 @@
         <v>1.22</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="CR3" t="n">
         <v>1.38</v>
@@ -2082,7 +2082,7 @@
         <v>1.76</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CY3" t="n">
         <v>1.95</v>
@@ -2103,7 +2103,7 @@
         <v>2.9</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DF3" t="n">
         <v>1.09</v>
@@ -2112,70 +2112,70 @@
         <v>-1</v>
       </c>
       <c r="DH3" t="n">
-        <v>91.62</v>
+        <v>90.54000000000001</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DJ3" t="n">
         <v>2</v>
       </c>
       <c r="DK3" t="n">
-        <v>4.05</v>
+        <v>3.95</v>
       </c>
       <c r="DL3" t="n">
         <v>-1</v>
       </c>
       <c r="DM3" t="n">
-        <v>44.95</v>
+        <v>44.64</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="DO3" t="n">
         <v>-1</v>
       </c>
       <c r="DP3" t="n">
-        <v>15.14</v>
+        <v>14.91</v>
       </c>
       <c r="DQ3" t="n">
-        <v>14.57</v>
+        <v>14.68</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.86</v>
+        <v>7.77</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>44.05</v>
+        <v>43.82</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="DX3" t="n">
-        <v>11.1</v>
+        <v>11.05</v>
       </c>
       <c r="DY3" t="n">
-        <v>7.19</v>
+        <v>7.13</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.9</v>
+        <v>3.91</v>
       </c>
       <c r="EA3" t="n">
-        <v>17.67</v>
+        <v>17.82</v>
       </c>
       <c r="EB3" t="n">
         <v>1.3</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="4">
@@ -2185,94 +2185,94 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4" t="n">
         <v>11</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="F4" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="G4" t="n">
         <v>-1</v>
       </c>
       <c r="H4" t="n">
-        <v>83.40000000000001</v>
+        <v>85.18000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J4" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="K4" t="n">
-        <v>3.5</v>
+        <v>3.27</v>
       </c>
       <c r="L4" t="n">
         <v>-1</v>
       </c>
       <c r="M4" t="n">
-        <v>45.6</v>
+        <v>46</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="O4" t="n">
         <v>-1</v>
       </c>
       <c r="P4" t="n">
-        <v>19.8</v>
+        <v>19.45</v>
       </c>
       <c r="Q4" t="n">
-        <v>12.1</v>
+        <v>12.73</v>
       </c>
       <c r="R4" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="T4" t="n">
-        <v>1.3</v>
+        <v>1.55</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>42.7</v>
+        <v>43.55</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z4" t="n">
-        <v>12.6</v>
+        <v>13.09</v>
       </c>
       <c r="AA4" t="n">
-        <v>8.5</v>
+        <v>8.73</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.1</v>
+        <v>4.36</v>
       </c>
       <c r="AC4" t="n">
-        <v>21.5</v>
+        <v>21.55</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="AF4" t="n">
         <v>0.18</v>
@@ -2356,31 +2356,31 @@
         <v>3.36</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="BH4" t="n">
-        <v>8.289999999999999</v>
+        <v>8</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.38</v>
+        <v>0.45</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.48</v>
+        <v>0.55</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.76</v>
+        <v>0.82</v>
       </c>
       <c r="BP4" t="n">
         <v>-1</v>
@@ -2389,37 +2389,37 @@
         <v>-1</v>
       </c>
       <c r="BR4" t="n">
-        <v>80.95</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BS4" t="n">
-        <v>61.9</v>
+        <v>63.64</v>
       </c>
       <c r="BT4" t="n">
-        <v>14.29</v>
+        <v>18.18</v>
       </c>
       <c r="BU4" t="n">
-        <v>4.76</v>
+        <v>9.09</v>
       </c>
       <c r="BV4" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>28.57</v>
+        <v>27.27</v>
       </c>
       <c r="BY4" t="n">
-        <v>2.46</v>
+        <v>2.36</v>
       </c>
       <c r="BZ4" t="n">
-        <v>2.65</v>
+        <v>2.53</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.38</v>
+        <v>3.44</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.48</v>
+        <v>3.55</v>
       </c>
       <c r="CC4" t="n">
         <v>3.61</v>
@@ -2431,7 +2431,7 @@
         <v>1.41</v>
       </c>
       <c r="CF4" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="CG4" t="n">
         <v>2.53</v>
@@ -2440,25 +2440,25 @@
         <v>1.27</v>
       </c>
       <c r="CI4" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="CK4" t="n">
         <v>1.47</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CP4" t="n">
         <v>2.17</v>
@@ -2479,10 +2479,10 @@
         <v>1.38</v>
       </c>
       <c r="CV4" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="CW4" t="n">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="CX4" t="n">
         <v>1.65</v>
@@ -2500,82 +2500,82 @@
         <v>1.43</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="DD4" t="n">
-        <v>4.47</v>
+        <v>4.43</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.24</v>
+        <v>0.27</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="DG4" t="n">
         <v>-1</v>
       </c>
       <c r="DH4" t="n">
-        <v>88.86</v>
+        <v>89.5</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DJ4" t="n">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="DK4" t="n">
-        <v>3.43</v>
+        <v>3.32</v>
       </c>
       <c r="DL4" t="n">
         <v>-1</v>
       </c>
       <c r="DM4" t="n">
-        <v>44.24</v>
+        <v>44.5</v>
       </c>
       <c r="DN4" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="DO4" t="n">
         <v>-1</v>
       </c>
       <c r="DP4" t="n">
-        <v>19.52</v>
+        <v>19.36</v>
       </c>
       <c r="DQ4" t="n">
-        <v>12.48</v>
+        <v>12.78</v>
       </c>
       <c r="DR4" t="n">
-        <v>7.81</v>
+        <v>7.5</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.19</v>
+        <v>0.22</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.19</v>
+        <v>0.22</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>45.14</v>
+        <v>45.46</v>
       </c>
       <c r="DW4" t="n">
         <v>0.09</v>
       </c>
       <c r="DX4" t="n">
-        <v>12.24</v>
+        <v>12.5</v>
       </c>
       <c r="DY4" t="n">
-        <v>8.140000000000001</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.09</v>
+        <v>4.22</v>
       </c>
       <c r="EA4" t="n">
-        <v>21.14</v>
+        <v>21.18</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="EC4" t="n">
         <v>3.05</v>
@@ -2588,94 +2588,94 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D5" t="n">
         <v>11</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="F5" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
         <v>-1</v>
       </c>
       <c r="H5" t="n">
-        <v>105.4</v>
+        <v>105.09</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="K5" t="n">
-        <v>4.9</v>
+        <v>5.27</v>
       </c>
       <c r="L5" t="n">
         <v>-1</v>
       </c>
       <c r="M5" t="n">
-        <v>53</v>
+        <v>52.36</v>
       </c>
       <c r="N5" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="O5" t="n">
         <v>-1</v>
       </c>
       <c r="P5" t="n">
-        <v>11</v>
+        <v>10.82</v>
       </c>
       <c r="Q5" t="n">
-        <v>17.5</v>
+        <v>17.27</v>
       </c>
       <c r="R5" t="n">
-        <v>8.4</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>58</v>
+        <v>58.64</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z5" t="n">
-        <v>14.3</v>
+        <v>14.45</v>
       </c>
       <c r="AA5" t="n">
-        <v>9.1</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.2</v>
+        <v>5.09</v>
       </c>
       <c r="AC5" t="n">
-        <v>20.4</v>
+        <v>20.73</v>
       </c>
       <c r="AD5" t="n">
         <v>1.65</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -2759,31 +2759,31 @@
         <v>2</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.57</v>
+        <v>2.64</v>
       </c>
       <c r="BH5" t="n">
-        <v>11.05</v>
+        <v>11.23</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.57</v>
+        <v>2.64</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="BN5" t="n">
         <v>1.05</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.52</v>
+        <v>1.59</v>
       </c>
       <c r="BP5" t="n">
         <v>-1</v>
@@ -2792,37 +2792,37 @@
         <v>-1</v>
       </c>
       <c r="BR5" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS5" t="n">
-        <v>61.9</v>
+        <v>63.64</v>
       </c>
       <c r="BT5" t="n">
-        <v>42.86</v>
+        <v>45.45</v>
       </c>
       <c r="BU5" t="n">
-        <v>33.33</v>
+        <v>36.36</v>
       </c>
       <c r="BV5" t="n">
-        <v>19.05</v>
+        <v>18.18</v>
       </c>
       <c r="BW5" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX5" t="n">
-        <v>47.62</v>
+        <v>50</v>
       </c>
       <c r="BY5" t="n">
         <v>1.86</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="CA5" t="n">
         <v>3.69</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.81</v>
+        <v>3.8</v>
       </c>
       <c r="CC5" t="n">
         <v>2.89</v>
@@ -2831,19 +2831,19 @@
         <v>3.11</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.79</v>
+        <v>2.81</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CJ5" t="n">
         <v>1.81</v>
@@ -2852,22 +2852,22 @@
         <v>1.49</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CO5" t="n">
         <v>1.28</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="CR5" t="n">
         <v>1.42</v>
@@ -2882,37 +2882,37 @@
         <v>1.4</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CY5" t="n">
         <v>1.94</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.37</v>
+        <v>2.39</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.37</v>
+        <v>3.42</v>
       </c>
       <c r="DE5" t="n">
         <v>0.14</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="DG5" t="n">
         <v>-1</v>
@@ -2924,64 +2924,64 @@
         <v>0</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.29</v>
+        <v>5.45</v>
       </c>
       <c r="DL5" t="n">
         <v>-1</v>
       </c>
       <c r="DM5" t="n">
-        <v>49.47</v>
+        <v>49.32</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="DO5" t="n">
         <v>-1</v>
       </c>
       <c r="DP5" t="n">
-        <v>11.81</v>
+        <v>11.69</v>
       </c>
       <c r="DQ5" t="n">
-        <v>15.95</v>
+        <v>15.91</v>
       </c>
       <c r="DR5" t="n">
-        <v>9.1</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>55.95</v>
+        <v>56.36</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DX5" t="n">
-        <v>13.62</v>
+        <v>13.72</v>
       </c>
       <c r="DY5" t="n">
-        <v>9</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="DZ5" t="n">
-        <v>4.62</v>
+        <v>4.59</v>
       </c>
       <c r="EA5" t="n">
-        <v>21.29</v>
+        <v>21.41</v>
       </c>
       <c r="EB5" t="n">
         <v>1.55</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="6">
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D6" t="n">
         <v>11</v>
@@ -3003,82 +3003,82 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="G6" t="n">
         <v>-1</v>
       </c>
       <c r="H6" t="n">
-        <v>101.2</v>
+        <v>99.55</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J6" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="K6" t="n">
-        <v>5.8</v>
+        <v>5.55</v>
       </c>
       <c r="L6" t="n">
         <v>-1</v>
       </c>
       <c r="M6" t="n">
-        <v>53.5</v>
+        <v>52.45</v>
       </c>
       <c r="N6" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="O6" t="n">
         <v>-1</v>
       </c>
       <c r="P6" t="n">
-        <v>12.3</v>
+        <v>12.73</v>
       </c>
       <c r="Q6" t="n">
-        <v>17.7</v>
+        <v>16.91</v>
       </c>
       <c r="R6" t="n">
-        <v>4.9</v>
+        <v>5.09</v>
       </c>
       <c r="S6" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="T6" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>57.3</v>
+        <v>56.36</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>16.7</v>
+        <v>16.18</v>
       </c>
       <c r="AA6" t="n">
-        <v>10.9</v>
+        <v>10.73</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.8</v>
+        <v>5.45</v>
       </c>
       <c r="AC6" t="n">
-        <v>20.7</v>
+        <v>20.64</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AF6" t="n">
         <v>0.09</v>
@@ -3162,31 +3162,31 @@
         <v>2.55</v>
       </c>
       <c r="BG6" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BH6" t="n">
-        <v>10.1</v>
+        <v>10.05</v>
       </c>
       <c r="BI6" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.86</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="BP6" t="n">
         <v>-1</v>
@@ -3195,37 +3195,37 @@
         <v>-1</v>
       </c>
       <c r="BR6" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS6" t="n">
-        <v>76.19</v>
+        <v>77.27</v>
       </c>
       <c r="BT6" t="n">
-        <v>61.9</v>
+        <v>63.64</v>
       </c>
       <c r="BU6" t="n">
-        <v>38.1</v>
+        <v>40.91</v>
       </c>
       <c r="BV6" t="n">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
       <c r="BW6" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX6" t="n">
-        <v>61.9</v>
+        <v>63.64</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.82</v>
+        <v>1.97</v>
       </c>
       <c r="BZ6" t="n">
-        <v>1.84</v>
+        <v>2.01</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.81</v>
+        <v>3.79</v>
       </c>
       <c r="CB6" t="n">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="CC6" t="n">
         <v>2.68</v>
@@ -3234,13 +3234,13 @@
         <v>2.72</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.29</v>
+        <v>3.27</v>
       </c>
       <c r="CH6" t="n">
         <v>1.5</v>
@@ -3255,13 +3255,13 @@
         <v>1.45</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CO6" t="n">
         <v>1.23</v>
@@ -3273,16 +3273,16 @@
         <v>2.83</v>
       </c>
       <c r="CR6" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="CT6" t="n">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CV6" t="n">
         <v>2.22</v>
@@ -3294,13 +3294,13 @@
         <v>1.54</v>
       </c>
       <c r="CY6" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="CZ6" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="DA6" t="n">
         <v>1.9</v>
-      </c>
-      <c r="CZ6" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="DA6" t="n">
-        <v>1.91</v>
       </c>
       <c r="DB6" t="n">
         <v>1.26</v>
@@ -3309,82 +3309,82 @@
         <v>1.83</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.02</v>
+        <v>3.03</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="DG6" t="n">
         <v>-1</v>
       </c>
       <c r="DH6" t="n">
-        <v>95.86</v>
+        <v>95.28</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="DK6" t="n">
-        <v>5.52</v>
+        <v>5.41</v>
       </c>
       <c r="DL6" t="n">
         <v>-1</v>
       </c>
       <c r="DM6" t="n">
-        <v>51.14</v>
+        <v>50.72</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="DO6" t="n">
         <v>-1</v>
       </c>
       <c r="DP6" t="n">
-        <v>13.48</v>
+        <v>13.64</v>
       </c>
       <c r="DQ6" t="n">
-        <v>16.47</v>
+        <v>16.13</v>
       </c>
       <c r="DR6" t="n">
-        <v>5.66</v>
+        <v>5.72</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>54.48</v>
+        <v>54.14</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DX6" t="n">
-        <v>16.05</v>
+        <v>15.81</v>
       </c>
       <c r="DY6" t="n">
-        <v>11.29</v>
+        <v>11.18</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.76</v>
+        <v>4.64</v>
       </c>
       <c r="EA6" t="n">
-        <v>20.62</v>
+        <v>20.6</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="7">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C7" t="n">
         <v>11</v>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3487,109 +3487,109 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AH7" t="n">
         <v>-1</v>
       </c>
       <c r="AI7" t="n">
-        <v>83.40000000000001</v>
+        <v>83.55</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AL7" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AM7" t="n">
         <v>-1</v>
       </c>
       <c r="AN7" t="n">
-        <v>33.1</v>
+        <v>32.91</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AP7" t="n">
         <v>-1</v>
       </c>
       <c r="AQ7" t="n">
-        <v>15.1</v>
+        <v>15.36</v>
       </c>
       <c r="AR7" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AS7" t="n">
-        <v>8.9</v>
+        <v>9.27</v>
       </c>
       <c r="AT7" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AX7" t="n">
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>47.3</v>
+        <v>47.36</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="BA7" t="n">
-        <v>7.7</v>
+        <v>7.45</v>
       </c>
       <c r="BB7" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="BD7" t="n">
-        <v>18.5</v>
+        <v>18.36</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.92</v>
+        <v>0.89</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.24</v>
+        <v>3.27</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.67</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.24</v>
+        <v>3.27</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.38</v>
+        <v>0.45</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="BL7" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.77</v>
       </c>
       <c r="BN7" t="n">
         <v>2</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="BP7" t="n">
         <v>-1</v>
@@ -3598,25 +3598,25 @@
         <v>-1</v>
       </c>
       <c r="BR7" t="n">
-        <v>90.48</v>
+        <v>90.91</v>
       </c>
       <c r="BS7" t="n">
-        <v>85.70999999999999</v>
+        <v>86.36</v>
       </c>
       <c r="BT7" t="n">
-        <v>71.43000000000001</v>
+        <v>72.73</v>
       </c>
       <c r="BU7" t="n">
-        <v>38.1</v>
+        <v>40.91</v>
       </c>
       <c r="BV7" t="n">
-        <v>23.81</v>
+        <v>22.73</v>
       </c>
       <c r="BW7" t="n">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
       <c r="BX7" t="n">
-        <v>61.9</v>
+        <v>59.09</v>
       </c>
       <c r="BY7" t="n">
         <v>4.69</v>
@@ -3625,55 +3625,55 @@
         <v>4.92</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.69</v>
+        <v>3.74</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.94</v>
+        <v>3.99</v>
       </c>
       <c r="CC7" t="n">
-        <v>4.7</v>
+        <v>5.14</v>
       </c>
       <c r="CD7" t="n">
-        <v>5.31</v>
+        <v>5.78</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.98</v>
+        <v>2.97</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CO7" t="n">
         <v>1.3</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.4</v>
+        <v>3.43</v>
       </c>
       <c r="CR7" t="n">
         <v>1.48</v>
@@ -3688,10 +3688,10 @@
         <v>1.41</v>
       </c>
       <c r="CV7" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="CX7" t="n">
         <v>1.6</v>
@@ -3712,49 +3712,49 @@
         <v>2.11</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.75</v>
+        <v>3.76</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="DG7" t="n">
         <v>-1</v>
       </c>
       <c r="DH7" t="n">
-        <v>80.34</v>
+        <v>80.55</v>
       </c>
       <c r="DI7" t="n">
         <v>0.09</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="DK7" t="n">
-        <v>3.38</v>
+        <v>3.27</v>
       </c>
       <c r="DL7" t="n">
         <v>-1</v>
       </c>
       <c r="DM7" t="n">
-        <v>34.95</v>
+        <v>34.78</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="DO7" t="n">
         <v>-1</v>
       </c>
       <c r="DP7" t="n">
-        <v>14.38</v>
+        <v>14.54</v>
       </c>
       <c r="DQ7" t="n">
-        <v>14.43</v>
+        <v>14.68</v>
       </c>
       <c r="DR7" t="n">
-        <v>8.81</v>
+        <v>9</v>
       </c>
       <c r="DS7" t="n">
         <v>0.09</v>
@@ -3766,28 +3766,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>46.05</v>
+        <v>46.14</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="DX7" t="n">
-        <v>7.95</v>
+        <v>7.82</v>
       </c>
       <c r="DY7" t="n">
-        <v>5.38</v>
+        <v>5.32</v>
       </c>
       <c r="DZ7" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="EA7" t="n">
-        <v>17.9</v>
+        <v>17.86</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.95</v>
+        <v>0.93</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.33</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="8">
@@ -3797,94 +3797,94 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D8" t="n">
         <v>10</v>
       </c>
       <c r="E8" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="F8" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="G8" t="n">
         <v>-1</v>
       </c>
       <c r="H8" t="n">
-        <v>95.45</v>
+        <v>95.42</v>
       </c>
       <c r="I8" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="J8" t="n">
-        <v>2.82</v>
+        <v>2.67</v>
       </c>
       <c r="K8" t="n">
-        <v>6</v>
+        <v>6.17</v>
       </c>
       <c r="L8" t="n">
         <v>-1</v>
       </c>
       <c r="M8" t="n">
-        <v>52.45</v>
+        <v>51.25</v>
       </c>
       <c r="N8" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="O8" t="n">
         <v>-1</v>
       </c>
       <c r="P8" t="n">
-        <v>13.82</v>
+        <v>13.67</v>
       </c>
       <c r="Q8" t="n">
-        <v>16.09</v>
+        <v>16.08</v>
       </c>
       <c r="R8" t="n">
-        <v>6.36</v>
+        <v>6.42</v>
       </c>
       <c r="S8" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="T8" t="n">
-        <v>2.18</v>
+        <v>2.42</v>
       </c>
       <c r="U8" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="V8" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>59.82</v>
+        <v>60.25</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="Z8" t="n">
-        <v>19.09</v>
+        <v>18.83</v>
       </c>
       <c r="AA8" t="n">
-        <v>13.73</v>
+        <v>13.42</v>
       </c>
       <c r="AB8" t="n">
-        <v>5.36</v>
+        <v>5.42</v>
       </c>
       <c r="AC8" t="n">
-        <v>20.73</v>
+        <v>20.83</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="AF8" t="n">
         <v>0.3</v>
@@ -3968,31 +3968,31 @@
         <v>1.7</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.76</v>
+        <v>2.86</v>
       </c>
       <c r="BH8" t="n">
-        <v>8.81</v>
+        <v>8.91</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.76</v>
+        <v>2.86</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.62</v>
+        <v>0.68</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.91</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.52</v>
+        <v>1.59</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="BP8" t="n">
         <v>-1</v>
@@ -4001,37 +4001,37 @@
         <v>-1</v>
       </c>
       <c r="BR8" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS8" t="n">
-        <v>80.95</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BT8" t="n">
-        <v>52.38</v>
+        <v>54.55</v>
       </c>
       <c r="BU8" t="n">
-        <v>19.05</v>
+        <v>22.73</v>
       </c>
       <c r="BV8" t="n">
-        <v>19.05</v>
+        <v>22.73</v>
       </c>
       <c r="BW8" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BX8" t="n">
-        <v>52.38</v>
+        <v>50</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="BZ8" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.9</v>
+        <v>3.97</v>
       </c>
       <c r="CB8" t="n">
-        <v>4.16</v>
+        <v>4.25</v>
       </c>
       <c r="CC8" t="n">
         <v>1.86</v>
@@ -4040,22 +4040,22 @@
         <v>1.88</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="CH8" t="n">
         <v>1.46</v>
       </c>
       <c r="CI8" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="CK8" t="n">
         <v>1.51</v>
@@ -4067,16 +4067,16 @@
         <v>2.42</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CO8" t="n">
         <v>1.26</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="CR8" t="n">
         <v>1.4</v>
@@ -4091,10 +4091,10 @@
         <v>1.44</v>
       </c>
       <c r="CV8" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="CX8" t="n">
         <v>1.59</v>
@@ -4118,79 +4118,79 @@
         <v>3.1</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.19</v>
+        <v>0.23</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="DG8" t="n">
         <v>-1</v>
       </c>
       <c r="DH8" t="n">
-        <v>93</v>
+        <v>93.09</v>
       </c>
       <c r="DI8" t="n">
         <v>0.14</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="DK8" t="n">
-        <v>5.33</v>
+        <v>5.46</v>
       </c>
       <c r="DL8" t="n">
         <v>-1</v>
       </c>
       <c r="DM8" t="n">
-        <v>46.38</v>
+        <v>46</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="DO8" t="n">
         <v>-1</v>
       </c>
       <c r="DP8" t="n">
-        <v>13.95</v>
+        <v>13.87</v>
       </c>
       <c r="DQ8" t="n">
-        <v>17.71</v>
+        <v>17.63</v>
       </c>
       <c r="DR8" t="n">
         <v>7.05</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>59.1</v>
+        <v>59.36</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DX8" t="n">
-        <v>16.43</v>
+        <v>16.41</v>
       </c>
       <c r="DY8" t="n">
-        <v>11.38</v>
+        <v>11.32</v>
       </c>
       <c r="DZ8" t="n">
-        <v>5.05</v>
+        <v>5.09</v>
       </c>
       <c r="EA8" t="n">
-        <v>20.67</v>
+        <v>20.73</v>
       </c>
       <c r="EB8" t="n">
         <v>1.72</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="9">
@@ -4200,61 +4200,61 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D9" t="n">
         <v>12</v>
       </c>
       <c r="E9" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="F9" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="G9" t="n">
         <v>-1</v>
       </c>
       <c r="H9" t="n">
-        <v>83.78</v>
+        <v>83.3</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="K9" t="n">
-        <v>3.89</v>
+        <v>4.2</v>
       </c>
       <c r="L9" t="n">
         <v>-1</v>
       </c>
       <c r="M9" t="n">
-        <v>38.67</v>
+        <v>37.9</v>
       </c>
       <c r="N9" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="O9" t="n">
         <v>-1</v>
       </c>
       <c r="P9" t="n">
-        <v>14.33</v>
+        <v>14.7</v>
       </c>
       <c r="Q9" t="n">
-        <v>14.67</v>
+        <v>14</v>
       </c>
       <c r="R9" t="n">
-        <v>8.56</v>
+        <v>8.4</v>
       </c>
       <c r="S9" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="T9" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -4269,25 +4269,25 @@
         <v>46</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z9" t="n">
-        <v>9.220000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="AA9" t="n">
-        <v>6.33</v>
+        <v>6.4</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.89</v>
+        <v>2.7</v>
       </c>
       <c r="AC9" t="n">
-        <v>20.78</v>
+        <v>20.7</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AF9" t="n">
         <v>0.08</v>
@@ -4371,31 +4371,31 @@
         <v>2.75</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.95</v>
+        <v>2.82</v>
       </c>
       <c r="BH9" t="n">
-        <v>9</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.95</v>
+        <v>2.82</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="BL9" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="BP9" t="n">
         <v>-1</v>
@@ -4404,37 +4404,37 @@
         <v>-1</v>
       </c>
       <c r="BR9" t="n">
-        <v>100</v>
+        <v>95.45</v>
       </c>
       <c r="BS9" t="n">
-        <v>95.23999999999999</v>
+        <v>90.91</v>
       </c>
       <c r="BT9" t="n">
-        <v>42.86</v>
+        <v>40.91</v>
       </c>
       <c r="BU9" t="n">
-        <v>33.33</v>
+        <v>31.82</v>
       </c>
       <c r="BV9" t="n">
-        <v>19.05</v>
+        <v>18.18</v>
       </c>
       <c r="BW9" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX9" t="n">
-        <v>42.86</v>
+        <v>40.91</v>
       </c>
       <c r="BY9" t="n">
-        <v>3.45</v>
+        <v>3.38</v>
       </c>
       <c r="BZ9" t="n">
-        <v>3.71</v>
+        <v>3.66</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.79</v>
+        <v>3.75</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.89</v>
+        <v>3.84</v>
       </c>
       <c r="CC9" t="n">
         <v>5.4</v>
@@ -4443,49 +4443,49 @@
         <v>5.71</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CI9" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="CJ9" t="n">
         <v>1.91</v>
       </c>
-      <c r="CJ9" t="n">
-        <v>1.9</v>
-      </c>
       <c r="CK9" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CP9" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.48</v>
+        <v>3.58</v>
       </c>
       <c r="CR9" t="n">
         <v>1.44</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="CT9" t="n">
         <v>2.9</v>
@@ -4494,10 +4494,10 @@
         <v>1.42</v>
       </c>
       <c r="CV9" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="CX9" t="n">
         <v>1.62</v>
@@ -4512,88 +4512,88 @@
         <v>1.81</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.74</v>
+        <v>3.91</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="DG9" t="n">
         <v>-1</v>
       </c>
       <c r="DH9" t="n">
-        <v>80.29000000000001</v>
+        <v>80.23</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.43</v>
+        <v>2.36</v>
       </c>
       <c r="DK9" t="n">
-        <v>3.1</v>
+        <v>3.27</v>
       </c>
       <c r="DL9" t="n">
         <v>-1</v>
       </c>
       <c r="DM9" t="n">
-        <v>34.53</v>
+        <v>34.37</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.66</v>
+        <v>0.63</v>
       </c>
       <c r="DO9" t="n">
         <v>-1</v>
       </c>
       <c r="DP9" t="n">
-        <v>14.76</v>
+        <v>14.91</v>
       </c>
       <c r="DQ9" t="n">
-        <v>13.9</v>
+        <v>13.63</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.19</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>46.43</v>
+        <v>46.41</v>
       </c>
       <c r="DW9" t="n">
         <v>0.09</v>
       </c>
       <c r="DX9" t="n">
-        <v>8.19</v>
+        <v>8.18</v>
       </c>
       <c r="DY9" t="n">
-        <v>5.62</v>
+        <v>5.68</v>
       </c>
       <c r="DZ9" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="EA9" t="n">
-        <v>19.57</v>
+        <v>19.59</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.33</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="10">
@@ -4603,94 +4603,94 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D10" t="n">
         <v>11</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="F10" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="G10" t="n">
         <v>-1</v>
       </c>
       <c r="H10" t="n">
-        <v>93.8</v>
+        <v>93.27</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J10" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="K10" t="n">
-        <v>3.4</v>
+        <v>3.91</v>
       </c>
       <c r="L10" t="n">
         <v>-1</v>
       </c>
       <c r="M10" t="n">
-        <v>47.2</v>
+        <v>47.64</v>
       </c>
       <c r="N10" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="O10" t="n">
         <v>-1</v>
       </c>
       <c r="P10" t="n">
-        <v>16</v>
+        <v>16.09</v>
       </c>
       <c r="Q10" t="n">
-        <v>13.8</v>
+        <v>13.64</v>
       </c>
       <c r="R10" t="n">
-        <v>6.6</v>
+        <v>6.64</v>
       </c>
       <c r="S10" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="T10" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="V10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>46.6</v>
+        <v>47.91</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="Z10" t="n">
-        <v>14.4</v>
+        <v>14.82</v>
       </c>
       <c r="AA10" t="n">
-        <v>8.5</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="AB10" t="n">
-        <v>5.9</v>
+        <v>6.27</v>
       </c>
       <c r="AC10" t="n">
-        <v>19</v>
+        <v>18.82</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AF10" t="n">
         <v>0.27</v>
@@ -4774,31 +4774,31 @@
         <v>2.45</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.43</v>
+        <v>3.55</v>
       </c>
       <c r="BH10" t="n">
-        <v>8.859999999999999</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.43</v>
+        <v>3.55</v>
       </c>
       <c r="BJ10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM10" t="n">
         <v>0.86</v>
       </c>
-      <c r="BK10" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>0.9</v>
-      </c>
       <c r="BN10" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.48</v>
+        <v>1.68</v>
       </c>
       <c r="BP10" t="n">
         <v>-1</v>
@@ -4810,34 +4810,34 @@
         <v>100</v>
       </c>
       <c r="BS10" t="n">
-        <v>90.48</v>
+        <v>90.91</v>
       </c>
       <c r="BT10" t="n">
-        <v>61.9</v>
+        <v>63.64</v>
       </c>
       <c r="BU10" t="n">
-        <v>38.1</v>
+        <v>40.91</v>
       </c>
       <c r="BV10" t="n">
-        <v>23.81</v>
+        <v>27.27</v>
       </c>
       <c r="BW10" t="n">
-        <v>19.05</v>
+        <v>22.73</v>
       </c>
       <c r="BX10" t="n">
-        <v>71.43000000000001</v>
+        <v>72.73</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="BZ10" t="n">
-        <v>2.13</v>
+        <v>2.07</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.67</v>
+        <v>3.7</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.82</v>
+        <v>3.88</v>
       </c>
       <c r="CC10" t="n">
         <v>2.7</v>
@@ -4849,28 +4849,28 @@
         <v>1.24</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CK10" t="n">
         <v>1.36</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CN10" t="n">
         <v>1.71</v>
@@ -4879,10 +4879,10 @@
         <v>1.13</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="CR10" t="n">
         <v>1.37</v>
@@ -4900,7 +4900,7 @@
         <v>2.21</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CX10" t="n">
         <v>1.54</v>
@@ -4924,79 +4924,79 @@
         <v>3.06</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.24</v>
+        <v>0.27</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="DG10" t="n">
         <v>-1</v>
       </c>
       <c r="DH10" t="n">
-        <v>94.14</v>
+        <v>93.86</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.53</v>
+        <v>2.41</v>
       </c>
       <c r="DK10" t="n">
-        <v>3.76</v>
+        <v>4</v>
       </c>
       <c r="DL10" t="n">
         <v>-1</v>
       </c>
       <c r="DM10" t="n">
-        <v>46.67</v>
+        <v>46.91</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="DO10" t="n">
         <v>-1</v>
       </c>
       <c r="DP10" t="n">
-        <v>15.24</v>
+        <v>15.32</v>
       </c>
       <c r="DQ10" t="n">
-        <v>14.38</v>
+        <v>14.28</v>
       </c>
       <c r="DR10" t="n">
         <v>6.95</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>49.19</v>
+        <v>49.73</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DX10" t="n">
-        <v>13.71</v>
+        <v>13.96</v>
       </c>
       <c r="DY10" t="n">
-        <v>8.33</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="DZ10" t="n">
-        <v>5.38</v>
+        <v>5.59</v>
       </c>
       <c r="EA10" t="n">
-        <v>18.09</v>
+        <v>18.05</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.33</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="11">
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C11" t="n">
         <v>11</v>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E11" t="n">
         <v>0.18</v>
@@ -5099,49 +5099,49 @@
         <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AH11" t="n">
         <v>-1</v>
       </c>
       <c r="AI11" t="n">
-        <v>109.8</v>
+        <v>107.27</v>
       </c>
       <c r="AJ11" t="n">
         <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AL11" t="n">
-        <v>4.2</v>
+        <v>4.36</v>
       </c>
       <c r="AM11" t="n">
         <v>-1</v>
       </c>
       <c r="AN11" t="n">
-        <v>47.2</v>
+        <v>46.91</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AP11" t="n">
         <v>-1</v>
       </c>
       <c r="AQ11" t="n">
-        <v>13.5</v>
+        <v>13.64</v>
       </c>
       <c r="AR11" t="n">
-        <v>18.8</v>
+        <v>18.09</v>
       </c>
       <c r="AS11" t="n">
-        <v>6.7</v>
+        <v>6.73</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="AV11" t="n">
         <v>0</v>
@@ -5153,55 +5153,55 @@
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>49.1</v>
+        <v>47.82</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="BA11" t="n">
-        <v>10</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="BB11" t="n">
-        <v>7.2</v>
+        <v>6.73</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="BD11" t="n">
-        <v>23.1</v>
+        <v>24.09</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="BH11" t="n">
-        <v>8.67</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.76</v>
+        <v>0.82</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.14</v>
+        <v>0.18</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="BN11" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="BP11" t="n">
         <v>-1</v>
@@ -5210,16 +5210,16 @@
         <v>-1</v>
       </c>
       <c r="BR11" t="n">
-        <v>90.48</v>
+        <v>90.91</v>
       </c>
       <c r="BS11" t="n">
-        <v>57.14</v>
+        <v>59.09</v>
       </c>
       <c r="BT11" t="n">
-        <v>14.29</v>
+        <v>18.18</v>
       </c>
       <c r="BU11" t="n">
-        <v>4.76</v>
+        <v>9.09</v>
       </c>
       <c r="BV11" t="n">
         <v>0</v>
@@ -5228,7 +5228,7 @@
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>23.81</v>
+        <v>27.27</v>
       </c>
       <c r="BY11" t="n">
         <v>2.91</v>
@@ -5237,22 +5237,22 @@
         <v>3.04</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.39</v>
+        <v>3.4</v>
       </c>
       <c r="CB11" t="n">
         <v>3.46</v>
       </c>
       <c r="CC11" t="n">
-        <v>5.02</v>
+        <v>5.01</v>
       </c>
       <c r="CD11" t="n">
-        <v>5.36</v>
+        <v>5.33</v>
       </c>
       <c r="CE11" t="n">
         <v>1.51</v>
       </c>
       <c r="CF11" t="n">
-        <v>3.43</v>
+        <v>3.42</v>
       </c>
       <c r="CG11" t="n">
         <v>2.55</v>
@@ -5264,7 +5264,7 @@
         <v>1.73</v>
       </c>
       <c r="CJ11" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CK11" t="n">
         <v>1.57</v>
@@ -5279,13 +5279,13 @@
         <v>1.78</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CP11" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="CQ11" t="n">
-        <v>4.4</v>
+        <v>4.38</v>
       </c>
       <c r="CR11" t="n">
         <v>1.5</v>
@@ -5306,64 +5306,64 @@
         <v>2.2</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="CY11" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.23</v>
+        <v>2.27</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="DC11" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="DD11" t="n">
-        <v>4.78</v>
+        <v>4.75</v>
       </c>
       <c r="DE11" t="n">
         <v>0.09</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="DG11" t="n">
         <v>-1</v>
       </c>
       <c r="DH11" t="n">
-        <v>106.47</v>
+        <v>105.36</v>
       </c>
       <c r="DI11" t="n">
         <v>0</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.14</v>
+        <v>2.09</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.67</v>
+        <v>4.72</v>
       </c>
       <c r="DL11" t="n">
         <v>-1</v>
       </c>
       <c r="DM11" t="n">
-        <v>49</v>
+        <v>48.78</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="DO11" t="n">
         <v>-1</v>
       </c>
       <c r="DP11" t="n">
-        <v>13.67</v>
+        <v>13.73</v>
       </c>
       <c r="DQ11" t="n">
-        <v>18.81</v>
+        <v>18.45</v>
       </c>
       <c r="DR11" t="n">
         <v>6.95</v>
@@ -5378,28 +5378,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>49.09</v>
+        <v>48.46</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX11" t="n">
-        <v>10.43</v>
+        <v>10.09</v>
       </c>
       <c r="DY11" t="n">
-        <v>7.62</v>
+        <v>7.36</v>
       </c>
       <c r="DZ11" t="n">
-        <v>2.81</v>
+        <v>2.73</v>
       </c>
       <c r="EA11" t="n">
-        <v>24.76</v>
+        <v>25.18</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="12">
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
         <v>11</v>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -5502,109 +5502,109 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AH12" t="n">
         <v>-1</v>
       </c>
       <c r="AI12" t="n">
-        <v>77.2</v>
+        <v>76.36</v>
       </c>
       <c r="AJ12" t="n">
         <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>3</v>
+        <v>2.73</v>
       </c>
       <c r="AL12" t="n">
-        <v>4.2</v>
+        <v>4.09</v>
       </c>
       <c r="AM12" t="n">
         <v>-1</v>
       </c>
       <c r="AN12" t="n">
-        <v>32.9</v>
+        <v>32.82</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AP12" t="n">
         <v>-1</v>
       </c>
       <c r="AQ12" t="n">
-        <v>17.7</v>
+        <v>17.18</v>
       </c>
       <c r="AR12" t="n">
-        <v>14.7</v>
+        <v>14.45</v>
       </c>
       <c r="AS12" t="n">
-        <v>9.1</v>
+        <v>8.91</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.8</v>
+        <v>2.09</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AX12" t="n">
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>40</v>
+        <v>39.55</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="BA12" t="n">
-        <v>10.5</v>
+        <v>10.64</v>
       </c>
       <c r="BB12" t="n">
-        <v>7</v>
+        <v>7.18</v>
       </c>
       <c r="BC12" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BD12" t="n">
-        <v>18.5</v>
+        <v>18.27</v>
       </c>
       <c r="BE12" t="n">
         <v>1.15</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.33</v>
+        <v>2.45</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.619999999999999</v>
+        <v>9.68</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.33</v>
+        <v>2.45</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="BP12" t="n">
         <v>-1</v>
@@ -5613,25 +5613,25 @@
         <v>-1</v>
       </c>
       <c r="BR12" t="n">
-        <v>90.48</v>
+        <v>90.91</v>
       </c>
       <c r="BS12" t="n">
-        <v>76.19</v>
+        <v>77.27</v>
       </c>
       <c r="BT12" t="n">
-        <v>52.38</v>
+        <v>54.55</v>
       </c>
       <c r="BU12" t="n">
-        <v>9.52</v>
+        <v>13.64</v>
       </c>
       <c r="BV12" t="n">
-        <v>4.76</v>
+        <v>9.09</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>33.33</v>
+        <v>31.82</v>
       </c>
       <c r="BY12" t="n">
         <v>3.9</v>
@@ -5640,46 +5640,46 @@
         <v>4.15</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.89</v>
+        <v>3.97</v>
       </c>
       <c r="CB12" t="n">
-        <v>4.2</v>
+        <v>4.29</v>
       </c>
       <c r="CC12" t="n">
-        <v>6.98</v>
+        <v>7.17</v>
       </c>
       <c r="CD12" t="n">
-        <v>7.51</v>
+        <v>7.95</v>
       </c>
       <c r="CE12" t="n">
         <v>1.33</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="CH12" t="n">
         <v>1.37</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="CM12" t="n">
         <v>2.35</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CO12" t="n">
         <v>1.23</v>
@@ -5688,7 +5688,7 @@
         <v>1.89</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.18</v>
+        <v>3.16</v>
       </c>
       <c r="CR12" t="n">
         <v>1.46</v>
@@ -5703,10 +5703,10 @@
         <v>1.42</v>
       </c>
       <c r="CV12" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="CX12" t="n">
         <v>1.58</v>
@@ -5733,76 +5733,76 @@
         <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="DG12" t="n">
         <v>-1</v>
       </c>
       <c r="DH12" t="n">
-        <v>84.62</v>
+        <v>83.86</v>
       </c>
       <c r="DI12" t="n">
         <v>0</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.71</v>
+        <v>2.59</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.43</v>
+        <v>4.36</v>
       </c>
       <c r="DL12" t="n">
         <v>-1</v>
       </c>
       <c r="DM12" t="n">
-        <v>39.9</v>
+        <v>39.54</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="DO12" t="n">
         <v>-1</v>
       </c>
       <c r="DP12" t="n">
-        <v>16.62</v>
+        <v>16.41</v>
       </c>
       <c r="DQ12" t="n">
-        <v>14.86</v>
+        <v>14.72</v>
       </c>
       <c r="DR12" t="n">
-        <v>8</v>
+        <v>7.95</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>43.86</v>
+        <v>43.46</v>
       </c>
       <c r="DW12" t="n">
         <v>0.09</v>
       </c>
       <c r="DX12" t="n">
-        <v>11.9</v>
+        <v>11.91</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.62</v>
+        <v>7.68</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.29</v>
+        <v>4.23</v>
       </c>
       <c r="EA12" t="n">
-        <v>18.33</v>
+        <v>18.22</v>
       </c>
       <c r="EB12" t="n">
         <v>1.34</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.57</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="13">
@@ -5812,94 +5812,94 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D13" t="n">
         <v>10</v>
       </c>
       <c r="E13" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="F13" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="G13" t="n">
         <v>-1</v>
       </c>
       <c r="H13" t="n">
-        <v>83.18000000000001</v>
+        <v>82.58</v>
       </c>
       <c r="I13" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="J13" t="n">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="K13" t="n">
-        <v>5.27</v>
+        <v>5.42</v>
       </c>
       <c r="L13" t="n">
         <v>-1</v>
       </c>
       <c r="M13" t="n">
-        <v>43.27</v>
+        <v>43.25</v>
       </c>
       <c r="N13" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="O13" t="n">
         <v>-1</v>
       </c>
       <c r="P13" t="n">
-        <v>16.36</v>
+        <v>16.25</v>
       </c>
       <c r="Q13" t="n">
-        <v>15.64</v>
+        <v>16.08</v>
       </c>
       <c r="R13" t="n">
-        <v>7.82</v>
+        <v>7.67</v>
       </c>
       <c r="S13" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="T13" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="U13" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="V13" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>49</v>
+        <v>48.67</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>12.73</v>
+        <v>12.83</v>
       </c>
       <c r="AA13" t="n">
-        <v>8.91</v>
+        <v>9</v>
       </c>
       <c r="AB13" t="n">
-        <v>3.82</v>
+        <v>3.83</v>
       </c>
       <c r="AC13" t="n">
-        <v>20.18</v>
+        <v>19.92</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -5983,31 +5983,31 @@
         <v>1.9</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="BH13" t="n">
-        <v>10.1</v>
+        <v>10.09</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.29</v>
+        <v>0.36</v>
       </c>
       <c r="BL13" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.86</v>
       </c>
       <c r="BP13" t="n">
         <v>-1</v>
@@ -6016,37 +6016,37 @@
         <v>-1</v>
       </c>
       <c r="BR13" t="n">
-        <v>90.48</v>
+        <v>90.91</v>
       </c>
       <c r="BS13" t="n">
-        <v>61.9</v>
+        <v>63.64</v>
       </c>
       <c r="BT13" t="n">
-        <v>42.86</v>
+        <v>40.91</v>
       </c>
       <c r="BU13" t="n">
-        <v>33.33</v>
+        <v>31.82</v>
       </c>
       <c r="BV13" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BW13" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX13" t="n">
-        <v>52.38</v>
+        <v>50</v>
       </c>
       <c r="BY13" t="n">
-        <v>3.85</v>
+        <v>3.86</v>
       </c>
       <c r="BZ13" t="n">
-        <v>4.42</v>
+        <v>4.41</v>
       </c>
       <c r="CA13" t="n">
-        <v>4.05</v>
+        <v>4.04</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.29</v>
+        <v>4.28</v>
       </c>
       <c r="CC13" t="n">
         <v>5.98</v>
@@ -6058,19 +6058,19 @@
         <v>1.35</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="CG13" t="n">
         <v>3.16</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CK13" t="n">
         <v>1.4</v>
@@ -6088,10 +6088,10 @@
         <v>1.25</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CQ13" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="CR13" t="n">
         <v>1.4</v>
@@ -6106,10 +6106,10 @@
         <v>1.56</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CW13" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CX13" t="n">
         <v>1.54</v>
@@ -6136,31 +6136,31 @@
         <v>0.09</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="DG13" t="n">
         <v>-1</v>
       </c>
       <c r="DH13" t="n">
-        <v>85.67</v>
+        <v>85.23</v>
       </c>
       <c r="DI13" t="n">
         <v>0.14</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.34</v>
+        <v>2.27</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.52</v>
+        <v>5.59</v>
       </c>
       <c r="DL13" t="n">
         <v>-1</v>
       </c>
       <c r="DM13" t="n">
-        <v>43.71</v>
+        <v>43.68</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="DO13" t="n">
         <v>-1</v>
@@ -6169,10 +6169,10 @@
         <v>14.95</v>
       </c>
       <c r="DQ13" t="n">
-        <v>15.86</v>
+        <v>16.09</v>
       </c>
       <c r="DR13" t="n">
-        <v>8.140000000000001</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="DS13" t="n">
         <v>0.14</v>
@@ -6184,28 +6184,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>48.67</v>
+        <v>48.5</v>
       </c>
       <c r="DW13" t="n">
         <v>0.05</v>
       </c>
       <c r="DX13" t="n">
-        <v>12.05</v>
+        <v>12.13</v>
       </c>
       <c r="DY13" t="n">
-        <v>8.140000000000001</v>
+        <v>8.23</v>
       </c>
       <c r="DZ13" t="n">
         <v>3.91</v>
       </c>
       <c r="EA13" t="n">
-        <v>21.48</v>
+        <v>21.27</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.29</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="14">
@@ -6215,13 +6215,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C14" t="n">
         <v>11</v>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E14" t="n">
         <v>0.09</v>
@@ -6308,109 +6308,109 @@
         <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AH14" t="n">
         <v>-1</v>
       </c>
       <c r="AI14" t="n">
-        <v>89.8</v>
+        <v>88</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="AL14" t="n">
-        <v>4</v>
+        <v>3.91</v>
       </c>
       <c r="AM14" t="n">
         <v>-1</v>
       </c>
       <c r="AN14" t="n">
-        <v>46.6</v>
+        <v>45.64</v>
       </c>
       <c r="AO14" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AP14" t="n">
         <v>-1</v>
       </c>
       <c r="AQ14" t="n">
-        <v>15.3</v>
+        <v>15.36</v>
       </c>
       <c r="AR14" t="n">
-        <v>17.5</v>
+        <v>17.45</v>
       </c>
       <c r="AS14" t="n">
-        <v>6.8</v>
+        <v>6.82</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AX14" t="n">
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>46.8</v>
+        <v>46.73</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="BA14" t="n">
-        <v>11.8</v>
+        <v>11.82</v>
       </c>
       <c r="BB14" t="n">
-        <v>7.8</v>
+        <v>7.73</v>
       </c>
       <c r="BC14" t="n">
-        <v>4</v>
+        <v>4.09</v>
       </c>
       <c r="BD14" t="n">
-        <v>21</v>
+        <v>21.73</v>
       </c>
       <c r="BE14" t="n">
         <v>1.36</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="BH14" t="n">
-        <v>7.9</v>
+        <v>7.86</v>
       </c>
       <c r="BI14" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="BP14" t="n">
         <v>-1</v>
@@ -6419,25 +6419,25 @@
         <v>-1</v>
       </c>
       <c r="BR14" t="n">
-        <v>90.48</v>
+        <v>90.91</v>
       </c>
       <c r="BS14" t="n">
-        <v>52.38</v>
+        <v>50</v>
       </c>
       <c r="BT14" t="n">
-        <v>23.81</v>
+        <v>22.73</v>
       </c>
       <c r="BU14" t="n">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
       <c r="BV14" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BW14" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX14" t="n">
-        <v>42.86</v>
+        <v>40.91</v>
       </c>
       <c r="BY14" t="n">
         <v>2.43</v>
@@ -6446,25 +6446,25 @@
         <v>2.5</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.57</v>
+        <v>3.56</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.65</v>
+        <v>3.64</v>
       </c>
       <c r="CC14" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="CD14" t="n">
         <v>4.29</v>
-      </c>
-      <c r="CD14" t="n">
-        <v>4.37</v>
       </c>
       <c r="CE14" t="n">
         <v>1.41</v>
       </c>
       <c r="CF14" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="CG14" t="n">
         <v>2.93</v>
-      </c>
-      <c r="CG14" t="n">
-        <v>2.95</v>
       </c>
       <c r="CH14" t="n">
         <v>1.41</v>
@@ -6485,16 +6485,16 @@
         <v>2.29</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CO14" t="n">
         <v>1.32</v>
       </c>
       <c r="CP14" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.47</v>
+        <v>3.5</v>
       </c>
       <c r="CR14" t="n">
         <v>1.37</v>
@@ -6533,82 +6533,82 @@
         <v>2.09</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.68</v>
+        <v>3.7</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="DG14" t="n">
         <v>-1</v>
       </c>
       <c r="DH14" t="n">
-        <v>94.67</v>
+        <v>93.54000000000001</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.67</v>
+        <v>2.64</v>
       </c>
       <c r="DK14" t="n">
-        <v>4.24</v>
+        <v>4.18</v>
       </c>
       <c r="DL14" t="n">
         <v>-1</v>
       </c>
       <c r="DM14" t="n">
-        <v>50.71</v>
+        <v>50.04</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="DO14" t="n">
         <v>-1</v>
       </c>
       <c r="DP14" t="n">
-        <v>14.52</v>
+        <v>14.59</v>
       </c>
       <c r="DQ14" t="n">
-        <v>17.47</v>
+        <v>17.45</v>
       </c>
       <c r="DR14" t="n">
-        <v>6.43</v>
+        <v>6.45</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>49</v>
+        <v>48.86</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DX14" t="n">
-        <v>12.81</v>
+        <v>12.78</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.91</v>
+        <v>8.82</v>
       </c>
       <c r="DZ14" t="n">
-        <v>3.91</v>
+        <v>3.95</v>
       </c>
       <c r="EA14" t="n">
-        <v>21.05</v>
+        <v>21.41</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="15">
@@ -6618,13 +6618,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C15" t="n">
         <v>11</v>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -6711,49 +6711,49 @@
         <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AH15" t="n">
         <v>-1</v>
       </c>
       <c r="AI15" t="n">
-        <v>80.59999999999999</v>
+        <v>81.18000000000001</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AK15" t="n">
-        <v>3.1</v>
+        <v>2.82</v>
       </c>
       <c r="AL15" t="n">
-        <v>4</v>
+        <v>3.73</v>
       </c>
       <c r="AM15" t="n">
         <v>-1</v>
       </c>
       <c r="AN15" t="n">
-        <v>36.6</v>
+        <v>37.18</v>
       </c>
       <c r="AO15" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AP15" t="n">
         <v>-1</v>
       </c>
       <c r="AQ15" t="n">
-        <v>17.5</v>
+        <v>16.82</v>
       </c>
       <c r="AR15" t="n">
-        <v>13.5</v>
+        <v>14.09</v>
       </c>
       <c r="AS15" t="n">
-        <v>8.699999999999999</v>
+        <v>8.82</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AV15" t="n">
         <v>0</v>
@@ -6765,55 +6765,55 @@
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>41.1</v>
+        <v>42.27</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>10.2</v>
+        <v>9.82</v>
       </c>
       <c r="BB15" t="n">
-        <v>7.6</v>
+        <v>7.27</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="BD15" t="n">
-        <v>18.2</v>
+        <v>19.36</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="BF15" t="n">
-        <v>3.1</v>
+        <v>2.82</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.24</v>
+        <v>2.14</v>
       </c>
       <c r="BH15" t="n">
-        <v>7.67</v>
+        <v>7.68</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.24</v>
+        <v>2.14</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="BO15" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BP15" t="n">
         <v>-1</v>
@@ -6822,25 +6822,25 @@
         <v>-1</v>
       </c>
       <c r="BR15" t="n">
-        <v>90.48</v>
+        <v>86.36</v>
       </c>
       <c r="BS15" t="n">
-        <v>61.9</v>
+        <v>59.09</v>
       </c>
       <c r="BT15" t="n">
-        <v>42.86</v>
+        <v>40.91</v>
       </c>
       <c r="BU15" t="n">
-        <v>19.05</v>
+        <v>18.18</v>
       </c>
       <c r="BV15" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BW15" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX15" t="n">
-        <v>33.33</v>
+        <v>31.82</v>
       </c>
       <c r="BY15" t="n">
         <v>3.01</v>
@@ -6849,55 +6849,55 @@
         <v>3.34</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.43</v>
+        <v>3.4</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.61</v>
+        <v>3.57</v>
       </c>
       <c r="CC15" t="n">
-        <v>4.29</v>
+        <v>4.12</v>
       </c>
       <c r="CD15" t="n">
-        <v>4.7</v>
+        <v>4.53</v>
       </c>
       <c r="CE15" t="n">
         <v>1.45</v>
       </c>
       <c r="CF15" t="n">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CL15" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CP15" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.77</v>
+        <v>3.85</v>
       </c>
       <c r="CR15" t="n">
         <v>1.39</v>
@@ -6912,10 +6912,10 @@
         <v>1.42</v>
       </c>
       <c r="CV15" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="CX15" t="n">
         <v>1.63</v>
@@ -6930,55 +6930,55 @@
         <v>1.8</v>
       </c>
       <c r="DB15" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.95</v>
+        <v>4.07</v>
       </c>
       <c r="DE15" t="n">
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="DG15" t="n">
         <v>-1</v>
       </c>
       <c r="DH15" t="n">
-        <v>84.81</v>
+        <v>84.91</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.52</v>
+        <v>2.41</v>
       </c>
       <c r="DK15" t="n">
-        <v>4.05</v>
+        <v>3.91</v>
       </c>
       <c r="DL15" t="n">
         <v>-1</v>
       </c>
       <c r="DM15" t="n">
-        <v>37.43</v>
+        <v>37.68</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="DO15" t="n">
         <v>-1</v>
       </c>
       <c r="DP15" t="n">
-        <v>16.43</v>
+        <v>16.14</v>
       </c>
       <c r="DQ15" t="n">
-        <v>15.05</v>
+        <v>15.27</v>
       </c>
       <c r="DR15" t="n">
-        <v>8.19</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="DS15" t="n">
         <v>0.09</v>
@@ -6990,28 +6990,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>41.34</v>
+        <v>41.91</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DX15" t="n">
-        <v>10.24</v>
+        <v>10.04</v>
       </c>
       <c r="DY15" t="n">
-        <v>7.24</v>
+        <v>7.09</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="EA15" t="n">
-        <v>19.57</v>
+        <v>20.09</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.48</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="16">
@@ -7021,13 +7021,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C16" t="n">
         <v>11</v>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E16" t="n">
         <v>0.09</v>
@@ -7114,109 +7114,109 @@
         <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AH16" t="n">
         <v>-1</v>
       </c>
       <c r="AI16" t="n">
-        <v>94.3</v>
+        <v>93.64</v>
       </c>
       <c r="AJ16" t="n">
         <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="AL16" t="n">
-        <v>5.6</v>
+        <v>5.36</v>
       </c>
       <c r="AM16" t="n">
         <v>-1</v>
       </c>
       <c r="AN16" t="n">
-        <v>50.3</v>
+        <v>49.91</v>
       </c>
       <c r="AO16" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AP16" t="n">
         <v>-1</v>
       </c>
       <c r="AQ16" t="n">
-        <v>16.4</v>
+        <v>16.82</v>
       </c>
       <c r="AR16" t="n">
-        <v>15.3</v>
+        <v>15.27</v>
       </c>
       <c r="AS16" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AX16" t="n">
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>62.4</v>
+        <v>61.73</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="BA16" t="n">
-        <v>13.1</v>
+        <v>13.18</v>
       </c>
       <c r="BB16" t="n">
-        <v>9.300000000000001</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="BC16" t="n">
-        <v>3.8</v>
+        <v>3.82</v>
       </c>
       <c r="BD16" t="n">
-        <v>19.6</v>
+        <v>19.45</v>
       </c>
       <c r="BE16" t="n">
         <v>1.46</v>
       </c>
       <c r="BF16" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="BG16" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="BH16" t="n">
-        <v>9</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="BI16" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.77</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="BP16" t="n">
         <v>-1</v>
@@ -7228,22 +7228,22 @@
         <v>100</v>
       </c>
       <c r="BS16" t="n">
-        <v>80.95</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BT16" t="n">
-        <v>57.14</v>
+        <v>54.55</v>
       </c>
       <c r="BU16" t="n">
-        <v>28.57</v>
+        <v>27.27</v>
       </c>
       <c r="BV16" t="n">
-        <v>19.05</v>
+        <v>18.18</v>
       </c>
       <c r="BW16" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BX16" t="n">
-        <v>61.9</v>
+        <v>59.09</v>
       </c>
       <c r="BY16" t="n">
         <v>1.65</v>
@@ -7255,19 +7255,19 @@
         <v>3.9</v>
       </c>
       <c r="CB16" t="n">
-        <v>4.22</v>
+        <v>4.21</v>
       </c>
       <c r="CC16" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="CD16" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="CE16" t="n">
         <v>1.37</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="CG16" t="n">
         <v>3.08</v>
@@ -7276,10 +7276,10 @@
         <v>1.47</v>
       </c>
       <c r="CI16" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CK16" t="n">
         <v>1.45</v>
@@ -7288,19 +7288,19 @@
         <v>1.93</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="CN16" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="CP16" t="n">
         <v>1.84</v>
       </c>
       <c r="CQ16" t="n">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
       <c r="CR16" t="n">
         <v>1.41</v>
@@ -7315,10 +7315,10 @@
         <v>1.46</v>
       </c>
       <c r="CV16" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CX16" t="n">
         <v>1.55</v>
@@ -7342,31 +7342,31 @@
         <v>3.41</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="DG16" t="n">
         <v>-1</v>
       </c>
       <c r="DH16" t="n">
-        <v>97.29000000000001</v>
+        <v>96.81999999999999</v>
       </c>
       <c r="DI16" t="n">
         <v>0</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.47</v>
+        <v>2.41</v>
       </c>
       <c r="DK16" t="n">
-        <v>5.57</v>
+        <v>5.45</v>
       </c>
       <c r="DL16" t="n">
         <v>-1</v>
       </c>
       <c r="DM16" t="n">
-        <v>50.38</v>
+        <v>50.18</v>
       </c>
       <c r="DN16" t="n">
         <v>1.05</v>
@@ -7375,46 +7375,46 @@
         <v>-1</v>
       </c>
       <c r="DP16" t="n">
-        <v>15.86</v>
+        <v>16.09</v>
       </c>
       <c r="DQ16" t="n">
-        <v>15.81</v>
+        <v>15.77</v>
       </c>
       <c r="DR16" t="n">
-        <v>6.29</v>
+        <v>6.36</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>61.33</v>
+        <v>61.04</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DX16" t="n">
-        <v>13</v>
+        <v>13.04</v>
       </c>
       <c r="DY16" t="n">
-        <v>9</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="DZ16" t="n">
         <v>4</v>
       </c>
       <c r="EA16" t="n">
-        <v>20.9</v>
+        <v>20.77</v>
       </c>
       <c r="EB16" t="n">
         <v>1.47</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.19</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="17">
@@ -7424,13 +7424,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C17" t="n">
         <v>11</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E17" t="n">
         <v>0.09</v>
@@ -7517,109 +7517,109 @@
         <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AH17" t="n">
         <v>-1</v>
       </c>
       <c r="AI17" t="n">
-        <v>92.8</v>
+        <v>93</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AL17" t="n">
-        <v>5.7</v>
+        <v>5.73</v>
       </c>
       <c r="AM17" t="n">
         <v>-1</v>
       </c>
       <c r="AN17" t="n">
-        <v>51.6</v>
+        <v>51</v>
       </c>
       <c r="AO17" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>9.449999999999999</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>21.82</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>60.27</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>11.36</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>7.09</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>19.27</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>9.41</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="BK17" t="n">
         <v>0.5</v>
       </c>
-      <c r="AP17" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>7</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>61</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>19</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="BH17" t="n">
-        <v>9.43</v>
-      </c>
-      <c r="BI17" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="BJ17" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="BK17" t="n">
-        <v>0.43</v>
-      </c>
       <c r="BL17" t="n">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="BP17" t="n">
         <v>-1</v>
@@ -7628,25 +7628,25 @@
         <v>-1</v>
       </c>
       <c r="BR17" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS17" t="n">
-        <v>80.95</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BT17" t="n">
-        <v>38.1</v>
+        <v>40.91</v>
       </c>
       <c r="BU17" t="n">
-        <v>19.05</v>
+        <v>22.73</v>
       </c>
       <c r="BV17" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BW17" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX17" t="n">
-        <v>42.86</v>
+        <v>45.45</v>
       </c>
       <c r="BY17" t="n">
         <v>1.4</v>
@@ -7655,16 +7655,16 @@
         <v>1.44</v>
       </c>
       <c r="CA17" t="n">
-        <v>4.67</v>
+        <v>4.61</v>
       </c>
       <c r="CB17" t="n">
-        <v>4.95</v>
+        <v>4.89</v>
       </c>
       <c r="CC17" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="CD17" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="CE17" t="n">
         <v>1.36</v>
@@ -7673,28 +7673,28 @@
         <v>2.71</v>
       </c>
       <c r="CG17" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="CH17" t="n">
         <v>1.48</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CJ17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CL17" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CO17" t="n">
         <v>1.26</v>
@@ -7703,37 +7703,37 @@
         <v>1.88</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="CR17" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CS17" t="n">
         <v>2.85</v>
       </c>
       <c r="CT17" t="n">
-        <v>2.93</v>
+        <v>2.96</v>
       </c>
       <c r="CU17" t="n">
         <v>1.48</v>
       </c>
       <c r="CV17" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CW17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="CX17" t="n">
         <v>1.56</v>
       </c>
       <c r="CY17" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="CZ17" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="DA17" t="n">
         <v>1.9</v>
-      </c>
-      <c r="CZ17" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="DA17" t="n">
-        <v>1.91</v>
       </c>
       <c r="DB17" t="n">
         <v>1.28</v>
@@ -7742,82 +7742,82 @@
         <v>1.87</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.13</v>
+        <v>3.14</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DF17" t="n">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="DG17" t="n">
         <v>-1</v>
       </c>
       <c r="DH17" t="n">
-        <v>92.43000000000001</v>
+        <v>92.54000000000001</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DJ17" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.67</v>
+        <v>5.68</v>
       </c>
       <c r="DL17" t="n">
         <v>-1</v>
       </c>
       <c r="DM17" t="n">
-        <v>50.33</v>
+        <v>50.09</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="DO17" t="n">
         <v>-1</v>
       </c>
       <c r="DP17" t="n">
-        <v>9.289999999999999</v>
+        <v>9.27</v>
       </c>
       <c r="DQ17" t="n">
-        <v>20.19</v>
+        <v>20.09</v>
       </c>
       <c r="DR17" t="n">
         <v>6.09</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>60.76</v>
+        <v>60.41</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DX17" t="n">
-        <v>13</v>
+        <v>12.96</v>
       </c>
       <c r="DY17" t="n">
-        <v>7.71</v>
+        <v>7.77</v>
       </c>
       <c r="DZ17" t="n">
-        <v>5.29</v>
+        <v>5.18</v>
       </c>
       <c r="EA17" t="n">
-        <v>19.14</v>
+        <v>19.27</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Russian_Premier_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Russian_Premier_League_2025-2026.xlsx
@@ -1445,7 +1445,7 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>46.36</v>
+        <v>46.27</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -1751,7 +1751,7 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>45.96</v>
+        <v>45.91</v>
       </c>
       <c r="DW2" t="n">
         <v>0.32</v>
@@ -1854,19 +1854,19 @@
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="AA3" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="AB3" t="n">
         <v>4.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AE3" t="n">
         <v>1.6</v>
@@ -1929,16 +1929,16 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>41.08</v>
+        <v>41.17</v>
       </c>
       <c r="AZ3" t="n">
         <v>0.17</v>
       </c>
       <c r="BA3" t="n">
-        <v>10.5</v>
+        <v>10.67</v>
       </c>
       <c r="BB3" t="n">
-        <v>7.08</v>
+        <v>7.25</v>
       </c>
       <c r="BC3" t="n">
         <v>3.42</v>
@@ -1947,7 +1947,7 @@
         <v>17</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="BF3" t="n">
         <v>2</v>
@@ -2154,25 +2154,25 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>43.82</v>
+        <v>43.87</v>
       </c>
       <c r="DW3" t="n">
         <v>0.09</v>
       </c>
       <c r="DX3" t="n">
-        <v>11.05</v>
+        <v>11.18</v>
       </c>
       <c r="DY3" t="n">
-        <v>7.13</v>
+        <v>7.27</v>
       </c>
       <c r="DZ3" t="n">
         <v>3.91</v>
       </c>
       <c r="EA3" t="n">
-        <v>17.82</v>
+        <v>17.86</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="EC3" t="n">
         <v>1.82</v>
@@ -2257,10 +2257,10 @@
         <v>0.09</v>
       </c>
       <c r="Z4" t="n">
-        <v>13.09</v>
+        <v>13.18</v>
       </c>
       <c r="AA4" t="n">
-        <v>8.73</v>
+        <v>8.82</v>
       </c>
       <c r="AB4" t="n">
         <v>4.36</v>
@@ -2269,7 +2269,7 @@
         <v>21.55</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AE4" t="n">
         <v>2.73</v>
@@ -2314,7 +2314,7 @@
         <v>12.82</v>
       </c>
       <c r="AS4" t="n">
-        <v>8</v>
+        <v>7.91</v>
       </c>
       <c r="AT4" t="n">
         <v>0.45</v>
@@ -2545,7 +2545,7 @@
         <v>12.78</v>
       </c>
       <c r="DR4" t="n">
-        <v>7.5</v>
+        <v>7.45</v>
       </c>
       <c r="DS4" t="n">
         <v>0.22</v>
@@ -2563,10 +2563,10 @@
         <v>0.09</v>
       </c>
       <c r="DX4" t="n">
-        <v>12.5</v>
+        <v>12.54</v>
       </c>
       <c r="DY4" t="n">
-        <v>8.279999999999999</v>
+        <v>8.32</v>
       </c>
       <c r="DZ4" t="n">
         <v>4.22</v>
@@ -2575,7 +2575,7 @@
         <v>21.18</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="EC4" t="n">
         <v>3.05</v>
@@ -2735,7 +2735,7 @@
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>54.09</v>
+        <v>54.18</v>
       </c>
       <c r="AZ5" t="n">
         <v>0.27</v>
@@ -2960,7 +2960,7 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>56.36</v>
+        <v>56.41</v>
       </c>
       <c r="DW5" t="n">
         <v>0.18</v>
@@ -3153,7 +3153,7 @@
         <v>3.82</v>
       </c>
       <c r="BD6" t="n">
-        <v>20.55</v>
+        <v>20.64</v>
       </c>
       <c r="BE6" t="n">
         <v>1.6</v>
@@ -3378,7 +3378,7 @@
         <v>4.64</v>
       </c>
       <c r="EA6" t="n">
-        <v>20.6</v>
+        <v>20.64</v>
       </c>
       <c r="EB6" t="n">
         <v>1.69</v>
@@ -3926,7 +3926,7 @@
         <v>19.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="AT8" t="n">
         <v>0.6</v>
@@ -3950,19 +3950,19 @@
         <v>0.1</v>
       </c>
       <c r="BA8" t="n">
-        <v>13.5</v>
+        <v>13.7</v>
       </c>
       <c r="BB8" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BD8" t="n">
         <v>20.6</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="BF8" t="n">
         <v>1.7</v>
@@ -4157,7 +4157,7 @@
         <v>17.63</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.05</v>
+        <v>7.09</v>
       </c>
       <c r="DS8" t="n">
         <v>0.18</v>
@@ -4175,19 +4175,19 @@
         <v>0.18</v>
       </c>
       <c r="DX8" t="n">
-        <v>16.41</v>
+        <v>16.5</v>
       </c>
       <c r="DY8" t="n">
         <v>11.32</v>
       </c>
       <c r="DZ8" t="n">
-        <v>5.09</v>
+        <v>5.18</v>
       </c>
       <c r="EA8" t="n">
         <v>20.73</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="EC8" t="n">
         <v>2.09</v>
@@ -4266,7 +4266,7 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>46</v>
+        <v>45.9</v>
       </c>
       <c r="Y9" t="n">
         <v>0.1</v>
@@ -4353,19 +4353,19 @@
         <v>0.08</v>
       </c>
       <c r="BA9" t="n">
-        <v>7.42</v>
+        <v>7.33</v>
       </c>
       <c r="BB9" t="n">
-        <v>5.08</v>
+        <v>5</v>
       </c>
       <c r="BC9" t="n">
         <v>2.33</v>
       </c>
       <c r="BD9" t="n">
-        <v>18.67</v>
+        <v>18.75</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.87</v>
+        <v>0.86</v>
       </c>
       <c r="BF9" t="n">
         <v>2.75</v>
@@ -4572,25 +4572,25 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>46.41</v>
+        <v>46.36</v>
       </c>
       <c r="DW9" t="n">
         <v>0.09</v>
       </c>
       <c r="DX9" t="n">
-        <v>8.18</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="DY9" t="n">
-        <v>5.68</v>
+        <v>5.64</v>
       </c>
       <c r="DZ9" t="n">
         <v>2.5</v>
       </c>
       <c r="EA9" t="n">
-        <v>19.59</v>
+        <v>19.64</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.95</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="EC9" t="n">
         <v>2.27</v>
@@ -4675,19 +4675,19 @@
         <v>0.18</v>
       </c>
       <c r="Z10" t="n">
-        <v>14.82</v>
+        <v>15</v>
       </c>
       <c r="AA10" t="n">
-        <v>8.550000000000001</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="AB10" t="n">
-        <v>6.27</v>
+        <v>6.36</v>
       </c>
       <c r="AC10" t="n">
         <v>18.82</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AE10" t="n">
         <v>2</v>
@@ -4756,10 +4756,10 @@
         <v>0.18</v>
       </c>
       <c r="BA10" t="n">
-        <v>13.09</v>
+        <v>13</v>
       </c>
       <c r="BB10" t="n">
-        <v>8.18</v>
+        <v>8.09</v>
       </c>
       <c r="BC10" t="n">
         <v>4.91</v>
@@ -4768,7 +4768,7 @@
         <v>17.27</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="BF10" t="n">
         <v>2.45</v>
@@ -4981,13 +4981,13 @@
         <v>0.18</v>
       </c>
       <c r="DX10" t="n">
-        <v>13.96</v>
+        <v>14</v>
       </c>
       <c r="DY10" t="n">
         <v>8.359999999999999</v>
       </c>
       <c r="DZ10" t="n">
-        <v>5.59</v>
+        <v>5.64</v>
       </c>
       <c r="EA10" t="n">
         <v>18.05</v>
@@ -5072,7 +5072,7 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>49.09</v>
+        <v>49</v>
       </c>
       <c r="Y11" t="n">
         <v>0.09</v>
@@ -5378,7 +5378,7 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>48.46</v>
+        <v>48.41</v>
       </c>
       <c r="DW11" t="n">
         <v>0.13</v>
@@ -5481,10 +5481,10 @@
         <v>0.09</v>
       </c>
       <c r="Z12" t="n">
-        <v>13.18</v>
+        <v>13.36</v>
       </c>
       <c r="AA12" t="n">
-        <v>8.18</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="AB12" t="n">
         <v>5</v>
@@ -5493,7 +5493,7 @@
         <v>18.18</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AE12" t="n">
         <v>2.36</v>
@@ -5538,7 +5538,7 @@
         <v>14.45</v>
       </c>
       <c r="AS12" t="n">
-        <v>8.91</v>
+        <v>8.82</v>
       </c>
       <c r="AT12" t="n">
         <v>2.09</v>
@@ -5769,7 +5769,7 @@
         <v>14.72</v>
       </c>
       <c r="DR12" t="n">
-        <v>7.95</v>
+        <v>7.91</v>
       </c>
       <c r="DS12" t="n">
         <v>0.18</v>
@@ -5787,10 +5787,10 @@
         <v>0.09</v>
       </c>
       <c r="DX12" t="n">
-        <v>11.91</v>
+        <v>12</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.68</v>
+        <v>7.77</v>
       </c>
       <c r="DZ12" t="n">
         <v>4.23</v>
@@ -5959,7 +5959,7 @@
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
       <c r="AZ13" t="n">
         <v>0.1</v>
@@ -5968,16 +5968,16 @@
         <v>11.3</v>
       </c>
       <c r="BB13" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="BC13" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BD13" t="n">
         <v>22.9</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="BF13" t="n">
         <v>1.9</v>
@@ -6184,7 +6184,7 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>48.5</v>
+        <v>48.55</v>
       </c>
       <c r="DW13" t="n">
         <v>0.05</v>
@@ -6193,16 +6193,16 @@
         <v>12.13</v>
       </c>
       <c r="DY13" t="n">
-        <v>8.23</v>
+        <v>8.27</v>
       </c>
       <c r="DZ13" t="n">
-        <v>3.91</v>
+        <v>3.86</v>
       </c>
       <c r="EA13" t="n">
         <v>21.27</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="EC13" t="n">
         <v>2.23</v>
@@ -6765,7 +6765,7 @@
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>42.27</v>
+        <v>42.36</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
@@ -6990,7 +6990,7 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>41.91</v>
+        <v>41.96</v>
       </c>
       <c r="DW15" t="n">
         <v>0.04</v>
@@ -7087,7 +7087,7 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>60.36</v>
+        <v>60.27</v>
       </c>
       <c r="Y16" t="n">
         <v>0.27</v>
@@ -7393,7 +7393,7 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>61.04</v>
+        <v>61</v>
       </c>
       <c r="DW16" t="n">
         <v>0.18</v>
@@ -7496,13 +7496,13 @@
         <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>14.55</v>
+        <v>14.64</v>
       </c>
       <c r="AA17" t="n">
-        <v>8.449999999999999</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="AB17" t="n">
-        <v>6.09</v>
+        <v>6</v>
       </c>
       <c r="AC17" t="n">
         <v>19.27</v>
@@ -7802,13 +7802,13 @@
         <v>0.04</v>
       </c>
       <c r="DX17" t="n">
-        <v>12.96</v>
+        <v>13</v>
       </c>
       <c r="DY17" t="n">
-        <v>7.77</v>
+        <v>7.86</v>
       </c>
       <c r="DZ17" t="n">
-        <v>5.18</v>
+        <v>5.14</v>
       </c>
       <c r="EA17" t="n">
         <v>19.27</v>

--- a/data/teams/leagues/Averages_Russian_Premier_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Russian_Premier_League_2025-2026.xlsx
@@ -1502,13 +1502,13 @@
         <v>-1</v>
       </c>
       <c r="AQ2" t="n">
-        <v>13.64</v>
+        <v>13.73</v>
       </c>
       <c r="AR2" t="n">
         <v>18.09</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.82</v>
+        <v>7.91</v>
       </c>
       <c r="AT2" t="n">
         <v>1.55</v>
@@ -1526,16 +1526,16 @@
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>45.55</v>
+        <v>45.64</v>
       </c>
       <c r="AZ2" t="n">
         <v>0.64</v>
       </c>
       <c r="BA2" t="n">
-        <v>10.45</v>
+        <v>10.64</v>
       </c>
       <c r="BB2" t="n">
-        <v>7.55</v>
+        <v>7.73</v>
       </c>
       <c r="BC2" t="n">
         <v>2.91</v>
@@ -1544,7 +1544,7 @@
         <v>20.82</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="BF2" t="n">
         <v>1.73</v>
@@ -1733,13 +1733,13 @@
         <v>-1</v>
       </c>
       <c r="DP2" t="n">
-        <v>12.14</v>
+        <v>12.18</v>
       </c>
       <c r="DQ2" t="n">
         <v>17.27</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.95</v>
+        <v>7</v>
       </c>
       <c r="DS2" t="n">
         <v>0.13</v>
@@ -1751,16 +1751,16 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>45.91</v>
+        <v>45.96</v>
       </c>
       <c r="DW2" t="n">
         <v>0.32</v>
       </c>
       <c r="DX2" t="n">
-        <v>12.18</v>
+        <v>12.28</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.460000000000001</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="DZ2" t="n">
         <v>3.73</v>
@@ -1769,7 +1769,7 @@
         <v>21.14</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="EC2" t="n">
         <v>1.82</v>
@@ -2630,7 +2630,7 @@
         <v>-1</v>
       </c>
       <c r="P5" t="n">
-        <v>10.82</v>
+        <v>10.91</v>
       </c>
       <c r="Q5" t="n">
         <v>17.27</v>
@@ -2654,16 +2654,16 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>58.64</v>
+        <v>58.55</v>
       </c>
       <c r="Y5" t="n">
         <v>0.09</v>
       </c>
       <c r="Z5" t="n">
-        <v>14.45</v>
+        <v>14.64</v>
       </c>
       <c r="AA5" t="n">
-        <v>9.359999999999999</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="AB5" t="n">
         <v>5.09</v>
@@ -2672,7 +2672,7 @@
         <v>20.73</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AE5" t="n">
         <v>1.55</v>
@@ -2942,7 +2942,7 @@
         <v>-1</v>
       </c>
       <c r="DP5" t="n">
-        <v>11.69</v>
+        <v>11.73</v>
       </c>
       <c r="DQ5" t="n">
         <v>15.91</v>
@@ -2960,16 +2960,16 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>56.41</v>
+        <v>56.36</v>
       </c>
       <c r="DW5" t="n">
         <v>0.18</v>
       </c>
       <c r="DX5" t="n">
-        <v>13.72</v>
+        <v>13.82</v>
       </c>
       <c r="DY5" t="n">
-        <v>9.140000000000001</v>
+        <v>9.23</v>
       </c>
       <c r="DZ5" t="n">
         <v>4.59</v>

--- a/data/teams/leagues/Averages_Russian_Premier_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Russian_Premier_League_2025-2026.xlsx
@@ -1379,94 +1379,94 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2" t="n">
         <v>11</v>
       </c>
       <c r="E2" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="F2" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="G2" t="n">
         <v>-1</v>
       </c>
       <c r="H2" t="n">
-        <v>90</v>
+        <v>90.08</v>
       </c>
       <c r="I2" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="K2" t="n">
-        <v>4.91</v>
+        <v>4.92</v>
       </c>
       <c r="L2" t="n">
         <v>-1</v>
       </c>
       <c r="M2" t="n">
-        <v>44.82</v>
+        <v>45.75</v>
       </c>
       <c r="N2" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="O2" t="n">
         <v>-1</v>
       </c>
       <c r="P2" t="n">
-        <v>10.64</v>
+        <v>10.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>16.45</v>
+        <v>16.5</v>
       </c>
       <c r="R2" t="n">
-        <v>6.09</v>
+        <v>6.42</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
       </c>
       <c r="T2" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="U2" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="V2" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>46.27</v>
+        <v>46</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="Z2" t="n">
-        <v>13.91</v>
+        <v>13.75</v>
       </c>
       <c r="AA2" t="n">
-        <v>9.359999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.55</v>
+        <v>4.25</v>
       </c>
       <c r="AC2" t="n">
-        <v>21.45</v>
+        <v>21.67</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -1550,31 +1550,31 @@
         <v>1.73</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="BH2" t="n">
-        <v>8.68</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="BP2" t="n">
         <v>-1</v>
@@ -1586,34 +1586,34 @@
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>72.73</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="BT2" t="n">
-        <v>45.45</v>
+        <v>43.48</v>
       </c>
       <c r="BU2" t="n">
-        <v>22.73</v>
+        <v>21.74</v>
       </c>
       <c r="BV2" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BW2" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX2" t="n">
-        <v>54.55</v>
+        <v>52.17</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.66</v>
+        <v>2.77</v>
       </c>
       <c r="BZ2" t="n">
-        <v>2.67</v>
+        <v>2.82</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.49</v>
+        <v>3.48</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.58</v>
+        <v>3.59</v>
       </c>
       <c r="CC2" t="n">
         <v>3.42</v>
@@ -1625,13 +1625,13 @@
         <v>1.41</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="CG2" t="n">
         <v>2.84</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CI2" t="n">
         <v>1.96</v>
@@ -1643,34 +1643,34 @@
         <v>1.49</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CM2" t="n">
         <v>2.47</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CO2" t="n">
         <v>1.32</v>
       </c>
       <c r="CP2" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.46</v>
+        <v>3.44</v>
       </c>
       <c r="CR2" t="n">
         <v>1.38</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="CT2" t="n">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CV2" t="n">
         <v>2.04</v>
@@ -1685,7 +1685,7 @@
         <v>1.91</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="DA2" t="n">
         <v>1.9</v>
@@ -1694,52 +1694,52 @@
         <v>1.32</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.54</v>
+        <v>3.52</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="DG2" t="n">
         <v>-1</v>
       </c>
       <c r="DH2" t="n">
-        <v>90.18000000000001</v>
+        <v>90.20999999999999</v>
       </c>
       <c r="DI2" t="n">
         <v>0.13</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="DK2" t="n">
-        <v>4.36</v>
+        <v>4.39</v>
       </c>
       <c r="DL2" t="n">
         <v>-1</v>
       </c>
       <c r="DM2" t="n">
-        <v>42.78</v>
+        <v>43.35</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="DO2" t="n">
         <v>-1</v>
       </c>
       <c r="DP2" t="n">
-        <v>12.18</v>
+        <v>12.04</v>
       </c>
       <c r="DQ2" t="n">
-        <v>17.27</v>
+        <v>17.26</v>
       </c>
       <c r="DR2" t="n">
-        <v>7</v>
+        <v>7.13</v>
       </c>
       <c r="DS2" t="n">
         <v>0.13</v>
@@ -1751,28 +1751,28 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>45.96</v>
+        <v>45.83</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.32</v>
+        <v>0.35</v>
       </c>
       <c r="DX2" t="n">
-        <v>12.28</v>
+        <v>12.26</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.539999999999999</v>
+        <v>8.65</v>
       </c>
       <c r="DZ2" t="n">
-        <v>3.73</v>
+        <v>3.61</v>
       </c>
       <c r="EA2" t="n">
-        <v>21.14</v>
+        <v>21.26</v>
       </c>
       <c r="EB2" t="n">
         <v>1.35</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.82</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="3">
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3" t="n">
         <v>12</v>
@@ -1794,82 +1794,82 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="G3" t="n">
         <v>-1</v>
       </c>
       <c r="H3" t="n">
-        <v>101</v>
+        <v>99.45</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="J3" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="K3" t="n">
-        <v>4.1</v>
+        <v>3.82</v>
       </c>
       <c r="L3" t="n">
         <v>-1</v>
       </c>
       <c r="M3" t="n">
-        <v>51.5</v>
+        <v>50.55</v>
       </c>
       <c r="N3" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="O3" t="n">
         <v>-1</v>
       </c>
       <c r="P3" t="n">
-        <v>15.3</v>
+        <v>15.09</v>
       </c>
       <c r="Q3" t="n">
-        <v>15.4</v>
+        <v>15.64</v>
       </c>
       <c r="R3" t="n">
-        <v>7.3</v>
+        <v>7.45</v>
       </c>
       <c r="S3" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="T3" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>47.1</v>
+        <v>46.91</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>11.8</v>
+        <v>11.36</v>
       </c>
       <c r="AA3" t="n">
-        <v>7.3</v>
+        <v>7</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.5</v>
+        <v>4.36</v>
       </c>
       <c r="AC3" t="n">
-        <v>18.9</v>
+        <v>19.18</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AF3" t="n">
         <v>0.08</v>
@@ -1953,31 +1953,31 @@
         <v>2</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="BH3" t="n">
-        <v>8.949999999999999</v>
+        <v>8.83</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="BP3" t="n">
         <v>-1</v>
@@ -1989,28 +1989,28 @@
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BT3" t="n">
-        <v>50</v>
+        <v>52.17</v>
       </c>
       <c r="BU3" t="n">
-        <v>27.27</v>
+        <v>26.09</v>
       </c>
       <c r="BV3" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BW3" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BX3" t="n">
-        <v>68.18000000000001</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="BY3" t="n">
-        <v>3.32</v>
+        <v>3.38</v>
       </c>
       <c r="BZ3" t="n">
-        <v>3.56</v>
+        <v>3.65</v>
       </c>
       <c r="CA3" t="n">
         <v>3.99</v>
@@ -2031,37 +2031,37 @@
         <v>2.55</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.3</v>
+        <v>3.31</v>
       </c>
       <c r="CH3" t="n">
         <v>1.52</v>
       </c>
       <c r="CI3" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="CJ3" t="n">
         <v>1.72</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CL3" t="n">
         <v>1.93</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="CN3" t="n">
         <v>1.93</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="CR3" t="n">
         <v>1.38</v>
@@ -2085,97 +2085,97 @@
         <v>1.54</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="CZ3" t="n">
         <v>2.42</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="DB3" t="n">
         <v>1.24</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="DD3" t="n">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="DE3" t="n">
         <v>0.04</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="DG3" t="n">
         <v>-1</v>
       </c>
       <c r="DH3" t="n">
-        <v>90.54000000000001</v>
+        <v>90.26000000000001</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="DK3" t="n">
-        <v>3.95</v>
+        <v>3.83</v>
       </c>
       <c r="DL3" t="n">
         <v>-1</v>
       </c>
       <c r="DM3" t="n">
-        <v>44.64</v>
+        <v>44.48</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="DO3" t="n">
         <v>-1</v>
       </c>
       <c r="DP3" t="n">
-        <v>14.91</v>
+        <v>14.82</v>
       </c>
       <c r="DQ3" t="n">
-        <v>14.68</v>
+        <v>14.83</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.77</v>
+        <v>7.83</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>43.87</v>
+        <v>43.92</v>
       </c>
       <c r="DW3" t="n">
         <v>0.09</v>
       </c>
       <c r="DX3" t="n">
-        <v>11.18</v>
+        <v>11</v>
       </c>
       <c r="DY3" t="n">
-        <v>7.27</v>
+        <v>7.13</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.91</v>
+        <v>3.87</v>
       </c>
       <c r="EA3" t="n">
-        <v>17.86</v>
+        <v>18.04</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="4">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C4" t="n">
         <v>11</v>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E4" t="n">
         <v>0.36</v>
@@ -2275,112 +2275,112 @@
         <v>2.73</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AH4" t="n">
         <v>-1</v>
       </c>
       <c r="AI4" t="n">
-        <v>93.81999999999999</v>
+        <v>93.67</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AK4" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="AL4" t="n">
-        <v>3.36</v>
+        <v>3.5</v>
       </c>
       <c r="AM4" t="n">
         <v>-1</v>
       </c>
       <c r="AN4" t="n">
-        <v>43</v>
+        <v>43.08</v>
       </c>
       <c r="AO4" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AP4" t="n">
         <v>-1</v>
       </c>
       <c r="AQ4" t="n">
-        <v>19.27</v>
+        <v>19.42</v>
       </c>
       <c r="AR4" t="n">
-        <v>12.82</v>
+        <v>13</v>
       </c>
       <c r="AS4" t="n">
-        <v>7.91</v>
+        <v>8</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.45</v>
+        <v>0.58</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>47.36</v>
+        <v>48.08</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="BA4" t="n">
-        <v>11.91</v>
+        <v>12</v>
       </c>
       <c r="BB4" t="n">
-        <v>7.82</v>
+        <v>7.92</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.09</v>
+        <v>4.08</v>
       </c>
       <c r="BD4" t="n">
-        <v>20.82</v>
+        <v>20.67</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="BF4" t="n">
-        <v>3.36</v>
+        <v>3.17</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="BH4" t="n">
-        <v>8</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.36</v>
+        <v>0.39</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.55</v>
+        <v>0.61</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.41</v>
+        <v>0.43</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.95</v>
+        <v>1.04</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BP4" t="n">
         <v>-1</v>
@@ -2389,25 +2389,25 @@
         <v>-1</v>
       </c>
       <c r="BR4" t="n">
-        <v>81.81999999999999</v>
+        <v>82.61</v>
       </c>
       <c r="BS4" t="n">
-        <v>63.64</v>
+        <v>65.22</v>
       </c>
       <c r="BT4" t="n">
-        <v>18.18</v>
+        <v>21.74</v>
       </c>
       <c r="BU4" t="n">
-        <v>9.09</v>
+        <v>13.04</v>
       </c>
       <c r="BV4" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>27.27</v>
+        <v>30.43</v>
       </c>
       <c r="BY4" t="n">
         <v>2.36</v>
@@ -2416,55 +2416,55 @@
         <v>2.53</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.44</v>
+        <v>3.42</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.55</v>
+        <v>3.53</v>
       </c>
       <c r="CC4" t="n">
-        <v>3.61</v>
+        <v>3.5</v>
       </c>
       <c r="CD4" t="n">
-        <v>3.9</v>
+        <v>3.76</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CF4" t="n">
-        <v>3.08</v>
+        <v>3.13</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="CH4" t="n">
         <v>1.27</v>
       </c>
       <c r="CI4" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="CN4" t="n">
         <v>1.77</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.17</v>
+        <v>2.22</v>
       </c>
       <c r="CQ4" t="n">
-        <v>4.01</v>
+        <v>4.11</v>
       </c>
       <c r="CR4" t="n">
         <v>1.47</v>
@@ -2488,13 +2488,13 @@
         <v>1.65</v>
       </c>
       <c r="CY4" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="DB4" t="n">
         <v>1.43</v>
@@ -2506,79 +2506,79 @@
         <v>4.43</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="DG4" t="n">
         <v>-1</v>
       </c>
       <c r="DH4" t="n">
-        <v>89.5</v>
+        <v>89.61</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DJ4" t="n">
-        <v>3.18</v>
+        <v>3.09</v>
       </c>
       <c r="DK4" t="n">
-        <v>3.32</v>
+        <v>3.39</v>
       </c>
       <c r="DL4" t="n">
         <v>-1</v>
       </c>
       <c r="DM4" t="n">
-        <v>44.5</v>
+        <v>44.48</v>
       </c>
       <c r="DN4" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="DO4" t="n">
         <v>-1</v>
       </c>
       <c r="DP4" t="n">
-        <v>19.36</v>
+        <v>19.43</v>
       </c>
       <c r="DQ4" t="n">
-        <v>12.78</v>
+        <v>12.87</v>
       </c>
       <c r="DR4" t="n">
-        <v>7.45</v>
+        <v>7.52</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>45.46</v>
+        <v>45.91</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX4" t="n">
-        <v>12.54</v>
+        <v>12.56</v>
       </c>
       <c r="DY4" t="n">
-        <v>8.32</v>
+        <v>8.35</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.22</v>
+        <v>4.21</v>
       </c>
       <c r="EA4" t="n">
-        <v>21.18</v>
+        <v>21.09</v>
       </c>
       <c r="EB4" t="n">
         <v>1.41</v>
       </c>
       <c r="EC4" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
     </row>
     <row r="5">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C5" t="n">
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E5" t="n">
         <v>0.27</v>
@@ -2678,112 +2678,112 @@
         <v>1.55</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AH5" t="n">
         <v>-1</v>
       </c>
       <c r="AI5" t="n">
-        <v>98.91</v>
+        <v>97.58</v>
       </c>
       <c r="AJ5" t="n">
         <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="AL5" t="n">
-        <v>5.64</v>
+        <v>5.58</v>
       </c>
       <c r="AM5" t="n">
         <v>-1</v>
       </c>
       <c r="AN5" t="n">
-        <v>46.27</v>
+        <v>46.92</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AP5" t="n">
         <v>-1</v>
       </c>
       <c r="AQ5" t="n">
-        <v>12.55</v>
+        <v>13</v>
       </c>
       <c r="AR5" t="n">
-        <v>14.55</v>
+        <v>14.67</v>
       </c>
       <c r="AS5" t="n">
-        <v>9.73</v>
+        <v>9.58</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>54.18</v>
+        <v>54.25</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="BA5" t="n">
-        <v>13</v>
+        <v>13.25</v>
       </c>
       <c r="BB5" t="n">
-        <v>8.91</v>
+        <v>9.25</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.09</v>
+        <v>4</v>
       </c>
       <c r="BD5" t="n">
-        <v>22.09</v>
+        <v>21.83</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="BF5" t="n">
         <v>2</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="BH5" t="n">
-        <v>11.23</v>
+        <v>11</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.36</v>
+        <v>0.39</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="BP5" t="n">
         <v>-1</v>
@@ -2792,25 +2792,25 @@
         <v>-1</v>
       </c>
       <c r="BR5" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS5" t="n">
-        <v>63.64</v>
+        <v>65.22</v>
       </c>
       <c r="BT5" t="n">
-        <v>45.45</v>
+        <v>47.83</v>
       </c>
       <c r="BU5" t="n">
-        <v>36.36</v>
+        <v>34.78</v>
       </c>
       <c r="BV5" t="n">
-        <v>18.18</v>
+        <v>17.39</v>
       </c>
       <c r="BW5" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX5" t="n">
-        <v>50</v>
+        <v>52.17</v>
       </c>
       <c r="BY5" t="n">
         <v>1.86</v>
@@ -2819,55 +2819,55 @@
         <v>1.92</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.69</v>
+        <v>3.7</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.8</v>
+        <v>3.82</v>
       </c>
       <c r="CC5" t="n">
-        <v>2.89</v>
+        <v>2.79</v>
       </c>
       <c r="CD5" t="n">
-        <v>3.11</v>
+        <v>2.99</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.81</v>
+        <v>2.79</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CO5" t="n">
         <v>1.28</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.28</v>
+        <v>3.24</v>
       </c>
       <c r="CR5" t="n">
         <v>1.42</v>
@@ -2891,34 +2891,34 @@
         <v>1.56</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="CZ5" t="n">
         <v>2.39</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.42</v>
+        <v>3.36</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.14</v>
+        <v>0.17</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="DG5" t="n">
         <v>-1</v>
       </c>
       <c r="DH5" t="n">
-        <v>102</v>
+        <v>101.17</v>
       </c>
       <c r="DI5" t="n">
         <v>0</v>
@@ -2927,28 +2927,28 @@
         <v>2.04</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.45</v>
+        <v>5.43</v>
       </c>
       <c r="DL5" t="n">
         <v>-1</v>
       </c>
       <c r="DM5" t="n">
-        <v>49.32</v>
+        <v>49.52</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="DO5" t="n">
         <v>-1</v>
       </c>
       <c r="DP5" t="n">
-        <v>11.73</v>
+        <v>12</v>
       </c>
       <c r="DQ5" t="n">
         <v>15.91</v>
       </c>
       <c r="DR5" t="n">
-        <v>9.039999999999999</v>
+        <v>9</v>
       </c>
       <c r="DS5" t="n">
         <v>0.22</v>
@@ -2960,25 +2960,25 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>56.36</v>
+        <v>56.31</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DX5" t="n">
-        <v>13.82</v>
+        <v>13.91</v>
       </c>
       <c r="DY5" t="n">
-        <v>9.23</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="DZ5" t="n">
-        <v>4.59</v>
+        <v>4.52</v>
       </c>
       <c r="EA5" t="n">
-        <v>21.41</v>
+        <v>21.3</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="EC5" t="n">
         <v>1.78</v>
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D6" t="n">
         <v>11</v>
@@ -3003,82 +3003,82 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="G6" t="n">
         <v>-1</v>
       </c>
       <c r="H6" t="n">
-        <v>99.55</v>
+        <v>99.75</v>
       </c>
       <c r="I6" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="K6" t="n">
-        <v>5.55</v>
+        <v>5.33</v>
       </c>
       <c r="L6" t="n">
         <v>-1</v>
       </c>
       <c r="M6" t="n">
-        <v>52.45</v>
+        <v>52</v>
       </c>
       <c r="N6" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="O6" t="n">
         <v>-1</v>
       </c>
       <c r="P6" t="n">
-        <v>12.73</v>
+        <v>12.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>16.91</v>
+        <v>17.17</v>
       </c>
       <c r="R6" t="n">
-        <v>5.09</v>
+        <v>5.25</v>
       </c>
       <c r="S6" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="T6" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="U6" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="V6" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>56.36</v>
+        <v>57</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>16.18</v>
+        <v>16.33</v>
       </c>
       <c r="AA6" t="n">
-        <v>10.73</v>
+        <v>10.92</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.45</v>
+        <v>5.42</v>
       </c>
       <c r="AC6" t="n">
-        <v>20.64</v>
+        <v>20.75</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AF6" t="n">
         <v>0.09</v>
@@ -3162,31 +3162,31 @@
         <v>2.55</v>
       </c>
       <c r="BG6" t="n">
-        <v>3.05</v>
+        <v>3.17</v>
       </c>
       <c r="BH6" t="n">
-        <v>10.05</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.05</v>
+        <v>3.17</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.64</v>
+        <v>0.7</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="BL6" t="n">
         <v>0.91</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.64</v>
+        <v>0.7</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="BP6" t="n">
         <v>-1</v>
@@ -3195,37 +3195,37 @@
         <v>-1</v>
       </c>
       <c r="BR6" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS6" t="n">
-        <v>77.27</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="BT6" t="n">
-        <v>63.64</v>
+        <v>65.22</v>
       </c>
       <c r="BU6" t="n">
-        <v>40.91</v>
+        <v>43.48</v>
       </c>
       <c r="BV6" t="n">
-        <v>13.64</v>
+        <v>17.39</v>
       </c>
       <c r="BW6" t="n">
-        <v>4.55</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BX6" t="n">
-        <v>63.64</v>
+        <v>65.22</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="BZ6" t="n">
-        <v>2.01</v>
+        <v>1.96</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.79</v>
+        <v>3.82</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.98</v>
+        <v>4.03</v>
       </c>
       <c r="CC6" t="n">
         <v>2.68</v>
@@ -3234,19 +3234,19 @@
         <v>2.72</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.27</v>
+        <v>3.28</v>
       </c>
       <c r="CH6" t="n">
         <v>1.5</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CJ6" t="n">
         <v>1.69</v>
@@ -3255,22 +3255,22 @@
         <v>1.45</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CO6" t="n">
         <v>1.23</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="CR6" t="n">
         <v>1.36</v>
@@ -3294,34 +3294,34 @@
         <v>1.54</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="CZ6" t="n">
         <v>2.43</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.03</v>
+        <v>2.99</v>
       </c>
       <c r="DE6" t="n">
         <v>0.04</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="DG6" t="n">
         <v>-1</v>
       </c>
       <c r="DH6" t="n">
-        <v>95.28</v>
+        <v>95.56999999999999</v>
       </c>
       <c r="DI6" t="n">
         <v>0.04</v>
@@ -3330,13 +3330,13 @@
         <v>2</v>
       </c>
       <c r="DK6" t="n">
-        <v>5.41</v>
+        <v>5.3</v>
       </c>
       <c r="DL6" t="n">
         <v>-1</v>
       </c>
       <c r="DM6" t="n">
-        <v>50.72</v>
+        <v>50.57</v>
       </c>
       <c r="DN6" t="n">
         <v>0.91</v>
@@ -3345,13 +3345,13 @@
         <v>-1</v>
       </c>
       <c r="DP6" t="n">
-        <v>13.64</v>
+        <v>13.35</v>
       </c>
       <c r="DQ6" t="n">
-        <v>16.13</v>
+        <v>16.3</v>
       </c>
       <c r="DR6" t="n">
-        <v>5.72</v>
+        <v>5.78</v>
       </c>
       <c r="DS6" t="n">
         <v>0.13</v>
@@ -3363,28 +3363,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>54.14</v>
+        <v>54.57</v>
       </c>
       <c r="DW6" t="n">
         <v>0.04</v>
       </c>
       <c r="DX6" t="n">
-        <v>15.81</v>
+        <v>15.91</v>
       </c>
       <c r="DY6" t="n">
-        <v>11.18</v>
+        <v>11.26</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.64</v>
+        <v>4.65</v>
       </c>
       <c r="EA6" t="n">
-        <v>20.64</v>
+        <v>20.7</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="EC6" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="7">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C8" t="n">
         <v>12</v>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E8" t="n">
         <v>0.17</v>
@@ -3887,112 +3887,112 @@
         <v>2.42</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AH8" t="n">
         <v>-1</v>
       </c>
       <c r="AI8" t="n">
-        <v>90.3</v>
+        <v>91</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AL8" t="n">
-        <v>4.6</v>
+        <v>4.55</v>
       </c>
       <c r="AM8" t="n">
         <v>-1</v>
       </c>
       <c r="AN8" t="n">
-        <v>39.7</v>
+        <v>39.64</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AP8" t="n">
         <v>-1</v>
       </c>
       <c r="AQ8" t="n">
-        <v>14.1</v>
+        <v>14</v>
       </c>
       <c r="AR8" t="n">
-        <v>19.5</v>
+        <v>18.73</v>
       </c>
       <c r="AS8" t="n">
-        <v>7.9</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>58.3</v>
+        <v>58.18</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="BA8" t="n">
-        <v>13.7</v>
+        <v>13.45</v>
       </c>
       <c r="BB8" t="n">
-        <v>8.800000000000001</v>
+        <v>8.82</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.9</v>
+        <v>4.64</v>
       </c>
       <c r="BD8" t="n">
-        <v>20.6</v>
+        <v>19.91</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="BH8" t="n">
         <v>8.91</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="BP8" t="n">
         <v>-1</v>
@@ -4001,25 +4001,25 @@
         <v>-1</v>
       </c>
       <c r="BR8" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS8" t="n">
-        <v>81.81999999999999</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="BT8" t="n">
-        <v>54.55</v>
+        <v>52.17</v>
       </c>
       <c r="BU8" t="n">
-        <v>22.73</v>
+        <v>21.74</v>
       </c>
       <c r="BV8" t="n">
-        <v>22.73</v>
+        <v>21.74</v>
       </c>
       <c r="BW8" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BX8" t="n">
-        <v>50</v>
+        <v>47.83</v>
       </c>
       <c r="BY8" t="n">
         <v>1.68</v>
@@ -4028,13 +4028,13 @@
         <v>1.67</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.97</v>
+        <v>3.95</v>
       </c>
       <c r="CB8" t="n">
-        <v>4.25</v>
+        <v>4.23</v>
       </c>
       <c r="CC8" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CD8" t="n">
         <v>1.88</v>
@@ -4055,7 +4055,7 @@
         <v>1.93</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CK8" t="n">
         <v>1.51</v>
@@ -4064,7 +4064,7 @@
         <v>2</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="CN8" t="n">
         <v>1.86</v>
@@ -4076,16 +4076,16 @@
         <v>1.89</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="CR8" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="CT8" t="n">
-        <v>3.01</v>
+        <v>3.04</v>
       </c>
       <c r="CU8" t="n">
         <v>1.44</v>
@@ -4106,7 +4106,7 @@
         <v>2.35</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="DB8" t="n">
         <v>1.27</v>
@@ -4118,76 +4118,76 @@
         <v>3.1</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.54</v>
+        <v>1.61</v>
       </c>
       <c r="DG8" t="n">
         <v>-1</v>
       </c>
       <c r="DH8" t="n">
-        <v>93.09</v>
+        <v>93.31</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="DK8" t="n">
-        <v>5.46</v>
+        <v>5.4</v>
       </c>
       <c r="DL8" t="n">
         <v>-1</v>
       </c>
       <c r="DM8" t="n">
-        <v>46</v>
+        <v>45.7</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="DO8" t="n">
         <v>-1</v>
       </c>
       <c r="DP8" t="n">
-        <v>13.87</v>
+        <v>13.83</v>
       </c>
       <c r="DQ8" t="n">
-        <v>17.63</v>
+        <v>17.35</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.09</v>
+        <v>7.39</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>59.36</v>
+        <v>59.26</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="DX8" t="n">
-        <v>16.5</v>
+        <v>16.26</v>
       </c>
       <c r="DY8" t="n">
-        <v>11.32</v>
+        <v>11.22</v>
       </c>
       <c r="DZ8" t="n">
-        <v>5.18</v>
+        <v>5.05</v>
       </c>
       <c r="EA8" t="n">
-        <v>20.73</v>
+        <v>20.39</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="EC8" t="n">
         <v>2.09</v>
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
         <v>10</v>
       </c>
       <c r="D9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E9" t="n">
         <v>0.2</v>
@@ -4293,49 +4293,49 @@
         <v>0.08</v>
       </c>
       <c r="AG9" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AH9" t="n">
         <v>-1</v>
       </c>
       <c r="AI9" t="n">
-        <v>77.67</v>
+        <v>78.31</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.83</v>
+        <v>2.69</v>
       </c>
       <c r="AL9" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AM9" t="n">
         <v>-1</v>
       </c>
       <c r="AN9" t="n">
-        <v>31.42</v>
+        <v>32.46</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AP9" t="n">
         <v>-1</v>
       </c>
       <c r="AQ9" t="n">
-        <v>15.08</v>
+        <v>14.69</v>
       </c>
       <c r="AR9" t="n">
-        <v>13.33</v>
+        <v>13.23</v>
       </c>
       <c r="AS9" t="n">
-        <v>7.92</v>
+        <v>8.31</v>
       </c>
       <c r="AT9" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AV9" t="n">
         <v>0.08</v>
@@ -4347,55 +4347,55 @@
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>46.75</v>
+        <v>46.77</v>
       </c>
       <c r="AZ9" t="n">
         <v>0.08</v>
       </c>
       <c r="BA9" t="n">
-        <v>7.33</v>
+        <v>7.62</v>
       </c>
       <c r="BB9" t="n">
-        <v>5</v>
+        <v>5.08</v>
       </c>
       <c r="BC9" t="n">
-        <v>2.33</v>
+        <v>2.54</v>
       </c>
       <c r="BD9" t="n">
-        <v>18.75</v>
+        <v>18.92</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.86</v>
+        <v>0.9</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="BH9" t="n">
-        <v>8.949999999999999</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.86</v>
+        <v>0.83</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="BL9" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="BP9" t="n">
         <v>-1</v>
@@ -4404,25 +4404,25 @@
         <v>-1</v>
       </c>
       <c r="BR9" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS9" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BT9" t="n">
-        <v>40.91</v>
+        <v>43.48</v>
       </c>
       <c r="BU9" t="n">
-        <v>31.82</v>
+        <v>30.43</v>
       </c>
       <c r="BV9" t="n">
-        <v>18.18</v>
+        <v>17.39</v>
       </c>
       <c r="BW9" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX9" t="n">
-        <v>40.91</v>
+        <v>43.48</v>
       </c>
       <c r="BY9" t="n">
         <v>3.38</v>
@@ -4431,37 +4431,37 @@
         <v>3.66</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.75</v>
+        <v>3.88</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.84</v>
+        <v>3.96</v>
       </c>
       <c r="CC9" t="n">
-        <v>5.4</v>
+        <v>6.06</v>
       </c>
       <c r="CD9" t="n">
-        <v>5.71</v>
+        <v>6.33</v>
       </c>
       <c r="CE9" t="n">
         <v>1.41</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.94</v>
+        <v>2.91</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.92</v>
+        <v>2.95</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CL9" t="n">
         <v>2.09</v>
@@ -4476,10 +4476,10 @@
         <v>1.33</v>
       </c>
       <c r="CP9" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.58</v>
+        <v>3.53</v>
       </c>
       <c r="CR9" t="n">
         <v>1.44</v>
@@ -4500,10 +4500,10 @@
         <v>1.98</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CY9" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CZ9" t="n">
         <v>2.29</v>
@@ -4515,85 +4515,85 @@
         <v>1.36</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.91</v>
+        <v>3.84</v>
       </c>
       <c r="DE9" t="n">
         <v>0.13</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="DG9" t="n">
         <v>-1</v>
       </c>
       <c r="DH9" t="n">
-        <v>80.23</v>
+        <v>80.48</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="DK9" t="n">
-        <v>3.27</v>
+        <v>3.26</v>
       </c>
       <c r="DL9" t="n">
         <v>-1</v>
       </c>
       <c r="DM9" t="n">
-        <v>34.37</v>
+        <v>34.83</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="DO9" t="n">
         <v>-1</v>
       </c>
       <c r="DP9" t="n">
-        <v>14.91</v>
+        <v>14.69</v>
       </c>
       <c r="DQ9" t="n">
-        <v>13.63</v>
+        <v>13.56</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.140000000000001</v>
+        <v>8.35</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>46.36</v>
+        <v>46.39</v>
       </c>
       <c r="DW9" t="n">
         <v>0.09</v>
       </c>
       <c r="DX9" t="n">
-        <v>8.130000000000001</v>
+        <v>8.26</v>
       </c>
       <c r="DY9" t="n">
-        <v>5.64</v>
+        <v>5.65</v>
       </c>
       <c r="DZ9" t="n">
-        <v>2.5</v>
+        <v>2.61</v>
       </c>
       <c r="EA9" t="n">
-        <v>19.64</v>
+        <v>19.69</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.96</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.27</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="10">
@@ -5006,94 +5006,94 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D11" t="n">
         <v>11</v>
       </c>
       <c r="E11" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="F11" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="G11" t="n">
         <v>-1</v>
       </c>
       <c r="H11" t="n">
-        <v>103.45</v>
+        <v>102.83</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>5.09</v>
+        <v>5</v>
       </c>
       <c r="L11" t="n">
         <v>-1</v>
       </c>
       <c r="M11" t="n">
-        <v>50.64</v>
+        <v>49.75</v>
       </c>
       <c r="N11" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="O11" t="n">
         <v>-1</v>
       </c>
       <c r="P11" t="n">
-        <v>13.82</v>
+        <v>13.83</v>
       </c>
       <c r="Q11" t="n">
-        <v>18.82</v>
+        <v>19.08</v>
       </c>
       <c r="R11" t="n">
-        <v>7.18</v>
+        <v>7.08</v>
       </c>
       <c r="S11" t="n">
-        <v>0.64</v>
+        <v>0.75</v>
       </c>
       <c r="T11" t="n">
-        <v>0.82</v>
+        <v>0.92</v>
       </c>
       <c r="U11" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="V11" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>49</v>
+        <v>48.58</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z11" t="n">
-        <v>10.82</v>
+        <v>11</v>
       </c>
       <c r="AA11" t="n">
-        <v>8</v>
+        <v>8.08</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.82</v>
+        <v>2.92</v>
       </c>
       <c r="AC11" t="n">
-        <v>26.27</v>
+        <v>26.25</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE11" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -5177,28 +5177,28 @@
         <v>1.82</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="BH11" t="n">
-        <v>8.949999999999999</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.27</v>
+        <v>0.3</v>
       </c>
       <c r="BN11" t="n">
-        <v>0.77</v>
+        <v>0.87</v>
       </c>
       <c r="BO11" t="n">
         <v>1</v>
@@ -5210,16 +5210,16 @@
         <v>-1</v>
       </c>
       <c r="BR11" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BS11" t="n">
-        <v>59.09</v>
+        <v>60.87</v>
       </c>
       <c r="BT11" t="n">
-        <v>18.18</v>
+        <v>21.74</v>
       </c>
       <c r="BU11" t="n">
-        <v>9.09</v>
+        <v>13.04</v>
       </c>
       <c r="BV11" t="n">
         <v>0</v>
@@ -5228,19 +5228,19 @@
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>27.27</v>
+        <v>30.43</v>
       </c>
       <c r="BY11" t="n">
-        <v>2.91</v>
+        <v>2.96</v>
       </c>
       <c r="BZ11" t="n">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.4</v>
+        <v>3.39</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.46</v>
+        <v>3.45</v>
       </c>
       <c r="CC11" t="n">
         <v>5.01</v>
@@ -5249,43 +5249,43 @@
         <v>5.33</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CF11" t="n">
-        <v>3.42</v>
+        <v>3.45</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CJ11" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="CN11" t="n">
         <v>1.78</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CP11" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="CQ11" t="n">
-        <v>4.38</v>
+        <v>4.47</v>
       </c>
       <c r="CR11" t="n">
         <v>1.5</v>
@@ -5309,13 +5309,13 @@
         <v>1.64</v>
       </c>
       <c r="CY11" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="DB11" t="n">
         <v>1.47</v>
@@ -5330,76 +5330,76 @@
         <v>0.09</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="DG11" t="n">
         <v>-1</v>
       </c>
       <c r="DH11" t="n">
-        <v>105.36</v>
+        <v>104.95</v>
       </c>
       <c r="DI11" t="n">
         <v>0</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.72</v>
+        <v>4.69</v>
       </c>
       <c r="DL11" t="n">
         <v>-1</v>
       </c>
       <c r="DM11" t="n">
-        <v>48.78</v>
+        <v>48.39</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="DO11" t="n">
         <v>-1</v>
       </c>
       <c r="DP11" t="n">
-        <v>13.73</v>
+        <v>13.74</v>
       </c>
       <c r="DQ11" t="n">
-        <v>18.45</v>
+        <v>18.61</v>
       </c>
       <c r="DR11" t="n">
-        <v>6.95</v>
+        <v>6.91</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>48.41</v>
+        <v>48.22</v>
       </c>
       <c r="DW11" t="n">
         <v>0.13</v>
       </c>
       <c r="DX11" t="n">
-        <v>10.09</v>
+        <v>10.22</v>
       </c>
       <c r="DY11" t="n">
-        <v>7.36</v>
+        <v>7.43</v>
       </c>
       <c r="DZ11" t="n">
-        <v>2.73</v>
+        <v>2.79</v>
       </c>
       <c r="EA11" t="n">
-        <v>25.18</v>
+        <v>25.22</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="12">
@@ -5409,10 +5409,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D12" t="n">
         <v>11</v>
@@ -5421,82 +5421,82 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="G12" t="n">
         <v>-1</v>
       </c>
       <c r="H12" t="n">
-        <v>91.36</v>
+        <v>89.67</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="K12" t="n">
-        <v>4.64</v>
+        <v>4.92</v>
       </c>
       <c r="L12" t="n">
         <v>-1</v>
       </c>
       <c r="M12" t="n">
-        <v>46.27</v>
+        <v>44.5</v>
       </c>
       <c r="N12" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="O12" t="n">
         <v>-1</v>
       </c>
       <c r="P12" t="n">
-        <v>15.64</v>
+        <v>15.75</v>
       </c>
       <c r="Q12" t="n">
         <v>15</v>
       </c>
       <c r="R12" t="n">
-        <v>7</v>
+        <v>6.92</v>
       </c>
       <c r="S12" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T12" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="U12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="V12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>47.36</v>
+        <v>47.42</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z12" t="n">
-        <v>13.36</v>
+        <v>12.83</v>
       </c>
       <c r="AA12" t="n">
-        <v>8.359999999999999</v>
+        <v>8.25</v>
       </c>
       <c r="AB12" t="n">
-        <v>5</v>
+        <v>4.58</v>
       </c>
       <c r="AC12" t="n">
-        <v>18.18</v>
+        <v>18.58</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -5580,31 +5580,31 @@
         <v>2.55</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.68</v>
+        <v>9.91</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.32</v>
+        <v>0.35</v>
       </c>
       <c r="BL12" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="BP12" t="n">
         <v>-1</v>
@@ -5613,37 +5613,37 @@
         <v>-1</v>
       </c>
       <c r="BR12" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BS12" t="n">
-        <v>77.27</v>
+        <v>73.91</v>
       </c>
       <c r="BT12" t="n">
-        <v>54.55</v>
+        <v>52.17</v>
       </c>
       <c r="BU12" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BV12" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>31.82</v>
+        <v>30.43</v>
       </c>
       <c r="BY12" t="n">
-        <v>3.9</v>
+        <v>3.84</v>
       </c>
       <c r="BZ12" t="n">
-        <v>4.15</v>
+        <v>4.07</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.97</v>
+        <v>3.93</v>
       </c>
       <c r="CB12" t="n">
-        <v>4.29</v>
+        <v>4.24</v>
       </c>
       <c r="CC12" t="n">
         <v>7.17</v>
@@ -5655,10 +5655,10 @@
         <v>1.33</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.72</v>
+        <v>2.75</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="CH12" t="n">
         <v>1.37</v>
@@ -5670,25 +5670,25 @@
         <v>1.83</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="CN12" t="n">
         <v>1.8</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.16</v>
+        <v>3.21</v>
       </c>
       <c r="CR12" t="n">
         <v>1.46</v>
@@ -5724,85 +5724,85 @@
         <v>1.34</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.64</v>
+        <v>3.7</v>
       </c>
       <c r="DE12" t="n">
         <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="DG12" t="n">
         <v>-1</v>
       </c>
       <c r="DH12" t="n">
-        <v>83.86</v>
+        <v>83.3</v>
       </c>
       <c r="DI12" t="n">
         <v>0</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.59</v>
+        <v>2.57</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.36</v>
+        <v>4.52</v>
       </c>
       <c r="DL12" t="n">
         <v>-1</v>
       </c>
       <c r="DM12" t="n">
-        <v>39.54</v>
+        <v>38.91</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DO12" t="n">
         <v>-1</v>
       </c>
       <c r="DP12" t="n">
-        <v>16.41</v>
+        <v>16.43</v>
       </c>
       <c r="DQ12" t="n">
-        <v>14.72</v>
+        <v>14.74</v>
       </c>
       <c r="DR12" t="n">
-        <v>7.91</v>
+        <v>7.83</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>43.46</v>
+        <v>43.66</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX12" t="n">
-        <v>12</v>
+        <v>11.78</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.77</v>
+        <v>7.74</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.23</v>
+        <v>4.04</v>
       </c>
       <c r="EA12" t="n">
-        <v>18.22</v>
+        <v>18.43</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="13">
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C13" t="n">
         <v>12</v>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E13" t="n">
         <v>0.17</v>
@@ -5905,109 +5905,109 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AH13" t="n">
         <v>-1</v>
       </c>
       <c r="AI13" t="n">
-        <v>88.40000000000001</v>
+        <v>87.81999999999999</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
       </c>
       <c r="AK13" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>5.36</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>44.27</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>13.73</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>15.18</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>8.359999999999999</v>
+      </c>
+      <c r="AT13" t="n">
         <v>2</v>
       </c>
-      <c r="AL13" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>44.2</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AU13" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AX13" t="n">
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>48.4</v>
+        <v>47.27</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="BA13" t="n">
-        <v>11.3</v>
+        <v>11.18</v>
       </c>
       <c r="BB13" t="n">
-        <v>7.4</v>
+        <v>7.36</v>
       </c>
       <c r="BC13" t="n">
-        <v>3.9</v>
+        <v>3.82</v>
       </c>
       <c r="BD13" t="n">
-        <v>22.9</v>
+        <v>22.55</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.9</v>
+        <v>2.09</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.45</v>
+        <v>2.61</v>
       </c>
       <c r="BH13" t="n">
-        <v>10.09</v>
+        <v>9.83</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.45</v>
+        <v>2.61</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.36</v>
+        <v>0.39</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.64</v>
+        <v>0.7</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.86</v>
+        <v>0.96</v>
       </c>
       <c r="BP13" t="n">
         <v>-1</v>
@@ -6016,25 +6016,25 @@
         <v>-1</v>
       </c>
       <c r="BR13" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BS13" t="n">
-        <v>63.64</v>
+        <v>65.22</v>
       </c>
       <c r="BT13" t="n">
-        <v>40.91</v>
+        <v>43.48</v>
       </c>
       <c r="BU13" t="n">
-        <v>31.82</v>
+        <v>34.78</v>
       </c>
       <c r="BV13" t="n">
-        <v>9.09</v>
+        <v>13.04</v>
       </c>
       <c r="BW13" t="n">
-        <v>4.55</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BX13" t="n">
-        <v>50</v>
+        <v>52.17</v>
       </c>
       <c r="BY13" t="n">
         <v>3.86</v>
@@ -6043,25 +6043,25 @@
         <v>4.41</v>
       </c>
       <c r="CA13" t="n">
-        <v>4.04</v>
+        <v>4.06</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.28</v>
+        <v>4.31</v>
       </c>
       <c r="CC13" t="n">
-        <v>5.98</v>
+        <v>5.93</v>
       </c>
       <c r="CD13" t="n">
         <v>6.31</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.65</v>
+        <v>2.64</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.16</v>
+        <v>3.18</v>
       </c>
       <c r="CH13" t="n">
         <v>1.5</v>
@@ -6070,28 +6070,28 @@
         <v>2.03</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CK13" t="n">
         <v>1.4</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CM13" t="n">
         <v>2.76</v>
       </c>
       <c r="CN13" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.99</v>
+        <v>2.97</v>
       </c>
       <c r="CR13" t="n">
         <v>1.4</v>
@@ -6115,97 +6115,97 @@
         <v>1.54</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="CZ13" t="n">
         <v>2.43</v>
       </c>
       <c r="DA13" t="n">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="DD13" t="n">
-        <v>3.16</v>
+        <v>3.11</v>
       </c>
       <c r="DE13" t="n">
         <v>0.09</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="DG13" t="n">
         <v>-1</v>
       </c>
       <c r="DH13" t="n">
-        <v>85.23</v>
+        <v>85.09</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.27</v>
+        <v>2.35</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.59</v>
+        <v>5.39</v>
       </c>
       <c r="DL13" t="n">
         <v>-1</v>
       </c>
       <c r="DM13" t="n">
-        <v>43.68</v>
+        <v>43.74</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.77</v>
+        <v>0.83</v>
       </c>
       <c r="DO13" t="n">
         <v>-1</v>
       </c>
       <c r="DP13" t="n">
-        <v>14.95</v>
+        <v>15.04</v>
       </c>
       <c r="DQ13" t="n">
-        <v>16.09</v>
+        <v>15.65</v>
       </c>
       <c r="DR13" t="n">
-        <v>8.050000000000001</v>
+        <v>8</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>48.55</v>
+        <v>48</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DX13" t="n">
-        <v>12.13</v>
+        <v>12.04</v>
       </c>
       <c r="DY13" t="n">
-        <v>8.27</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="DZ13" t="n">
-        <v>3.86</v>
+        <v>3.83</v>
       </c>
       <c r="EA13" t="n">
-        <v>21.27</v>
+        <v>21.18</v>
       </c>
       <c r="EB13" t="n">
         <v>1.35</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="14">
@@ -6215,13 +6215,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C14" t="n">
         <v>11</v>
       </c>
       <c r="D14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E14" t="n">
         <v>0.09</v>
@@ -6308,109 +6308,109 @@
         <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AH14" t="n">
         <v>-1</v>
       </c>
       <c r="AI14" t="n">
-        <v>88</v>
+        <v>89.33</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="AL14" t="n">
-        <v>3.91</v>
+        <v>4.17</v>
       </c>
       <c r="AM14" t="n">
         <v>-1</v>
       </c>
       <c r="AN14" t="n">
-        <v>45.64</v>
+        <v>46.75</v>
       </c>
       <c r="AO14" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AP14" t="n">
         <v>-1</v>
       </c>
       <c r="AQ14" t="n">
-        <v>15.36</v>
+        <v>15.25</v>
       </c>
       <c r="AR14" t="n">
-        <v>17.45</v>
+        <v>17.67</v>
       </c>
       <c r="AS14" t="n">
-        <v>6.82</v>
+        <v>6.83</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AX14" t="n">
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>46.73</v>
+        <v>47.17</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="BA14" t="n">
-        <v>11.82</v>
+        <v>11.67</v>
       </c>
       <c r="BB14" t="n">
-        <v>7.73</v>
+        <v>7.67</v>
       </c>
       <c r="BC14" t="n">
-        <v>4.09</v>
+        <v>4</v>
       </c>
       <c r="BD14" t="n">
-        <v>21.73</v>
+        <v>21.92</v>
       </c>
       <c r="BE14" t="n">
         <v>1.36</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="BH14" t="n">
-        <v>7.86</v>
+        <v>8.17</v>
       </c>
       <c r="BI14" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.41</v>
+        <v>0.43</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BP14" t="n">
         <v>-1</v>
@@ -6419,25 +6419,25 @@
         <v>-1</v>
       </c>
       <c r="BR14" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BS14" t="n">
-        <v>50</v>
+        <v>47.83</v>
       </c>
       <c r="BT14" t="n">
-        <v>22.73</v>
+        <v>21.74</v>
       </c>
       <c r="BU14" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BV14" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BW14" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX14" t="n">
-        <v>40.91</v>
+        <v>39.13</v>
       </c>
       <c r="BY14" t="n">
         <v>2.43</v>
@@ -6446,31 +6446,31 @@
         <v>2.5</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.56</v>
+        <v>3.53</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.64</v>
+        <v>3.62</v>
       </c>
       <c r="CC14" t="n">
-        <v>4.18</v>
+        <v>4.03</v>
       </c>
       <c r="CD14" t="n">
-        <v>4.29</v>
+        <v>4.13</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.93</v>
+        <v>2.91</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CJ14" t="n">
         <v>1.85</v>
@@ -6479,22 +6479,22 @@
         <v>1.58</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CO14" t="n">
         <v>1.32</v>
       </c>
       <c r="CP14" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.5</v>
+        <v>3.53</v>
       </c>
       <c r="CR14" t="n">
         <v>1.37</v>
@@ -6530,52 +6530,52 @@
         <v>1.35</v>
       </c>
       <c r="DC14" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.7</v>
+        <v>3.76</v>
       </c>
       <c r="DE14" t="n">
         <v>0.04</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="DG14" t="n">
         <v>-1</v>
       </c>
       <c r="DH14" t="n">
-        <v>93.54000000000001</v>
+        <v>94</v>
       </c>
       <c r="DI14" t="n">
         <v>0.13</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="DK14" t="n">
-        <v>4.18</v>
+        <v>4.3</v>
       </c>
       <c r="DL14" t="n">
         <v>-1</v>
       </c>
       <c r="DM14" t="n">
-        <v>50.04</v>
+        <v>50.43</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="DO14" t="n">
         <v>-1</v>
       </c>
       <c r="DP14" t="n">
-        <v>14.59</v>
+        <v>14.57</v>
       </c>
       <c r="DQ14" t="n">
-        <v>17.45</v>
+        <v>17.56</v>
       </c>
       <c r="DR14" t="n">
-        <v>6.45</v>
+        <v>6.48</v>
       </c>
       <c r="DS14" t="n">
         <v>0.13</v>
@@ -6587,28 +6587,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>48.86</v>
+        <v>49</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="DX14" t="n">
-        <v>12.78</v>
+        <v>12.66</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.82</v>
+        <v>8.74</v>
       </c>
       <c r="DZ14" t="n">
-        <v>3.95</v>
+        <v>3.91</v>
       </c>
       <c r="EA14" t="n">
-        <v>21.41</v>
+        <v>21.52</v>
       </c>
       <c r="EB14" t="n">
         <v>1.44</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="15">
@@ -7424,94 +7424,94 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D17" t="n">
         <v>11</v>
       </c>
       <c r="E17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F17" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="G17" t="n">
         <v>-1</v>
       </c>
       <c r="H17" t="n">
-        <v>92.09</v>
+        <v>91.92</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="K17" t="n">
-        <v>5.64</v>
+        <v>5.67</v>
       </c>
       <c r="L17" t="n">
         <v>-1</v>
       </c>
       <c r="M17" t="n">
-        <v>49.18</v>
+        <v>49.5</v>
       </c>
       <c r="N17" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="O17" t="n">
         <v>-1</v>
       </c>
       <c r="P17" t="n">
-        <v>9.09</v>
+        <v>9.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>18.36</v>
+        <v>17.83</v>
       </c>
       <c r="R17" t="n">
-        <v>5.27</v>
+        <v>5.33</v>
       </c>
       <c r="S17" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="T17" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="U17" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="V17" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>60.55</v>
+        <v>59.92</v>
       </c>
       <c r="Y17" t="n">
         <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>14.64</v>
+        <v>14.75</v>
       </c>
       <c r="AA17" t="n">
-        <v>8.640000000000001</v>
+        <v>8.83</v>
       </c>
       <c r="AB17" t="n">
-        <v>6</v>
+        <v>5.92</v>
       </c>
       <c r="AC17" t="n">
-        <v>19.27</v>
+        <v>19.58</v>
       </c>
       <c r="AD17" t="n">
         <v>1.7</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -7595,31 +7595,31 @@
         <v>1.27</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.41</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.91</v>
+        <v>0.96</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="BP17" t="n">
         <v>-1</v>
@@ -7628,37 +7628,37 @@
         <v>-1</v>
       </c>
       <c r="BR17" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS17" t="n">
-        <v>81.81999999999999</v>
+        <v>82.61</v>
       </c>
       <c r="BT17" t="n">
-        <v>40.91</v>
+        <v>43.48</v>
       </c>
       <c r="BU17" t="n">
-        <v>22.73</v>
+        <v>21.74</v>
       </c>
       <c r="BV17" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BW17" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX17" t="n">
-        <v>45.45</v>
+        <v>47.83</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="BZ17" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="CA17" t="n">
-        <v>4.61</v>
+        <v>4.7</v>
       </c>
       <c r="CB17" t="n">
-        <v>4.89</v>
+        <v>4.97</v>
       </c>
       <c r="CC17" t="n">
         <v>1.74</v>
@@ -7667,43 +7667,43 @@
         <v>1.8</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="CG17" t="n">
-        <v>3.14</v>
+        <v>3.16</v>
       </c>
       <c r="CH17" t="n">
         <v>1.48</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CJ17" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CK17" t="n">
         <v>1.48</v>
       </c>
       <c r="CL17" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="CN17" t="n">
         <v>1.93</v>
       </c>
       <c r="CO17" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3.05</v>
+        <v>3.03</v>
       </c>
       <c r="CR17" t="n">
         <v>1.41</v>
@@ -7727,7 +7727,7 @@
         <v>1.56</v>
       </c>
       <c r="CY17" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CZ17" t="n">
         <v>2.39</v>
@@ -7736,88 +7736,88 @@
         <v>1.9</v>
       </c>
       <c r="DB17" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.14</v>
+        <v>3.11</v>
       </c>
       <c r="DE17" t="n">
         <v>0.04</v>
       </c>
       <c r="DF17" t="n">
-        <v>0.87</v>
+        <v>0.91</v>
       </c>
       <c r="DG17" t="n">
         <v>-1</v>
       </c>
       <c r="DH17" t="n">
-        <v>92.54000000000001</v>
+        <v>92.44</v>
       </c>
       <c r="DI17" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ17" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.68</v>
+        <v>5.7</v>
       </c>
       <c r="DL17" t="n">
         <v>-1</v>
       </c>
       <c r="DM17" t="n">
-        <v>50.09</v>
+        <v>50.22</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="DO17" t="n">
         <v>-1</v>
       </c>
       <c r="DP17" t="n">
-        <v>9.27</v>
+        <v>9.48</v>
       </c>
       <c r="DQ17" t="n">
-        <v>20.09</v>
+        <v>19.74</v>
       </c>
       <c r="DR17" t="n">
         <v>6.09</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>60.41</v>
+        <v>60.09</v>
       </c>
       <c r="DW17" t="n">
         <v>0.04</v>
       </c>
       <c r="DX17" t="n">
-        <v>13</v>
+        <v>13.13</v>
       </c>
       <c r="DY17" t="n">
-        <v>7.86</v>
+        <v>8</v>
       </c>
       <c r="DZ17" t="n">
-        <v>5.14</v>
+        <v>5.13</v>
       </c>
       <c r="EA17" t="n">
-        <v>19.27</v>
+        <v>19.43</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Russian_Premier_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Russian_Premier_League_2025-2026.xlsx
@@ -1848,7 +1848,7 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>46.91</v>
+        <v>46.82</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
@@ -2154,7 +2154,7 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>43.92</v>
+        <v>43.87</v>
       </c>
       <c r="DW3" t="n">
         <v>0.09</v>
@@ -2314,7 +2314,7 @@
         <v>13</v>
       </c>
       <c r="AS4" t="n">
-        <v>8</v>
+        <v>8.08</v>
       </c>
       <c r="AT4" t="n">
         <v>0.58</v>
@@ -2488,22 +2488,22 @@
         <v>1.65</v>
       </c>
       <c r="CY4" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.35</v>
+        <v>2.41</v>
       </c>
       <c r="DD4" t="n">
-        <v>4.43</v>
+        <v>4.55</v>
       </c>
       <c r="DE4" t="n">
         <v>0.26</v>
@@ -2545,7 +2545,7 @@
         <v>12.87</v>
       </c>
       <c r="DR4" t="n">
-        <v>7.52</v>
+        <v>7.56</v>
       </c>
       <c r="DS4" t="n">
         <v>0.21</v>
@@ -2717,7 +2717,7 @@
         <v>14.67</v>
       </c>
       <c r="AS5" t="n">
-        <v>9.58</v>
+        <v>9.67</v>
       </c>
       <c r="AT5" t="n">
         <v>1.17</v>
@@ -2735,7 +2735,7 @@
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>54.25</v>
+        <v>54.33</v>
       </c>
       <c r="AZ5" t="n">
         <v>0.25</v>
@@ -2948,7 +2948,7 @@
         <v>15.91</v>
       </c>
       <c r="DR5" t="n">
-        <v>9</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="DS5" t="n">
         <v>0.22</v>
@@ -2960,7 +2960,7 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>56.31</v>
+        <v>56.35</v>
       </c>
       <c r="DW5" t="n">
         <v>0.17</v>
@@ -3057,7 +3057,7 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>57</v>
+        <v>57.08</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
@@ -3363,7 +3363,7 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>54.57</v>
+        <v>54.61</v>
       </c>
       <c r="DW6" t="n">
         <v>0.04</v>
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D7" t="n">
         <v>11</v>
@@ -3406,82 +3406,82 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="G7" t="n">
         <v>-1</v>
       </c>
       <c r="H7" t="n">
-        <v>77.55</v>
+        <v>80</v>
       </c>
       <c r="I7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J7" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="K7" t="n">
-        <v>4.27</v>
+        <v>4.42</v>
       </c>
       <c r="L7" t="n">
         <v>-1</v>
       </c>
       <c r="M7" t="n">
-        <v>36.64</v>
+        <v>38</v>
       </c>
       <c r="N7" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="O7" t="n">
         <v>-1</v>
       </c>
       <c r="P7" t="n">
-        <v>13.73</v>
+        <v>13.83</v>
       </c>
       <c r="Q7" t="n">
-        <v>14.36</v>
+        <v>14.75</v>
       </c>
       <c r="R7" t="n">
-        <v>8.73</v>
+        <v>8.42</v>
       </c>
       <c r="S7" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="T7" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="U7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="V7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>44.91</v>
+        <v>45.5</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>8.18</v>
+        <v>8.75</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.64</v>
+        <v>6.08</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.55</v>
+        <v>2.67</v>
       </c>
       <c r="AC7" t="n">
-        <v>17.36</v>
+        <v>17.42</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.97</v>
+        <v>1.02</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -3565,31 +3565,31 @@
         <v>2.18</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.27</v>
+        <v>3.17</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.359999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.27</v>
+        <v>3.17</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BL7" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="BN7" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="BP7" t="n">
         <v>-1</v>
@@ -3598,37 +3598,37 @@
         <v>-1</v>
       </c>
       <c r="BR7" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BS7" t="n">
-        <v>86.36</v>
+        <v>82.61</v>
       </c>
       <c r="BT7" t="n">
-        <v>72.73</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="BU7" t="n">
-        <v>40.91</v>
+        <v>39.13</v>
       </c>
       <c r="BV7" t="n">
-        <v>22.73</v>
+        <v>21.74</v>
       </c>
       <c r="BW7" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BX7" t="n">
-        <v>59.09</v>
+        <v>56.52</v>
       </c>
       <c r="BY7" t="n">
-        <v>4.69</v>
+        <v>4.62</v>
       </c>
       <c r="BZ7" t="n">
-        <v>4.92</v>
+        <v>4.85</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.74</v>
+        <v>3.71</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.99</v>
+        <v>3.96</v>
       </c>
       <c r="CC7" t="n">
         <v>5.14</v>
@@ -3640,49 +3640,49 @@
         <v>1.41</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.93</v>
+        <v>2.96</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.97</v>
+        <v>2.94</v>
       </c>
       <c r="CH7" t="n">
         <v>1.41</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CL7" t="n">
         <v>2.01</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.43</v>
+        <v>3.49</v>
       </c>
       <c r="CR7" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CS7" t="n">
         <v>2.96</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="CU7" t="n">
         <v>1.41</v>
@@ -3718,76 +3718,76 @@
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="DG7" t="n">
         <v>-1</v>
       </c>
       <c r="DH7" t="n">
-        <v>80.55</v>
+        <v>81.7</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="DK7" t="n">
-        <v>3.27</v>
+        <v>3.39</v>
       </c>
       <c r="DL7" t="n">
         <v>-1</v>
       </c>
       <c r="DM7" t="n">
-        <v>34.78</v>
+        <v>35.57</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="DO7" t="n">
         <v>-1</v>
       </c>
       <c r="DP7" t="n">
-        <v>14.54</v>
+        <v>14.56</v>
       </c>
       <c r="DQ7" t="n">
-        <v>14.68</v>
+        <v>14.87</v>
       </c>
       <c r="DR7" t="n">
-        <v>9</v>
+        <v>8.83</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>46.14</v>
+        <v>46.39</v>
       </c>
       <c r="DW7" t="n">
         <v>0.09</v>
       </c>
       <c r="DX7" t="n">
-        <v>7.82</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="DY7" t="n">
-        <v>5.32</v>
+        <v>5.56</v>
       </c>
       <c r="DZ7" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="EA7" t="n">
-        <v>17.86</v>
+        <v>17.87</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.93</v>
+        <v>0.96</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="8">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C10" t="n">
         <v>11</v>
       </c>
       <c r="D10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E10" t="n">
         <v>0.27</v>
@@ -4693,112 +4693,112 @@
         <v>2</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="AH10" t="n">
         <v>-1</v>
       </c>
       <c r="AI10" t="n">
-        <v>94.45</v>
+        <v>92.92</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.64</v>
+        <v>2.83</v>
       </c>
       <c r="AL10" t="n">
-        <v>4.09</v>
+        <v>4</v>
       </c>
       <c r="AM10" t="n">
         <v>-1</v>
       </c>
       <c r="AN10" t="n">
-        <v>46.18</v>
+        <v>44.83</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AP10" t="n">
         <v>-1</v>
       </c>
       <c r="AQ10" t="n">
-        <v>14.55</v>
+        <v>14.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>14.91</v>
+        <v>15</v>
       </c>
       <c r="AS10" t="n">
-        <v>7.27</v>
+        <v>7.67</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>51.55</v>
+        <v>50.42</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="BA10" t="n">
-        <v>13</v>
+        <v>12.75</v>
       </c>
       <c r="BB10" t="n">
-        <v>8.09</v>
+        <v>7.92</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.91</v>
+        <v>4.83</v>
       </c>
       <c r="BD10" t="n">
-        <v>17.27</v>
+        <v>17.75</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.45</v>
+        <v>2.58</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.55</v>
+        <v>3.52</v>
       </c>
       <c r="BH10" t="n">
-        <v>8.949999999999999</v>
+        <v>8.83</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.55</v>
+        <v>3.52</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="BL10" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.86</v>
+        <v>0.83</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="BP10" t="n">
         <v>-1</v>
@@ -4810,22 +4810,22 @@
         <v>100</v>
       </c>
       <c r="BS10" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BT10" t="n">
-        <v>63.64</v>
+        <v>65.22</v>
       </c>
       <c r="BU10" t="n">
-        <v>40.91</v>
+        <v>39.13</v>
       </c>
       <c r="BV10" t="n">
-        <v>27.27</v>
+        <v>26.09</v>
       </c>
       <c r="BW10" t="n">
-        <v>22.73</v>
+        <v>21.74</v>
       </c>
       <c r="BX10" t="n">
-        <v>72.73</v>
+        <v>73.91</v>
       </c>
       <c r="BY10" t="n">
         <v>1.92</v>
@@ -4834,16 +4834,16 @@
         <v>2.07</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.7</v>
+        <v>3.69</v>
       </c>
       <c r="CB10" t="n">
         <v>3.88</v>
       </c>
       <c r="CC10" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="CD10" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="CE10" t="n">
         <v>1.24</v>
@@ -4852,19 +4852,19 @@
         <v>2.46</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="CJ10" t="n">
         <v>1.58</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CL10" t="n">
         <v>1.84</v>
@@ -4873,7 +4873,7 @@
         <v>2.22</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CO10" t="n">
         <v>1.13</v>
@@ -4882,13 +4882,13 @@
         <v>1.64</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="CR10" t="n">
         <v>1.37</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.71</v>
+        <v>2.69</v>
       </c>
       <c r="CT10" t="n">
         <v>3.15</v>
@@ -4924,46 +4924,46 @@
         <v>3.06</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.59</v>
+        <v>1.74</v>
       </c>
       <c r="DG10" t="n">
         <v>-1</v>
       </c>
       <c r="DH10" t="n">
-        <v>93.86</v>
+        <v>93.09</v>
       </c>
       <c r="DI10" t="n">
         <v>0.13</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.41</v>
+        <v>2.52</v>
       </c>
       <c r="DK10" t="n">
-        <v>4</v>
+        <v>3.96</v>
       </c>
       <c r="DL10" t="n">
         <v>-1</v>
       </c>
       <c r="DM10" t="n">
-        <v>46.91</v>
+        <v>46.17</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="DO10" t="n">
         <v>-1</v>
       </c>
       <c r="DP10" t="n">
-        <v>15.32</v>
+        <v>15.26</v>
       </c>
       <c r="DQ10" t="n">
-        <v>14.28</v>
+        <v>14.35</v>
       </c>
       <c r="DR10" t="n">
-        <v>6.95</v>
+        <v>7.18</v>
       </c>
       <c r="DS10" t="n">
         <v>0.22</v>
@@ -4975,28 +4975,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>49.73</v>
+        <v>49.22</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="DX10" t="n">
-        <v>14</v>
+        <v>13.83</v>
       </c>
       <c r="DY10" t="n">
-        <v>8.359999999999999</v>
+        <v>8.26</v>
       </c>
       <c r="DZ10" t="n">
-        <v>5.64</v>
+        <v>5.56</v>
       </c>
       <c r="EA10" t="n">
-        <v>18.05</v>
+        <v>18.26</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="11">
@@ -5309,22 +5309,22 @@
         <v>1.64</v>
       </c>
       <c r="CY11" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="DC11" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="DD11" t="n">
-        <v>4.75</v>
+        <v>4.84</v>
       </c>
       <c r="DE11" t="n">
         <v>0.09</v>
@@ -5451,7 +5451,7 @@
         <v>-1</v>
       </c>
       <c r="P12" t="n">
-        <v>15.75</v>
+        <v>15.83</v>
       </c>
       <c r="Q12" t="n">
         <v>15</v>
@@ -5475,25 +5475,25 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>47.42</v>
+        <v>47.5</v>
       </c>
       <c r="Y12" t="n">
         <v>0.08</v>
       </c>
       <c r="Z12" t="n">
-        <v>12.83</v>
+        <v>12.92</v>
       </c>
       <c r="AA12" t="n">
         <v>8.25</v>
       </c>
       <c r="AB12" t="n">
-        <v>4.58</v>
+        <v>4.67</v>
       </c>
       <c r="AC12" t="n">
         <v>18.58</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AE12" t="n">
         <v>2.33</v>
@@ -5694,13 +5694,13 @@
         <v>1.46</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.96</v>
+        <v>3.03</v>
       </c>
       <c r="CT12" t="n">
-        <v>2.82</v>
+        <v>2.79</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="CV12" t="n">
         <v>1.9</v>
@@ -5763,7 +5763,7 @@
         <v>-1</v>
       </c>
       <c r="DP12" t="n">
-        <v>16.43</v>
+        <v>16.48</v>
       </c>
       <c r="DQ12" t="n">
         <v>14.74</v>
@@ -5781,19 +5781,19 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>43.66</v>
+        <v>43.7</v>
       </c>
       <c r="DW12" t="n">
         <v>0.08</v>
       </c>
       <c r="DX12" t="n">
-        <v>11.78</v>
+        <v>11.83</v>
       </c>
       <c r="DY12" t="n">
         <v>7.74</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.04</v>
+        <v>4.09</v>
       </c>
       <c r="EA12" t="n">
         <v>18.43</v>
@@ -5959,7 +5959,7 @@
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>47.27</v>
+        <v>47.18</v>
       </c>
       <c r="AZ13" t="n">
         <v>0.09</v>
@@ -6184,7 +6184,7 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>48</v>
+        <v>47.96</v>
       </c>
       <c r="DW13" t="n">
         <v>0.04</v>
@@ -6362,22 +6362,22 @@
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>47.17</v>
+        <v>47.08</v>
       </c>
       <c r="AZ14" t="n">
         <v>0.17</v>
       </c>
       <c r="BA14" t="n">
-        <v>11.67</v>
+        <v>11.75</v>
       </c>
       <c r="BB14" t="n">
-        <v>7.67</v>
+        <v>7.75</v>
       </c>
       <c r="BC14" t="n">
         <v>4</v>
       </c>
       <c r="BD14" t="n">
-        <v>21.92</v>
+        <v>22</v>
       </c>
       <c r="BE14" t="n">
         <v>1.36</v>
@@ -6497,16 +6497,16 @@
         <v>3.53</v>
       </c>
       <c r="CR14" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.76</v>
+        <v>2.85</v>
       </c>
       <c r="CT14" t="n">
-        <v>3.14</v>
+        <v>3.05</v>
       </c>
       <c r="CU14" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="CV14" t="n">
         <v>1.97</v>
@@ -6587,22 +6587,22 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>49</v>
+        <v>48.95</v>
       </c>
       <c r="DW14" t="n">
         <v>0.26</v>
       </c>
       <c r="DX14" t="n">
-        <v>12.66</v>
+        <v>12.7</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.74</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="DZ14" t="n">
         <v>3.91</v>
       </c>
       <c r="EA14" t="n">
-        <v>21.52</v>
+        <v>21.56</v>
       </c>
       <c r="EB14" t="n">
         <v>1.44</v>
@@ -6618,13 +6618,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C15" t="n">
         <v>11</v>
       </c>
       <c r="D15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -6711,49 +6711,49 @@
         <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AH15" t="n">
         <v>-1</v>
       </c>
       <c r="AI15" t="n">
-        <v>81.18000000000001</v>
+        <v>81.33</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="AL15" t="n">
-        <v>3.73</v>
+        <v>3.5</v>
       </c>
       <c r="AM15" t="n">
         <v>-1</v>
       </c>
       <c r="AN15" t="n">
-        <v>37.18</v>
+        <v>36.83</v>
       </c>
       <c r="AO15" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AP15" t="n">
         <v>-1</v>
       </c>
       <c r="AQ15" t="n">
-        <v>16.82</v>
+        <v>16.92</v>
       </c>
       <c r="AR15" t="n">
-        <v>14.09</v>
+        <v>14.75</v>
       </c>
       <c r="AS15" t="n">
-        <v>8.82</v>
+        <v>8.83</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AV15" t="n">
         <v>0</v>
@@ -6765,55 +6765,55 @@
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>42.36</v>
+        <v>42.83</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>9.82</v>
+        <v>9.5</v>
       </c>
       <c r="BB15" t="n">
-        <v>7.27</v>
+        <v>7.08</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="BD15" t="n">
-        <v>19.36</v>
+        <v>19.5</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="BF15" t="n">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.14</v>
+        <v>2.09</v>
       </c>
       <c r="BH15" t="n">
-        <v>7.68</v>
+        <v>7.65</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.14</v>
+        <v>2.09</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.41</v>
+        <v>0.43</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="BO15" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="BP15" t="n">
         <v>-1</v>
@@ -6822,25 +6822,25 @@
         <v>-1</v>
       </c>
       <c r="BR15" t="n">
-        <v>86.36</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="BS15" t="n">
-        <v>59.09</v>
+        <v>56.52</v>
       </c>
       <c r="BT15" t="n">
-        <v>40.91</v>
+        <v>39.13</v>
       </c>
       <c r="BU15" t="n">
-        <v>18.18</v>
+        <v>17.39</v>
       </c>
       <c r="BV15" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BW15" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX15" t="n">
-        <v>31.82</v>
+        <v>30.43</v>
       </c>
       <c r="BY15" t="n">
         <v>3.01</v>
@@ -6849,34 +6849,34 @@
         <v>3.34</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.4</v>
+        <v>3.39</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.57</v>
+        <v>3.56</v>
       </c>
       <c r="CC15" t="n">
-        <v>4.12</v>
+        <v>3.93</v>
       </c>
       <c r="CD15" t="n">
-        <v>4.53</v>
+        <v>4.32</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CF15" t="n">
-        <v>3.13</v>
+        <v>3.15</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.73</v>
+        <v>2.71</v>
       </c>
       <c r="CH15" t="n">
         <v>1.36</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CK15" t="n">
         <v>1.57</v>
@@ -6885,28 +6885,28 @@
         <v>2.09</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CP15" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.85</v>
+        <v>3.89</v>
       </c>
       <c r="CR15" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="CS15" t="n">
         <v>2.92</v>
       </c>
       <c r="CT15" t="n">
-        <v>3.05</v>
+        <v>2.99</v>
       </c>
       <c r="CU15" t="n">
         <v>1.42</v>
@@ -6942,43 +6942,43 @@
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="DG15" t="n">
         <v>-1</v>
       </c>
       <c r="DH15" t="n">
-        <v>84.91</v>
+        <v>84.83</v>
       </c>
       <c r="DI15" t="n">
         <v>0.09</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="DK15" t="n">
-        <v>3.91</v>
+        <v>3.78</v>
       </c>
       <c r="DL15" t="n">
         <v>-1</v>
       </c>
       <c r="DM15" t="n">
-        <v>37.68</v>
+        <v>37.48</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.86</v>
+        <v>0.83</v>
       </c>
       <c r="DO15" t="n">
         <v>-1</v>
       </c>
       <c r="DP15" t="n">
-        <v>16.14</v>
+        <v>16.22</v>
       </c>
       <c r="DQ15" t="n">
-        <v>15.27</v>
+        <v>15.56</v>
       </c>
       <c r="DR15" t="n">
-        <v>8.279999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="DS15" t="n">
         <v>0.09</v>
@@ -6990,28 +6990,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>41.96</v>
+        <v>42.22</v>
       </c>
       <c r="DW15" t="n">
         <v>0.04</v>
       </c>
       <c r="DX15" t="n">
-        <v>10.04</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="DY15" t="n">
-        <v>7.09</v>
+        <v>7</v>
       </c>
       <c r="DZ15" t="n">
-        <v>2.95</v>
+        <v>2.87</v>
       </c>
       <c r="EA15" t="n">
-        <v>20.09</v>
+        <v>20.13</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="16">
@@ -7021,94 +7021,94 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D16" t="n">
         <v>11</v>
       </c>
       <c r="E16" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F16" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="G16" t="n">
         <v>-1</v>
       </c>
       <c r="H16" t="n">
-        <v>100</v>
+        <v>99.83</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="K16" t="n">
-        <v>5.55</v>
+        <v>5.33</v>
       </c>
       <c r="L16" t="n">
         <v>-1</v>
       </c>
       <c r="M16" t="n">
-        <v>50.45</v>
+        <v>50.83</v>
       </c>
       <c r="N16" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="O16" t="n">
         <v>-1</v>
       </c>
       <c r="P16" t="n">
-        <v>15.36</v>
+        <v>15.33</v>
       </c>
       <c r="Q16" t="n">
-        <v>16.27</v>
+        <v>16</v>
       </c>
       <c r="R16" t="n">
-        <v>6.73</v>
+        <v>6.58</v>
       </c>
       <c r="S16" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="T16" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="U16" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="V16" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>60.27</v>
+        <v>60.42</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="Z16" t="n">
-        <v>12.91</v>
+        <v>13.17</v>
       </c>
       <c r="AA16" t="n">
-        <v>8.73</v>
+        <v>8.83</v>
       </c>
       <c r="AB16" t="n">
-        <v>4.18</v>
+        <v>4.33</v>
       </c>
       <c r="AC16" t="n">
-        <v>22.09</v>
+        <v>21.92</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -7192,31 +7192,31 @@
         <v>2.45</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="BH16" t="n">
-        <v>9.050000000000001</v>
+        <v>8.91</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.86</v>
+        <v>0.83</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.77</v>
+        <v>0.83</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="BP16" t="n">
         <v>-1</v>
@@ -7228,34 +7228,34 @@
         <v>100</v>
       </c>
       <c r="BS16" t="n">
-        <v>81.81999999999999</v>
+        <v>82.61</v>
       </c>
       <c r="BT16" t="n">
-        <v>54.55</v>
+        <v>56.52</v>
       </c>
       <c r="BU16" t="n">
-        <v>27.27</v>
+        <v>26.09</v>
       </c>
       <c r="BV16" t="n">
-        <v>18.18</v>
+        <v>17.39</v>
       </c>
       <c r="BW16" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BX16" t="n">
-        <v>59.09</v>
+        <v>60.87</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="BZ16" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.9</v>
+        <v>3.89</v>
       </c>
       <c r="CB16" t="n">
-        <v>4.21</v>
+        <v>4.2</v>
       </c>
       <c r="CC16" t="n">
         <v>2.34</v>
@@ -7264,49 +7264,49 @@
         <v>2.42</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.08</v>
+        <v>3.09</v>
       </c>
       <c r="CH16" t="n">
         <v>1.47</v>
       </c>
       <c r="CI16" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CK16" t="n">
         <v>1.45</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="CN16" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CO16" t="n">
         <v>1.25</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CQ16" t="n">
-        <v>3.04</v>
+        <v>3.01</v>
       </c>
       <c r="CR16" t="n">
         <v>1.41</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.82</v>
+        <v>2.79</v>
       </c>
       <c r="CT16" t="n">
         <v>2.98</v>
@@ -7324,7 +7324,7 @@
         <v>1.55</v>
       </c>
       <c r="CY16" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CZ16" t="n">
         <v>2.42</v>
@@ -7345,76 +7345,76 @@
         <v>0.04</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="DG16" t="n">
         <v>-1</v>
       </c>
       <c r="DH16" t="n">
-        <v>96.81999999999999</v>
+        <v>96.87</v>
       </c>
       <c r="DI16" t="n">
         <v>0</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.41</v>
+        <v>2.35</v>
       </c>
       <c r="DK16" t="n">
-        <v>5.45</v>
+        <v>5.34</v>
       </c>
       <c r="DL16" t="n">
         <v>-1</v>
       </c>
       <c r="DM16" t="n">
-        <v>50.18</v>
+        <v>50.39</v>
       </c>
       <c r="DN16" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="DO16" t="n">
         <v>-1</v>
       </c>
       <c r="DP16" t="n">
-        <v>16.09</v>
+        <v>16.04</v>
       </c>
       <c r="DQ16" t="n">
-        <v>15.77</v>
+        <v>15.65</v>
       </c>
       <c r="DR16" t="n">
-        <v>6.36</v>
+        <v>6.3</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>61</v>
+        <v>61.05</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DX16" t="n">
-        <v>13.04</v>
+        <v>13.17</v>
       </c>
       <c r="DY16" t="n">
-        <v>9.039999999999999</v>
+        <v>9.08</v>
       </c>
       <c r="DZ16" t="n">
-        <v>4</v>
+        <v>4.09</v>
       </c>
       <c r="EA16" t="n">
-        <v>20.77</v>
+        <v>20.74</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="17">

--- a/data/teams/leagues/Averages_Russian_Premier_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Russian_Premier_League_2025-2026.xlsx
@@ -3436,7 +3436,7 @@
         <v>-1</v>
       </c>
       <c r="P7" t="n">
-        <v>13.83</v>
+        <v>14</v>
       </c>
       <c r="Q7" t="n">
         <v>14.75</v>
@@ -3466,19 +3466,19 @@
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>8.75</v>
+        <v>8.92</v>
       </c>
       <c r="AA7" t="n">
-        <v>6.08</v>
+        <v>6.17</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.67</v>
+        <v>2.75</v>
       </c>
       <c r="AC7" t="n">
-        <v>17.42</v>
+        <v>17.58</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AE7" t="n">
         <v>2.33</v>
@@ -3748,7 +3748,7 @@
         <v>-1</v>
       </c>
       <c r="DP7" t="n">
-        <v>14.56</v>
+        <v>14.65</v>
       </c>
       <c r="DQ7" t="n">
         <v>14.87</v>
@@ -3772,19 +3772,19 @@
         <v>0.09</v>
       </c>
       <c r="DX7" t="n">
-        <v>8.130000000000001</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="DY7" t="n">
-        <v>5.56</v>
+        <v>5.61</v>
       </c>
       <c r="DZ7" t="n">
-        <v>2.56</v>
+        <v>2.61</v>
       </c>
       <c r="EA7" t="n">
-        <v>17.87</v>
+        <v>17.95</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="EC7" t="n">
         <v>2.26</v>
@@ -6747,7 +6747,7 @@
         <v>14.75</v>
       </c>
       <c r="AS15" t="n">
-        <v>8.83</v>
+        <v>8.92</v>
       </c>
       <c r="AT15" t="n">
         <v>1.33</v>
@@ -6780,7 +6780,7 @@
         <v>2.42</v>
       </c>
       <c r="BD15" t="n">
-        <v>19.5</v>
+        <v>19.58</v>
       </c>
       <c r="BE15" t="n">
         <v>1.04</v>
@@ -6978,7 +6978,7 @@
         <v>15.56</v>
       </c>
       <c r="DR15" t="n">
-        <v>8.300000000000001</v>
+        <v>8.35</v>
       </c>
       <c r="DS15" t="n">
         <v>0.09</v>
@@ -7005,7 +7005,7 @@
         <v>2.87</v>
       </c>
       <c r="EA15" t="n">
-        <v>20.13</v>
+        <v>20.17</v>
       </c>
       <c r="EB15" t="n">
         <v>1.1</v>

--- a/data/teams/leagues/Averages_Russian_Premier_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Russian_Premier_League_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C2" t="n">
         <v>12</v>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" t="n">
         <v>0.25</v>
@@ -1469,112 +1469,112 @@
         <v>1.75</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AH2" t="n">
         <v>-1</v>
       </c>
       <c r="AI2" t="n">
-        <v>90.36</v>
+        <v>90.17</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="AL2" t="n">
-        <v>3.82</v>
+        <v>3.83</v>
       </c>
       <c r="AM2" t="n">
         <v>-1</v>
       </c>
       <c r="AN2" t="n">
-        <v>40.73</v>
+        <v>40.33</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AP2" t="n">
         <v>-1</v>
       </c>
       <c r="AQ2" t="n">
-        <v>13.73</v>
+        <v>14.08</v>
       </c>
       <c r="AR2" t="n">
-        <v>18.09</v>
+        <v>17.75</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.91</v>
+        <v>7.67</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AU2" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>45.64</v>
+        <v>45.08</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="BA2" t="n">
-        <v>10.64</v>
+        <v>10.67</v>
       </c>
       <c r="BB2" t="n">
-        <v>7.73</v>
+        <v>7.75</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="BD2" t="n">
-        <v>20.82</v>
+        <v>20.67</v>
       </c>
       <c r="BE2" t="n">
         <v>1.18</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="BH2" t="n">
-        <v>8.699999999999999</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.52</v>
+        <v>0.58</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="BP2" t="n">
         <v>-1</v>
@@ -1586,22 +1586,22 @@
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>69.56999999999999</v>
+        <v>70.83</v>
       </c>
       <c r="BT2" t="n">
-        <v>43.48</v>
+        <v>45.83</v>
       </c>
       <c r="BU2" t="n">
-        <v>21.74</v>
+        <v>25</v>
       </c>
       <c r="BV2" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BW2" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BX2" t="n">
-        <v>52.17</v>
+        <v>54.17</v>
       </c>
       <c r="BY2" t="n">
         <v>2.77</v>
@@ -1610,28 +1610,28 @@
         <v>2.82</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.48</v>
+        <v>3.47</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.59</v>
+        <v>3.58</v>
       </c>
       <c r="CC2" t="n">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="CD2" t="n">
-        <v>3.5</v>
+        <v>3.43</v>
       </c>
       <c r="CE2" t="n">
         <v>1.41</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CI2" t="n">
         <v>1.96</v>
@@ -1643,10 +1643,10 @@
         <v>1.49</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="CN2" t="n">
         <v>1.91</v>
@@ -1655,10 +1655,10 @@
         <v>1.32</v>
       </c>
       <c r="CP2" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CQ2" t="n">
-        <v>3.44</v>
+        <v>3.47</v>
       </c>
       <c r="CR2" t="n">
         <v>1.38</v>
@@ -1697,82 +1697,82 @@
         <v>2.02</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.52</v>
+        <v>3.53</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="DG2" t="n">
         <v>-1</v>
       </c>
       <c r="DH2" t="n">
-        <v>90.20999999999999</v>
+        <v>90.12</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.31</v>
+        <v>2.34</v>
       </c>
       <c r="DK2" t="n">
-        <v>4.39</v>
+        <v>4.38</v>
       </c>
       <c r="DL2" t="n">
         <v>-1</v>
       </c>
       <c r="DM2" t="n">
-        <v>43.35</v>
+        <v>43.04</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="DO2" t="n">
         <v>-1</v>
       </c>
       <c r="DP2" t="n">
-        <v>12.04</v>
+        <v>12.29</v>
       </c>
       <c r="DQ2" t="n">
-        <v>17.26</v>
+        <v>17.12</v>
       </c>
       <c r="DR2" t="n">
-        <v>7.13</v>
+        <v>7.04</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>45.83</v>
+        <v>45.54</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="DX2" t="n">
-        <v>12.26</v>
+        <v>12.21</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.65</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="DZ2" t="n">
-        <v>3.61</v>
+        <v>3.58</v>
       </c>
       <c r="EA2" t="n">
-        <v>21.26</v>
+        <v>21.17</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="3">
@@ -2185,34 +2185,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4" t="n">
         <v>12</v>
       </c>
       <c r="E4" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="F4" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="G4" t="n">
         <v>-1</v>
       </c>
       <c r="H4" t="n">
-        <v>85.18000000000001</v>
+        <v>85.67</v>
       </c>
       <c r="I4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J4" t="n">
-        <v>2.91</v>
+        <v>2.75</v>
       </c>
       <c r="K4" t="n">
-        <v>3.27</v>
+        <v>3.33</v>
       </c>
       <c r="L4" t="n">
         <v>-1</v>
@@ -2221,58 +2221,58 @@
         <v>46</v>
       </c>
       <c r="N4" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="O4" t="n">
         <v>-1</v>
       </c>
       <c r="P4" t="n">
-        <v>19.45</v>
+        <v>18.83</v>
       </c>
       <c r="Q4" t="n">
-        <v>12.73</v>
+        <v>13</v>
       </c>
       <c r="R4" t="n">
         <v>7</v>
       </c>
       <c r="S4" t="n">
-        <v>0.36</v>
+        <v>0.5</v>
       </c>
       <c r="T4" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="U4" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="V4" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>43.55</v>
+        <v>44.75</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z4" t="n">
-        <v>13.18</v>
+        <v>13.17</v>
       </c>
       <c r="AA4" t="n">
-        <v>8.82</v>
+        <v>8.83</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.36</v>
+        <v>4.33</v>
       </c>
       <c r="AC4" t="n">
-        <v>21.55</v>
+        <v>21.5</v>
       </c>
       <c r="AD4" t="n">
         <v>1.47</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.73</v>
+        <v>2.58</v>
       </c>
       <c r="AF4" t="n">
         <v>0.17</v>
@@ -2356,28 +2356,28 @@
         <v>3.17</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.87</v>
+        <v>1.96</v>
       </c>
       <c r="BH4" t="n">
-        <v>8.039999999999999</v>
+        <v>8.08</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.87</v>
+        <v>1.96</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.61</v>
+        <v>0.67</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.43</v>
+        <v>0.46</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="BO4" t="n">
         <v>0.83</v>
@@ -2389,37 +2389,37 @@
         <v>-1</v>
       </c>
       <c r="BR4" t="n">
-        <v>82.61</v>
+        <v>83.33</v>
       </c>
       <c r="BS4" t="n">
-        <v>65.22</v>
+        <v>66.67</v>
       </c>
       <c r="BT4" t="n">
-        <v>21.74</v>
+        <v>25</v>
       </c>
       <c r="BU4" t="n">
-        <v>13.04</v>
+        <v>16.67</v>
       </c>
       <c r="BV4" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>30.43</v>
+        <v>33.33</v>
       </c>
       <c r="BY4" t="n">
-        <v>2.36</v>
+        <v>2.29</v>
       </c>
       <c r="BZ4" t="n">
-        <v>2.53</v>
+        <v>2.46</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.42</v>
+        <v>3.44</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.53</v>
+        <v>3.54</v>
       </c>
       <c r="CC4" t="n">
         <v>3.5</v>
@@ -2428,10 +2428,10 @@
         <v>3.76</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CF4" t="n">
-        <v>3.13</v>
+        <v>3.14</v>
       </c>
       <c r="CG4" t="n">
         <v>2.52</v>
@@ -2443,28 +2443,28 @@
         <v>1.65</v>
       </c>
       <c r="CJ4" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="CQ4" t="n">
-        <v>4.11</v>
+        <v>4.12</v>
       </c>
       <c r="CR4" t="n">
         <v>1.47</v>
@@ -2506,79 +2506,79 @@
         <v>4.55</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="DG4" t="n">
         <v>-1</v>
       </c>
       <c r="DH4" t="n">
-        <v>89.61</v>
+        <v>89.67</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DJ4" t="n">
-        <v>3.09</v>
+        <v>3</v>
       </c>
       <c r="DK4" t="n">
-        <v>3.39</v>
+        <v>3.42</v>
       </c>
       <c r="DL4" t="n">
         <v>-1</v>
       </c>
       <c r="DM4" t="n">
-        <v>44.48</v>
+        <v>44.54</v>
       </c>
       <c r="DN4" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="DO4" t="n">
         <v>-1</v>
       </c>
       <c r="DP4" t="n">
-        <v>19.43</v>
+        <v>19.12</v>
       </c>
       <c r="DQ4" t="n">
-        <v>12.87</v>
+        <v>13</v>
       </c>
       <c r="DR4" t="n">
-        <v>7.56</v>
+        <v>7.54</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>45.91</v>
+        <v>46.42</v>
       </c>
       <c r="DW4" t="n">
         <v>0.08</v>
       </c>
       <c r="DX4" t="n">
-        <v>12.56</v>
+        <v>12.58</v>
       </c>
       <c r="DY4" t="n">
-        <v>8.35</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.21</v>
+        <v>4.2</v>
       </c>
       <c r="EA4" t="n">
-        <v>21.09</v>
+        <v>21.08</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="5">
@@ -4200,61 +4200,61 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D9" t="n">
         <v>13</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="F9" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="G9" t="n">
         <v>-1</v>
       </c>
       <c r="H9" t="n">
-        <v>83.3</v>
+        <v>85.45</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="K9" t="n">
-        <v>4.2</v>
+        <v>4.82</v>
       </c>
       <c r="L9" t="n">
         <v>-1</v>
       </c>
       <c r="M9" t="n">
-        <v>37.9</v>
+        <v>39.45</v>
       </c>
       <c r="N9" t="n">
-        <v>0.4</v>
+        <v>0.55</v>
       </c>
       <c r="O9" t="n">
         <v>-1</v>
       </c>
       <c r="P9" t="n">
-        <v>14.7</v>
+        <v>14.45</v>
       </c>
       <c r="Q9" t="n">
-        <v>14</v>
+        <v>14.36</v>
       </c>
       <c r="R9" t="n">
-        <v>8.4</v>
+        <v>8.27</v>
       </c>
       <c r="S9" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="T9" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -4266,28 +4266,28 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>45.9</v>
+        <v>47.27</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z9" t="n">
-        <v>9.1</v>
+        <v>9.09</v>
       </c>
       <c r="AA9" t="n">
-        <v>6.4</v>
+        <v>6.09</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="AC9" t="n">
-        <v>20.7</v>
+        <v>20.91</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AF9" t="n">
         <v>0.08</v>
@@ -4371,31 +4371,31 @@
         <v>2.62</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="BH9" t="n">
-        <v>8.960000000000001</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="BJ9" t="n">
         <v>0.83</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.39</v>
+        <v>0.46</v>
       </c>
       <c r="BL9" t="n">
         <v>1.04</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="BP9" t="n">
         <v>-1</v>
@@ -4404,37 +4404,37 @@
         <v>-1</v>
       </c>
       <c r="BR9" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BS9" t="n">
-        <v>91.3</v>
+        <v>91.67</v>
       </c>
       <c r="BT9" t="n">
-        <v>43.48</v>
+        <v>45.83</v>
       </c>
       <c r="BU9" t="n">
-        <v>30.43</v>
+        <v>33.33</v>
       </c>
       <c r="BV9" t="n">
-        <v>17.39</v>
+        <v>16.67</v>
       </c>
       <c r="BW9" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BX9" t="n">
-        <v>43.48</v>
+        <v>45.83</v>
       </c>
       <c r="BY9" t="n">
-        <v>3.38</v>
+        <v>3.34</v>
       </c>
       <c r="BZ9" t="n">
-        <v>3.66</v>
+        <v>3.57</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.88</v>
+        <v>3.85</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.96</v>
+        <v>3.94</v>
       </c>
       <c r="CC9" t="n">
         <v>6.06</v>
@@ -4446,13 +4446,13 @@
         <v>1.41</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.91</v>
+        <v>2.93</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CI9" t="n">
         <v>1.88</v>
@@ -4464,7 +4464,7 @@
         <v>1.54</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CM9" t="n">
         <v>2.35</v>
@@ -4476,10 +4476,10 @@
         <v>1.33</v>
       </c>
       <c r="CP9" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.53</v>
+        <v>3.56</v>
       </c>
       <c r="CR9" t="n">
         <v>1.44</v>
@@ -4521,79 +4521,79 @@
         <v>3.84</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="DG9" t="n">
         <v>-1</v>
       </c>
       <c r="DH9" t="n">
-        <v>80.48</v>
+        <v>81.58</v>
       </c>
       <c r="DI9" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="DK9" t="n">
-        <v>3.26</v>
+        <v>3.59</v>
       </c>
       <c r="DL9" t="n">
         <v>-1</v>
       </c>
       <c r="DM9" t="n">
-        <v>34.83</v>
+        <v>35.66</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.65</v>
+        <v>0.71</v>
       </c>
       <c r="DO9" t="n">
         <v>-1</v>
       </c>
       <c r="DP9" t="n">
-        <v>14.69</v>
+        <v>14.58</v>
       </c>
       <c r="DQ9" t="n">
-        <v>13.56</v>
+        <v>13.75</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.35</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>46.39</v>
+        <v>47</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX9" t="n">
-        <v>8.26</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="DY9" t="n">
-        <v>5.65</v>
+        <v>5.54</v>
       </c>
       <c r="DZ9" t="n">
-        <v>2.61</v>
+        <v>2.75</v>
       </c>
       <c r="EA9" t="n">
-        <v>19.69</v>
+        <v>19.83</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.96</v>
+        <v>0.98</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="10">
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
         <v>12</v>
       </c>
       <c r="D12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -5499,109 +5499,109 @@
         <v>2.33</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AH12" t="n">
         <v>-1</v>
       </c>
       <c r="AI12" t="n">
-        <v>76.36</v>
+        <v>75.92</v>
       </c>
       <c r="AJ12" t="n">
         <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.73</v>
+        <v>2.67</v>
       </c>
       <c r="AL12" t="n">
-        <v>4.09</v>
+        <v>4.17</v>
       </c>
       <c r="AM12" t="n">
         <v>-1</v>
       </c>
       <c r="AN12" t="n">
-        <v>32.82</v>
+        <v>32.75</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.82</v>
+        <v>0.92</v>
       </c>
       <c r="AP12" t="n">
         <v>-1</v>
       </c>
       <c r="AQ12" t="n">
-        <v>17.18</v>
+        <v>17.08</v>
       </c>
       <c r="AR12" t="n">
-        <v>14.45</v>
+        <v>14.42</v>
       </c>
       <c r="AS12" t="n">
-        <v>8.82</v>
+        <v>8.58</v>
       </c>
       <c r="AT12" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.45</v>
+        <v>0.58</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AX12" t="n">
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>39.55</v>
+        <v>39.75</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="BA12" t="n">
-        <v>10.64</v>
+        <v>10.33</v>
       </c>
       <c r="BB12" t="n">
-        <v>7.18</v>
+        <v>6.83</v>
       </c>
       <c r="BC12" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>18.27</v>
+        <v>19.08</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.39</v>
+        <v>2.46</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.91</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.39</v>
+        <v>2.46</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.35</v>
+        <v>0.38</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="BO12" t="n">
         <v>0.96</v>
@@ -5613,25 +5613,25 @@
         <v>-1</v>
       </c>
       <c r="BR12" t="n">
-        <v>91.3</v>
+        <v>91.67</v>
       </c>
       <c r="BS12" t="n">
-        <v>73.91</v>
+        <v>75</v>
       </c>
       <c r="BT12" t="n">
-        <v>52.17</v>
+        <v>54.17</v>
       </c>
       <c r="BU12" t="n">
-        <v>13.04</v>
+        <v>16.67</v>
       </c>
       <c r="BV12" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>30.43</v>
+        <v>33.33</v>
       </c>
       <c r="BY12" t="n">
         <v>3.84</v>
@@ -5640,55 +5640,55 @@
         <v>4.07</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.93</v>
+        <v>3.92</v>
       </c>
       <c r="CB12" t="n">
-        <v>4.24</v>
+        <v>4.22</v>
       </c>
       <c r="CC12" t="n">
-        <v>7.17</v>
+        <v>7.14</v>
       </c>
       <c r="CD12" t="n">
-        <v>7.95</v>
+        <v>7.79</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="CG12" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="CH12" t="n">
         <v>1.37</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CL12" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="CN12" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="CO12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="CP12" t="n">
         <v>1.92</v>
       </c>
-      <c r="CM12" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="CN12" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="CO12" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="CP12" t="n">
-        <v>1.9</v>
-      </c>
       <c r="CQ12" t="n">
-        <v>3.21</v>
+        <v>3.26</v>
       </c>
       <c r="CR12" t="n">
         <v>1.46</v>
@@ -5730,79 +5730,79 @@
         <v>3.7</v>
       </c>
       <c r="DE12" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="DG12" t="n">
         <v>-1</v>
       </c>
       <c r="DH12" t="n">
-        <v>83.3</v>
+        <v>82.8</v>
       </c>
       <c r="DI12" t="n">
         <v>0</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.57</v>
+        <v>2.54</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.52</v>
+        <v>4.54</v>
       </c>
       <c r="DL12" t="n">
         <v>-1</v>
       </c>
       <c r="DM12" t="n">
-        <v>38.91</v>
+        <v>38.62</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="DO12" t="n">
         <v>-1</v>
       </c>
       <c r="DP12" t="n">
-        <v>16.48</v>
+        <v>16.45</v>
       </c>
       <c r="DQ12" t="n">
-        <v>14.74</v>
+        <v>14.71</v>
       </c>
       <c r="DR12" t="n">
-        <v>7.83</v>
+        <v>7.75</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>43.7</v>
+        <v>43.62</v>
       </c>
       <c r="DW12" t="n">
         <v>0.08</v>
       </c>
       <c r="DX12" t="n">
-        <v>11.83</v>
+        <v>11.62</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.74</v>
+        <v>7.54</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.09</v>
+        <v>4.08</v>
       </c>
       <c r="EA12" t="n">
-        <v>18.43</v>
+        <v>18.83</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="13">
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C13" t="n">
         <v>12</v>
       </c>
       <c r="D13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E13" t="n">
         <v>0.17</v>
@@ -5905,109 +5905,109 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AH13" t="n">
         <v>-1</v>
       </c>
       <c r="AI13" t="n">
-        <v>87.81999999999999</v>
+        <v>87.58</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AL13" t="n">
-        <v>5.36</v>
+        <v>5.33</v>
       </c>
       <c r="AM13" t="n">
         <v>-1</v>
       </c>
       <c r="AN13" t="n">
-        <v>44.27</v>
+        <v>44.33</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="AP13" t="n">
         <v>-1</v>
       </c>
       <c r="AQ13" t="n">
-        <v>13.73</v>
+        <v>14.08</v>
       </c>
       <c r="AR13" t="n">
-        <v>15.18</v>
+        <v>15.17</v>
       </c>
       <c r="AS13" t="n">
-        <v>8.359999999999999</v>
+        <v>8</v>
       </c>
       <c r="AT13" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AU13" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AX13" t="n">
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>47.18</v>
+        <v>46.75</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="BA13" t="n">
-        <v>11.18</v>
+        <v>11.42</v>
       </c>
       <c r="BB13" t="n">
-        <v>7.36</v>
+        <v>7.67</v>
       </c>
       <c r="BC13" t="n">
-        <v>3.82</v>
+        <v>3.75</v>
       </c>
       <c r="BD13" t="n">
-        <v>22.55</v>
+        <v>22.67</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.61</v>
+        <v>2.5</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.83</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.61</v>
+        <v>2.5</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="BP13" t="n">
         <v>-1</v>
@@ -6016,25 +6016,25 @@
         <v>-1</v>
       </c>
       <c r="BR13" t="n">
-        <v>91.3</v>
+        <v>87.5</v>
       </c>
       <c r="BS13" t="n">
-        <v>65.22</v>
+        <v>62.5</v>
       </c>
       <c r="BT13" t="n">
-        <v>43.48</v>
+        <v>41.67</v>
       </c>
       <c r="BU13" t="n">
-        <v>34.78</v>
+        <v>33.33</v>
       </c>
       <c r="BV13" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="BW13" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BX13" t="n">
-        <v>52.17</v>
+        <v>50</v>
       </c>
       <c r="BY13" t="n">
         <v>3.86</v>
@@ -6043,55 +6043,55 @@
         <v>4.41</v>
       </c>
       <c r="CA13" t="n">
-        <v>4.06</v>
+        <v>4.03</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.31</v>
+        <v>4.26</v>
       </c>
       <c r="CC13" t="n">
-        <v>5.93</v>
+        <v>5.73</v>
       </c>
       <c r="CD13" t="n">
-        <v>6.31</v>
+        <v>6.06</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.18</v>
+        <v>3.16</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="CN13" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.97</v>
+        <v>3.02</v>
       </c>
       <c r="CR13" t="n">
         <v>1.4</v>
@@ -6112,100 +6112,100 @@
         <v>1.8</v>
       </c>
       <c r="CX13" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="CY13" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="CZ13" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="DA13" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="DB13" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="DC13" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="DD13" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="DE13" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="DF13" t="n">
         <v>1.54</v>
       </c>
-      <c r="CY13" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="CZ13" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="DA13" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="DB13" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="DC13" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="DD13" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="DE13" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="DF13" t="n">
-        <v>1.52</v>
-      </c>
       <c r="DG13" t="n">
         <v>-1</v>
       </c>
       <c r="DH13" t="n">
-        <v>85.09</v>
+        <v>85.08</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.39</v>
+        <v>5.38</v>
       </c>
       <c r="DL13" t="n">
         <v>-1</v>
       </c>
       <c r="DM13" t="n">
-        <v>43.74</v>
+        <v>43.79</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="DO13" t="n">
         <v>-1</v>
       </c>
       <c r="DP13" t="n">
-        <v>15.04</v>
+        <v>15.16</v>
       </c>
       <c r="DQ13" t="n">
-        <v>15.65</v>
+        <v>15.62</v>
       </c>
       <c r="DR13" t="n">
-        <v>8</v>
+        <v>7.84</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>47.96</v>
+        <v>47.71</v>
       </c>
       <c r="DW13" t="n">
         <v>0.04</v>
       </c>
       <c r="DX13" t="n">
-        <v>12.04</v>
+        <v>12.12</v>
       </c>
       <c r="DY13" t="n">
-        <v>8.220000000000001</v>
+        <v>8.33</v>
       </c>
       <c r="DZ13" t="n">
-        <v>3.83</v>
+        <v>3.79</v>
       </c>
       <c r="EA13" t="n">
-        <v>21.18</v>
+        <v>21.3</v>
       </c>
       <c r="EB13" t="n">
         <v>1.35</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="14">
@@ -6618,10 +6618,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D15" t="n">
         <v>12</v>
@@ -6630,82 +6630,82 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="G15" t="n">
         <v>-1</v>
       </c>
       <c r="H15" t="n">
-        <v>88.64</v>
+        <v>88.33</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="K15" t="n">
-        <v>4.09</v>
+        <v>3.92</v>
       </c>
       <c r="L15" t="n">
         <v>-1</v>
       </c>
       <c r="M15" t="n">
-        <v>38.18</v>
+        <v>37.17</v>
       </c>
       <c r="N15" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="O15" t="n">
         <v>-1</v>
       </c>
       <c r="P15" t="n">
-        <v>15.45</v>
+        <v>15.17</v>
       </c>
       <c r="Q15" t="n">
-        <v>16.45</v>
+        <v>16.67</v>
       </c>
       <c r="R15" t="n">
-        <v>7.73</v>
+        <v>8.25</v>
       </c>
       <c r="S15" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="T15" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="U15" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="V15" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>41.55</v>
+        <v>42.92</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z15" t="n">
-        <v>10.27</v>
+        <v>9.83</v>
       </c>
       <c r="AA15" t="n">
-        <v>6.91</v>
+        <v>6.67</v>
       </c>
       <c r="AB15" t="n">
-        <v>3.36</v>
+        <v>3.17</v>
       </c>
       <c r="AC15" t="n">
-        <v>20.82</v>
+        <v>20.83</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -6789,31 +6789,31 @@
         <v>2.75</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="BH15" t="n">
-        <v>7.65</v>
+        <v>7.62</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="BO15" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="BP15" t="n">
         <v>-1</v>
@@ -6822,37 +6822,37 @@
         <v>-1</v>
       </c>
       <c r="BR15" t="n">
-        <v>86.95999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BS15" t="n">
-        <v>56.52</v>
+        <v>54.17</v>
       </c>
       <c r="BT15" t="n">
-        <v>39.13</v>
+        <v>37.5</v>
       </c>
       <c r="BU15" t="n">
-        <v>17.39</v>
+        <v>16.67</v>
       </c>
       <c r="BV15" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BW15" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BX15" t="n">
-        <v>30.43</v>
+        <v>29.17</v>
       </c>
       <c r="BY15" t="n">
-        <v>3.01</v>
+        <v>2.93</v>
       </c>
       <c r="BZ15" t="n">
-        <v>3.34</v>
+        <v>3.26</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.39</v>
+        <v>3.38</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.56</v>
+        <v>3.54</v>
       </c>
       <c r="CC15" t="n">
         <v>3.93</v>
@@ -6864,7 +6864,7 @@
         <v>1.46</v>
       </c>
       <c r="CF15" t="n">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="CG15" t="n">
         <v>2.71</v>
@@ -6873,7 +6873,7 @@
         <v>1.36</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CJ15" t="n">
         <v>1.95</v>
@@ -6882,7 +6882,7 @@
         <v>1.57</v>
       </c>
       <c r="CL15" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CM15" t="n">
         <v>2.3</v>
@@ -6897,7 +6897,7 @@
         <v>2.22</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.89</v>
+        <v>3.91</v>
       </c>
       <c r="CR15" t="n">
         <v>1.41</v>
@@ -6924,25 +6924,25 @@
         <v>2.04</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="DB15" t="n">
         <v>1.39</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="DD15" t="n">
-        <v>4.07</v>
+        <v>4.09</v>
       </c>
       <c r="DE15" t="n">
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="DG15" t="n">
         <v>-1</v>
@@ -6951,67 +6951,67 @@
         <v>84.83</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.39</v>
+        <v>2.34</v>
       </c>
       <c r="DK15" t="n">
-        <v>3.78</v>
+        <v>3.71</v>
       </c>
       <c r="DL15" t="n">
         <v>-1</v>
       </c>
       <c r="DM15" t="n">
-        <v>37.48</v>
+        <v>37</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="DO15" t="n">
         <v>-1</v>
       </c>
       <c r="DP15" t="n">
-        <v>16.22</v>
+        <v>16.05</v>
       </c>
       <c r="DQ15" t="n">
-        <v>15.56</v>
+        <v>15.71</v>
       </c>
       <c r="DR15" t="n">
-        <v>8.35</v>
+        <v>8.58</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>42.22</v>
+        <v>42.88</v>
       </c>
       <c r="DW15" t="n">
         <v>0.04</v>
       </c>
       <c r="DX15" t="n">
-        <v>9.869999999999999</v>
+        <v>9.67</v>
       </c>
       <c r="DY15" t="n">
-        <v>7</v>
+        <v>6.88</v>
       </c>
       <c r="DZ15" t="n">
-        <v>2.87</v>
+        <v>2.8</v>
       </c>
       <c r="EA15" t="n">
-        <v>20.17</v>
+        <v>20.2</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="16">

--- a/data/teams/leagues/Averages_Russian_Premier_League_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Russian_Premier_League_2025-2026.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -706,667 +694,667 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team_name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>total_games</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>home_games</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>away_games</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>home_avg_0_10_min_goals</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>home_avg_2h_cards</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>home_avg_2h_corners</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>home_avg_attacks</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>home_avg_cards_0_10_min</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>home_avg_cards_num</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>home_avg_corners</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>home_avg_corners_0_10_min</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>home_avg_dangerous_attacks</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>home_avg_fh_cards</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>home_avg_fh_corners</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>home_avg_fouls</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>home_avg_freekicks</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>home_avg_goalkicks</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>home_avg_goals_conceded</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>home_avg_goals_scored</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>home_avg_penalties_won</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>home_avg_penalty_goals</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>home_avg_penalty_missed</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>home_avg_possession</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>home_avg_red_cards</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>home_avg_shots</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>home_avg_shotsOffTarget</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>home_avg_shotsOnTarget</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>home_avg_throwins</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>home_avg_xg</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>home_avg_yellow_cards</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>away_avg_0_10_min_goals</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>away_avg_2h_cards</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>away_avg_2h_corners</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>away_avg_attacks</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>away_avg_cards_0_10_min</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>away_avg_cards_num</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>away_avg_corners</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>away_avg_corners_0_10_min</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>away_avg_dangerous_attacks</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>away_avg_fh_cards</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>away_avg_fh_corners</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>away_avg_fouls</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>away_avg_freekicks</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>away_avg_goalkicks</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>away_avg_goals_conceded</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>away_avg_goals_scored</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>away_avg_penalties_won</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>away_avg_penalty_goals</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>away_avg_penalty_missed</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>away_avg_possession</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>away_avg_red_cards</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>away_avg_shots</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>away_avg_shotsOffTarget</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>away_avg_shotsOnTarget</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>away_avg_throwins</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>away_avg_xg</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>away_avg_yellow_cards</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>totalGoalCount</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>totalCornerCount</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>overallGoalCount</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>ht_goals_team_a</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>ht_goals_team_b</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>goals_2hg_team_a</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>goals_2hg_team_b</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>GoalCount_2hg</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BO1" t="inlineStr">
         <is>
           <t>HTGoalCount</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BP1" t="inlineStr">
         <is>
           <t>corner_fh_count</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BQ1" t="inlineStr">
         <is>
           <t>corner_2h_count</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BR1" t="inlineStr">
         <is>
           <t>over05</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BS1" t="inlineStr">
         <is>
           <t>over15</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BT1" t="inlineStr">
         <is>
           <t>over25</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BU1" t="inlineStr">
         <is>
           <t>over35</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BV1" t="inlineStr">
         <is>
           <t>over45</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BW1" t="inlineStr">
         <is>
           <t>over55</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BX1" t="inlineStr">
         <is>
           <t>btts</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="BY1" t="inlineStr">
         <is>
           <t>avg_odds_ft_1</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="BZ1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_1_odd</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CA1" t="inlineStr">
         <is>
           <t>avg_odds_ft_x</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CB1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_x_odd</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CC1" t="inlineStr">
         <is>
           <t>avg_odds_ft_2</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CD1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_2_odd</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CE1" t="inlineStr">
         <is>
           <t>avg_odds_1st_half_over05</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CF1" t="inlineStr">
         <is>
           <t>avg_odds_1st_half_over15</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CG1" t="inlineStr">
         <is>
           <t>avg_odds_1st_half_under05</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CH1" t="inlineStr">
         <is>
           <t>avg_odds_1st_half_under15</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CI1" t="inlineStr">
         <is>
           <t>avg_odds_btts_no</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CJ1" t="inlineStr">
         <is>
           <t>avg_odds_btts_yes</t>
         </is>
       </c>
-      <c r="CK1" s="1" t="inlineStr">
+      <c r="CK1" t="inlineStr">
         <is>
           <t>avg_odds_corners_over_85</t>
         </is>
       </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="CL1" t="inlineStr">
         <is>
           <t>avg_odds_corners_over_95</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="CM1" t="inlineStr">
         <is>
           <t>avg_odds_corners_under_85</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
+      <c r="CN1" t="inlineStr">
         <is>
           <t>avg_odds_corners_under_95</t>
         </is>
       </c>
-      <c r="CO1" s="1" t="inlineStr">
+      <c r="CO1" t="inlineStr">
         <is>
           <t>avg_odds_ft_over15</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CP1" t="inlineStr">
         <is>
           <t>avg_odds_ft_over25</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
+      <c r="CQ1" t="inlineStr">
         <is>
           <t>avg_odds_ft_over35</t>
         </is>
       </c>
-      <c r="CR1" s="1" t="inlineStr">
+      <c r="CR1" t="inlineStr">
         <is>
           <t>avg_pinnacle_1st_half_over05_odd</t>
         </is>
       </c>
-      <c r="CS1" s="1" t="inlineStr">
+      <c r="CS1" t="inlineStr">
         <is>
           <t>avg_pinnacle_1st_half_over15_odd</t>
         </is>
       </c>
-      <c r="CT1" s="1" t="inlineStr">
+      <c r="CT1" t="inlineStr">
         <is>
           <t>avg_pinnacle_1st_half_under05_odd</t>
         </is>
       </c>
-      <c r="CU1" s="1" t="inlineStr">
+      <c r="CU1" t="inlineStr">
         <is>
           <t>avg_pinnacle_1st_half_under15_odd</t>
         </is>
       </c>
-      <c r="CV1" s="1" t="inlineStr">
+      <c r="CV1" t="inlineStr">
         <is>
           <t>avg_pinnacle_btts_no_odd</t>
         </is>
       </c>
-      <c r="CW1" s="1" t="inlineStr">
+      <c r="CW1" t="inlineStr">
         <is>
           <t>avg_pinnacle_btts_yes_odd</t>
         </is>
       </c>
-      <c r="CX1" s="1" t="inlineStr">
+      <c r="CX1" t="inlineStr">
         <is>
           <t>avg_pinnacle_corners_over_85_odd</t>
         </is>
       </c>
-      <c r="CY1" s="1" t="inlineStr">
+      <c r="CY1" t="inlineStr">
         <is>
           <t>avg_pinnacle_corners_over_95_odd</t>
         </is>
       </c>
-      <c r="CZ1" s="1" t="inlineStr">
+      <c r="CZ1" t="inlineStr">
         <is>
           <t>avg_pinnacle_corners_under_85_odd</t>
         </is>
       </c>
-      <c r="DA1" s="1" t="inlineStr">
+      <c r="DA1" t="inlineStr">
         <is>
           <t>avg_pinnacle_corners_under_95_odd</t>
         </is>
       </c>
-      <c r="DB1" s="1" t="inlineStr">
+      <c r="DB1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_over15_odd</t>
         </is>
       </c>
-      <c r="DC1" s="1" t="inlineStr">
+      <c r="DC1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_over25_odd</t>
         </is>
       </c>
-      <c r="DD1" s="1" t="inlineStr">
+      <c r="DD1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_over35_odd</t>
         </is>
       </c>
-      <c r="DE1" s="1" t="inlineStr">
+      <c r="DE1" t="inlineStr">
         <is>
           <t>total_avg_0_10_min_goals</t>
         </is>
       </c>
-      <c r="DF1" s="1" t="inlineStr">
+      <c r="DF1" t="inlineStr">
         <is>
           <t>total_avg_2h_cards</t>
         </is>
       </c>
-      <c r="DG1" s="1" t="inlineStr">
+      <c r="DG1" t="inlineStr">
         <is>
           <t>total_avg_2h_corners</t>
         </is>
       </c>
-      <c r="DH1" s="1" t="inlineStr">
+      <c r="DH1" t="inlineStr">
         <is>
           <t>total_avg_attacks</t>
         </is>
       </c>
-      <c r="DI1" s="1" t="inlineStr">
+      <c r="DI1" t="inlineStr">
         <is>
           <t>total_avg_cards_0_10_min</t>
         </is>
       </c>
-      <c r="DJ1" s="1" t="inlineStr">
+      <c r="DJ1" t="inlineStr">
         <is>
           <t>total_avg_cards_num</t>
         </is>
       </c>
-      <c r="DK1" s="1" t="inlineStr">
+      <c r="DK1" t="inlineStr">
         <is>
           <t>total_avg_corners</t>
         </is>
       </c>
-      <c r="DL1" s="1" t="inlineStr">
+      <c r="DL1" t="inlineStr">
         <is>
           <t>total_avg_corners_0_10_min</t>
         </is>
       </c>
-      <c r="DM1" s="1" t="inlineStr">
+      <c r="DM1" t="inlineStr">
         <is>
           <t>total_avg_dangerous_attacks</t>
         </is>
       </c>
-      <c r="DN1" s="1" t="inlineStr">
+      <c r="DN1" t="inlineStr">
         <is>
           <t>total_avg_fh_cards</t>
         </is>
       </c>
-      <c r="DO1" s="1" t="inlineStr">
+      <c r="DO1" t="inlineStr">
         <is>
           <t>total_avg_fh_corners</t>
         </is>
       </c>
-      <c r="DP1" s="1" t="inlineStr">
+      <c r="DP1" t="inlineStr">
         <is>
           <t>total_avg_fouls</t>
         </is>
       </c>
-      <c r="DQ1" s="1" t="inlineStr">
+      <c r="DQ1" t="inlineStr">
         <is>
           <t>total_avg_freekicks</t>
         </is>
       </c>
-      <c r="DR1" s="1" t="inlineStr">
+      <c r="DR1" t="inlineStr">
         <is>
           <t>total_avg_goalkicks</t>
         </is>
       </c>
-      <c r="DS1" s="1" t="inlineStr">
+      <c r="DS1" t="inlineStr">
         <is>
           <t>total_avg_penalties_won</t>
         </is>
       </c>
-      <c r="DT1" s="1" t="inlineStr">
+      <c r="DT1" t="inlineStr">
         <is>
           <t>total_avg_penalty_goals</t>
         </is>
       </c>
-      <c r="DU1" s="1" t="inlineStr">
+      <c r="DU1" t="inlineStr">
         <is>
           <t>total_avg_penalty_missed</t>
         </is>
       </c>
-      <c r="DV1" s="1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>total_avg_possession</t>
         </is>
       </c>
-      <c r="DW1" s="1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>total_avg_red_cards</t>
         </is>
       </c>
-      <c r="DX1" s="1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>total_avg_shots</t>
         </is>
       </c>
-      <c r="DY1" s="1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>total_avg_shotsOffTarget</t>
         </is>
       </c>
-      <c r="DZ1" s="1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>total_avg_shotsOnTarget</t>
         </is>
       </c>
-      <c r="EA1" s="1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>total_avg_throwins</t>
         </is>
       </c>
-      <c r="EB1" s="1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>total_avg_xg</t>
         </is>
       </c>
-      <c r="EC1" s="1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>total_avg_yellow_cards</t>
         </is>
@@ -1379,16 +1367,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C2" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E2" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="F2" t="n">
         <v>1.67</v>
@@ -1397,184 +1385,184 @@
         <v>-1</v>
       </c>
       <c r="H2" t="n">
-        <v>90.08</v>
+        <v>90.93000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="K2" t="n">
-        <v>4.92</v>
+        <v>5.07</v>
       </c>
       <c r="L2" t="n">
         <v>-1</v>
       </c>
       <c r="M2" t="n">
-        <v>45.75</v>
+        <v>46.73</v>
       </c>
       <c r="N2" t="n">
-        <v>0.17</v>
+        <v>0.27</v>
       </c>
       <c r="O2" t="n">
         <v>-1</v>
       </c>
       <c r="P2" t="n">
-        <v>10.5</v>
+        <v>11.07</v>
       </c>
       <c r="Q2" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="R2" t="n">
-        <v>6.42</v>
+        <v>6.2</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="T2" t="n">
         <v>1.33</v>
       </c>
       <c r="U2" t="n">
-        <v>0.17</v>
+        <v>0.13</v>
       </c>
       <c r="V2" t="n">
-        <v>0.17</v>
+        <v>0.13</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Z2" t="n">
-        <v>13.75</v>
+        <v>13.2</v>
       </c>
       <c r="AA2" t="n">
-        <v>9.5</v>
+        <v>9.27</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.25</v>
+        <v>3.93</v>
       </c>
       <c r="AC2" t="n">
-        <v>21.67</v>
+        <v>21.87</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.58</v>
+        <v>1.33</v>
       </c>
       <c r="AH2" t="n">
         <v>-1</v>
       </c>
       <c r="AI2" t="n">
-        <v>90.17</v>
+        <v>85.13</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.17</v>
+        <v>0.13</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.75</v>
+        <v>2.33</v>
       </c>
       <c r="AL2" t="n">
-        <v>3.83</v>
+        <v>4</v>
       </c>
       <c r="AM2" t="n">
         <v>-1</v>
       </c>
       <c r="AN2" t="n">
-        <v>40.33</v>
+        <v>38.73</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.83</v>
+        <v>0.73</v>
       </c>
       <c r="AP2" t="n">
         <v>-1</v>
       </c>
       <c r="AQ2" t="n">
-        <v>14.08</v>
+        <v>14.6</v>
       </c>
       <c r="AR2" t="n">
-        <v>17.75</v>
+        <v>16.8</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.67</v>
+        <v>7.6</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.17</v>
+        <v>0.13</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.17</v>
+        <v>0.13</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>45.08</v>
+        <v>43.6</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.58</v>
+        <v>0.47</v>
       </c>
       <c r="BA2" t="n">
-        <v>10.67</v>
+        <v>10.33</v>
       </c>
       <c r="BB2" t="n">
-        <v>7.75</v>
+        <v>7.33</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="BD2" t="n">
-        <v>20.67</v>
+        <v>20.53</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.83</v>
+        <v>1.6</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="BH2" t="n">
-        <v>8.960000000000001</v>
+        <v>9.07</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.58</v>
+        <v>0.53</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="BP2" t="n">
         <v>-1</v>
@@ -1586,40 +1574,40 @@
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>70.83</v>
+        <v>76.67</v>
       </c>
       <c r="BT2" t="n">
-        <v>45.83</v>
+        <v>40</v>
       </c>
       <c r="BU2" t="n">
-        <v>25</v>
+        <v>23.33</v>
       </c>
       <c r="BV2" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>56.67</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="CD2" t="n">
         <v>4.17</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>4.17</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>54.17</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>3.47</v>
-      </c>
-      <c r="CB2" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="CC2" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="CD2" t="n">
-        <v>3.43</v>
       </c>
       <c r="CE2" t="n">
         <v>1.41</v>
@@ -1628,31 +1616,31 @@
         <v>2.94</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="CH2" t="n">
         <v>1.4</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="CP2" t="n">
         <v>2.03</v>
@@ -1664,10 +1652,10 @@
         <v>1.38</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="CT2" t="n">
-        <v>3.12</v>
+        <v>3.13</v>
       </c>
       <c r="CU2" t="n">
         <v>1.44</v>
@@ -1679,16 +1667,16 @@
         <v>1.85</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CY2" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="DB2" t="n">
         <v>1.32</v>
@@ -1700,31 +1688,31 @@
         <v>3.53</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="DG2" t="n">
         <v>-1</v>
       </c>
       <c r="DH2" t="n">
-        <v>90.12</v>
+        <v>88.03</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.34</v>
+        <v>2.16</v>
       </c>
       <c r="DK2" t="n">
-        <v>4.38</v>
+        <v>4.54</v>
       </c>
       <c r="DL2" t="n">
         <v>-1</v>
       </c>
       <c r="DM2" t="n">
-        <v>43.04</v>
+        <v>42.73</v>
       </c>
       <c r="DN2" t="n">
         <v>0.5</v>
@@ -1733,46 +1721,46 @@
         <v>-1</v>
       </c>
       <c r="DP2" t="n">
-        <v>12.29</v>
+        <v>12.84</v>
       </c>
       <c r="DQ2" t="n">
-        <v>17.12</v>
+        <v>16.9</v>
       </c>
       <c r="DR2" t="n">
-        <v>7.04</v>
+        <v>6.9</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.17</v>
+        <v>0.13</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.17</v>
+        <v>0.13</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>45.54</v>
+        <v>45.3</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.33</v>
+        <v>0.27</v>
       </c>
       <c r="DX2" t="n">
-        <v>12.21</v>
+        <v>11.76</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.619999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="DZ2" t="n">
-        <v>3.58</v>
+        <v>3.47</v>
       </c>
       <c r="EA2" t="n">
-        <v>21.17</v>
+        <v>21.2</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="3">
@@ -1782,16 +1770,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="C3" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D3" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F3" t="n">
         <v>0.73</v>
@@ -1800,184 +1788,184 @@
         <v>-1</v>
       </c>
       <c r="H3" t="n">
-        <v>99.45</v>
+        <v>97.87</v>
       </c>
       <c r="I3" t="n">
-        <v>0.18</v>
+        <v>0.13</v>
       </c>
       <c r="J3" t="n">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="K3" t="n">
-        <v>3.82</v>
+        <v>4.07</v>
       </c>
       <c r="L3" t="n">
         <v>-1</v>
       </c>
       <c r="M3" t="n">
-        <v>50.55</v>
+        <v>50.2</v>
       </c>
       <c r="N3" t="n">
-        <v>0.82</v>
+        <v>0.67</v>
       </c>
       <c r="O3" t="n">
         <v>-1</v>
       </c>
       <c r="P3" t="n">
-        <v>15.09</v>
+        <v>14.4</v>
       </c>
       <c r="Q3" t="n">
-        <v>15.64</v>
+        <v>14.87</v>
       </c>
       <c r="R3" t="n">
-        <v>7.45</v>
+        <v>7.6</v>
       </c>
       <c r="S3" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="T3" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>46.87</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>7.07</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>20.07</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>82.2</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>40</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>41.87</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>10.53</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>17.73</v>
+      </c>
+      <c r="BE3" t="n">
         <v>1.18</v>
       </c>
-      <c r="U3" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>46.82</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>11.36</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>7</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>4.36</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>19.18</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>81.83</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>3.83</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>38.92</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>14.58</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>14.08</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>8.17</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>41.17</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>10.67</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>7.25</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>17</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>1.2</v>
-      </c>
       <c r="BF3" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.96</v>
+        <v>2.93</v>
       </c>
       <c r="BH3" t="n">
-        <v>8.83</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.96</v>
+        <v>2.93</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.91</v>
+        <v>0.93</v>
       </c>
       <c r="BK3" t="n">
         <v>0.7</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.65</v>
+        <v>0.57</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="BP3" t="n">
         <v>-1</v>
@@ -1989,91 +1977,91 @@
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>91.3</v>
+        <v>86.67</v>
       </c>
       <c r="BT3" t="n">
-        <v>52.17</v>
+        <v>50</v>
       </c>
       <c r="BU3" t="n">
-        <v>26.09</v>
+        <v>30</v>
       </c>
       <c r="BV3" t="n">
-        <v>13.04</v>
+        <v>16.67</v>
       </c>
       <c r="BW3" t="n">
-        <v>8.699999999999999</v>
+        <v>6.67</v>
       </c>
       <c r="BX3" t="n">
-        <v>69.56999999999999</v>
+        <v>70</v>
       </c>
       <c r="BY3" t="n">
-        <v>3.38</v>
+        <v>3.45</v>
       </c>
       <c r="BZ3" t="n">
-        <v>3.65</v>
+        <v>3.68</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.99</v>
+        <v>3.91</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.29</v>
+        <v>4.16</v>
       </c>
       <c r="CC3" t="n">
-        <v>5.73</v>
+        <v>5.35</v>
       </c>
       <c r="CD3" t="n">
-        <v>6.14</v>
+        <v>5.7</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.55</v>
+        <v>2.61</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.31</v>
+        <v>3.23</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="CI3" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="CJ3" t="n">
         <v>1.72</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.93</v>
+        <v>1.99</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.51</v>
+        <v>2.45</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="CR3" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.71</v>
+        <v>2.77</v>
       </c>
       <c r="CT3" t="n">
-        <v>3.11</v>
+        <v>3.06</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="CV3" t="n">
         <v>2.16</v>
@@ -2082,100 +2070,100 @@
         <v>1.76</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="DD3" t="n">
-        <v>2.87</v>
+        <v>3.03</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="DG3" t="n">
         <v>-1</v>
       </c>
       <c r="DH3" t="n">
-        <v>90.26000000000001</v>
+        <v>90.04000000000001</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.17</v>
+        <v>0.13</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="DK3" t="n">
-        <v>3.83</v>
+        <v>3.87</v>
       </c>
       <c r="DL3" t="n">
         <v>-1</v>
       </c>
       <c r="DM3" t="n">
-        <v>44.48</v>
+        <v>45.1</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="DO3" t="n">
         <v>-1</v>
       </c>
       <c r="DP3" t="n">
-        <v>14.82</v>
+        <v>14</v>
       </c>
       <c r="DQ3" t="n">
-        <v>14.83</v>
+        <v>14.63</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.83</v>
+        <v>7.9</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.22</v>
+        <v>0.24</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.22</v>
+        <v>0.24</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>43.87</v>
+        <v>44.37</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="DX3" t="n">
-        <v>11</v>
+        <v>11.26</v>
       </c>
       <c r="DY3" t="n">
-        <v>7.13</v>
+        <v>7.24</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.87</v>
+        <v>4.03</v>
       </c>
       <c r="EA3" t="n">
-        <v>18.04</v>
+        <v>18.9</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="4">
@@ -2185,202 +2173,202 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E4" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>88.93000000000001</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>49.13</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="O4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P4" t="n">
+        <v>19.27</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>12.47</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U4" t="n">
         <v>0.33</v>
       </c>
-      <c r="F4" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="G4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="H4" t="n">
-        <v>85.67</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="J4" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="K4" t="n">
+      <c r="V4" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>46.87</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>13.27</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>22.47</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>90.2</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AL4" t="n">
         <v>3.33</v>
       </c>
-      <c r="L4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M4" t="n">
+      <c r="AM4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>42</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>19.27</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>12.87</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>7.67</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY4" t="n">
         <v>46</v>
       </c>
-      <c r="N4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="P4" t="n">
-        <v>18.83</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>13</v>
-      </c>
-      <c r="R4" t="n">
-        <v>7</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>44.75</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>13.17</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>8.83</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>93.67</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>43.08</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>19.42</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>13</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>8.08</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>48.08</v>
-      </c>
       <c r="AZ4" t="n">
-        <v>0.08</v>
+        <v>0.13</v>
       </c>
       <c r="BA4" t="n">
         <v>12</v>
       </c>
       <c r="BB4" t="n">
-        <v>7.92</v>
+        <v>7.93</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.08</v>
+        <v>4.07</v>
       </c>
       <c r="BD4" t="n">
-        <v>20.67</v>
+        <v>20.2</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="BF4" t="n">
-        <v>3.17</v>
+        <v>3.2</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="BH4" t="n">
-        <v>8.08</v>
+        <v>7.83</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.42</v>
+        <v>0.37</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="BL4" t="n">
         <v>0.67</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="BP4" t="n">
         <v>-1</v>
@@ -2389,43 +2377,43 @@
         <v>-1</v>
       </c>
       <c r="BR4" t="n">
-        <v>83.33</v>
+        <v>86.67</v>
       </c>
       <c r="BS4" t="n">
-        <v>66.67</v>
+        <v>63.33</v>
       </c>
       <c r="BT4" t="n">
-        <v>25</v>
+        <v>26.67</v>
       </c>
       <c r="BU4" t="n">
         <v>16.67</v>
       </c>
       <c r="BV4" t="n">
-        <v>4.17</v>
+        <v>3.33</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>33.33</v>
+        <v>36.67</v>
       </c>
       <c r="BY4" t="n">
-        <v>2.29</v>
+        <v>2.24</v>
       </c>
       <c r="BZ4" t="n">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.44</v>
+        <v>3.46</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.54</v>
+        <v>3.56</v>
       </c>
       <c r="CC4" t="n">
-        <v>3.5</v>
+        <v>3.59</v>
       </c>
       <c r="CD4" t="n">
-        <v>3.76</v>
+        <v>3.87</v>
       </c>
       <c r="CE4" t="n">
         <v>1.43</v>
@@ -2434,37 +2422,37 @@
         <v>3.14</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="CI4" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="CJ4" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.96</v>
+        <v>2.08</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.27</v>
+        <v>2.23</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CQ4" t="n">
-        <v>4.12</v>
+        <v>4.08</v>
       </c>
       <c r="CR4" t="n">
         <v>1.47</v>
@@ -2485,100 +2473,100 @@
         <v>2.14</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="CY4" t="n">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.41</v>
+        <v>2.32</v>
       </c>
       <c r="DD4" t="n">
-        <v>4.55</v>
+        <v>4.33</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="DG4" t="n">
         <v>-1</v>
       </c>
       <c r="DH4" t="n">
-        <v>89.67</v>
+        <v>89.56</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="DJ4" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="DK4" t="n">
-        <v>3.42</v>
+        <v>3.47</v>
       </c>
       <c r="DL4" t="n">
         <v>-1</v>
       </c>
       <c r="DM4" t="n">
-        <v>44.54</v>
+        <v>45.57</v>
       </c>
       <c r="DN4" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="DO4" t="n">
         <v>-1</v>
       </c>
       <c r="DP4" t="n">
-        <v>19.12</v>
+        <v>19.27</v>
       </c>
       <c r="DQ4" t="n">
-        <v>13</v>
+        <v>12.67</v>
       </c>
       <c r="DR4" t="n">
-        <v>7.54</v>
+        <v>6.97</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>46.42</v>
+        <v>46.43</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.08</v>
+        <v>0.13</v>
       </c>
       <c r="DX4" t="n">
-        <v>12.58</v>
+        <v>12.63</v>
       </c>
       <c r="DY4" t="n">
-        <v>8.380000000000001</v>
+        <v>8.56</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.2</v>
+        <v>4.07</v>
       </c>
       <c r="EA4" t="n">
-        <v>21.08</v>
+        <v>21.33</v>
       </c>
       <c r="EB4" t="n">
         <v>1.42</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="5">
@@ -2588,13 +2576,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="C5" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D5" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E5" t="n">
         <v>0.27</v>
@@ -2606,43 +2594,43 @@
         <v>-1</v>
       </c>
       <c r="H5" t="n">
-        <v>105.09</v>
+        <v>103.2</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="K5" t="n">
-        <v>5.27</v>
+        <v>5.47</v>
       </c>
       <c r="L5" t="n">
         <v>-1</v>
       </c>
       <c r="M5" t="n">
-        <v>52.36</v>
+        <v>51.53</v>
       </c>
       <c r="N5" t="n">
-        <v>0.64</v>
+        <v>0.53</v>
       </c>
       <c r="O5" t="n">
         <v>-1</v>
       </c>
       <c r="P5" t="n">
-        <v>10.91</v>
+        <v>11.13</v>
       </c>
       <c r="Q5" t="n">
-        <v>17.27</v>
+        <v>16.33</v>
       </c>
       <c r="R5" t="n">
-        <v>8.359999999999999</v>
+        <v>8.07</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="T5" t="n">
-        <v>2.18</v>
+        <v>1.93</v>
       </c>
       <c r="U5" t="n">
         <v>0.27</v>
@@ -2654,136 +2642,136 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>58.55</v>
+        <v>57.6</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Z5" t="n">
-        <v>14.64</v>
+        <v>14.13</v>
       </c>
       <c r="AA5" t="n">
-        <v>9.550000000000001</v>
+        <v>9.33</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.09</v>
+        <v>4.8</v>
       </c>
       <c r="AC5" t="n">
-        <v>20.73</v>
+        <v>21</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AH5" t="n">
         <v>-1</v>
       </c>
       <c r="AI5" t="n">
-        <v>97.58</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="AJ5" t="n">
         <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AL5" t="n">
-        <v>5.58</v>
+        <v>5.2</v>
       </c>
       <c r="AM5" t="n">
         <v>-1</v>
       </c>
       <c r="AN5" t="n">
-        <v>46.92</v>
+        <v>49.13</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AP5" t="n">
         <v>-1</v>
       </c>
       <c r="AQ5" t="n">
-        <v>13</v>
+        <v>12.2</v>
       </c>
       <c r="AR5" t="n">
         <v>14.67</v>
       </c>
       <c r="AS5" t="n">
-        <v>9.67</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="AU5" t="n">
         <v>1</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.17</v>
+        <v>0.13</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.17</v>
+        <v>0.13</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>54.33</v>
+        <v>55</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="BA5" t="n">
-        <v>13.25</v>
+        <v>13.53</v>
       </c>
       <c r="BB5" t="n">
-        <v>9.25</v>
+        <v>9.6</v>
       </c>
       <c r="BC5" t="n">
-        <v>4</v>
+        <v>3.93</v>
       </c>
       <c r="BD5" t="n">
-        <v>21.83</v>
+        <v>20.87</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="BF5" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.65</v>
+        <v>2.57</v>
       </c>
       <c r="BH5" t="n">
-        <v>11</v>
+        <v>11.03</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.65</v>
+        <v>2.57</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.96</v>
+        <v>0.83</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.61</v>
+        <v>0.57</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.39</v>
+        <v>0.5</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="BP5" t="n">
         <v>-1</v>
@@ -2792,43 +2780,43 @@
         <v>-1</v>
       </c>
       <c r="BR5" t="n">
-        <v>95.65000000000001</v>
+        <v>93.33</v>
       </c>
       <c r="BS5" t="n">
-        <v>65.22</v>
+        <v>66.67</v>
       </c>
       <c r="BT5" t="n">
-        <v>47.83</v>
+        <v>46.67</v>
       </c>
       <c r="BU5" t="n">
-        <v>34.78</v>
+        <v>33.33</v>
       </c>
       <c r="BV5" t="n">
-        <v>17.39</v>
+        <v>13.33</v>
       </c>
       <c r="BW5" t="n">
-        <v>4.35</v>
+        <v>3.33</v>
       </c>
       <c r="BX5" t="n">
-        <v>52.17</v>
+        <v>56.67</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.86</v>
+        <v>2.03</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1.92</v>
+        <v>2.15</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.7</v>
+        <v>3.77</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.82</v>
+        <v>3.87</v>
       </c>
       <c r="CC5" t="n">
-        <v>2.79</v>
+        <v>2.67</v>
       </c>
       <c r="CD5" t="n">
-        <v>2.99</v>
+        <v>2.84</v>
       </c>
       <c r="CE5" t="n">
         <v>1.38</v>
@@ -2840,25 +2828,25 @@
         <v>3</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CJ5" t="n">
         <v>1.8</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CO5" t="n">
         <v>1.28</v>
@@ -2867,19 +2855,19 @@
         <v>1.94</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="CR5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="CS5" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="CT5" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="CU5" t="n">
         <v>1.42</v>
-      </c>
-      <c r="CS5" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="CT5" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="CU5" t="n">
-        <v>1.4</v>
       </c>
       <c r="CV5" t="n">
         <v>2.05</v>
@@ -2888,100 +2876,100 @@
         <v>1.84</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CY5" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="CZ5" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="DA5" t="n">
         <v>1.91</v>
-      </c>
-      <c r="CZ5" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="DA5" t="n">
-        <v>1.9</v>
       </c>
       <c r="DB5" t="n">
         <v>1.3</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.36</v>
+        <v>3.34</v>
       </c>
       <c r="DE5" t="n">
         <v>0.17</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="DG5" t="n">
         <v>-1</v>
       </c>
       <c r="DH5" t="n">
-        <v>101.17</v>
+        <v>100.9</v>
       </c>
       <c r="DI5" t="n">
         <v>0</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.04</v>
+        <v>1.9</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.43</v>
+        <v>5.34</v>
       </c>
       <c r="DL5" t="n">
         <v>-1</v>
       </c>
       <c r="DM5" t="n">
-        <v>49.52</v>
+        <v>50.33</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="DO5" t="n">
         <v>-1</v>
       </c>
       <c r="DP5" t="n">
-        <v>12</v>
+        <v>11.66</v>
       </c>
       <c r="DQ5" t="n">
-        <v>15.91</v>
+        <v>15.5</v>
       </c>
       <c r="DR5" t="n">
-        <v>9.039999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>56.35</v>
+        <v>56.3</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.17</v>
+        <v>0.13</v>
       </c>
       <c r="DX5" t="n">
-        <v>13.91</v>
+        <v>13.83</v>
       </c>
       <c r="DY5" t="n">
-        <v>9.390000000000001</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="DZ5" t="n">
-        <v>4.52</v>
+        <v>4.36</v>
       </c>
       <c r="EA5" t="n">
-        <v>21.3</v>
+        <v>20.94</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="6">
@@ -2991,298 +2979,298 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="C6" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.58</v>
+        <v>0.73</v>
       </c>
       <c r="G6" t="n">
         <v>-1</v>
       </c>
       <c r="H6" t="n">
-        <v>99.75</v>
+        <v>97.87</v>
       </c>
       <c r="I6" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="K6" t="n">
-        <v>5.33</v>
+        <v>5.27</v>
       </c>
       <c r="L6" t="n">
         <v>-1</v>
       </c>
       <c r="M6" t="n">
-        <v>52</v>
+        <v>50.33</v>
       </c>
       <c r="N6" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="O6" t="n">
         <v>-1</v>
       </c>
       <c r="P6" t="n">
-        <v>12.25</v>
+        <v>12.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>17.17</v>
+        <v>17.4</v>
       </c>
       <c r="R6" t="n">
-        <v>5.25</v>
+        <v>5.93</v>
       </c>
       <c r="S6" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="T6" t="n">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="U6" t="n">
-        <v>0.17</v>
+        <v>0.13</v>
       </c>
       <c r="V6" t="n">
-        <v>0.17</v>
+        <v>0.13</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>57.08</v>
+        <v>55.87</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>16.33</v>
+        <v>15.6</v>
       </c>
       <c r="AA6" t="n">
-        <v>10.92</v>
+        <v>10.13</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.42</v>
+        <v>5.47</v>
       </c>
       <c r="AC6" t="n">
-        <v>20.75</v>
+        <v>21</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AH6" t="n">
         <v>-1</v>
       </c>
       <c r="AI6" t="n">
-        <v>91</v>
+        <v>92.33</v>
       </c>
       <c r="AJ6" t="n">
         <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.64</v>
+        <v>2.4</v>
       </c>
       <c r="AL6" t="n">
-        <v>5.27</v>
+        <v>5.67</v>
       </c>
       <c r="AM6" t="n">
         <v>-1</v>
       </c>
       <c r="AN6" t="n">
-        <v>49</v>
+        <v>47.67</v>
       </c>
       <c r="AO6" t="n">
-        <v>1</v>
+        <v>0.73</v>
       </c>
       <c r="AP6" t="n">
         <v>-1</v>
       </c>
       <c r="AQ6" t="n">
-        <v>14.55</v>
+        <v>13.2</v>
       </c>
       <c r="AR6" t="n">
-        <v>15.36</v>
+        <v>16.27</v>
       </c>
       <c r="AS6" t="n">
-        <v>6.36</v>
+        <v>6.07</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="AX6" t="n">
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>51.91</v>
+        <v>53.13</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BA6" t="n">
-        <v>15.45</v>
+        <v>15</v>
       </c>
       <c r="BB6" t="n">
-        <v>11.64</v>
+        <v>10.87</v>
       </c>
       <c r="BC6" t="n">
-        <v>3.82</v>
+        <v>4.13</v>
       </c>
       <c r="BD6" t="n">
-        <v>20.64</v>
+        <v>21.33</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="BF6" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>10.17</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>96.67</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>80</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>60</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>36.67</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>16.67</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>2</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="CF6" t="n">
         <v>2.55</v>
       </c>
-      <c r="BG6" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>9.779999999999999</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>95.65000000000001</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>78.26000000000001</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>65.22</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>43.48</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>17.39</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="BX6" t="n">
-        <v>65.22</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="BZ6" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="CA6" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="CB6" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="CC6" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="CD6" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="CE6" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="CF6" t="n">
-        <v>2.57</v>
-      </c>
       <c r="CG6" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CI6" t="n">
         <v>2.15</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="CN6" t="n">
         <v>1.96</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="CR6" t="n">
         <v>1.36</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="CT6" t="n">
         <v>3.21</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="CV6" t="n">
         <v>2.22</v>
@@ -3291,67 +3279,67 @@
         <v>1.71</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="DB6" t="n">
         <v>1.25</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.99</v>
+        <v>2.97</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="DG6" t="n">
         <v>-1</v>
       </c>
       <c r="DH6" t="n">
-        <v>95.56999999999999</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="DI6" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="DK6" t="n">
-        <v>5.3</v>
+        <v>5.47</v>
       </c>
       <c r="DL6" t="n">
         <v>-1</v>
       </c>
       <c r="DM6" t="n">
-        <v>50.57</v>
+        <v>49</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.91</v>
+        <v>0.76</v>
       </c>
       <c r="DO6" t="n">
         <v>-1</v>
       </c>
       <c r="DP6" t="n">
-        <v>13.35</v>
+        <v>12.9</v>
       </c>
       <c r="DQ6" t="n">
-        <v>16.3</v>
+        <v>16.83</v>
       </c>
       <c r="DR6" t="n">
-        <v>5.78</v>
+        <v>6</v>
       </c>
       <c r="DS6" t="n">
         <v>0.13</v>
@@ -3363,28 +3351,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>54.61</v>
+        <v>54.5</v>
       </c>
       <c r="DW6" t="n">
         <v>0.04</v>
       </c>
       <c r="DX6" t="n">
-        <v>15.91</v>
+        <v>15.3</v>
       </c>
       <c r="DY6" t="n">
-        <v>11.26</v>
+        <v>10.5</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.65</v>
+        <v>4.8</v>
       </c>
       <c r="EA6" t="n">
-        <v>20.7</v>
+        <v>21.17</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="EC6" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="7">
@@ -3394,203 +3382,203 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="C7" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="G7" t="n">
         <v>-1</v>
       </c>
       <c r="H7" t="n">
-        <v>80</v>
+        <v>78.53</v>
       </c>
       <c r="I7" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>2.33</v>
+        <v>2.27</v>
       </c>
       <c r="K7" t="n">
-        <v>4.42</v>
+        <v>4.67</v>
       </c>
       <c r="L7" t="n">
         <v>-1</v>
       </c>
       <c r="M7" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="N7" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="O7" t="n">
         <v>-1</v>
       </c>
       <c r="P7" t="n">
-        <v>14</v>
+        <v>13.87</v>
       </c>
       <c r="Q7" t="n">
-        <v>14.75</v>
+        <v>14.33</v>
       </c>
       <c r="R7" t="n">
-        <v>8.42</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="S7" t="n">
-        <v>2.08</v>
+        <v>1.87</v>
       </c>
       <c r="T7" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>45.5</v>
+        <v>47.4</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>8.92</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="AA7" t="n">
-        <v>6.17</v>
+        <v>6.73</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.75</v>
+        <v>3.13</v>
       </c>
       <c r="AC7" t="n">
-        <v>17.58</v>
+        <v>17.73</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.33</v>
+        <v>2.27</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AH7" t="n">
         <v>-1</v>
       </c>
       <c r="AI7" t="n">
-        <v>83.55</v>
+        <v>83.87</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="AL7" t="n">
-        <v>2.27</v>
+        <v>2.67</v>
       </c>
       <c r="AM7" t="n">
         <v>-1</v>
       </c>
       <c r="AN7" t="n">
-        <v>32.91</v>
+        <v>34.87</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.73</v>
+        <v>0.93</v>
       </c>
       <c r="AP7" t="n">
         <v>-1</v>
       </c>
       <c r="AQ7" t="n">
-        <v>15.36</v>
+        <v>16</v>
       </c>
       <c r="AR7" t="n">
-        <v>15</v>
+        <v>13.8</v>
       </c>
       <c r="AS7" t="n">
-        <v>9.27</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="AT7" t="n">
-        <v>2.55</v>
+        <v>2.13</v>
       </c>
       <c r="AU7" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="AX7" t="n">
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>47.36</v>
+        <v>45.87</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.18</v>
+        <v>0.13</v>
       </c>
       <c r="BA7" t="n">
-        <v>7.45</v>
+        <v>7.87</v>
       </c>
       <c r="BB7" t="n">
-        <v>5</v>
+        <v>5.27</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="BD7" t="n">
-        <v>18.36</v>
+        <v>18.87</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.89</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.18</v>
+        <v>2.4</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.17</v>
+        <v>2.97</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.300000000000001</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.17</v>
+        <v>2.97</v>
       </c>
       <c r="BJ7" t="n">
         <v>0.43</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.83</v>
+        <v>0.73</v>
       </c>
       <c r="BL7" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO7" t="n">
         <v>1.17</v>
       </c>
-      <c r="BM7" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>1.26</v>
-      </c>
       <c r="BP7" t="n">
         <v>-1</v>
       </c>
@@ -3598,196 +3586,196 @@
         <v>-1</v>
       </c>
       <c r="BR7" t="n">
-        <v>91.3</v>
+        <v>93.33</v>
       </c>
       <c r="BS7" t="n">
-        <v>82.61</v>
+        <v>80</v>
       </c>
       <c r="BT7" t="n">
-        <v>69.56999999999999</v>
+        <v>63.33</v>
       </c>
       <c r="BU7" t="n">
-        <v>39.13</v>
+        <v>33.33</v>
       </c>
       <c r="BV7" t="n">
-        <v>21.74</v>
+        <v>16.67</v>
       </c>
       <c r="BW7" t="n">
-        <v>13.04</v>
+        <v>10</v>
       </c>
       <c r="BX7" t="n">
-        <v>56.52</v>
+        <v>56.67</v>
       </c>
       <c r="BY7" t="n">
-        <v>4.62</v>
+        <v>4.21</v>
       </c>
       <c r="BZ7" t="n">
-        <v>4.85</v>
+        <v>4.49</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.71</v>
+        <v>4</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.96</v>
+        <v>4.21</v>
       </c>
       <c r="CC7" t="n">
-        <v>5.14</v>
+        <v>6.4</v>
       </c>
       <c r="CD7" t="n">
-        <v>5.78</v>
+        <v>7.01</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.96</v>
+        <v>2.87</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.94</v>
+        <v>3.04</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.49</v>
+        <v>3.32</v>
       </c>
       <c r="CR7" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.96</v>
+        <v>2.83</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="CV7" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CW7" t="n">
         <v>2</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CY7" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.11</v>
+        <v>2.04</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.76</v>
+        <v>3.6</v>
       </c>
       <c r="DE7" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="DG7" t="n">
         <v>-1</v>
       </c>
       <c r="DH7" t="n">
-        <v>81.7</v>
+        <v>81.2</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.39</v>
+        <v>2.44</v>
       </c>
       <c r="DK7" t="n">
-        <v>3.39</v>
+        <v>3.67</v>
       </c>
       <c r="DL7" t="n">
         <v>-1</v>
       </c>
       <c r="DM7" t="n">
-        <v>35.57</v>
+        <v>36.93</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.78</v>
+        <v>0.87</v>
       </c>
       <c r="DO7" t="n">
         <v>-1</v>
       </c>
       <c r="DP7" t="n">
-        <v>14.65</v>
+        <v>14.93</v>
       </c>
       <c r="DQ7" t="n">
-        <v>14.87</v>
+        <v>14.06</v>
       </c>
       <c r="DR7" t="n">
-        <v>8.83</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>46.39</v>
+        <v>46.64</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="DX7" t="n">
-        <v>8.220000000000001</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="DY7" t="n">
-        <v>5.61</v>
+        <v>6</v>
       </c>
       <c r="DZ7" t="n">
-        <v>2.61</v>
+        <v>2.86</v>
       </c>
       <c r="EA7" t="n">
-        <v>17.95</v>
+        <v>18.3</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.97</v>
+        <v>1.03</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="8">
@@ -3797,202 +3785,202 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="C8" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D8" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E8" t="n">
-        <v>0.17</v>
+        <v>0.13</v>
       </c>
       <c r="F8" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="G8" t="n">
         <v>-1</v>
       </c>
       <c r="H8" t="n">
-        <v>95.42</v>
+        <v>90.33</v>
       </c>
       <c r="I8" t="n">
-        <v>0.17</v>
+        <v>0.13</v>
       </c>
       <c r="J8" t="n">
-        <v>2.67</v>
+        <v>2.53</v>
       </c>
       <c r="K8" t="n">
-        <v>6.17</v>
+        <v>6</v>
       </c>
       <c r="L8" t="n">
         <v>-1</v>
       </c>
       <c r="M8" t="n">
-        <v>51.25</v>
+        <v>49.67</v>
       </c>
       <c r="N8" t="n">
-        <v>0.83</v>
+        <v>0.87</v>
       </c>
       <c r="O8" t="n">
         <v>-1</v>
       </c>
       <c r="P8" t="n">
-        <v>13.67</v>
+        <v>13.13</v>
       </c>
       <c r="Q8" t="n">
-        <v>16.08</v>
+        <v>15.33</v>
       </c>
       <c r="R8" t="n">
-        <v>6.42</v>
+        <v>6.4</v>
       </c>
       <c r="S8" t="n">
-        <v>0.83</v>
+        <v>0.87</v>
       </c>
       <c r="T8" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="U8" t="n">
-        <v>0.17</v>
+        <v>0.13</v>
       </c>
       <c r="V8" t="n">
-        <v>0.17</v>
+        <v>0.13</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>60.25</v>
+        <v>61.53</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="Z8" t="n">
-        <v>18.83</v>
+        <v>18.8</v>
       </c>
       <c r="AA8" t="n">
-        <v>13.42</v>
+        <v>13.07</v>
       </c>
       <c r="AB8" t="n">
-        <v>5.42</v>
+        <v>5.73</v>
       </c>
       <c r="AC8" t="n">
-        <v>20.83</v>
+        <v>21</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.42</v>
+        <v>2.33</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.27</v>
+        <v>0.2</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AH8" t="n">
         <v>-1</v>
       </c>
       <c r="AI8" t="n">
-        <v>91</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AK8" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AL8" t="n">
-        <v>4.55</v>
+        <v>4.33</v>
       </c>
       <c r="AM8" t="n">
         <v>-1</v>
       </c>
       <c r="AN8" t="n">
-        <v>39.64</v>
+        <v>41.2</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.55</v>
+        <v>0.4</v>
       </c>
       <c r="AP8" t="n">
         <v>-1</v>
       </c>
       <c r="AQ8" t="n">
-        <v>14</v>
+        <v>14.2</v>
       </c>
       <c r="AR8" t="n">
-        <v>18.73</v>
+        <v>17.67</v>
       </c>
       <c r="AS8" t="n">
-        <v>8.449999999999999</v>
+        <v>7.87</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.55</v>
+        <v>0.67</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>58.18</v>
+        <v>58.13</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.18</v>
+        <v>0.13</v>
       </c>
       <c r="BA8" t="n">
-        <v>13.45</v>
+        <v>13.13</v>
       </c>
       <c r="BB8" t="n">
-        <v>8.82</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.64</v>
+        <v>4.6</v>
       </c>
       <c r="BD8" t="n">
-        <v>19.91</v>
+        <v>20.07</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="BH8" t="n">
-        <v>8.91</v>
+        <v>8.6</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="BK8" t="n">
         <v>0.57</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.87</v>
+        <v>0.9</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BN8" t="n">
         <v>1.57</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="BP8" t="n">
         <v>-1</v>
@@ -4001,52 +3989,52 @@
         <v>-1</v>
       </c>
       <c r="BR8" t="n">
-        <v>95.65000000000001</v>
+        <v>96.67</v>
       </c>
       <c r="BS8" t="n">
-        <v>78.26000000000001</v>
+        <v>80</v>
       </c>
       <c r="BT8" t="n">
-        <v>52.17</v>
+        <v>56.67</v>
       </c>
       <c r="BU8" t="n">
-        <v>21.74</v>
+        <v>20</v>
       </c>
       <c r="BV8" t="n">
-        <v>21.74</v>
+        <v>16.67</v>
       </c>
       <c r="BW8" t="n">
-        <v>8.699999999999999</v>
+        <v>6.67</v>
       </c>
       <c r="BX8" t="n">
-        <v>47.83</v>
+        <v>53.33</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="BZ8" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.95</v>
+        <v>4.02</v>
       </c>
       <c r="CB8" t="n">
-        <v>4.23</v>
+        <v>4.33</v>
       </c>
       <c r="CC8" t="n">
-        <v>1.85</v>
+        <v>2.02</v>
       </c>
       <c r="CD8" t="n">
-        <v>1.88</v>
+        <v>2.08</v>
       </c>
       <c r="CE8" t="n">
         <v>1.36</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.08</v>
+        <v>3.11</v>
       </c>
       <c r="CH8" t="n">
         <v>1.46</v>
@@ -4058,25 +4046,25 @@
         <v>1.85</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="CL8" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.41</v>
+        <v>2.36</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="CR8" t="n">
         <v>1.39</v>
@@ -4097,100 +4085,100 @@
         <v>1.91</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="DD8" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.22</v>
+        <v>0.16</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="DG8" t="n">
         <v>-1</v>
       </c>
       <c r="DH8" t="n">
-        <v>93.31</v>
+        <v>90.36</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.35</v>
+        <v>2.16</v>
       </c>
       <c r="DK8" t="n">
-        <v>5.4</v>
+        <v>5.16</v>
       </c>
       <c r="DL8" t="n">
         <v>-1</v>
       </c>
       <c r="DM8" t="n">
-        <v>45.7</v>
+        <v>45.44</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="DO8" t="n">
         <v>-1</v>
       </c>
       <c r="DP8" t="n">
-        <v>13.83</v>
+        <v>13.66</v>
       </c>
       <c r="DQ8" t="n">
-        <v>17.35</v>
+        <v>16.5</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.39</v>
+        <v>7.14</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>59.26</v>
+        <v>59.83</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.22</v>
+        <v>0.16</v>
       </c>
       <c r="DX8" t="n">
-        <v>16.26</v>
+        <v>15.97</v>
       </c>
       <c r="DY8" t="n">
-        <v>11.22</v>
+        <v>10.8</v>
       </c>
       <c r="DZ8" t="n">
-        <v>5.05</v>
+        <v>5.16</v>
       </c>
       <c r="EA8" t="n">
-        <v>20.39</v>
+        <v>20.54</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.09</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="9">
@@ -4200,202 +4188,202 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C9" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E9" t="n">
-        <v>0.27</v>
+        <v>0.2</v>
       </c>
       <c r="F9" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="G9" t="n">
         <v>-1</v>
       </c>
       <c r="H9" t="n">
-        <v>85.45</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1.91</v>
+        <v>2.07</v>
       </c>
       <c r="K9" t="n">
-        <v>4.82</v>
+        <v>4.53</v>
       </c>
       <c r="L9" t="n">
         <v>-1</v>
       </c>
       <c r="M9" t="n">
-        <v>39.45</v>
+        <v>37.13</v>
       </c>
       <c r="N9" t="n">
-        <v>0.55</v>
+        <v>0.67</v>
       </c>
       <c r="O9" t="n">
         <v>-1</v>
       </c>
       <c r="P9" t="n">
-        <v>14.45</v>
+        <v>14.07</v>
       </c>
       <c r="Q9" t="n">
-        <v>14.36</v>
+        <v>13.93</v>
       </c>
       <c r="R9" t="n">
-        <v>8.27</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="S9" t="n">
-        <v>1.27</v>
+        <v>1.13</v>
       </c>
       <c r="T9" t="n">
-        <v>1.36</v>
+        <v>1.6</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>47.27</v>
+        <v>44.73</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Z9" t="n">
-        <v>9.09</v>
+        <v>9.67</v>
       </c>
       <c r="AA9" t="n">
-        <v>6.09</v>
+        <v>6.27</v>
       </c>
       <c r="AB9" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="AC9" t="n">
-        <v>20.91</v>
+        <v>19.2</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AH9" t="n">
         <v>-1</v>
       </c>
       <c r="AI9" t="n">
-        <v>78.31</v>
+        <v>77.2</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.69</v>
+        <v>3.13</v>
       </c>
       <c r="AL9" t="n">
-        <v>2.54</v>
+        <v>2.87</v>
       </c>
       <c r="AM9" t="n">
         <v>-1</v>
       </c>
       <c r="AN9" t="n">
-        <v>32.46</v>
+        <v>33.53</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.85</v>
+        <v>0.87</v>
       </c>
       <c r="AP9" t="n">
         <v>-1</v>
       </c>
       <c r="AQ9" t="n">
-        <v>14.69</v>
+        <v>14.8</v>
       </c>
       <c r="AR9" t="n">
-        <v>13.23</v>
+        <v>13.4</v>
       </c>
       <c r="AS9" t="n">
-        <v>8.31</v>
+        <v>8.93</v>
       </c>
       <c r="AT9" t="n">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.77</v>
+        <v>0.73</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>46.77</v>
+        <v>47.67</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.08</v>
+        <v>0.2</v>
       </c>
       <c r="BA9" t="n">
-        <v>7.62</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB9" t="n">
-        <v>5.08</v>
+        <v>5.4</v>
       </c>
       <c r="BC9" t="n">
-        <v>2.54</v>
+        <v>2.8</v>
       </c>
       <c r="BD9" t="n">
-        <v>18.92</v>
+        <v>18.47</v>
       </c>
       <c r="BE9" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>9.470000000000001</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="BJ9" t="n">
         <v>0.9</v>
       </c>
-      <c r="BF9" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>9.210000000000001</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>0.83</v>
-      </c>
       <c r="BK9" t="n">
-        <v>0.46</v>
+        <v>0.4</v>
       </c>
       <c r="BL9" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.54</v>
+        <v>0.53</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="BP9" t="n">
         <v>-1</v>
@@ -4404,25 +4392,25 @@
         <v>-1</v>
       </c>
       <c r="BR9" t="n">
-        <v>95.83</v>
+        <v>96.67</v>
       </c>
       <c r="BS9" t="n">
-        <v>91.67</v>
+        <v>90</v>
       </c>
       <c r="BT9" t="n">
-        <v>45.83</v>
+        <v>46.67</v>
       </c>
       <c r="BU9" t="n">
-        <v>33.33</v>
+        <v>30</v>
       </c>
       <c r="BV9" t="n">
         <v>16.67</v>
       </c>
       <c r="BW9" t="n">
-        <v>4.17</v>
+        <v>3.33</v>
       </c>
       <c r="BX9" t="n">
-        <v>45.83</v>
+        <v>50</v>
       </c>
       <c r="BY9" t="n">
         <v>3.34</v>
@@ -4431,67 +4419,67 @@
         <v>3.57</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.85</v>
+        <v>3.78</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.94</v>
+        <v>3.88</v>
       </c>
       <c r="CC9" t="n">
-        <v>6.06</v>
+        <v>5.65</v>
       </c>
       <c r="CD9" t="n">
-        <v>6.33</v>
+        <v>5.93</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.93</v>
+        <v>2.89</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CI9" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="CJ9" t="n">
         <v>1.88</v>
-      </c>
-      <c r="CJ9" t="n">
-        <v>1.93</v>
       </c>
       <c r="CK9" t="n">
         <v>1.54</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="CP9" t="n">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.56</v>
+        <v>3.45</v>
       </c>
       <c r="CR9" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.96</v>
+        <v>2.93</v>
       </c>
       <c r="CT9" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CV9" t="n">
         <v>1.91</v>
@@ -4500,100 +4488,100 @@
         <v>1.98</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="CY9" t="n">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.84</v>
+        <v>3.71</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.17</v>
+        <v>0.13</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.63</v>
+        <v>1.8</v>
       </c>
       <c r="DG9" t="n">
         <v>-1</v>
       </c>
       <c r="DH9" t="n">
-        <v>81.58</v>
+        <v>77.8</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.33</v>
+        <v>2.6</v>
       </c>
       <c r="DK9" t="n">
-        <v>3.59</v>
+        <v>3.7</v>
       </c>
       <c r="DL9" t="n">
         <v>-1</v>
       </c>
       <c r="DM9" t="n">
-        <v>35.66</v>
+        <v>35.33</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.71</v>
+        <v>0.77</v>
       </c>
       <c r="DO9" t="n">
         <v>-1</v>
       </c>
       <c r="DP9" t="n">
-        <v>14.58</v>
+        <v>14.44</v>
       </c>
       <c r="DQ9" t="n">
-        <v>13.75</v>
+        <v>13.66</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.289999999999999</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>47</v>
+        <v>46.2</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.08</v>
+        <v>0.13</v>
       </c>
       <c r="DX9" t="n">
-        <v>8.289999999999999</v>
+        <v>8.94</v>
       </c>
       <c r="DY9" t="n">
-        <v>5.54</v>
+        <v>5.84</v>
       </c>
       <c r="DZ9" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="EA9" t="n">
-        <v>19.83</v>
+        <v>18.83</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.98</v>
+        <v>1.04</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.25</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="10">
@@ -4603,40 +4591,40 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D10" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E10" t="n">
         <v>0.27</v>
       </c>
       <c r="F10" t="n">
-        <v>1.45</v>
+        <v>1.8</v>
       </c>
       <c r="G10" t="n">
         <v>-1</v>
       </c>
       <c r="H10" t="n">
-        <v>93.27</v>
+        <v>95.67</v>
       </c>
       <c r="I10" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>2.18</v>
+        <v>2.53</v>
       </c>
       <c r="K10" t="n">
-        <v>3.91</v>
+        <v>4.27</v>
       </c>
       <c r="L10" t="n">
         <v>-1</v>
       </c>
       <c r="M10" t="n">
-        <v>47.64</v>
+        <v>50.67</v>
       </c>
       <c r="N10" t="n">
         <v>0.73</v>
@@ -4645,55 +4633,55 @@
         <v>-1</v>
       </c>
       <c r="P10" t="n">
-        <v>16.09</v>
+        <v>15.93</v>
       </c>
       <c r="Q10" t="n">
-        <v>13.64</v>
+        <v>13.2</v>
       </c>
       <c r="R10" t="n">
-        <v>6.64</v>
+        <v>6.47</v>
       </c>
       <c r="S10" t="n">
-        <v>1.09</v>
+        <v>0.93</v>
       </c>
       <c r="T10" t="n">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="V10" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>47.91</v>
+        <v>50</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.18</v>
+        <v>0.13</v>
       </c>
       <c r="Z10" t="n">
-        <v>15</v>
+        <v>14.73</v>
       </c>
       <c r="AA10" t="n">
-        <v>8.640000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AB10" t="n">
-        <v>6.36</v>
+        <v>5.93</v>
       </c>
       <c r="AC10" t="n">
-        <v>18.82</v>
+        <v>18.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="AE10" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AG10" t="n">
         <v>2</v>
@@ -4702,103 +4690,103 @@
         <v>-1</v>
       </c>
       <c r="AI10" t="n">
-        <v>92.92</v>
+        <v>90.53</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.17</v>
+        <v>0.13</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.83</v>
+        <v>2.87</v>
       </c>
       <c r="AL10" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="AM10" t="n">
         <v>-1</v>
       </c>
       <c r="AN10" t="n">
-        <v>44.83</v>
+        <v>46.8</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.83</v>
+        <v>0.87</v>
       </c>
       <c r="AP10" t="n">
         <v>-1</v>
       </c>
       <c r="AQ10" t="n">
-        <v>14.5</v>
+        <v>14.13</v>
       </c>
       <c r="AR10" t="n">
-        <v>15</v>
+        <v>14.27</v>
       </c>
       <c r="AS10" t="n">
-        <v>7.67</v>
+        <v>7.53</v>
       </c>
       <c r="AT10" t="n">
         <v>1.67</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.83</v>
+        <v>1.6</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.33</v>
+        <v>0.27</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.33</v>
+        <v>0.27</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>50.42</v>
+        <v>52</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="BA10" t="n">
-        <v>12.75</v>
+        <v>13.47</v>
       </c>
       <c r="BB10" t="n">
-        <v>7.92</v>
+        <v>8.73</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.83</v>
+        <v>4.73</v>
       </c>
       <c r="BD10" t="n">
-        <v>17.75</v>
+        <v>17.8</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.58</v>
+        <v>2.67</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.52</v>
+        <v>3.1</v>
       </c>
       <c r="BH10" t="n">
-        <v>8.83</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.52</v>
+        <v>3.1</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1</v>
+        <v>0.87</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.65</v>
+        <v>0.53</v>
       </c>
       <c r="BL10" t="n">
-        <v>1.04</v>
+        <v>0.97</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.83</v>
+        <v>0.73</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="BP10" t="n">
         <v>-1</v>
@@ -4807,94 +4795,94 @@
         <v>-1</v>
       </c>
       <c r="BR10" t="n">
-        <v>100</v>
+        <v>96.67</v>
       </c>
       <c r="BS10" t="n">
-        <v>91.3</v>
+        <v>83.33</v>
       </c>
       <c r="BT10" t="n">
-        <v>65.22</v>
+        <v>53.33</v>
       </c>
       <c r="BU10" t="n">
-        <v>39.13</v>
+        <v>33.33</v>
       </c>
       <c r="BV10" t="n">
-        <v>26.09</v>
+        <v>20</v>
       </c>
       <c r="BW10" t="n">
-        <v>21.74</v>
+        <v>16.67</v>
       </c>
       <c r="BX10" t="n">
-        <v>73.91</v>
+        <v>66.67</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="BZ10" t="n">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.69</v>
+        <v>3.67</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.88</v>
+        <v>3.85</v>
       </c>
       <c r="CC10" t="n">
-        <v>2.76</v>
+        <v>2.65</v>
       </c>
       <c r="CD10" t="n">
-        <v>3.05</v>
+        <v>2.87</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.71</v>
+        <v>2.79</v>
       </c>
       <c r="CR10" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="CT10" t="n">
-        <v>3.15</v>
+        <v>3.18</v>
       </c>
       <c r="CU10" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CV10" t="n">
         <v>2.21</v>
@@ -4906,97 +4894,97 @@
         <v>1.54</v>
       </c>
       <c r="CY10" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="DA10" t="n">
         <v>1.91</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.74</v>
+        <v>1.9</v>
       </c>
       <c r="DG10" t="n">
         <v>-1</v>
       </c>
       <c r="DH10" t="n">
-        <v>93.09</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.52</v>
+        <v>2.7</v>
       </c>
       <c r="DK10" t="n">
-        <v>3.96</v>
+        <v>4.44</v>
       </c>
       <c r="DL10" t="n">
         <v>-1</v>
       </c>
       <c r="DM10" t="n">
-        <v>46.17</v>
+        <v>48.74</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="DO10" t="n">
         <v>-1</v>
       </c>
       <c r="DP10" t="n">
-        <v>15.26</v>
+        <v>15.03</v>
       </c>
       <c r="DQ10" t="n">
-        <v>14.35</v>
+        <v>13.73</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.18</v>
+        <v>7</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.22</v>
+        <v>0.17</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.22</v>
+        <v>0.17</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>49.22</v>
+        <v>51</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.22</v>
+        <v>0.16</v>
       </c>
       <c r="DX10" t="n">
-        <v>13.83</v>
+        <v>14.1</v>
       </c>
       <c r="DY10" t="n">
-        <v>8.26</v>
+        <v>8.77</v>
       </c>
       <c r="DZ10" t="n">
-        <v>5.56</v>
+        <v>5.33</v>
       </c>
       <c r="EA10" t="n">
-        <v>18.26</v>
+        <v>18.2</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.3</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="11">
@@ -5006,16 +4994,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D11" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E11" t="n">
-        <v>0.17</v>
+        <v>0.13</v>
       </c>
       <c r="F11" t="n">
         <v>1.33</v>
@@ -5024,184 +5012,184 @@
         <v>-1</v>
       </c>
       <c r="H11" t="n">
-        <v>102.83</v>
+        <v>97.87</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="K11" t="n">
-        <v>5</v>
+        <v>4.73</v>
       </c>
       <c r="L11" t="n">
         <v>-1</v>
       </c>
       <c r="M11" t="n">
-        <v>49.75</v>
+        <v>48</v>
       </c>
       <c r="N11" t="n">
-        <v>0.58</v>
+        <v>0.67</v>
       </c>
       <c r="O11" t="n">
         <v>-1</v>
       </c>
       <c r="P11" t="n">
-        <v>13.83</v>
+        <v>14.07</v>
       </c>
       <c r="Q11" t="n">
-        <v>19.08</v>
+        <v>18.13</v>
       </c>
       <c r="R11" t="n">
-        <v>7.08</v>
+        <v>7.73</v>
       </c>
       <c r="S11" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="T11" t="n">
-        <v>0.92</v>
+        <v>0.8</v>
       </c>
       <c r="U11" t="n">
-        <v>0.25</v>
+        <v>0.27</v>
       </c>
       <c r="V11" t="n">
-        <v>0.25</v>
+        <v>0.27</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>48.58</v>
+        <v>47.2</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Z11" t="n">
-        <v>11</v>
+        <v>10.4</v>
       </c>
       <c r="AA11" t="n">
-        <v>8.08</v>
+        <v>7.73</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.92</v>
+        <v>2.67</v>
       </c>
       <c r="AC11" t="n">
-        <v>26.25</v>
+        <v>26.67</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AH11" t="n">
         <v>-1</v>
       </c>
       <c r="AI11" t="n">
-        <v>107.27</v>
+        <v>103</v>
       </c>
       <c r="AJ11" t="n">
         <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AL11" t="n">
-        <v>4.36</v>
+        <v>4.27</v>
       </c>
       <c r="AM11" t="n">
         <v>-1</v>
       </c>
       <c r="AN11" t="n">
-        <v>46.91</v>
+        <v>47.07</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.55</v>
+        <v>0.53</v>
       </c>
       <c r="AP11" t="n">
         <v>-1</v>
       </c>
       <c r="AQ11" t="n">
-        <v>13.64</v>
+        <v>13.47</v>
       </c>
       <c r="AR11" t="n">
-        <v>18.09</v>
+        <v>16.93</v>
       </c>
       <c r="AS11" t="n">
-        <v>6.73</v>
+        <v>7.73</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.27</v>
+        <v>0.47</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>47.82</v>
+        <v>46.13</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="BA11" t="n">
-        <v>9.359999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB11" t="n">
-        <v>6.73</v>
+        <v>6.47</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.64</v>
+        <v>2.73</v>
       </c>
       <c r="BD11" t="n">
-        <v>24.09</v>
+        <v>23.13</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="BG11" t="n">
         <v>1.87</v>
       </c>
       <c r="BH11" t="n">
-        <v>8.960000000000001</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="BI11" t="n">
         <v>1.87</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.78</v>
+        <v>0.67</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.22</v>
+        <v>0.27</v>
       </c>
       <c r="BL11" t="n">
         <v>0.57</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.3</v>
+        <v>0.37</v>
       </c>
       <c r="BN11" t="n">
-        <v>0.87</v>
+        <v>0.93</v>
       </c>
       <c r="BO11" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="BP11" t="n">
         <v>-1</v>
@@ -5210,16 +5198,16 @@
         <v>-1</v>
       </c>
       <c r="BR11" t="n">
-        <v>91.3</v>
+        <v>90</v>
       </c>
       <c r="BS11" t="n">
-        <v>60.87</v>
+        <v>63.33</v>
       </c>
       <c r="BT11" t="n">
-        <v>21.74</v>
+        <v>23.33</v>
       </c>
       <c r="BU11" t="n">
-        <v>13.04</v>
+        <v>10</v>
       </c>
       <c r="BV11" t="n">
         <v>0</v>
@@ -5228,40 +5216,40 @@
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>30.43</v>
+        <v>40</v>
       </c>
       <c r="BY11" t="n">
-        <v>2.96</v>
+        <v>3.24</v>
       </c>
       <c r="BZ11" t="n">
-        <v>3.1</v>
+        <v>3.41</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.39</v>
+        <v>3.43</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.45</v>
+        <v>3.48</v>
       </c>
       <c r="CC11" t="n">
-        <v>5.01</v>
+        <v>4.97</v>
       </c>
       <c r="CD11" t="n">
-        <v>5.33</v>
+        <v>5.37</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CF11" t="n">
-        <v>3.45</v>
+        <v>3.43</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CJ11" t="n">
         <v>2.1</v>
@@ -5270,10 +5258,10 @@
         <v>1.58</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CN11" t="n">
         <v>1.78</v>
@@ -5282,10 +5270,10 @@
         <v>1.46</v>
       </c>
       <c r="CP11" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="CQ11" t="n">
-        <v>4.47</v>
+        <v>4.4</v>
       </c>
       <c r="CR11" t="n">
         <v>1.5</v>
@@ -5294,7 +5282,7 @@
         <v>3.15</v>
       </c>
       <c r="CT11" t="n">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="CU11" t="n">
         <v>1.37</v>
@@ -5306,37 +5294,37 @@
         <v>2.2</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="CY11" t="n">
-        <v>2.03</v>
+        <v>2.07</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.27</v>
+        <v>2.22</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="DC11" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="DD11" t="n">
-        <v>4.84</v>
+        <v>4.65</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="DG11" t="n">
         <v>-1</v>
       </c>
       <c r="DH11" t="n">
-        <v>104.95</v>
+        <v>100.44</v>
       </c>
       <c r="DI11" t="n">
         <v>0</v>
@@ -5345,58 +5333,58 @@
         <v>2</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.69</v>
+        <v>4.5</v>
       </c>
       <c r="DL11" t="n">
         <v>-1</v>
       </c>
       <c r="DM11" t="n">
-        <v>48.39</v>
+        <v>47.54</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="DO11" t="n">
         <v>-1</v>
       </c>
       <c r="DP11" t="n">
-        <v>13.74</v>
+        <v>13.77</v>
       </c>
       <c r="DQ11" t="n">
-        <v>18.61</v>
+        <v>17.53</v>
       </c>
       <c r="DR11" t="n">
-        <v>6.91</v>
+        <v>7.73</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>48.22</v>
+        <v>46.66</v>
       </c>
       <c r="DW11" t="n">
         <v>0.13</v>
       </c>
       <c r="DX11" t="n">
-        <v>10.22</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="DY11" t="n">
-        <v>7.43</v>
+        <v>7.1</v>
       </c>
       <c r="DZ11" t="n">
-        <v>2.79</v>
+        <v>2.7</v>
       </c>
       <c r="EA11" t="n">
-        <v>25.22</v>
+        <v>24.9</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="EC11" t="n">
         <v>1.83</v>
@@ -5409,203 +5397,203 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="G12" t="n">
         <v>-1</v>
       </c>
       <c r="H12" t="n">
-        <v>89.67</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>2.42</v>
+        <v>2.73</v>
       </c>
       <c r="K12" t="n">
-        <v>4.92</v>
+        <v>4.6</v>
       </c>
       <c r="L12" t="n">
         <v>-1</v>
       </c>
       <c r="M12" t="n">
-        <v>44.5</v>
+        <v>42.53</v>
       </c>
       <c r="N12" t="n">
-        <v>0.58</v>
+        <v>0.73</v>
       </c>
       <c r="O12" t="n">
         <v>-1</v>
       </c>
       <c r="P12" t="n">
-        <v>15.83</v>
+        <v>15.67</v>
       </c>
       <c r="Q12" t="n">
-        <v>15</v>
+        <v>14.2</v>
       </c>
       <c r="R12" t="n">
-        <v>6.92</v>
+        <v>7.6</v>
       </c>
       <c r="S12" t="n">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="T12" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="U12" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="V12" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>47.5</v>
+        <v>44.67</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.08</v>
+        <v>0.2</v>
       </c>
       <c r="Z12" t="n">
-        <v>12.92</v>
+        <v>12.27</v>
       </c>
       <c r="AA12" t="n">
-        <v>8.25</v>
+        <v>8</v>
       </c>
       <c r="AB12" t="n">
-        <v>4.67</v>
+        <v>4.27</v>
       </c>
       <c r="AC12" t="n">
-        <v>18.58</v>
+        <v>18.47</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.33</v>
+        <v>2.53</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AH12" t="n">
         <v>-1</v>
       </c>
       <c r="AI12" t="n">
-        <v>75.92</v>
+        <v>77.87</v>
       </c>
       <c r="AJ12" t="n">
         <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.67</v>
+        <v>2.4</v>
       </c>
       <c r="AL12" t="n">
-        <v>4.17</v>
+        <v>4.33</v>
       </c>
       <c r="AM12" t="n">
         <v>-1</v>
       </c>
       <c r="AN12" t="n">
-        <v>32.75</v>
+        <v>35.53</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.92</v>
+        <v>0.8</v>
       </c>
       <c r="AP12" t="n">
         <v>-1</v>
       </c>
       <c r="AQ12" t="n">
-        <v>17.08</v>
+        <v>16.47</v>
       </c>
       <c r="AR12" t="n">
-        <v>14.42</v>
+        <v>13.73</v>
       </c>
       <c r="AS12" t="n">
-        <v>8.58</v>
+        <v>8.73</v>
       </c>
       <c r="AT12" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.58</v>
+        <v>0.67</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.25</v>
+        <v>0.27</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.25</v>
+        <v>0.27</v>
       </c>
       <c r="AX12" t="n">
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>39.75</v>
+        <v>42</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BA12" t="n">
-        <v>10.33</v>
+        <v>11.13</v>
       </c>
       <c r="BB12" t="n">
-        <v>6.83</v>
+        <v>7.73</v>
       </c>
       <c r="BC12" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="BD12" t="n">
-        <v>19.08</v>
+        <v>18.27</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.46</v>
+        <v>2.53</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.880000000000001</v>
+        <v>10.27</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.46</v>
+        <v>2.53</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.38</v>
+        <v>0.4</v>
       </c>
       <c r="BL12" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BO12" t="n">
         <v>1</v>
       </c>
-      <c r="BM12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BO12" t="n">
-        <v>0.96</v>
-      </c>
       <c r="BP12" t="n">
         <v>-1</v>
       </c>
@@ -5613,49 +5601,49 @@
         <v>-1</v>
       </c>
       <c r="BR12" t="n">
-        <v>91.67</v>
+        <v>93.33</v>
       </c>
       <c r="BS12" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BT12" t="n">
-        <v>54.17</v>
+        <v>56.67</v>
       </c>
       <c r="BU12" t="n">
         <v>16.67</v>
       </c>
       <c r="BV12" t="n">
-        <v>8.33</v>
+        <v>6.67</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>33.33</v>
+        <v>43.33</v>
       </c>
       <c r="BY12" t="n">
-        <v>3.84</v>
+        <v>3.97</v>
       </c>
       <c r="BZ12" t="n">
-        <v>4.07</v>
+        <v>4.27</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.92</v>
+        <v>3.87</v>
       </c>
       <c r="CB12" t="n">
-        <v>4.22</v>
+        <v>4.14</v>
       </c>
       <c r="CC12" t="n">
-        <v>7.14</v>
+        <v>6.53</v>
       </c>
       <c r="CD12" t="n">
-        <v>7.79</v>
+        <v>7.05</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="CG12" t="n">
         <v>2.87</v>
@@ -5664,40 +5652,40 @@
         <v>1.37</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="CM12" t="n">
         <v>2.33</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.26</v>
+        <v>3.28</v>
       </c>
       <c r="CR12" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CS12" t="n">
-        <v>3.03</v>
+        <v>3.02</v>
       </c>
       <c r="CT12" t="n">
-        <v>2.79</v>
+        <v>2.83</v>
       </c>
       <c r="CU12" t="n">
         <v>1.4</v>
@@ -5712,97 +5700,97 @@
         <v>1.58</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CZ12" t="n">
         <v>2.35</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="DE12" t="n">
         <v>0.04</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="DG12" t="n">
         <v>-1</v>
       </c>
       <c r="DH12" t="n">
-        <v>82.8</v>
+        <v>82.14</v>
       </c>
       <c r="DI12" t="n">
         <v>0</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.54</v>
+        <v>4.46</v>
       </c>
       <c r="DL12" t="n">
         <v>-1</v>
       </c>
       <c r="DM12" t="n">
-        <v>38.62</v>
+        <v>39.03</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="DO12" t="n">
         <v>-1</v>
       </c>
       <c r="DP12" t="n">
-        <v>16.45</v>
+        <v>16.07</v>
       </c>
       <c r="DQ12" t="n">
-        <v>14.71</v>
+        <v>13.97</v>
       </c>
       <c r="DR12" t="n">
-        <v>7.75</v>
+        <v>8.17</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>43.62</v>
+        <v>43.34</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.08</v>
+        <v>0.13</v>
       </c>
       <c r="DX12" t="n">
-        <v>11.62</v>
+        <v>11.7</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.54</v>
+        <v>7.86</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.08</v>
+        <v>3.84</v>
       </c>
       <c r="EA12" t="n">
-        <v>18.83</v>
+        <v>18.37</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="13">
@@ -5812,16 +5800,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C13" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D13" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E13" t="n">
-        <v>0.17</v>
+        <v>0.13</v>
       </c>
       <c r="F13" t="n">
         <v>1.33</v>
@@ -5830,184 +5818,184 @@
         <v>-1</v>
       </c>
       <c r="H13" t="n">
-        <v>82.58</v>
+        <v>79.73</v>
       </c>
       <c r="I13" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="J13" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="K13" t="n">
-        <v>5.42</v>
+        <v>5.33</v>
       </c>
       <c r="L13" t="n">
         <v>-1</v>
       </c>
       <c r="M13" t="n">
-        <v>43.25</v>
+        <v>43.67</v>
       </c>
       <c r="N13" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="O13" t="n">
         <v>-1</v>
       </c>
       <c r="P13" t="n">
-        <v>16.25</v>
+        <v>15.73</v>
       </c>
       <c r="Q13" t="n">
-        <v>16.08</v>
+        <v>16.4</v>
       </c>
       <c r="R13" t="n">
-        <v>7.67</v>
+        <v>7.33</v>
       </c>
       <c r="S13" t="n">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="T13" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="U13" t="n">
-        <v>0.17</v>
+        <v>0.13</v>
       </c>
       <c r="V13" t="n">
-        <v>0.17</v>
+        <v>0.13</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>48.67</v>
+        <v>47.67</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>12.83</v>
+        <v>13.13</v>
       </c>
       <c r="AA13" t="n">
-        <v>9</v>
+        <v>9.27</v>
       </c>
       <c r="AB13" t="n">
-        <v>3.83</v>
+        <v>3.87</v>
       </c>
       <c r="AC13" t="n">
-        <v>19.92</v>
+        <v>19.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AH13" t="n">
         <v>-1</v>
       </c>
       <c r="AI13" t="n">
-        <v>87.58</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AL13" t="n">
-        <v>5.33</v>
+        <v>5.4</v>
       </c>
       <c r="AM13" t="n">
         <v>-1</v>
       </c>
       <c r="AN13" t="n">
-        <v>44.33</v>
+        <v>41.73</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="AP13" t="n">
         <v>-1</v>
       </c>
       <c r="AQ13" t="n">
-        <v>14.08</v>
+        <v>14.33</v>
       </c>
       <c r="AR13" t="n">
-        <v>15.17</v>
+        <v>14.33</v>
       </c>
       <c r="AS13" t="n">
-        <v>8</v>
+        <v>7.73</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.92</v>
+        <v>0.87</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AX13" t="n">
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>46.75</v>
+        <v>46</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BA13" t="n">
-        <v>11.42</v>
+        <v>11.47</v>
       </c>
       <c r="BB13" t="n">
-        <v>7.67</v>
+        <v>7.93</v>
       </c>
       <c r="BC13" t="n">
-        <v>3.75</v>
+        <v>3.53</v>
       </c>
       <c r="BD13" t="n">
-        <v>22.67</v>
+        <v>23.33</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.710000000000001</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.92</v>
+        <v>0.9</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.92</v>
+        <v>0.9</v>
       </c>
       <c r="BP13" t="n">
         <v>-1</v>
@@ -6016,94 +6004,94 @@
         <v>-1</v>
       </c>
       <c r="BR13" t="n">
-        <v>87.5</v>
+        <v>90</v>
       </c>
       <c r="BS13" t="n">
-        <v>62.5</v>
+        <v>60</v>
       </c>
       <c r="BT13" t="n">
-        <v>41.67</v>
+        <v>43.33</v>
       </c>
       <c r="BU13" t="n">
-        <v>33.33</v>
+        <v>30</v>
       </c>
       <c r="BV13" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="BW13" t="n">
-        <v>8.33</v>
+        <v>6.67</v>
       </c>
       <c r="BX13" t="n">
-        <v>50</v>
+        <v>46.67</v>
       </c>
       <c r="BY13" t="n">
-        <v>3.86</v>
+        <v>3.55</v>
       </c>
       <c r="BZ13" t="n">
-        <v>4.41</v>
+        <v>3.99</v>
       </c>
       <c r="CA13" t="n">
-        <v>4.03</v>
+        <v>4</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.26</v>
+        <v>4.27</v>
       </c>
       <c r="CC13" t="n">
-        <v>5.73</v>
+        <v>5.54</v>
       </c>
       <c r="CD13" t="n">
-        <v>6.06</v>
+        <v>6.18</v>
       </c>
       <c r="CE13" t="n">
         <v>1.35</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.16</v>
+        <v>3.13</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CJ13" t="n">
         <v>1.79</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="CN13" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="CO13" t="n">
         <v>1.25</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CQ13" t="n">
-        <v>3.02</v>
+        <v>3.03</v>
       </c>
       <c r="CR13" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CS13" t="n">
-        <v>2.62</v>
+        <v>2.67</v>
       </c>
       <c r="CT13" t="n">
-        <v>3.09</v>
+        <v>3.07</v>
       </c>
       <c r="CU13" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="CV13" t="n">
         <v>2.1</v>
@@ -6112,100 +6100,100 @@
         <v>1.8</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="DA13" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="DB13" t="n">
         <v>1.28</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="DD13" t="n">
         <v>3.19</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="DG13" t="n">
         <v>-1</v>
       </c>
       <c r="DH13" t="n">
-        <v>85.08</v>
+        <v>81.16</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.38</v>
+        <v>5.36</v>
       </c>
       <c r="DL13" t="n">
         <v>-1</v>
       </c>
       <c r="DM13" t="n">
-        <v>43.79</v>
+        <v>42.7</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="DO13" t="n">
         <v>-1</v>
       </c>
       <c r="DP13" t="n">
-        <v>15.16</v>
+        <v>15.03</v>
       </c>
       <c r="DQ13" t="n">
-        <v>15.62</v>
+        <v>15.36</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.84</v>
+        <v>7.53</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>47.71</v>
+        <v>46.84</v>
       </c>
       <c r="DW13" t="n">
         <v>0.04</v>
       </c>
       <c r="DX13" t="n">
-        <v>12.12</v>
+        <v>12.3</v>
       </c>
       <c r="DY13" t="n">
-        <v>8.33</v>
+        <v>8.6</v>
       </c>
       <c r="DZ13" t="n">
-        <v>3.79</v>
+        <v>3.7</v>
       </c>
       <c r="EA13" t="n">
-        <v>21.3</v>
+        <v>21.46</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="14">
@@ -6215,202 +6203,202 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="C14" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D14" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E14" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="G14" t="n">
         <v>-1</v>
       </c>
       <c r="H14" t="n">
-        <v>99.09</v>
+        <v>93.73</v>
       </c>
       <c r="I14" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="J14" t="n">
-        <v>2.64</v>
+        <v>2.47</v>
       </c>
       <c r="K14" t="n">
-        <v>4.45</v>
+        <v>4.47</v>
       </c>
       <c r="L14" t="n">
         <v>-1</v>
       </c>
       <c r="M14" t="n">
-        <v>54.45</v>
+        <v>51.07</v>
       </c>
       <c r="N14" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="O14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P14" t="n">
+        <v>13.73</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="R14" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>50.87</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>12.53</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>20.07</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>86.93000000000001</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>15.27</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>17.27</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AU14" t="n">
         <v>1</v>
       </c>
-      <c r="O14" t="n">
-        <v>-1</v>
-      </c>
-      <c r="P14" t="n">
-        <v>13.82</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>17.45</v>
-      </c>
-      <c r="R14" t="n">
-        <v>6.09</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>51</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>13.73</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>9.91</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>21.09</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>89.33</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>4.17</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>46.75</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>15.25</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>17.67</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>6.83</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>0.75</v>
-      </c>
       <c r="AV14" t="n">
-        <v>0.17</v>
+        <v>0.13</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.17</v>
+        <v>0.13</v>
       </c>
       <c r="AX14" t="n">
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>47.08</v>
+        <v>45.6</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.17</v>
+        <v>0.13</v>
       </c>
       <c r="BA14" t="n">
-        <v>11.75</v>
+        <v>11.27</v>
       </c>
       <c r="BB14" t="n">
-        <v>7.75</v>
+        <v>7.4</v>
       </c>
       <c r="BC14" t="n">
-        <v>4</v>
+        <v>3.87</v>
       </c>
       <c r="BD14" t="n">
-        <v>22</v>
+        <v>21.73</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="BH14" t="n">
-        <v>8.17</v>
+        <v>8.4</v>
       </c>
       <c r="BI14" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.43</v>
+        <v>0.57</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.04</v>
+        <v>0.97</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.83</v>
+        <v>0.93</v>
       </c>
       <c r="BP14" t="n">
         <v>-1</v>
@@ -6419,94 +6407,94 @@
         <v>-1</v>
       </c>
       <c r="BR14" t="n">
-        <v>91.3</v>
+        <v>93.33</v>
       </c>
       <c r="BS14" t="n">
-        <v>47.83</v>
+        <v>50</v>
       </c>
       <c r="BT14" t="n">
-        <v>21.74</v>
+        <v>23.33</v>
       </c>
       <c r="BU14" t="n">
-        <v>13.04</v>
+        <v>13.33</v>
       </c>
       <c r="BV14" t="n">
-        <v>8.699999999999999</v>
+        <v>6.67</v>
       </c>
       <c r="BW14" t="n">
-        <v>4.35</v>
+        <v>3.33</v>
       </c>
       <c r="BX14" t="n">
-        <v>39.13</v>
+        <v>43.33</v>
       </c>
       <c r="BY14" t="n">
-        <v>2.43</v>
+        <v>2.75</v>
       </c>
       <c r="BZ14" t="n">
-        <v>2.5</v>
+        <v>2.79</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.53</v>
+        <v>3.57</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="CC14" t="n">
-        <v>4.03</v>
+        <v>3.8</v>
       </c>
       <c r="CD14" t="n">
-        <v>4.13</v>
+        <v>3.87</v>
       </c>
       <c r="CE14" t="n">
         <v>1.42</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="CH14" t="n">
         <v>1.4</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="CK14" t="n">
         <v>1.58</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="CN14" t="n">
         <v>1.76</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CP14" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.53</v>
+        <v>3.56</v>
       </c>
       <c r="CR14" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.85</v>
+        <v>2.89</v>
       </c>
       <c r="CT14" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="CU14" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CV14" t="n">
         <v>1.97</v>
@@ -6515,67 +6503,67 @@
         <v>1.92</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CY14" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CZ14" t="n">
         <v>2.22</v>
       </c>
       <c r="DA14" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="DB14" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="DC14" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="DD14" t="n">
-        <v>3.76</v>
+        <v>3.78</v>
       </c>
       <c r="DE14" t="n">
         <v>0.04</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="DG14" t="n">
         <v>-1</v>
       </c>
       <c r="DH14" t="n">
-        <v>94</v>
+        <v>90.33</v>
       </c>
       <c r="DI14" t="n">
         <v>0.13</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.66</v>
+        <v>2.54</v>
       </c>
       <c r="DK14" t="n">
-        <v>4.3</v>
+        <v>4.27</v>
       </c>
       <c r="DL14" t="n">
         <v>-1</v>
       </c>
       <c r="DM14" t="n">
-        <v>50.43</v>
+        <v>48.14</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.04</v>
+        <v>0.87</v>
       </c>
       <c r="DO14" t="n">
         <v>-1</v>
       </c>
       <c r="DP14" t="n">
-        <v>14.57</v>
+        <v>14.5</v>
       </c>
       <c r="DQ14" t="n">
-        <v>17.56</v>
+        <v>17.43</v>
       </c>
       <c r="DR14" t="n">
-        <v>6.48</v>
+        <v>6.56</v>
       </c>
       <c r="DS14" t="n">
         <v>0.13</v>
@@ -6587,28 +6575,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>48.95</v>
+        <v>48.24</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.26</v>
+        <v>0.23</v>
       </c>
       <c r="DX14" t="n">
-        <v>12.7</v>
+        <v>11.9</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.779999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="DZ14" t="n">
-        <v>3.91</v>
+        <v>3.8</v>
       </c>
       <c r="EA14" t="n">
-        <v>21.56</v>
+        <v>20.9</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="15">
@@ -6618,142 +6606,142 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C15" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D15" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="G15" t="n">
         <v>-1</v>
       </c>
       <c r="H15" t="n">
-        <v>88.33</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>1.92</v>
+        <v>2.07</v>
       </c>
       <c r="K15" t="n">
-        <v>3.92</v>
+        <v>4</v>
       </c>
       <c r="L15" t="n">
         <v>-1</v>
       </c>
       <c r="M15" t="n">
-        <v>37.17</v>
+        <v>40.53</v>
       </c>
       <c r="N15" t="n">
-        <v>0.42</v>
+        <v>0.6</v>
       </c>
       <c r="O15" t="n">
         <v>-1</v>
       </c>
       <c r="P15" t="n">
-        <v>15.17</v>
+        <v>14.8</v>
       </c>
       <c r="Q15" t="n">
-        <v>16.67</v>
+        <v>15.53</v>
       </c>
       <c r="R15" t="n">
-        <v>8.25</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="S15" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="T15" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="U15" t="n">
-        <v>0.17</v>
+        <v>0.13</v>
       </c>
       <c r="V15" t="n">
-        <v>0.17</v>
+        <v>0.13</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>42.92</v>
+        <v>44.87</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Z15" t="n">
-        <v>9.83</v>
+        <v>11.2</v>
       </c>
       <c r="AA15" t="n">
-        <v>6.67</v>
+        <v>7.6</v>
       </c>
       <c r="AB15" t="n">
-        <v>3.17</v>
+        <v>3.6</v>
       </c>
       <c r="AC15" t="n">
-        <v>20.83</v>
+        <v>19.73</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.12</v>
+        <v>1.26</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AH15" t="n">
         <v>-1</v>
       </c>
       <c r="AI15" t="n">
-        <v>81.33</v>
+        <v>79.53</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.17</v>
+        <v>0.13</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="AL15" t="n">
-        <v>3.5</v>
+        <v>3.73</v>
       </c>
       <c r="AM15" t="n">
         <v>-1</v>
       </c>
       <c r="AN15" t="n">
-        <v>36.83</v>
+        <v>36.2</v>
       </c>
       <c r="AO15" t="n">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="AP15" t="n">
         <v>-1</v>
       </c>
       <c r="AQ15" t="n">
-        <v>16.92</v>
+        <v>16.2</v>
       </c>
       <c r="AR15" t="n">
-        <v>14.75</v>
+        <v>14.93</v>
       </c>
       <c r="AS15" t="n">
-        <v>8.92</v>
+        <v>9</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="AV15" t="n">
         <v>0</v>
@@ -6765,55 +6753,55 @@
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>42.83</v>
+        <v>42.07</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>9.5</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="BB15" t="n">
-        <v>7.08</v>
+        <v>6.87</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.42</v>
+        <v>2.6</v>
       </c>
       <c r="BD15" t="n">
-        <v>19.58</v>
+        <v>19.6</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="BF15" t="n">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="BG15" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="BH15" t="n">
-        <v>7.62</v>
+        <v>8.1</v>
       </c>
       <c r="BI15" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="BO15" t="n">
-        <v>0.92</v>
+        <v>0.87</v>
       </c>
       <c r="BP15" t="n">
         <v>-1</v>
@@ -6825,40 +6813,40 @@
         <v>83.33</v>
       </c>
       <c r="BS15" t="n">
-        <v>54.17</v>
+        <v>53.33</v>
       </c>
       <c r="BT15" t="n">
-        <v>37.5</v>
+        <v>36.67</v>
       </c>
       <c r="BU15" t="n">
         <v>16.67</v>
       </c>
       <c r="BV15" t="n">
-        <v>4.17</v>
+        <v>3.33</v>
       </c>
       <c r="BW15" t="n">
-        <v>4.17</v>
+        <v>3.33</v>
       </c>
       <c r="BX15" t="n">
-        <v>29.17</v>
+        <v>33.33</v>
       </c>
       <c r="BY15" t="n">
-        <v>2.93</v>
+        <v>2.83</v>
       </c>
       <c r="BZ15" t="n">
-        <v>3.26</v>
+        <v>3.1</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.38</v>
+        <v>3.43</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.54</v>
+        <v>3.55</v>
       </c>
       <c r="CC15" t="n">
-        <v>3.93</v>
+        <v>4.11</v>
       </c>
       <c r="CD15" t="n">
-        <v>4.32</v>
+        <v>4.55</v>
       </c>
       <c r="CE15" t="n">
         <v>1.46</v>
@@ -6870,25 +6858,25 @@
         <v>2.71</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CJ15" t="n">
         <v>1.95</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="CL15" t="n">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="CO15" t="n">
         <v>1.37</v>
@@ -6897,7 +6885,7 @@
         <v>2.22</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.91</v>
+        <v>3.93</v>
       </c>
       <c r="CR15" t="n">
         <v>1.41</v>
@@ -6918,100 +6906,100 @@
         <v>2.01</v>
       </c>
       <c r="CX15" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="CY15" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="DB15" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.24</v>
+        <v>2.21</v>
       </c>
       <c r="DD15" t="n">
-        <v>4.09</v>
+        <v>4.01</v>
       </c>
       <c r="DE15" t="n">
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="DG15" t="n">
         <v>-1</v>
       </c>
       <c r="DH15" t="n">
-        <v>84.83</v>
+        <v>83.56</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="DK15" t="n">
-        <v>3.71</v>
+        <v>3.86</v>
       </c>
       <c r="DL15" t="n">
         <v>-1</v>
       </c>
       <c r="DM15" t="n">
-        <v>37</v>
+        <v>38.36</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.8</v>
+        <v>0.84</v>
       </c>
       <c r="DO15" t="n">
         <v>-1</v>
       </c>
       <c r="DP15" t="n">
-        <v>16.05</v>
+        <v>15.5</v>
       </c>
       <c r="DQ15" t="n">
-        <v>15.71</v>
+        <v>15.23</v>
       </c>
       <c r="DR15" t="n">
-        <v>8.58</v>
+        <v>8.76</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>42.88</v>
+        <v>43.47</v>
       </c>
       <c r="DW15" t="n">
         <v>0.04</v>
       </c>
       <c r="DX15" t="n">
-        <v>9.67</v>
+        <v>10.34</v>
       </c>
       <c r="DY15" t="n">
-        <v>6.88</v>
+        <v>7.24</v>
       </c>
       <c r="DZ15" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="EA15" t="n">
-        <v>20.2</v>
+        <v>19.67</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.29</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="16">
@@ -7021,31 +7009,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="C16" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D16" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E16" t="n">
-        <v>0.08</v>
+        <v>0.13</v>
       </c>
       <c r="F16" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="G16" t="n">
         <v>-1</v>
       </c>
       <c r="H16" t="n">
-        <v>99.83</v>
+        <v>99.53</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>2.17</v>
+        <v>1.93</v>
       </c>
       <c r="K16" t="n">
         <v>5.33</v>
@@ -7054,262 +7042,262 @@
         <v>-1</v>
       </c>
       <c r="M16" t="n">
-        <v>50.83</v>
+        <v>53.13</v>
       </c>
       <c r="N16" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="O16" t="n">
         <v>-1</v>
       </c>
       <c r="P16" t="n">
-        <v>15.33</v>
+        <v>15.13</v>
       </c>
       <c r="Q16" t="n">
-        <v>16</v>
+        <v>15.8</v>
       </c>
       <c r="R16" t="n">
-        <v>6.58</v>
+        <v>5.8</v>
       </c>
       <c r="S16" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="T16" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="U16" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="V16" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>60.42</v>
+        <v>60.47</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="Z16" t="n">
-        <v>13.17</v>
+        <v>13.93</v>
       </c>
       <c r="AA16" t="n">
-        <v>8.83</v>
+        <v>9.4</v>
       </c>
       <c r="AB16" t="n">
-        <v>4.33</v>
+        <v>4.53</v>
       </c>
       <c r="AC16" t="n">
-        <v>21.92</v>
+        <v>20.93</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AH16" t="n">
         <v>-1</v>
       </c>
       <c r="AI16" t="n">
-        <v>93.64</v>
+        <v>97.06999999999999</v>
       </c>
       <c r="AJ16" t="n">
         <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="AL16" t="n">
-        <v>5.36</v>
+        <v>5.6</v>
       </c>
       <c r="AM16" t="n">
         <v>-1</v>
       </c>
       <c r="AN16" t="n">
-        <v>49.91</v>
+        <v>51.53</v>
       </c>
       <c r="AO16" t="n">
-        <v>1.27</v>
+        <v>1.07</v>
       </c>
       <c r="AP16" t="n">
         <v>-1</v>
       </c>
       <c r="AQ16" t="n">
-        <v>16.82</v>
+        <v>17.13</v>
       </c>
       <c r="AR16" t="n">
-        <v>15.27</v>
+        <v>14.6</v>
       </c>
       <c r="AS16" t="n">
-        <v>6</v>
+        <v>5.93</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.64</v>
+        <v>1.47</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="AX16" t="n">
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>61.73</v>
+        <v>62.67</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="BA16" t="n">
-        <v>13.18</v>
+        <v>13.27</v>
       </c>
       <c r="BB16" t="n">
-        <v>9.359999999999999</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="BC16" t="n">
-        <v>3.82</v>
+        <v>4.13</v>
       </c>
       <c r="BD16" t="n">
-        <v>19.45</v>
+        <v>22.8</v>
       </c>
       <c r="BE16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>96.67</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>83.33</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>60</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>23.33</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>13.33</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="CB16" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="CC16" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="CD16" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="CE16" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="CF16" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="CG16" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="CH16" t="n">
         <v>1.46</v>
       </c>
-      <c r="BF16" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>8.91</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="BJ16" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="BK16" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="BM16" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="BN16" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="BO16" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="BP16" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BQ16" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BR16" t="n">
-        <v>100</v>
-      </c>
-      <c r="BS16" t="n">
-        <v>82.61</v>
-      </c>
-      <c r="BT16" t="n">
-        <v>56.52</v>
-      </c>
-      <c r="BU16" t="n">
-        <v>26.09</v>
-      </c>
-      <c r="BV16" t="n">
-        <v>17.39</v>
-      </c>
-      <c r="BW16" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="BX16" t="n">
-        <v>60.87</v>
-      </c>
-      <c r="BY16" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="BZ16" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="CA16" t="n">
-        <v>3.89</v>
-      </c>
-      <c r="CB16" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="CC16" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="CD16" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="CE16" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="CF16" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="CG16" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="CH16" t="n">
-        <v>1.47</v>
-      </c>
       <c r="CI16" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="CL16" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="CM16" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="CN16" t="n">
         <v>1.92</v>
       </c>
-      <c r="CM16" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="CN16" t="n">
-        <v>1.97</v>
-      </c>
       <c r="CO16" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="CQ16" t="n">
-        <v>3.01</v>
+        <v>3.07</v>
       </c>
       <c r="CR16" t="n">
         <v>1.41</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="CT16" t="n">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="CU16" t="n">
         <v>1.46</v>
@@ -7321,100 +7309,100 @@
         <v>1.89</v>
       </c>
       <c r="CX16" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CY16" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="DA16" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="DB16" t="n">
         <v>1.31</v>
       </c>
       <c r="DC16" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="DD16" t="n">
-        <v>3.41</v>
+        <v>3.39</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="DG16" t="n">
         <v>-1</v>
       </c>
       <c r="DH16" t="n">
-        <v>96.87</v>
+        <v>98.3</v>
       </c>
       <c r="DI16" t="n">
         <v>0</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.35</v>
+        <v>2.23</v>
       </c>
       <c r="DK16" t="n">
-        <v>5.34</v>
+        <v>5.46</v>
       </c>
       <c r="DL16" t="n">
         <v>-1</v>
       </c>
       <c r="DM16" t="n">
-        <v>50.39</v>
+        <v>52.33</v>
       </c>
       <c r="DN16" t="n">
-        <v>1</v>
+        <v>0.84</v>
       </c>
       <c r="DO16" t="n">
         <v>-1</v>
       </c>
       <c r="DP16" t="n">
-        <v>16.04</v>
+        <v>16.13</v>
       </c>
       <c r="DQ16" t="n">
-        <v>15.65</v>
+        <v>15.2</v>
       </c>
       <c r="DR16" t="n">
-        <v>6.3</v>
+        <v>5.86</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>61.05</v>
+        <v>61.57</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DX16" t="n">
-        <v>13.17</v>
+        <v>13.6</v>
       </c>
       <c r="DY16" t="n">
-        <v>9.08</v>
+        <v>9.27</v>
       </c>
       <c r="DZ16" t="n">
-        <v>4.09</v>
+        <v>4.33</v>
       </c>
       <c r="EA16" t="n">
-        <v>20.74</v>
+        <v>21.86</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.08</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="17">
@@ -7424,16 +7412,16 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="C17" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D17" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E17" t="n">
-        <v>0.08</v>
+        <v>0.13</v>
       </c>
       <c r="F17" t="n">
         <v>1</v>
@@ -7442,124 +7430,124 @@
         <v>-1</v>
       </c>
       <c r="H17" t="n">
-        <v>91.92</v>
+        <v>94.93000000000001</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="K17" t="n">
-        <v>5.67</v>
+        <v>5.6</v>
       </c>
       <c r="L17" t="n">
         <v>-1</v>
       </c>
       <c r="M17" t="n">
-        <v>49.5</v>
+        <v>50.93</v>
       </c>
       <c r="N17" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="O17" t="n">
         <v>-1</v>
       </c>
       <c r="P17" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="Q17" t="n">
-        <v>17.83</v>
+        <v>17.67</v>
       </c>
       <c r="R17" t="n">
-        <v>5.33</v>
+        <v>5.6</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="T17" t="n">
-        <v>2.17</v>
+        <v>2.07</v>
       </c>
       <c r="U17" t="n">
-        <v>0.42</v>
+        <v>0.33</v>
       </c>
       <c r="V17" t="n">
-        <v>0.42</v>
+        <v>0.33</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>59.92</v>
+        <v>59.4</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Z17" t="n">
-        <v>14.75</v>
+        <v>14.47</v>
       </c>
       <c r="AA17" t="n">
-        <v>8.83</v>
+        <v>8.93</v>
       </c>
       <c r="AB17" t="n">
-        <v>5.92</v>
+        <v>5.53</v>
       </c>
       <c r="AC17" t="n">
-        <v>19.58</v>
+        <v>20.53</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.82</v>
+        <v>1.13</v>
       </c>
       <c r="AH17" t="n">
         <v>-1</v>
       </c>
       <c r="AI17" t="n">
-        <v>93</v>
+        <v>90.33</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.36</v>
+        <v>1.73</v>
       </c>
       <c r="AL17" t="n">
-        <v>5.73</v>
+        <v>5.87</v>
       </c>
       <c r="AM17" t="n">
         <v>-1</v>
       </c>
       <c r="AN17" t="n">
-        <v>51</v>
+        <v>50.2</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.55</v>
+        <v>0.6</v>
       </c>
       <c r="AP17" t="n">
         <v>-1</v>
       </c>
       <c r="AQ17" t="n">
-        <v>9.449999999999999</v>
+        <v>9.73</v>
       </c>
       <c r="AR17" t="n">
-        <v>21.82</v>
+        <v>20.13</v>
       </c>
       <c r="AS17" t="n">
-        <v>6.91</v>
+        <v>7</v>
       </c>
       <c r="AT17" t="n">
-        <v>0.91</v>
+        <v>0.73</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="AV17" t="n">
         <v>0.27</v>
@@ -7571,55 +7559,55 @@
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>60.27</v>
+        <v>59.27</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BA17" t="n">
-        <v>11.36</v>
+        <v>11.93</v>
       </c>
       <c r="BB17" t="n">
-        <v>7.09</v>
+        <v>7.47</v>
       </c>
       <c r="BC17" t="n">
-        <v>4.27</v>
+        <v>4.47</v>
       </c>
       <c r="BD17" t="n">
-        <v>19.27</v>
+        <v>19.4</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.27</v>
+        <v>1.67</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.57</v>
+        <v>2.4</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.390000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.57</v>
+        <v>2.4</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.96</v>
+        <v>0.8</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="BP17" t="n">
         <v>-1</v>
@@ -7628,94 +7616,94 @@
         <v>-1</v>
       </c>
       <c r="BR17" t="n">
-        <v>95.65000000000001</v>
+        <v>93.33</v>
       </c>
       <c r="BS17" t="n">
-        <v>82.61</v>
+        <v>76.67</v>
       </c>
       <c r="BT17" t="n">
-        <v>43.48</v>
+        <v>40</v>
       </c>
       <c r="BU17" t="n">
-        <v>21.74</v>
+        <v>20</v>
       </c>
       <c r="BV17" t="n">
-        <v>4.35</v>
+        <v>3.33</v>
       </c>
       <c r="BW17" t="n">
-        <v>4.35</v>
+        <v>3.33</v>
       </c>
       <c r="BX17" t="n">
-        <v>47.83</v>
+        <v>46.67</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="BZ17" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="CA17" t="n">
-        <v>4.7</v>
+        <v>4.65</v>
       </c>
       <c r="CB17" t="n">
-        <v>4.97</v>
+        <v>4.89</v>
       </c>
       <c r="CC17" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CD17" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="CG17" t="n">
-        <v>3.16</v>
+        <v>3.14</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="CJ17" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="CL17" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.54</v>
+        <v>2.45</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="CO17" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3.03</v>
+        <v>3.13</v>
       </c>
       <c r="CR17" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="CT17" t="n">
-        <v>2.96</v>
+        <v>2.93</v>
       </c>
       <c r="CU17" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="CV17" t="n">
         <v>1.86</v>
@@ -7724,100 +7712,100 @@
         <v>2.05</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="CY17" t="n">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.39</v>
+        <v>2.33</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="DB17" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.11</v>
+        <v>3.18</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="DF17" t="n">
-        <v>0.91</v>
+        <v>1.06</v>
       </c>
       <c r="DG17" t="n">
         <v>-1</v>
       </c>
       <c r="DH17" t="n">
-        <v>92.44</v>
+        <v>92.63</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="DJ17" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.7</v>
+        <v>5.74</v>
       </c>
       <c r="DL17" t="n">
         <v>-1</v>
       </c>
       <c r="DM17" t="n">
-        <v>50.22</v>
+        <v>50.57</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="DO17" t="n">
         <v>-1</v>
       </c>
       <c r="DP17" t="n">
-        <v>9.48</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="DQ17" t="n">
-        <v>19.74</v>
+        <v>18.9</v>
       </c>
       <c r="DR17" t="n">
-        <v>6.09</v>
+        <v>6.3</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>60.09</v>
+        <v>59.34</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX17" t="n">
-        <v>13.13</v>
+        <v>13.2</v>
       </c>
       <c r="DY17" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="DZ17" t="n">
-        <v>5.13</v>
+        <v>5</v>
       </c>
       <c r="EA17" t="n">
-        <v>19.43</v>
+        <v>19.96</v>
       </c>
       <c r="EB17" t="n">
         <v>1.55</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.39</v>
+        <v>1.54</v>
       </c>
     </row>
   </sheetData>
